--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872A5FAF-3508-41B4-9C6A-91448C22D520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63F1C5A-A64A-4FB6-A25E-9AF5B9620F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="360" windowWidth="17490" windowHeight="9240" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -10803,115 +10803,115 @@
       </c>
       <c r="B3">
         <f>Data!I25</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="C3">
         <f>Data!J25</f>
-        <v>0.30697688955366859</v>
+        <v>0.30697688951733509</v>
       </c>
       <c r="D3">
         <f>Data!K25</f>
-        <v>0.30769353631198043</v>
+        <v>0.30769353627583379</v>
       </c>
       <c r="E3">
         <f>Data!L25</f>
-        <v>0.30864929954161624</v>
+        <v>0.30864929950571873</v>
       </c>
       <c r="F3">
         <f>Data!M25</f>
-        <v>0.30991873901568157</v>
+        <v>0.30991873898011502</v>
       </c>
       <c r="G3">
         <f>Data!N25</f>
-        <v>0.31159563622314707</v>
+        <v>0.31159563618801772</v>
       </c>
       <c r="H3">
         <f>Data!O25</f>
-        <v>0.31379489609651995</v>
+        <v>0.31379489606196392</v>
       </c>
       <c r="I3">
         <f>Data!P25</f>
-        <v>0.31665218169291087</v>
+        <v>0.31665218165909981</v>
       </c>
       <c r="J3">
         <f>Data!Q25</f>
-        <v>0.32031926321671017</v>
+        <v>0.32031926318385517</v>
       </c>
       <c r="K3">
         <f>Data!R25</f>
-        <v>0.32495249513093305</v>
+        <v>0.32495249509928592</v>
       </c>
       <c r="L3">
         <f>Data!S25</f>
-        <v>0.33069193089989313</v>
+        <v>0.33069193086974236</v>
       </c>
       <c r="M3">
         <f>Data!T25</f>
-        <v>0.33763022578538127</v>
+        <v>0.33763022575703938</v>
       </c>
       <c r="N3">
         <f>Data!U25</f>
-        <v>0.34577450263754761</v>
+        <v>0.34577450261132897</v>
       </c>
       <c r="O3">
         <f>Data!V25</f>
-        <v>0.3550105126051174</v>
+        <v>0.35501051258130667</v>
       </c>
       <c r="P3">
         <f>Data!W25</f>
-        <v>0.36508401650950512</v>
+        <v>0.36508401648832067</v>
       </c>
       <c r="Q3">
         <f>Data!X25</f>
-        <v>0.37561423811298911</v>
+        <v>0.37561423809454991</v>
       </c>
       <c r="R3">
         <f>Data!Y25</f>
-        <v>0.38614445971647304</v>
+        <v>0.38614445970077915</v>
       </c>
       <c r="S3">
         <f>Data!Z25</f>
-        <v>0.39621796362086076</v>
+        <v>0.39621796360779316</v>
       </c>
       <c r="T3">
         <f>Data!AA25</f>
-        <v>0.40545397358843055</v>
+        <v>0.40545397357777085</v>
       </c>
       <c r="U3">
         <f>Data!AB25</f>
-        <v>0.41359825044059684</v>
+        <v>0.41359825043206044</v>
       </c>
       <c r="V3">
         <f>Data!AC25</f>
-        <v>0.42053654532608503</v>
+        <v>0.42053654531935747</v>
       </c>
       <c r="W3">
         <f>Data!AD25</f>
-        <v>0.42627598109504511</v>
+        <v>0.4262759810898139</v>
       </c>
       <c r="X3">
         <f>Data!AE25</f>
-        <v>0.43090921300926799</v>
+        <v>0.43090921300524465</v>
       </c>
       <c r="Y3">
         <f>Data!AF25</f>
-        <v>0.43457629453306729</v>
+        <v>0.43457629453000002</v>
       </c>
       <c r="Z3">
         <f>Data!AG25</f>
-        <v>0.43743358012945821</v>
+        <v>0.43743358012713585</v>
       </c>
       <c r="AA3">
         <f>Data!AH25</f>
-        <v>0.43963284000283109</v>
+        <v>0.43963284000108216</v>
       </c>
       <c r="AB3">
         <f>Data!AI25</f>
-        <v>0.44130973721029659</v>
+        <v>0.44130973720898481</v>
       </c>
       <c r="AC3">
         <f>Data!AJ25</f>
-        <v>0.44257917668436197</v>
+        <v>0.44257917668338109</v>
       </c>
       <c r="AD3">
         <f>Data!AK25</f>
@@ -10928,115 +10928,115 @@
       </c>
       <c r="B4">
         <f>Data!I26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="C4">
         <f>Data!J26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="D4">
         <f>Data!K26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="E4">
         <f>Data!L26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="F4">
         <f>Data!M26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="G4">
         <f>Data!N26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="H4">
         <f>Data!O26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="I4">
         <f>Data!P26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="J4">
         <f>Data!Q26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="K4">
         <f>Data!R26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="L4">
         <f>Data!S26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="M4">
         <f>Data!T26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="N4">
         <f>Data!U26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="O4">
         <f>Data!V26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="P4">
         <f>Data!W26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="Q4">
         <f>Data!X26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="R4">
         <f>Data!Y26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="S4">
         <f>Data!Z26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="T4">
         <f>Data!AA26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="U4">
         <f>Data!AB26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="V4">
         <f>Data!AC26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="W4">
         <f>Data!AD26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="X4">
         <f>Data!AE26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="Y4">
         <f>Data!AF26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="Z4">
         <f>Data!AG26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AA4">
         <f>Data!AH26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AB4">
         <f>Data!AI26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AC4">
         <f>Data!AJ26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AD4">
         <f>Data!AK26</f>
@@ -11303,115 +11303,115 @@
       </c>
       <c r="B7">
         <f>Data!I29</f>
-        <v>0.12967078621379674</v>
+        <v>0.12967078621466466</v>
       </c>
       <c r="C7">
         <f>Data!J29</f>
-        <v>0.12967078621379358</v>
+        <v>0.12967078621466044</v>
       </c>
       <c r="D7">
         <f>Data!K29</f>
-        <v>0.14540917710224477</v>
+        <v>0.14540917710321821</v>
       </c>
       <c r="E7">
         <f>Data!L29</f>
-        <v>0.16114756799069241</v>
+        <v>0.16114756799177243</v>
       </c>
       <c r="F7">
         <f>Data!M29</f>
-        <v>0.1768859588791436</v>
+        <v>0.17688595888033021</v>
       </c>
       <c r="G7">
         <f>Data!N29</f>
-        <v>0.19262434976759479</v>
+        <v>0.19262434976888443</v>
       </c>
       <c r="H7">
         <f>Data!O29</f>
-        <v>0.20836274065604599</v>
+        <v>0.2083627406574422</v>
       </c>
       <c r="I7">
         <f>Data!P29</f>
-        <v>0.22410113154449718</v>
+        <v>0.22410113154599642</v>
       </c>
       <c r="J7">
         <f>Data!Q29</f>
-        <v>0.23983952243294837</v>
+        <v>0.2398395224345542</v>
       </c>
       <c r="K7">
         <f>Data!R29</f>
-        <v>0.25557791332139956</v>
+        <v>0.25557791332310842</v>
       </c>
       <c r="L7">
         <f>Data!S29</f>
-        <v>0.27131630420985076</v>
+        <v>0.27131630421166619</v>
       </c>
       <c r="M7">
         <f>Data!T29</f>
-        <v>0.28705469509830195</v>
+        <v>0.28705469510022041</v>
       </c>
       <c r="N7">
         <f>Data!U29</f>
-        <v>0.30279308598675314</v>
+        <v>0.30279308598877819</v>
       </c>
       <c r="O7">
         <f>Data!V29</f>
-        <v>0.31853147687520433</v>
+        <v>0.31853147687733596</v>
       </c>
       <c r="P7">
         <f>Data!W29</f>
-        <v>0.33426986776365553</v>
+        <v>0.33426986776589374</v>
       </c>
       <c r="Q7">
         <f>Data!X29</f>
-        <v>0.35000825865210672</v>
+        <v>0.3500082586544444</v>
       </c>
       <c r="R7">
         <f>Data!Y29</f>
-        <v>0.36574664954055791</v>
+        <v>0.36574664954300218</v>
       </c>
       <c r="S7">
         <f>Data!Z29</f>
-        <v>0.381485040429002</v>
+        <v>0.38148504043155995</v>
       </c>
       <c r="T7">
         <f>Data!AA29</f>
-        <v>0.39722343131745319</v>
+        <v>0.39722343132011773</v>
       </c>
       <c r="U7">
         <f>Data!AB29</f>
-        <v>0.41296182220590438</v>
+        <v>0.41296182220866839</v>
       </c>
       <c r="V7">
         <f>Data!AC29</f>
-        <v>0.42870021309435558</v>
+        <v>0.42870021309722617</v>
       </c>
       <c r="W7">
         <f>Data!AD29</f>
-        <v>0.44443860398280677</v>
+        <v>0.44443860398578394</v>
       </c>
       <c r="X7">
         <f>Data!AE29</f>
-        <v>0.46017699487125796</v>
+        <v>0.46017699487434172</v>
       </c>
       <c r="Y7">
         <f>Data!AF29</f>
-        <v>0.47591538575970915</v>
+        <v>0.47591538576289238</v>
       </c>
       <c r="Z7">
         <f>Data!AG29</f>
-        <v>0.49165377664816035</v>
+        <v>0.49165377665145016</v>
       </c>
       <c r="AA7">
         <f>Data!AH29</f>
-        <v>0.50739216753661154</v>
+        <v>0.50739216754000793</v>
       </c>
       <c r="AB7">
         <f>Data!AI29</f>
-        <v>0.52313055842506273</v>
+        <v>0.52313055842856571</v>
       </c>
       <c r="AC7">
         <f>Data!AJ29</f>
-        <v>0.53886894931351392</v>
+        <v>0.53886894931712348</v>
       </c>
       <c r="AD7">
         <f>Data!AK29</f>
@@ -11428,115 +11428,115 @@
       </c>
       <c r="B8">
         <f>Data!I30</f>
-        <v>1.0880490304811035E-4</v>
+        <v>1.088049030359405E-4</v>
       </c>
       <c r="C8">
         <f>Data!J30</f>
-        <v>8.4589900062574685E-4</v>
+        <v>8.4589900061375677E-4</v>
       </c>
       <c r="D8">
         <f>Data!K30</f>
-        <v>1.0986614672101446E-3</v>
+        <v>1.0986614671982162E-3</v>
       </c>
       <c r="E8">
         <f>Data!L30</f>
-        <v>1.4357606985839016E-3</v>
+        <v>1.4357606985720554E-3</v>
       </c>
       <c r="F8">
         <f>Data!M30</f>
-        <v>1.8834940468798042E-3</v>
+        <v>1.883494046868067E-3</v>
       </c>
       <c r="G8">
         <f>Data!N30</f>
-        <v>2.4749383943933924E-3</v>
+        <v>2.4749383943817997E-3</v>
       </c>
       <c r="H8">
         <f>Data!O30</f>
-        <v>3.2506208959975401E-3</v>
+        <v>3.2506208959861365E-3</v>
       </c>
       <c r="I8">
         <f>Data!P30</f>
-        <v>4.2583901305659581E-3</v>
+        <v>4.2583901305548004E-3</v>
       </c>
       <c r="J8">
         <f>Data!Q30</f>
-        <v>5.5517756937757106E-3</v>
+        <v>5.5517756937648686E-3</v>
       </c>
       <c r="K8">
         <f>Data!R30</f>
-        <v>7.185924056708733E-3</v>
+        <v>7.1859240566982891E-3</v>
       </c>
       <c r="L8">
         <f>Data!S30</f>
-        <v>9.2102323019346774E-3</v>
+        <v>9.210232301924727E-3</v>
       </c>
       <c r="M8">
         <f>Data!T30</f>
-        <v>1.1657380089607801E-2</v>
+        <v>1.1657380089598447E-2</v>
       </c>
       <c r="N8">
         <f>Data!U30</f>
-        <v>1.452987966045502E-2</v>
+        <v>1.4529879660446367E-2</v>
       </c>
       <c r="O8">
         <f>Data!V30</f>
-        <v>1.7787435260511523E-2</v>
+        <v>1.7787435260503668E-2</v>
       </c>
       <c r="P8">
         <f>Data!W30</f>
-        <v>2.1340376321765452E-2</v>
+        <v>2.1340376321758465E-2</v>
       </c>
       <c r="Q8">
         <f>Data!X30</f>
-        <v>2.5054402451524054E-2</v>
+        <v>2.5054402451517972E-2</v>
       </c>
       <c r="R8">
         <f>Data!Y30</f>
-        <v>2.8768428581282656E-2</v>
+        <v>2.876842858127748E-2</v>
       </c>
       <c r="S8">
         <f>Data!Z30</f>
-        <v>3.2321369642536582E-2</v>
+        <v>3.2321369642532273E-2</v>
       </c>
       <c r="T8">
         <f>Data!AA30</f>
-        <v>3.5578925242593096E-2</v>
+        <v>3.5578925242589578E-2</v>
       </c>
       <c r="U8">
         <f>Data!AB30</f>
-        <v>3.8451424813440313E-2</v>
+        <v>3.8451424813437496E-2</v>
       </c>
       <c r="V8">
         <f>Data!AC30</f>
-        <v>4.0898572601113438E-2</v>
+        <v>4.0898572601111217E-2</v>
       </c>
       <c r="W8">
         <f>Data!AD30</f>
-        <v>4.2922880846339384E-2</v>
+        <v>4.2922880846337656E-2</v>
       </c>
       <c r="X8">
         <f>Data!AE30</f>
-        <v>4.4557029209272403E-2</v>
+        <v>4.4557029209271078E-2</v>
       </c>
       <c r="Y8">
         <f>Data!AF30</f>
-        <v>4.5850414772482161E-2</v>
+        <v>4.5850414772481148E-2</v>
       </c>
       <c r="Z8">
         <f>Data!AG30</f>
-        <v>4.6858184007050573E-2</v>
+        <v>4.6858184007049809E-2</v>
       </c>
       <c r="AA8">
         <f>Data!AH30</f>
-        <v>4.7633866508654726E-2</v>
+        <v>4.763386650865415E-2</v>
       </c>
       <c r="AB8">
         <f>Data!AI30</f>
-        <v>4.822531085616831E-2</v>
+        <v>4.822531085616788E-2</v>
       </c>
       <c r="AC8">
         <f>Data!AJ30</f>
-        <v>4.8673044204464208E-2</v>
+        <v>4.8673044204463882E-2</v>
       </c>
       <c r="AD8">
         <f>Data!AK30</f>
@@ -14742,115 +14742,115 @@
       </c>
       <c r="B2">
         <f>Data!I52</f>
-        <v>0.93664816809218165</v>
+        <v>0.93664816810144857</v>
       </c>
       <c r="C2">
         <f>Data!J52</f>
-        <v>0.93758413006461472</v>
+        <v>0.93758413007374464</v>
       </c>
       <c r="D2">
         <f>Data!K52</f>
-        <v>0.93790508780604664</v>
+        <v>0.93790508781512971</v>
       </c>
       <c r="E2">
         <f>Data!L52</f>
-        <v>0.93833313635851656</v>
+        <v>0.93833313636753701</v>
       </c>
       <c r="F2">
         <f>Data!M52</f>
-        <v>0.93890166809574294</v>
+        <v>0.93890166810468023</v>
       </c>
       <c r="G2">
         <f>Data!N52</f>
-        <v>0.93965268403780833</v>
+        <v>0.93965268404663582</v>
       </c>
       <c r="H2">
         <f>Data!O52</f>
-        <v>0.94063764555977569</v>
+        <v>0.94063764556845908</v>
       </c>
       <c r="I2">
         <f>Data!P52</f>
-        <v>0.94191731077978458</v>
+        <v>0.94191731078828078</v>
       </c>
       <c r="J2">
         <f>Data!Q52</f>
-        <v>0.94355965157024346</v>
+        <v>0.94355965157849941</v>
       </c>
       <c r="K2">
         <f>Data!R52</f>
-        <v>0.94563469291170243</v>
+        <v>0.94563469291965474</v>
       </c>
       <c r="L2">
         <f>Data!S52</f>
-        <v>0.94820515921205761</v>
+        <v>0.94820515921963411</v>
       </c>
       <c r="M2">
         <f>Data!T52</f>
-        <v>0.95131254709877777</v>
+        <v>0.95131254710589963</v>
       </c>
       <c r="N2">
         <f>Data!U52</f>
-        <v>0.95496004661475364</v>
+        <v>0.95496004662134204</v>
       </c>
       <c r="O2">
         <f>Data!V52</f>
-        <v>0.95909649021776056</v>
+        <v>0.95909649022374377</v>
       </c>
       <c r="P2">
         <f>Data!W52</f>
-        <v>0.96360801423424369</v>
+        <v>0.96360801423956699</v>
       </c>
       <c r="Q2">
         <f>Data!X52</f>
-        <v>0.96832408404609083</v>
+        <v>0.96832408405072434</v>
       </c>
       <c r="R2">
         <f>Data!Y52</f>
-        <v>0.97304015385793796</v>
+        <v>0.97304015386188158</v>
       </c>
       <c r="S2">
         <f>Data!Z52</f>
-        <v>0.9775516778744211</v>
+        <v>0.97755167787770481</v>
       </c>
       <c r="T2">
         <f>Data!AA52</f>
-        <v>0.98168812147742801</v>
+        <v>0.98168812148010653</v>
       </c>
       <c r="U2">
         <f>Data!AB52</f>
-        <v>0.98533562099340388</v>
+        <v>0.98533562099554894</v>
       </c>
       <c r="V2">
         <f>Data!AC52</f>
-        <v>0.98844300888012404</v>
+        <v>0.98844300888181458</v>
       </c>
       <c r="W2">
         <f>Data!AD52</f>
-        <v>0.99101347518047922</v>
+        <v>0.99101347518179383</v>
       </c>
       <c r="X2">
         <f>Data!AE52</f>
-        <v>0.99308851652193819</v>
+        <v>0.99308851652294916</v>
       </c>
       <c r="Y2">
         <f>Data!AF52</f>
-        <v>0.99473085731239708</v>
+        <v>0.99473085731316779</v>
       </c>
       <c r="Z2">
         <f>Data!AG52</f>
-        <v>0.99601052253240596</v>
+        <v>0.9960105225329895</v>
       </c>
       <c r="AA2">
         <f>Data!AH52</f>
-        <v>0.99699548405437333</v>
+        <v>0.99699548405481275</v>
       </c>
       <c r="AB2">
         <f>Data!AI52</f>
-        <v>0.99774649999643872</v>
+        <v>0.99774649999676845</v>
       </c>
       <c r="AC2">
         <f>Data!AJ52</f>
-        <v>0.99831503173366509</v>
+        <v>0.99831503173391156</v>
       </c>
       <c r="AD2">
         <f>Data!AK52</f>
@@ -15117,111 +15117,111 @@
       </c>
       <c r="B5">
         <f>Data!I55</f>
-        <v>6.3351831907818346E-2</v>
+        <v>6.3351831898551425E-2</v>
       </c>
       <c r="C5">
         <f>Data!J55</f>
-        <v>6.3351831907809242E-2</v>
+        <v>6.3351831898543765E-2</v>
       </c>
       <c r="D5">
         <f>Data!K55</f>
-        <v>9.9376761449818218E-2</v>
+        <v>9.9376761440908012E-2</v>
       </c>
       <c r="E5">
         <f>Data!L55</f>
-        <v>0.13540169099182719</v>
+        <v>0.13540169098327226</v>
       </c>
       <c r="F5">
         <f>Data!M55</f>
-        <v>0.17142662053383617</v>
+        <v>0.17142662052563651</v>
       </c>
       <c r="G5">
         <f>Data!N55</f>
-        <v>0.20745155007584515</v>
+        <v>0.20745155006800076</v>
       </c>
       <c r="H5">
         <f>Data!O55</f>
-        <v>0.24347647961785412</v>
+        <v>0.243476479610365</v>
       </c>
       <c r="I5">
         <f>Data!P55</f>
-        <v>0.2795014091598631</v>
+        <v>0.27950140915272925</v>
       </c>
       <c r="J5">
         <f>Data!Q55</f>
-        <v>0.31552633870185787</v>
+        <v>0.3155263386950935</v>
       </c>
       <c r="K5">
         <f>Data!R55</f>
-        <v>0.35155126824386684</v>
+        <v>0.35155126823745775</v>
       </c>
       <c r="L5">
         <f>Data!S55</f>
-        <v>0.38757619778587582</v>
+        <v>0.387576197779822</v>
       </c>
       <c r="M5">
         <f>Data!T55</f>
-        <v>0.4236011273278848</v>
+        <v>0.42360112732218624</v>
       </c>
       <c r="N5">
         <f>Data!U55</f>
-        <v>0.45962605686989377</v>
+        <v>0.45962605686455049</v>
       </c>
       <c r="O5">
         <f>Data!V55</f>
-        <v>0.49565098641190275</v>
+        <v>0.49565098640691474</v>
       </c>
       <c r="P5">
         <f>Data!W55</f>
-        <v>0.53167591595391173</v>
+        <v>0.53167591594927899</v>
       </c>
       <c r="Q5">
         <f>Data!X55</f>
-        <v>0.56770084549590649</v>
+        <v>0.56770084549164324</v>
       </c>
       <c r="R5">
         <f>Data!Y55</f>
-        <v>0.60372577503791547</v>
+        <v>0.60372577503400748</v>
       </c>
       <c r="S5">
         <f>Data!Z55</f>
-        <v>0.63975070457992445</v>
+        <v>0.63975070457635752</v>
       </c>
       <c r="T5">
         <f>Data!AA55</f>
-        <v>0.67577563412193342</v>
+        <v>0.67577563411872177</v>
       </c>
       <c r="U5">
         <f>Data!AB55</f>
-        <v>0.7118005636639424</v>
+        <v>0.71180056366108602</v>
       </c>
       <c r="V5">
         <f>Data!AC55</f>
-        <v>0.74782549320595137</v>
+        <v>0.74782549320345026</v>
       </c>
       <c r="W5">
         <f>Data!AD55</f>
-        <v>0.78385042274796035</v>
+        <v>0.78385042274581451</v>
       </c>
       <c r="X5">
         <f>Data!AE55</f>
-        <v>0.81987535228995512</v>
+        <v>0.81987535228817876</v>
       </c>
       <c r="Y5">
         <f>Data!AF55</f>
-        <v>0.85590028183196409</v>
+        <v>0.85590028183054301</v>
       </c>
       <c r="Z5">
         <f>Data!AG55</f>
-        <v>0.89192521137397307</v>
+        <v>0.89192521137290726</v>
       </c>
       <c r="AA5">
         <f>Data!AH55</f>
-        <v>0.92795014091598205</v>
+        <v>0.9279501409152715</v>
       </c>
       <c r="AB5">
         <f>Data!AI55</f>
-        <v>0.96397507045799102</v>
+        <v>0.96397507045763575</v>
       </c>
       <c r="AC5">
         <f>Data!AJ55</f>
@@ -52302,188 +52302,188 @@
     <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>111</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>2799214</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2">
         <v>16648</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>256819978</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>1348635</v>
       </c>
-      <c r="F2" s="5">
-        <v>1130472.0000000002</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2">
+        <v>1130472</v>
+      </c>
+      <c r="G2">
         <v>16384</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2">
         <v>15809</v>
       </c>
       <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>300</v>
       </c>
-      <c r="C3" s="5">
-        <v>123405.86316307285</v>
-      </c>
-      <c r="D3" s="5">
-        <v>98369.804893824577</v>
-      </c>
-      <c r="E3" s="5">
-        <v>703911.92875736777</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>41837.429476286045</v>
-      </c>
-      <c r="H3" s="5">
-        <v>105.31556700313551</v>
+      <c r="C3">
+        <v>123405.86320000001</v>
+      </c>
+      <c r="D3">
+        <v>98369.804889999999</v>
+      </c>
+      <c r="E3">
+        <v>703911.92879999999</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>41837.429479999999</v>
+      </c>
+      <c r="H3">
+        <v>105.315567</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5">
-        <v>2563.6060360683009</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>173.39396393169866</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="B5">
+        <v>2563.6060360000001</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>173.39396389999999</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>10231405.018379824</v>
-      </c>
-      <c r="E6" s="5">
-        <v>2473594.5350763109</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>10231405.02</v>
+      </c>
+      <c r="E6">
+        <v>2473594.5350000001</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>9516910</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
@@ -62085,7 +62085,7 @@
       </c>
       <c r="E25" s="22">
         <f>'SYVbT-passenger'!D3/SUM('SYVbT-passenger'!3:3)*3</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="F25" s="22">
         <f>F32*3</f>
@@ -62097,115 +62097,115 @@
       </c>
       <c r="I25" s="22">
         <f t="shared" si="1"/>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="J25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,J$9))</f>
-        <v>0.30697688955366859</v>
+        <v>0.30697688951733509</v>
       </c>
       <c r="K25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,K$9))</f>
-        <v>0.30769353631198043</v>
+        <v>0.30769353627583379</v>
       </c>
       <c r="L25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,L$9))</f>
-        <v>0.30864929954161624</v>
+        <v>0.30864929950571873</v>
       </c>
       <c r="M25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,M$9))</f>
-        <v>0.30991873901568157</v>
+        <v>0.30991873898011502</v>
       </c>
       <c r="N25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,N$9))</f>
-        <v>0.31159563622314707</v>
+        <v>0.31159563618801772</v>
       </c>
       <c r="O25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,O$9))</f>
-        <v>0.31379489609651995</v>
+        <v>0.31379489606196392</v>
       </c>
       <c r="P25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,P$9))</f>
-        <v>0.31665218169291087</v>
+        <v>0.31665218165909981</v>
       </c>
       <c r="Q25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Q$9))</f>
-        <v>0.32031926321671017</v>
+        <v>0.32031926318385517</v>
       </c>
       <c r="R25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,R$9))</f>
-        <v>0.32495249513093305</v>
+        <v>0.32495249509928592</v>
       </c>
       <c r="S25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,S$9))</f>
-        <v>0.33069193089989313</v>
+        <v>0.33069193086974236</v>
       </c>
       <c r="T25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,T$9))</f>
-        <v>0.33763022578538127</v>
+        <v>0.33763022575703938</v>
       </c>
       <c r="U25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,U$9))</f>
-        <v>0.34577450263754761</v>
+        <v>0.34577450261132897</v>
       </c>
       <c r="V25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,V$9))</f>
-        <v>0.3550105126051174</v>
+        <v>0.35501051258130667</v>
       </c>
       <c r="W25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,W$9))</f>
-        <v>0.36508401650950512</v>
+        <v>0.36508401648832067</v>
       </c>
       <c r="X25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,X$9))</f>
-        <v>0.37561423811298911</v>
+        <v>0.37561423809454991</v>
       </c>
       <c r="Y25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Y$9))</f>
-        <v>0.38614445971647304</v>
+        <v>0.38614445970077915</v>
       </c>
       <c r="Z25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Z$9))</f>
-        <v>0.39621796362086076</v>
+        <v>0.39621796360779316</v>
       </c>
       <c r="AA25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AA$9))</f>
-        <v>0.40545397358843055</v>
+        <v>0.40545397357777085</v>
       </c>
       <c r="AB25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AB$9))</f>
-        <v>0.41359825044059684</v>
+        <v>0.41359825043206044</v>
       </c>
       <c r="AC25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AC$9))</f>
-        <v>0.42053654532608503</v>
+        <v>0.42053654531935747</v>
       </c>
       <c r="AD25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AD$9))</f>
-        <v>0.42627598109504511</v>
+        <v>0.4262759810898139</v>
       </c>
       <c r="AE25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AE$9))</f>
-        <v>0.43090921300926799</v>
+        <v>0.43090921300524465</v>
       </c>
       <c r="AF25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AF$9))</f>
-        <v>0.43457629453306729</v>
+        <v>0.43457629453000002</v>
       </c>
       <c r="AG25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AG$9))</f>
-        <v>0.43743358012945821</v>
+        <v>0.43743358012713585</v>
       </c>
       <c r="AH25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AH$9))</f>
-        <v>0.43963284000283109</v>
+        <v>0.43963284000108216</v>
       </c>
       <c r="AI25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AI$9))</f>
-        <v>0.44130973721029659</v>
+        <v>0.44130973720898481</v>
       </c>
       <c r="AJ25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AJ$9))</f>
-        <v>0.44257917668436197</v>
+        <v>0.44257917668338109</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
@@ -62214,11 +62214,11 @@
       </c>
       <c r="E26" s="22">
         <f>'SYVbT-passenger'!D3/SUM('SYVbT-passenger'!3:3)*3</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="F26" s="22">
         <f>E26</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="G26" s="7" t="str">
         <f>IF(E26=F26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -62226,115 +62226,115 @@
       </c>
       <c r="I26" s="22">
         <f t="shared" si="1"/>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="J26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,J$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="K26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,K$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="L26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,L$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="M26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,M$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="N26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,N$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="O26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,O$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="P26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,P$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="Q26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Q$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="R26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,R$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="S26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,S$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="T26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,T$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="U26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,U$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="V26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,V$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="W26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,W$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="X26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,X$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="Y26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Y$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="Z26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Z$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AA26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AA$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AB26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AB$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AC26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AC$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AD26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AD$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AE26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AE$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AF26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AF$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AG26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AG$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AH26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AH$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AI26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AI$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
       <c r="AJ26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AJ$9))</f>
-        <v>0.30488703775431764</v>
+        <v>0.3048870377174393</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
@@ -62599,11 +62599,11 @@
       </c>
       <c r="E29" s="22">
         <f>'SYVbT-passenger'!G3/SUM('SYVbT-passenger'!3:3)*3</f>
-        <v>0.12967078621379674</v>
+        <v>0.12967078621466466</v>
       </c>
       <c r="F29" s="22">
         <f>F36*($E$29/$E$36)*3</f>
-        <v>0.53886894931351725</v>
+        <v>0.53886894931712415</v>
       </c>
       <c r="G29" s="7" t="str">
         <f>IF(E29=F29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -62611,115 +62611,115 @@
       </c>
       <c r="I29" s="22">
         <f t="shared" si="1"/>
-        <v>0.12967078621379674</v>
+        <v>0.12967078621466466</v>
       </c>
       <c r="J29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,J$9))</f>
-        <v>0.12967078621379358</v>
+        <v>0.12967078621466044</v>
       </c>
       <c r="K29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,K$9))</f>
-        <v>0.14540917710224477</v>
+        <v>0.14540917710321821</v>
       </c>
       <c r="L29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,L$9))</f>
-        <v>0.16114756799069241</v>
+        <v>0.16114756799177243</v>
       </c>
       <c r="M29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,M$9))</f>
-        <v>0.1768859588791436</v>
+        <v>0.17688595888033021</v>
       </c>
       <c r="N29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,N$9))</f>
-        <v>0.19262434976759479</v>
+        <v>0.19262434976888443</v>
       </c>
       <c r="O29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,O$9))</f>
-        <v>0.20836274065604599</v>
+        <v>0.2083627406574422</v>
       </c>
       <c r="P29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,P$9))</f>
-        <v>0.22410113154449718</v>
+        <v>0.22410113154599642</v>
       </c>
       <c r="Q29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Q$9))</f>
-        <v>0.23983952243294837</v>
+        <v>0.2398395224345542</v>
       </c>
       <c r="R29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,R$9))</f>
-        <v>0.25557791332139956</v>
+        <v>0.25557791332310842</v>
       </c>
       <c r="S29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,S$9))</f>
-        <v>0.27131630420985076</v>
+        <v>0.27131630421166619</v>
       </c>
       <c r="T29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,T$9))</f>
-        <v>0.28705469509830195</v>
+        <v>0.28705469510022041</v>
       </c>
       <c r="U29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,U$9))</f>
-        <v>0.30279308598675314</v>
+        <v>0.30279308598877819</v>
       </c>
       <c r="V29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,V$9))</f>
-        <v>0.31853147687520433</v>
+        <v>0.31853147687733596</v>
       </c>
       <c r="W29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,W$9))</f>
-        <v>0.33426986776365553</v>
+        <v>0.33426986776589374</v>
       </c>
       <c r="X29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,X$9))</f>
-        <v>0.35000825865210672</v>
+        <v>0.3500082586544444</v>
       </c>
       <c r="Y29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Y$9))</f>
-        <v>0.36574664954055791</v>
+        <v>0.36574664954300218</v>
       </c>
       <c r="Z29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Z$9))</f>
-        <v>0.381485040429002</v>
+        <v>0.38148504043155995</v>
       </c>
       <c r="AA29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AA$9))</f>
-        <v>0.39722343131745319</v>
+        <v>0.39722343132011773</v>
       </c>
       <c r="AB29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AB$9))</f>
-        <v>0.41296182220590438</v>
+        <v>0.41296182220866839</v>
       </c>
       <c r="AC29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AC$9))</f>
-        <v>0.42870021309435558</v>
+        <v>0.42870021309722617</v>
       </c>
       <c r="AD29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AD$9))</f>
-        <v>0.44443860398280677</v>
+        <v>0.44443860398578394</v>
       </c>
       <c r="AE29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AE$9))</f>
-        <v>0.46017699487125796</v>
+        <v>0.46017699487434172</v>
       </c>
       <c r="AF29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AF$9))</f>
-        <v>0.47591538575970915</v>
+        <v>0.47591538576289238</v>
       </c>
       <c r="AG29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AG$9))</f>
-        <v>0.49165377664816035</v>
+        <v>0.49165377665145016</v>
       </c>
       <c r="AH29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AH$9))</f>
-        <v>0.50739216753661154</v>
+        <v>0.50739216754000793</v>
       </c>
       <c r="AI29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AI$9))</f>
-        <v>0.52313055842506273</v>
+        <v>0.52313055842856571</v>
       </c>
       <c r="AJ29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AJ$9))</f>
-        <v>0.53886894931351392</v>
+        <v>0.53886894931712348</v>
       </c>
     </row>
     <row r="30" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -62731,7 +62731,7 @@
       <c r="D30" s="23"/>
       <c r="E30" s="26">
         <f>'SYVbT-passenger'!H3/SUM('SYVbT-passenger'!3:3)</f>
-        <v>1.0880490304811035E-4</v>
+        <v>1.088049030359405E-4</v>
       </c>
       <c r="F30" s="26">
         <v>0.05</v>
@@ -62742,115 +62742,115 @@
       </c>
       <c r="I30" s="22">
         <f t="shared" si="1"/>
-        <v>1.0880490304811035E-4</v>
+        <v>1.088049030359405E-4</v>
       </c>
       <c r="J30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,J$9))</f>
-        <v>8.4589900062574685E-4</v>
+        <v>8.4589900061375677E-4</v>
       </c>
       <c r="K30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,K$9))</f>
-        <v>1.0986614672101446E-3</v>
+        <v>1.0986614671982162E-3</v>
       </c>
       <c r="L30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,L$9))</f>
-        <v>1.4357606985839016E-3</v>
+        <v>1.4357606985720554E-3</v>
       </c>
       <c r="M30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,M$9))</f>
-        <v>1.8834940468798042E-3</v>
+        <v>1.883494046868067E-3</v>
       </c>
       <c r="N30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,N$9))</f>
-        <v>2.4749383943933924E-3</v>
+        <v>2.4749383943817997E-3</v>
       </c>
       <c r="O30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,O$9))</f>
-        <v>3.2506208959975401E-3</v>
+        <v>3.2506208959861365E-3</v>
       </c>
       <c r="P30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,P$9))</f>
-        <v>4.2583901305659581E-3</v>
+        <v>4.2583901305548004E-3</v>
       </c>
       <c r="Q30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Q$9))</f>
-        <v>5.5517756937757106E-3</v>
+        <v>5.5517756937648686E-3</v>
       </c>
       <c r="R30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,R$9))</f>
-        <v>7.185924056708733E-3</v>
+        <v>7.1859240566982891E-3</v>
       </c>
       <c r="S30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,S$9))</f>
-        <v>9.2102323019346774E-3</v>
+        <v>9.210232301924727E-3</v>
       </c>
       <c r="T30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,T$9))</f>
-        <v>1.1657380089607801E-2</v>
+        <v>1.1657380089598447E-2</v>
       </c>
       <c r="U30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,U$9))</f>
-        <v>1.452987966045502E-2</v>
+        <v>1.4529879660446367E-2</v>
       </c>
       <c r="V30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,V$9))</f>
-        <v>1.7787435260511523E-2</v>
+        <v>1.7787435260503668E-2</v>
       </c>
       <c r="W30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,W$9))</f>
-        <v>2.1340376321765452E-2</v>
+        <v>2.1340376321758465E-2</v>
       </c>
       <c r="X30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,X$9))</f>
-        <v>2.5054402451524054E-2</v>
+        <v>2.5054402451517972E-2</v>
       </c>
       <c r="Y30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Y$9))</f>
-        <v>2.8768428581282656E-2</v>
+        <v>2.876842858127748E-2</v>
       </c>
       <c r="Z30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Z$9))</f>
-        <v>3.2321369642536582E-2</v>
+        <v>3.2321369642532273E-2</v>
       </c>
       <c r="AA30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AA$9))</f>
-        <v>3.5578925242593096E-2</v>
+        <v>3.5578925242589578E-2</v>
       </c>
       <c r="AB30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AB$9))</f>
-        <v>3.8451424813440313E-2</v>
+        <v>3.8451424813437496E-2</v>
       </c>
       <c r="AC30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AC$9))</f>
-        <v>4.0898572601113438E-2</v>
+        <v>4.0898572601111217E-2</v>
       </c>
       <c r="AD30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AD$9))</f>
-        <v>4.2922880846339384E-2</v>
+        <v>4.2922880846337656E-2</v>
       </c>
       <c r="AE30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AE$9))</f>
-        <v>4.4557029209272403E-2</v>
+        <v>4.4557029209271078E-2</v>
       </c>
       <c r="AF30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AF$9))</f>
-        <v>4.5850414772482161E-2</v>
+        <v>4.5850414772481148E-2</v>
       </c>
       <c r="AG30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AG$9))</f>
-        <v>4.6858184007050573E-2</v>
+        <v>4.6858184007049809E-2</v>
       </c>
       <c r="AH30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AH$9))</f>
-        <v>4.7633866508654726E-2</v>
+        <v>4.763386650865415E-2</v>
       </c>
       <c r="AI30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AI$9))</f>
-        <v>4.822531085616831E-2</v>
+        <v>4.822531085616788E-2</v>
       </c>
       <c r="AJ30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AJ$9))</f>
-        <v>4.8673044204464208E-2</v>
+        <v>4.8673044204463882E-2</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
@@ -65563,7 +65563,7 @@
       </c>
       <c r="E52" s="22">
         <f>'SYVbT-passenger'!B5/SUM('SYVbT-passenger'!B5:H5)</f>
-        <v>0.93664816809218165</v>
+        <v>0.93664816810144857</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -65574,115 +65574,115 @@
       </c>
       <c r="I52" s="22">
         <f t="shared" si="2"/>
-        <v>0.93664816809218165</v>
+        <v>0.93664816810144857</v>
       </c>
       <c r="J52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,J$9))</f>
-        <v>0.93758413006461472</v>
+        <v>0.93758413007374464</v>
       </c>
       <c r="K52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,K$9))</f>
-        <v>0.93790508780604664</v>
+        <v>0.93790508781512971</v>
       </c>
       <c r="L52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,L$9))</f>
-        <v>0.93833313635851656</v>
+        <v>0.93833313636753701</v>
       </c>
       <c r="M52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,M$9))</f>
-        <v>0.93890166809574294</v>
+        <v>0.93890166810468023</v>
       </c>
       <c r="N52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,N$9))</f>
-        <v>0.93965268403780833</v>
+        <v>0.93965268404663582</v>
       </c>
       <c r="O52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,O$9))</f>
-        <v>0.94063764555977569</v>
+        <v>0.94063764556845908</v>
       </c>
       <c r="P52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,P$9))</f>
-        <v>0.94191731077978458</v>
+        <v>0.94191731078828078</v>
       </c>
       <c r="Q52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Q$9))</f>
-        <v>0.94355965157024346</v>
+        <v>0.94355965157849941</v>
       </c>
       <c r="R52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,R$9))</f>
-        <v>0.94563469291170243</v>
+        <v>0.94563469291965474</v>
       </c>
       <c r="S52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,S$9))</f>
-        <v>0.94820515921205761</v>
+        <v>0.94820515921963411</v>
       </c>
       <c r="T52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,T$9))</f>
-        <v>0.95131254709877777</v>
+        <v>0.95131254710589963</v>
       </c>
       <c r="U52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,U$9))</f>
-        <v>0.95496004661475364</v>
+        <v>0.95496004662134204</v>
       </c>
       <c r="V52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,V$9))</f>
-        <v>0.95909649021776056</v>
+        <v>0.95909649022374377</v>
       </c>
       <c r="W52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,W$9))</f>
-        <v>0.96360801423424369</v>
+        <v>0.96360801423956699</v>
       </c>
       <c r="X52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,X$9))</f>
-        <v>0.96832408404609083</v>
+        <v>0.96832408405072434</v>
       </c>
       <c r="Y52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Y$9))</f>
-        <v>0.97304015385793796</v>
+        <v>0.97304015386188158</v>
       </c>
       <c r="Z52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Z$9))</f>
-        <v>0.9775516778744211</v>
+        <v>0.97755167787770481</v>
       </c>
       <c r="AA52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AA$9))</f>
-        <v>0.98168812147742801</v>
+        <v>0.98168812148010653</v>
       </c>
       <c r="AB52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AB$9))</f>
-        <v>0.98533562099340388</v>
+        <v>0.98533562099554894</v>
       </c>
       <c r="AC52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AC$9))</f>
-        <v>0.98844300888012404</v>
+        <v>0.98844300888181458</v>
       </c>
       <c r="AD52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AD$9))</f>
-        <v>0.99101347518047922</v>
+        <v>0.99101347518179383</v>
       </c>
       <c r="AE52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AE$9))</f>
-        <v>0.99308851652193819</v>
+        <v>0.99308851652294916</v>
       </c>
       <c r="AF52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AF$9))</f>
-        <v>0.99473085731239708</v>
+        <v>0.99473085731316779</v>
       </c>
       <c r="AG52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AG$9))</f>
-        <v>0.99601052253240596</v>
+        <v>0.9960105225329895</v>
       </c>
       <c r="AH52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AH$9))</f>
-        <v>0.99699548405437333</v>
+        <v>0.99699548405481275</v>
       </c>
       <c r="AI52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AI$9))</f>
-        <v>0.99774649999643872</v>
+        <v>0.99774649999676845</v>
       </c>
       <c r="AJ52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AJ$9))</f>
-        <v>0.99831503173366509</v>
+        <v>0.99831503173391156</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
@@ -65945,7 +65945,7 @@
       </c>
       <c r="E55" s="22">
         <f>1-E52</f>
-        <v>6.3351831907818346E-2</v>
+        <v>6.3351831898551425E-2</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -65956,111 +65956,111 @@
       </c>
       <c r="I55" s="22">
         <f t="shared" si="2"/>
-        <v>6.3351831907818346E-2</v>
+        <v>6.3351831898551425E-2</v>
       </c>
       <c r="J55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,J$9))</f>
-        <v>6.3351831907809242E-2</v>
+        <v>6.3351831898543765E-2</v>
       </c>
       <c r="K55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,K$9))</f>
-        <v>9.9376761449818218E-2</v>
+        <v>9.9376761440908012E-2</v>
       </c>
       <c r="L55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,L$9))</f>
-        <v>0.13540169099182719</v>
+        <v>0.13540169098327226</v>
       </c>
       <c r="M55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,M$9))</f>
-        <v>0.17142662053383617</v>
+        <v>0.17142662052563651</v>
       </c>
       <c r="N55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,N$9))</f>
-        <v>0.20745155007584515</v>
+        <v>0.20745155006800076</v>
       </c>
       <c r="O55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,O$9))</f>
-        <v>0.24347647961785412</v>
+        <v>0.243476479610365</v>
       </c>
       <c r="P55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,P$9))</f>
-        <v>0.2795014091598631</v>
+        <v>0.27950140915272925</v>
       </c>
       <c r="Q55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Q$9))</f>
-        <v>0.31552633870185787</v>
+        <v>0.3155263386950935</v>
       </c>
       <c r="R55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,R$9))</f>
-        <v>0.35155126824386684</v>
+        <v>0.35155126823745775</v>
       </c>
       <c r="S55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,S$9))</f>
-        <v>0.38757619778587582</v>
+        <v>0.387576197779822</v>
       </c>
       <c r="T55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,T$9))</f>
-        <v>0.4236011273278848</v>
+        <v>0.42360112732218624</v>
       </c>
       <c r="U55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,U$9))</f>
-        <v>0.45962605686989377</v>
+        <v>0.45962605686455049</v>
       </c>
       <c r="V55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,V$9))</f>
-        <v>0.49565098641190275</v>
+        <v>0.49565098640691474</v>
       </c>
       <c r="W55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,W$9))</f>
-        <v>0.53167591595391173</v>
+        <v>0.53167591594927899</v>
       </c>
       <c r="X55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,X$9))</f>
-        <v>0.56770084549590649</v>
+        <v>0.56770084549164324</v>
       </c>
       <c r="Y55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Y$9))</f>
-        <v>0.60372577503791547</v>
+        <v>0.60372577503400748</v>
       </c>
       <c r="Z55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Z$9))</f>
-        <v>0.63975070457992445</v>
+        <v>0.63975070457635752</v>
       </c>
       <c r="AA55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AA$9))</f>
-        <v>0.67577563412193342</v>
+        <v>0.67577563411872177</v>
       </c>
       <c r="AB55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AB$9))</f>
-        <v>0.7118005636639424</v>
+        <v>0.71180056366108602</v>
       </c>
       <c r="AC55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AC$9))</f>
-        <v>0.74782549320595137</v>
+        <v>0.74782549320345026</v>
       </c>
       <c r="AD55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AD$9))</f>
-        <v>0.78385042274796035</v>
+        <v>0.78385042274581451</v>
       </c>
       <c r="AE55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AE$9))</f>
-        <v>0.81987535228995512</v>
+        <v>0.81987535228817876</v>
       </c>
       <c r="AF55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AF$9))</f>
-        <v>0.85590028183196409</v>
+        <v>0.85590028183054301</v>
       </c>
       <c r="AG55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AG$9))</f>
-        <v>0.89192521137397307</v>
+        <v>0.89192521137290726</v>
       </c>
       <c r="AH55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AH$9))</f>
-        <v>0.92795014091598205</v>
+        <v>0.9279501409152715</v>
       </c>
       <c r="AI55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AI$9))</f>
-        <v>0.96397507045799102</v>
+        <v>0.96397507045763575</v>
       </c>
       <c r="AJ55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AJ$9))</f>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63F1C5A-A64A-4FB6-A25E-9AF5B9620F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010E36AA-CE35-4844-9DE2-50CAD4083547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="360" windowWidth="17490" windowHeight="9240" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="AEO 39" sheetId="4" r:id="rId2"/>
-    <sheet name="AEO 49" sheetId="5" r:id="rId3"/>
+    <sheet name="AEO 2025 Table 39" sheetId="4" r:id="rId2"/>
+    <sheet name="AEO 2025 Table 49" sheetId="5" r:id="rId3"/>
     <sheet name="SYVbT-passenger" sheetId="6" r:id="rId4"/>
     <sheet name="SYVbT-freight" sheetId="19" r:id="rId5"/>
     <sheet name="Assumptions" sheetId="7" r:id="rId6"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="950">
   <si>
     <t>Source:</t>
   </si>
@@ -2896,6 +2896,9 @@
   </si>
   <si>
     <t>Annual Energy Outlook 2025</t>
+  </si>
+  <si>
+    <t>Alternative Transportation</t>
   </si>
 </sst>
 </file>
@@ -10023,18 +10026,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B124"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B126"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="56.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -10042,494 +10045,504 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B11" s="12" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B12" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B13" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B14" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="28" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="B15" s="28" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B17" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B18" s="3">
         <v>2022</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B19" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B20" s="30" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="30"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B21" s="30"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B22" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B23" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B24" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="30" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B25" s="30" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B27" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B29" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B30" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B31" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B32" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="12" t="s">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B35" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B36" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B38" s="12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B39" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="3">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B40" s="3">
         <v>2014</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B41" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B44" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="3">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B45" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B46" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B47" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A49" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A50" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A51" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A52" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="30" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A53" s="30" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A54" s="1"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A55" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A56" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A58" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A59" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A60" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A61" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A63" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B61" s="14"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="14"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B65" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B67" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B68" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B69" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B71" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B72" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B74" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B75" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B76" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="12" t="s">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B78" s="12" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B80" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B81" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" s="12" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B83" s="12" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B85" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B86" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B87" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="12" t="s">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B89" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B91" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B92" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B93" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B94" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B96" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B97" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B98" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B99" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B100" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B101" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" t="s">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B102" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B101" t="s">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B103" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B106" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B107" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
+    <row r="108" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B108" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B107" t="s">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B109" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B111" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B112" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B113" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B114" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B113" t="s">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B115" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B116" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B118" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B120" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
+    <row r="121" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B121" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B122" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
+    <row r="123" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B123" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B124" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B125" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.75">
+      <c r="B126" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A51" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A53" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -10542,12 +10555,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -10672,7 +10685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10797,7 +10810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10922,7 +10935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11047,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11172,7 +11185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11297,7 +11310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -11422,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -11558,12 +11571,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -11688,7 +11701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11813,7 +11826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11938,7 +11951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12063,7 +12076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12188,7 +12201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12313,7 +12326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -12438,7 +12451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -12574,12 +12587,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -12704,7 +12717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12829,7 +12842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12954,7 +12967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13079,7 +13092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13204,7 +13217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13329,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -13454,7 +13467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -13590,12 +13603,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -13720,7 +13733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13845,7 +13858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13970,7 +13983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14095,7 +14108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14220,7 +14233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14345,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -14470,7 +14483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -14606,12 +14619,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -14736,7 +14749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14861,7 +14874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14986,7 +14999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15111,7 +15124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15236,7 +15249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15361,7 +15374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -15486,7 +15499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -15622,12 +15635,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -15752,7 +15765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15877,7 +15890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16002,7 +16015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -16127,7 +16140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -16252,7 +16265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16377,7 +16390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -16502,7 +16515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -16638,12 +16651,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -16768,7 +16781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16893,7 +16906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17018,7 +17031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -17143,7 +17156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -17268,7 +17281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -17393,7 +17406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -17518,7 +17531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -17654,12 +17667,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -17784,7 +17797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17909,7 +17922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -18034,7 +18047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -18159,7 +18172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -18284,7 +18297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -18409,7 +18422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -18534,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -18670,12 +18683,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -18800,7 +18813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -18925,7 +18938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -19050,7 +19063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -19175,7 +19188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -19300,7 +19313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -19425,7 +19438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -19550,7 +19563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -19686,12 +19699,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -19816,7 +19829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -19911,7 +19924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -20006,7 +20019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -20101,7 +20114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -20196,7 +20209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -20291,7 +20304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -20386,7 +20399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -20489,13 +20502,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH67"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.86328125" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="E1">
         <v>2023</v>
       </c>
@@ -20584,27 +20597,27 @@
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B14" t="s">
         <v>127</v>
       </c>
@@ -20702,17 +20715,17 @@
         <v>306</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>131</v>
       </c>
@@ -20810,7 +20823,7 @@
         <v>-3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>133</v>
       </c>
@@ -20908,7 +20921,7 @@
         <v>-8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>134</v>
       </c>
@@ -21006,12 +21019,12 @@
         <v>-3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -21109,7 +21122,7 @@
         <v>-8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>305</v>
       </c>
@@ -21207,7 +21220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>304</v>
       </c>
@@ -21305,7 +21318,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>303</v>
       </c>
@@ -21403,7 +21416,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>302</v>
       </c>
@@ -21501,7 +21514,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>301</v>
       </c>
@@ -21599,7 +21612,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -21697,7 +21710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -21795,7 +21808,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>139</v>
       </c>
@@ -21893,7 +21906,7 @@
         <v>-8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>140</v>
       </c>
@@ -21991,7 +22004,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>141</v>
       </c>
@@ -22089,7 +22102,7 @@
         <v>-6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>142</v>
       </c>
@@ -22187,7 +22200,7 @@
         <v>-6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -22285,7 +22298,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>144</v>
       </c>
@@ -22383,7 +22396,7 @@
         <v>-4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>145</v>
       </c>
@@ -22481,7 +22494,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -22579,17 +22592,17 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>131</v>
       </c>
@@ -22687,7 +22700,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>133</v>
       </c>
@@ -22785,7 +22798,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>147</v>
       </c>
@@ -22883,12 +22896,12 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -22986,7 +22999,7 @@
         <v>-5.5E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>305</v>
       </c>
@@ -23084,7 +23097,7 @@
         <v>-8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>304</v>
       </c>
@@ -23182,7 +23195,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>303</v>
       </c>
@@ -23280,7 +23293,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>302</v>
       </c>
@@ -23378,7 +23391,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>301</v>
       </c>
@@ -23476,7 +23489,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>137</v>
       </c>
@@ -23574,7 +23587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -23672,7 +23685,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>139</v>
       </c>
@@ -23770,7 +23783,7 @@
         <v>-6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>140</v>
       </c>
@@ -23868,7 +23881,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -23966,7 +23979,7 @@
         <v>-6.3E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>142</v>
       </c>
@@ -24064,7 +24077,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>143</v>
       </c>
@@ -24162,7 +24175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -24260,7 +24273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>149</v>
       </c>
@@ -24358,7 +24371,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -24456,7 +24469,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -24558,7 +24571,7 @@
       </c>
       <c r="AH59" s="29"/>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>152</v>
       </c>
@@ -24656,7 +24669,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>153</v>
       </c>
@@ -24754,7 +24767,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>154</v>
       </c>
@@ -24852,7 +24865,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>155</v>
       </c>
@@ -24950,7 +24963,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:34" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -25048,7 +25061,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>157</v>
       </c>
@@ -25146,7 +25159,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>158</v>
       </c>
@@ -25244,7 +25257,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -25351,13 +25364,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AG323"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.40625" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="E1">
         <v>2023</v>
       </c>
@@ -25446,36 +25459,27 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>127</v>
       </c>
@@ -25573,22 +25577,22 @@
         <v>306</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>167</v>
       </c>
@@ -25686,7 +25690,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -25784,7 +25788,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -25882,7 +25886,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -25980,7 +25984,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>171</v>
       </c>
@@ -26078,7 +26082,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>155</v>
       </c>
@@ -26176,7 +26180,7 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>172</v>
       </c>
@@ -26274,7 +26278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>173</v>
       </c>
@@ -26372,7 +26376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>159</v>
       </c>
@@ -26470,7 +26474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>300</v>
       </c>
@@ -26568,7 +26572,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>299</v>
       </c>
@@ -26666,7 +26670,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>298</v>
       </c>
@@ -26764,7 +26768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>174</v>
       </c>
@@ -26862,12 +26866,12 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>167</v>
       </c>
@@ -26965,7 +26969,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>168</v>
       </c>
@@ -27063,7 +27067,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>169</v>
       </c>
@@ -27161,7 +27165,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>170</v>
       </c>
@@ -27259,7 +27263,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>171</v>
       </c>
@@ -27357,7 +27361,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>155</v>
       </c>
@@ -27455,7 +27459,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>172</v>
       </c>
@@ -27553,7 +27557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>173</v>
       </c>
@@ -27651,7 +27655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>159</v>
       </c>
@@ -27749,7 +27753,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>300</v>
       </c>
@@ -27847,7 +27851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>299</v>
       </c>
@@ -27945,7 +27949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>298</v>
       </c>
@@ -28043,7 +28047,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>176</v>
       </c>
@@ -28141,12 +28145,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>167</v>
       </c>
@@ -28244,7 +28248,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>168</v>
       </c>
@@ -28342,7 +28346,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>169</v>
       </c>
@@ -28440,7 +28444,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>170</v>
       </c>
@@ -28538,7 +28542,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>171</v>
       </c>
@@ -28636,7 +28640,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>155</v>
       </c>
@@ -28734,7 +28738,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>172</v>
       </c>
@@ -28832,7 +28836,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>173</v>
       </c>
@@ -28930,7 +28934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -29028,7 +29032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>300</v>
       </c>
@@ -29126,7 +29130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>299</v>
       </c>
@@ -29224,7 +29228,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>298</v>
       </c>
@@ -29322,7 +29326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>178</v>
       </c>
@@ -29420,7 +29424,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>179</v>
       </c>
@@ -29518,17 +29522,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>167</v>
       </c>
@@ -29626,7 +29630,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>168</v>
       </c>
@@ -29724,7 +29728,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>169</v>
       </c>
@@ -29822,7 +29826,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>170</v>
       </c>
@@ -29920,7 +29924,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>171</v>
       </c>
@@ -30018,7 +30022,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>155</v>
       </c>
@@ -30116,7 +30120,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>172</v>
       </c>
@@ -30214,7 +30218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>173</v>
       </c>
@@ -30312,7 +30316,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>159</v>
       </c>
@@ -30410,7 +30414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>300</v>
       </c>
@@ -30508,7 +30512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>299</v>
       </c>
@@ -30606,7 +30610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>298</v>
       </c>
@@ -30704,7 +30708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>174</v>
       </c>
@@ -30802,12 +30806,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>167</v>
       </c>
@@ -30905,7 +30909,7 @@
         <v>-2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>168</v>
       </c>
@@ -31003,7 +31007,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>169</v>
       </c>
@@ -31101,7 +31105,7 @@
         <v>-0.104</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>170</v>
       </c>
@@ -31199,7 +31203,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -31297,7 +31301,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>155</v>
       </c>
@@ -31395,7 +31399,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -31493,7 +31497,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>173</v>
       </c>
@@ -31591,7 +31595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>159</v>
       </c>
@@ -31689,7 +31693,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>300</v>
       </c>
@@ -31787,7 +31791,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>299</v>
       </c>
@@ -31885,7 +31889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>298</v>
       </c>
@@ -31983,7 +31987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -32081,12 +32085,12 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>167</v>
       </c>
@@ -32184,7 +32188,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>168</v>
       </c>
@@ -32282,7 +32286,7 @@
         <v>-5.5E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>169</v>
       </c>
@@ -32380,7 +32384,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>170</v>
       </c>
@@ -32478,7 +32482,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
         <v>171</v>
       </c>
@@ -32576,7 +32580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>155</v>
       </c>
@@ -32674,7 +32678,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A97" t="s">
         <v>172</v>
       </c>
@@ -32772,7 +32776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A98" t="s">
         <v>173</v>
       </c>
@@ -32870,7 +32874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A99" t="s">
         <v>159</v>
       </c>
@@ -32968,7 +32972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A100" t="s">
         <v>300</v>
       </c>
@@ -33066,7 +33070,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A101" t="s">
         <v>299</v>
       </c>
@@ -33164,7 +33168,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A102" t="s">
         <v>298</v>
       </c>
@@ -33262,7 +33266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A103" t="s">
         <v>178</v>
       </c>
@@ -33360,7 +33364,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A104" t="s">
         <v>166</v>
       </c>
@@ -33371,7 +33375,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A105" t="s">
         <v>167</v>
       </c>
@@ -33469,7 +33473,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A106" t="s">
         <v>168</v>
       </c>
@@ -33567,7 +33571,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A107" t="s">
         <v>169</v>
       </c>
@@ -33665,7 +33669,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A108" t="s">
         <v>170</v>
       </c>
@@ -33763,7 +33767,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A109" t="s">
         <v>171</v>
       </c>
@@ -33861,7 +33865,7 @@
         <v>-0.109</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A110" t="s">
         <v>155</v>
       </c>
@@ -33959,7 +33963,7 @@
         <v>0.14099999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A111" t="s">
         <v>172</v>
       </c>
@@ -34057,7 +34061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A112" t="s">
         <v>173</v>
       </c>
@@ -34155,7 +34159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A113" t="s">
         <v>159</v>
       </c>
@@ -34253,7 +34257,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A114" t="s">
         <v>300</v>
       </c>
@@ -34351,7 +34355,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A115" t="s">
         <v>299</v>
       </c>
@@ -34449,7 +34453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A116" t="s">
         <v>298</v>
       </c>
@@ -34547,7 +34551,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A117" t="s">
         <v>182</v>
       </c>
@@ -34645,17 +34649,17 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A118" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A119" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A120" t="s">
         <v>167</v>
       </c>
@@ -34753,7 +34757,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A121" t="s">
         <v>168</v>
       </c>
@@ -34851,7 +34855,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A122" t="s">
         <v>169</v>
       </c>
@@ -34949,7 +34953,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A123" t="s">
         <v>170</v>
       </c>
@@ -35047,7 +35051,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A124" t="s">
         <v>171</v>
       </c>
@@ -35145,7 +35149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A125" t="s">
         <v>155</v>
       </c>
@@ -35243,7 +35247,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A126" t="s">
         <v>172</v>
       </c>
@@ -35341,7 +35345,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A127" t="s">
         <v>173</v>
       </c>
@@ -35439,7 +35443,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A128" t="s">
         <v>159</v>
       </c>
@@ -35537,7 +35541,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A129" t="s">
         <v>300</v>
       </c>
@@ -35635,7 +35639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A130" t="s">
         <v>299</v>
       </c>
@@ -35733,7 +35737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A131" t="s">
         <v>298</v>
       </c>
@@ -35831,7 +35835,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A132" t="s">
         <v>184</v>
       </c>
@@ -35926,12 +35930,12 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A133" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A134" t="s">
         <v>167</v>
       </c>
@@ -36029,7 +36033,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A135" t="s">
         <v>168</v>
       </c>
@@ -36127,7 +36131,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A136" t="s">
         <v>169</v>
       </c>
@@ -36225,7 +36229,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A137" t="s">
         <v>170</v>
       </c>
@@ -36323,7 +36327,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A138" t="s">
         <v>171</v>
       </c>
@@ -36421,7 +36425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -36519,7 +36523,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A140" t="s">
         <v>172</v>
       </c>
@@ -36617,7 +36621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A141" t="s">
         <v>173</v>
       </c>
@@ -36715,7 +36719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -36813,7 +36817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A143" t="s">
         <v>300</v>
       </c>
@@ -36911,7 +36915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A144" t="s">
         <v>299</v>
       </c>
@@ -37009,7 +37013,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A145" t="s">
         <v>298</v>
       </c>
@@ -37107,7 +37111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A146" t="s">
         <v>185</v>
       </c>
@@ -37202,12 +37206,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A147" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -37305,7 +37309,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -37403,7 +37407,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A150" t="s">
         <v>169</v>
       </c>
@@ -37501,7 +37505,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -37599,7 +37603,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A152" t="s">
         <v>171</v>
       </c>
@@ -37697,7 +37701,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -37795,7 +37799,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A154" t="s">
         <v>172</v>
       </c>
@@ -37893,7 +37897,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A155" t="s">
         <v>173</v>
       </c>
@@ -37991,7 +37995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A156" t="s">
         <v>159</v>
       </c>
@@ -38089,7 +38093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A157" t="s">
         <v>300</v>
       </c>
@@ -38187,7 +38191,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A158" t="s">
         <v>299</v>
       </c>
@@ -38285,7 +38289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A159" t="s">
         <v>298</v>
       </c>
@@ -38383,7 +38387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -38478,7 +38482,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A161" t="s">
         <v>187</v>
       </c>
@@ -38573,17 +38577,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A162" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A163" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A164" t="s">
         <v>167</v>
       </c>
@@ -38681,7 +38685,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -38779,7 +38783,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A166" t="s">
         <v>169</v>
       </c>
@@ -38877,7 +38881,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -38975,7 +38979,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A168" t="s">
         <v>171</v>
       </c>
@@ -39073,7 +39077,7 @@
         <v>-6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A169" t="s">
         <v>155</v>
       </c>
@@ -39171,7 +39175,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -39269,7 +39273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -39367,7 +39371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A172" t="s">
         <v>159</v>
       </c>
@@ -39465,7 +39469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A173" t="s">
         <v>300</v>
       </c>
@@ -39563,7 +39567,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A174" t="s">
         <v>299</v>
       </c>
@@ -39661,7 +39665,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A175" t="s">
         <v>298</v>
       </c>
@@ -39759,7 +39763,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A176" t="s">
         <v>174</v>
       </c>
@@ -39857,12 +39861,12 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A177" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A178" t="s">
         <v>167</v>
       </c>
@@ -39960,7 +39964,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A179" t="s">
         <v>168</v>
       </c>
@@ -40058,7 +40062,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A180" t="s">
         <v>169</v>
       </c>
@@ -40156,7 +40160,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A181" t="s">
         <v>170</v>
       </c>
@@ -40254,7 +40258,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A182" t="s">
         <v>171</v>
       </c>
@@ -40352,7 +40356,7 @@
         <v>-5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A183" t="s">
         <v>155</v>
       </c>
@@ -40450,7 +40454,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A184" t="s">
         <v>172</v>
       </c>
@@ -40548,7 +40552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A185" t="s">
         <v>173</v>
       </c>
@@ -40646,7 +40650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A186" t="s">
         <v>159</v>
       </c>
@@ -40744,7 +40748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A187" t="s">
         <v>300</v>
       </c>
@@ -40842,7 +40846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A188" t="s">
         <v>299</v>
       </c>
@@ -40940,7 +40944,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A189" t="s">
         <v>298</v>
       </c>
@@ -41038,7 +41042,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A190" t="s">
         <v>176</v>
       </c>
@@ -41136,12 +41140,12 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A191" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A192" t="s">
         <v>167</v>
       </c>
@@ -41239,7 +41243,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A193" t="s">
         <v>168</v>
       </c>
@@ -41337,7 +41341,7 @@
         <v>-6.3E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A194" t="s">
         <v>169</v>
       </c>
@@ -41435,7 +41439,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A195" t="s">
         <v>170</v>
       </c>
@@ -41533,7 +41537,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A196" t="s">
         <v>171</v>
       </c>
@@ -41631,7 +41635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A197" t="s">
         <v>155</v>
       </c>
@@ -41729,7 +41733,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A198" t="s">
         <v>172</v>
       </c>
@@ -41827,7 +41831,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A199" t="s">
         <v>173</v>
       </c>
@@ -41925,7 +41929,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A200" t="s">
         <v>159</v>
       </c>
@@ -42023,7 +42027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A201" t="s">
         <v>300</v>
       </c>
@@ -42121,7 +42125,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A202" t="s">
         <v>299</v>
       </c>
@@ -42219,7 +42223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A203" t="s">
         <v>298</v>
       </c>
@@ -42317,7 +42321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A204" t="s">
         <v>178</v>
       </c>
@@ -42415,7 +42419,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A205" t="s">
         <v>21</v>
       </c>
@@ -42513,22 +42517,22 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A206" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A207" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A208" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A209" t="s">
         <v>167</v>
       </c>
@@ -42626,7 +42630,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A210" t="s">
         <v>168</v>
       </c>
@@ -42724,7 +42728,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A211" t="s">
         <v>169</v>
       </c>
@@ -42822,7 +42826,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A212" t="s">
         <v>170</v>
       </c>
@@ -42920,7 +42924,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A213" t="s">
         <v>171</v>
       </c>
@@ -43018,7 +43022,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A214" t="s">
         <v>155</v>
       </c>
@@ -43116,7 +43120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A215" t="s">
         <v>172</v>
       </c>
@@ -43214,7 +43218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A216" t="s">
         <v>173</v>
       </c>
@@ -43312,7 +43316,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A217" t="s">
         <v>159</v>
       </c>
@@ -43410,7 +43414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A218" t="s">
         <v>300</v>
       </c>
@@ -43508,7 +43512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A219" t="s">
         <v>299</v>
       </c>
@@ -43606,7 +43610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A220" t="s">
         <v>298</v>
       </c>
@@ -43704,7 +43708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A221" t="s">
         <v>184</v>
       </c>
@@ -43799,12 +43803,12 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A222" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A223" t="s">
         <v>167</v>
       </c>
@@ -43902,7 +43906,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A224" t="s">
         <v>168</v>
       </c>
@@ -44000,7 +44004,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A225" t="s">
         <v>169</v>
       </c>
@@ -44098,7 +44102,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A226" t="s">
         <v>170</v>
       </c>
@@ -44196,7 +44200,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="227" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A227" t="s">
         <v>171</v>
       </c>
@@ -44294,7 +44298,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A228" t="s">
         <v>155</v>
       </c>
@@ -44392,7 +44396,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A229" t="s">
         <v>172</v>
       </c>
@@ -44490,7 +44494,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A230" t="s">
         <v>173</v>
       </c>
@@ -44588,7 +44592,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="231" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A231" t="s">
         <v>159</v>
       </c>
@@ -44686,7 +44690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A232" t="s">
         <v>300</v>
       </c>
@@ -44784,7 +44788,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A233" t="s">
         <v>299</v>
       </c>
@@ -44882,7 +44886,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A234" t="s">
         <v>298</v>
       </c>
@@ -44980,7 +44984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="235" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A235" t="s">
         <v>185</v>
       </c>
@@ -45075,12 +45079,12 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="236" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A236" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="237" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A237" t="s">
         <v>167</v>
       </c>
@@ -45178,7 +45182,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="238" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A238" t="s">
         <v>168</v>
       </c>
@@ -45276,7 +45280,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="239" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A239" t="s">
         <v>169</v>
       </c>
@@ -45374,7 +45378,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A240" t="s">
         <v>170</v>
       </c>
@@ -45472,7 +45476,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A241" t="s">
         <v>171</v>
       </c>
@@ -45570,7 +45574,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A242" t="s">
         <v>155</v>
       </c>
@@ -45668,7 +45672,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="243" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A243" t="s">
         <v>172</v>
       </c>
@@ -45766,7 +45770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A244" t="s">
         <v>173</v>
       </c>
@@ -45864,7 +45868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A245" t="s">
         <v>159</v>
       </c>
@@ -45962,7 +45966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A246" t="s">
         <v>300</v>
       </c>
@@ -46060,7 +46064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A247" t="s">
         <v>299</v>
       </c>
@@ -46158,7 +46162,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A248" t="s">
         <v>298</v>
       </c>
@@ -46256,7 +46260,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A249" t="s">
         <v>186</v>
       </c>
@@ -46351,7 +46355,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A250" t="s">
         <v>187</v>
       </c>
@@ -46446,17 +46450,17 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A251" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A252" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A253" t="s">
         <v>167</v>
       </c>
@@ -46554,7 +46558,7 @@
         <v>-7.8E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A254" t="s">
         <v>168</v>
       </c>
@@ -46652,7 +46656,7 @@
         <v>-6.2E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A255" t="s">
         <v>169</v>
       </c>
@@ -46750,7 +46754,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A256" t="s">
         <v>170</v>
       </c>
@@ -46848,7 +46852,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A257" t="s">
         <v>171</v>
       </c>
@@ -46946,7 +46950,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A258" t="s">
         <v>155</v>
       </c>
@@ -47044,7 +47048,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A259" t="s">
         <v>172</v>
       </c>
@@ -47142,7 +47146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A260" t="s">
         <v>173</v>
       </c>
@@ -47240,7 +47244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A261" t="s">
         <v>159</v>
       </c>
@@ -47338,7 +47342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A262" t="s">
         <v>300</v>
       </c>
@@ -47436,7 +47440,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A263" t="s">
         <v>299</v>
       </c>
@@ -47534,7 +47538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A264" t="s">
         <v>298</v>
       </c>
@@ -47632,7 +47636,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A265" t="s">
         <v>174</v>
       </c>
@@ -47730,12 +47734,12 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A266" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="267" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A267" t="s">
         <v>167</v>
       </c>
@@ -47833,7 +47837,7 @@
         <v>-2.3E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A268" t="s">
         <v>168</v>
       </c>
@@ -47931,7 +47935,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A269" t="s">
         <v>169</v>
       </c>
@@ -48029,7 +48033,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="270" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A270" t="s">
         <v>170</v>
       </c>
@@ -48127,7 +48131,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="271" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A271" t="s">
         <v>171</v>
       </c>
@@ -48225,7 +48229,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="272" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A272" t="s">
         <v>155</v>
       </c>
@@ -48323,7 +48327,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A273" t="s">
         <v>172</v>
       </c>
@@ -48421,7 +48425,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="274" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A274" t="s">
         <v>173</v>
       </c>
@@ -48519,7 +48523,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A275" t="s">
         <v>159</v>
       </c>
@@ -48617,7 +48621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="276" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A276" t="s">
         <v>300</v>
       </c>
@@ -48715,7 +48719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="277" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A277" t="s">
         <v>299</v>
       </c>
@@ -48813,7 +48817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="278" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A278" t="s">
         <v>298</v>
       </c>
@@ -48911,7 +48915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="279" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A279" t="s">
         <v>176</v>
       </c>
@@ -49009,12 +49013,12 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="280" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A280" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="281" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A281" t="s">
         <v>167</v>
       </c>
@@ -49112,7 +49116,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="282" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A282" t="s">
         <v>168</v>
       </c>
@@ -49210,7 +49214,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="283" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A283" t="s">
         <v>169</v>
       </c>
@@ -49308,7 +49312,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="284" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A284" t="s">
         <v>170</v>
       </c>
@@ -49406,7 +49410,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A285" t="s">
         <v>171</v>
       </c>
@@ -49504,7 +49508,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A286" t="s">
         <v>155</v>
       </c>
@@ -49602,7 +49606,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="287" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A287" t="s">
         <v>172</v>
       </c>
@@ -49700,7 +49704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A288" t="s">
         <v>173</v>
       </c>
@@ -49798,7 +49802,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A289" t="s">
         <v>159</v>
       </c>
@@ -49896,7 +49900,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A290" t="s">
         <v>300</v>
       </c>
@@ -49994,7 +49998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A291" t="s">
         <v>299</v>
       </c>
@@ -50092,7 +50096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A292" t="s">
         <v>298</v>
       </c>
@@ -50190,7 +50194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A293" t="s">
         <v>178</v>
       </c>
@@ -50288,7 +50292,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="294" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A294" t="s">
         <v>150</v>
       </c>
@@ -50386,12 +50390,12 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="295" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A295" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="296" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A296" t="s">
         <v>190</v>
       </c>
@@ -50489,7 +50493,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A297" t="s">
         <v>191</v>
       </c>
@@ -50587,12 +50591,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A298" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="299" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A299" t="s">
         <v>193</v>
       </c>
@@ -50690,7 +50694,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="300" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A300" t="s">
         <v>194</v>
       </c>
@@ -50788,7 +50792,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A301" t="s">
         <v>195</v>
       </c>
@@ -50886,7 +50890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A302" t="s">
         <v>196</v>
       </c>
@@ -50984,12 +50988,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A303" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="304" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A304" t="s">
         <v>197</v>
       </c>
@@ -51087,7 +51091,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="305" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A305" t="s">
         <v>191</v>
       </c>
@@ -51185,12 +51189,12 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="306" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A306" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="307" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A307" t="s">
         <v>193</v>
       </c>
@@ -51288,7 +51292,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A308" t="s">
         <v>194</v>
       </c>
@@ -51386,7 +51390,7 @@
         <v>-5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A309" t="s">
         <v>195</v>
       </c>
@@ -51484,7 +51488,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A310" t="s">
         <v>196</v>
       </c>
@@ -51582,12 +51586,12 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="311" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A311" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="312" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A312" t="s">
         <v>198</v>
       </c>
@@ -51685,7 +51689,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A313" t="s">
         <v>199</v>
       </c>
@@ -51783,7 +51787,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A314" t="s">
         <v>200</v>
       </c>
@@ -51881,12 +51885,12 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A315" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="316" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A316" t="s">
         <v>193</v>
       </c>
@@ -51984,7 +51988,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A317" t="s">
         <v>194</v>
       </c>
@@ -52082,7 +52086,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="318" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A318" t="s">
         <v>195</v>
       </c>
@@ -52180,7 +52184,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="319" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:33" ht="14.75" x14ac:dyDescent="0.75">
       <c r="A319" t="s">
         <v>196</v>
       </c>
@@ -52278,10 +52282,10 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:33" x14ac:dyDescent="0.25"/>
-    <row r="321" x14ac:dyDescent="0.25"/>
-    <row r="322" x14ac:dyDescent="0.25"/>
-    <row r="323" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:33" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="321" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="322" ht="14.75" x14ac:dyDescent="0.75"/>
+    <row r="323" ht="14.75" x14ac:dyDescent="0.75"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -52291,18 +52295,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="8" width="23.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.86328125" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.1328125" customWidth="1"/>
+    <col min="6" max="8" width="23.26953125" customWidth="1"/>
+    <col min="10" max="10" width="14.40625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>115</v>
       </c>
@@ -52328,7 +52332,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -52355,7 +52359,7 @@
       </c>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -52383,7 +52387,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="24"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -52409,7 +52413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -52435,7 +52439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -52461,7 +52465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -52487,7 +52491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.75">
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -52504,19 +52508,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="8" width="23.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.86328125" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="17.1328125" customWidth="1"/>
+    <col min="6" max="8" width="23.26953125" customWidth="1"/>
+    <col min="9" max="9" width="13.40625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>115</v>
       </c>
@@ -52542,7 +52546,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -52570,7 +52574,7 @@
       <c r="I2" s="24"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -52597,7 +52601,7 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -52623,7 +52627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -52649,7 +52653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -52675,7 +52679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -52709,81 +52713,81 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AE149"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="58.28515625" customWidth="1"/>
+    <col min="1" max="1" width="58.26953125" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A2" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A11" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>60</v>
       </c>
       <c r="N15" s="32"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>85</v>
       </c>
       <c r="N16" s="34"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -52792,13 +52796,13 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="35"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.75">
       <c r="N18" s="35"/>
       <c r="O18" s="36"/>
       <c r="P18" s="36"/>
       <c r="Q18" s="36"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -52807,7 +52811,7 @@
       <c r="P19" s="36"/>
       <c r="Q19" s="36"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -52816,7 +52820,7 @@
       <c r="P20" s="36"/>
       <c r="Q20" s="36"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -52825,7 +52829,7 @@
       <c r="P21" s="36"/>
       <c r="Q21" s="36"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -52834,7 +52838,7 @@
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>91</v>
       </c>
@@ -52843,7 +52847,7 @@
       <c r="P23" s="36"/>
       <c r="Q23" s="36"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -52852,7 +52856,7 @@
       <c r="P24" s="36"/>
       <c r="Q24" s="36"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -52861,13 +52865,13 @@
       <c r="P25" s="36"/>
       <c r="Q25" s="36"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.75">
       <c r="N26" s="35"/>
       <c r="O26" s="37"/>
       <c r="P26" s="36"/>
       <c r="Q26" s="36"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>216</v>
       </c>
@@ -52876,13 +52880,13 @@
       <c r="P27" s="36"/>
       <c r="Q27" s="36"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.75">
       <c r="N28" s="35"/>
       <c r="O28" s="37"/>
       <c r="P28" s="36"/>
       <c r="Q28" s="36"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>230</v>
       </c>
@@ -52891,13 +52895,13 @@
       <c r="P29" s="36"/>
       <c r="Q29" s="36"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.75">
       <c r="N30" s="35"/>
       <c r="O30" s="37"/>
       <c r="P30" s="36"/>
       <c r="Q30" s="36"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A31" s="28" t="s">
         <v>260</v>
       </c>
@@ -52906,7 +52910,7 @@
       <c r="P31" s="36"/>
       <c r="Q31" s="36"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A32" s="28"/>
       <c r="B32" t="s">
         <v>231</v>
@@ -52925,7 +52929,7 @@
       <c r="P32" s="36"/>
       <c r="Q32" s="36"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A33" s="40">
         <v>44947</v>
       </c>
@@ -52946,7 +52950,7 @@
       <c r="P33" s="36"/>
       <c r="Q33" s="36"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A34" s="40">
         <v>44978</v>
       </c>
@@ -52967,7 +52971,7 @@
       <c r="P34" s="36"/>
       <c r="Q34" s="36"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A35" s="40">
         <v>45006</v>
       </c>
@@ -52988,7 +52992,7 @@
       <c r="P35" s="36"/>
       <c r="Q35" s="36"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A36" s="40">
         <v>45037</v>
       </c>
@@ -53009,7 +53013,7 @@
       <c r="P36" s="36"/>
       <c r="Q36" s="36"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A37" s="40">
         <v>45067</v>
       </c>
@@ -53030,7 +53034,7 @@
       <c r="P37" s="36"/>
       <c r="Q37" s="36"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A38" s="40">
         <v>45098</v>
       </c>
@@ -53051,7 +53055,7 @@
       <c r="P38" s="36"/>
       <c r="Q38" s="36"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A39" s="40">
         <v>45128</v>
       </c>
@@ -53084,7 +53088,7 @@
       <c r="AC39" s="11"/>
       <c r="AD39" s="11"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A40" s="40">
         <v>45159</v>
       </c>
@@ -53105,7 +53109,7 @@
       <c r="P40" s="36"/>
       <c r="Q40" s="36"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A41" s="40">
         <v>45190</v>
       </c>
@@ -53126,7 +53130,7 @@
       <c r="P41" s="36"/>
       <c r="Q41" s="36"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A42" s="40">
         <v>45220</v>
       </c>
@@ -53147,7 +53151,7 @@
       <c r="P42" s="36"/>
       <c r="Q42" s="36"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A43" s="40">
         <v>45251</v>
       </c>
@@ -53168,7 +53172,7 @@
       <c r="P43" s="36"/>
       <c r="Q43" s="36"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A44" s="40">
         <v>45281</v>
       </c>
@@ -53189,7 +53193,7 @@
       <c r="P44" s="36"/>
       <c r="Q44" s="36"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A45" s="40">
         <v>44948</v>
       </c>
@@ -53210,7 +53214,7 @@
       <c r="P45" s="36"/>
       <c r="Q45" s="36"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A46" s="40">
         <v>44979</v>
       </c>
@@ -53231,7 +53235,7 @@
       <c r="P46" s="36"/>
       <c r="Q46" s="36"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A47" s="40">
         <v>45007</v>
       </c>
@@ -53252,7 +53256,7 @@
       <c r="P47" s="36"/>
       <c r="Q47" s="36"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A48" s="40">
         <v>45038</v>
       </c>
@@ -53273,7 +53277,7 @@
       <c r="P48" s="36"/>
       <c r="Q48" s="36"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A49" s="40">
         <v>45068</v>
       </c>
@@ -53294,7 +53298,7 @@
       <c r="P49" s="36"/>
       <c r="Q49" s="36"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A50" s="40">
         <v>45099</v>
       </c>
@@ -53315,7 +53319,7 @@
       <c r="P50" s="36"/>
       <c r="Q50" s="36"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A51" s="40">
         <v>45129</v>
       </c>
@@ -53336,7 +53340,7 @@
       <c r="P51" s="36"/>
       <c r="Q51" s="36"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A52" s="40">
         <v>45160</v>
       </c>
@@ -53357,7 +53361,7 @@
       <c r="P52" s="36"/>
       <c r="Q52" s="36"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A53" s="40">
         <v>45191</v>
       </c>
@@ -53378,7 +53382,7 @@
       <c r="P53" s="36"/>
       <c r="Q53" s="36"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A54" s="40">
         <v>45221</v>
       </c>
@@ -53399,7 +53403,7 @@
       <c r="P54" s="36"/>
       <c r="Q54" s="36"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A55" s="40">
         <v>45252</v>
       </c>
@@ -53420,7 +53424,7 @@
       <c r="P55" s="36"/>
       <c r="Q55" s="36"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A56" s="40">
         <v>45282</v>
       </c>
@@ -53441,7 +53445,7 @@
       <c r="P56" s="36"/>
       <c r="Q56" s="36"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A57" s="40">
         <v>45314</v>
       </c>
@@ -53462,7 +53466,7 @@
       <c r="P57" s="36"/>
       <c r="Q57" s="36"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A58" s="40">
         <v>45345</v>
       </c>
@@ -53483,7 +53487,7 @@
       <c r="P58" s="36"/>
       <c r="Q58" s="36"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A59" s="40">
         <v>45374</v>
       </c>
@@ -53504,7 +53508,7 @@
       <c r="P59" s="36"/>
       <c r="Q59" s="36"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A60" s="40">
         <v>45405</v>
       </c>
@@ -53525,7 +53529,7 @@
       <c r="P60" s="36"/>
       <c r="Q60" s="36"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A61" s="40">
         <v>45435</v>
       </c>
@@ -53546,7 +53550,7 @@
       <c r="P61" s="36"/>
       <c r="Q61" s="36"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A62" s="40">
         <v>45466</v>
       </c>
@@ -53567,7 +53571,7 @@
       <c r="P62" s="36"/>
       <c r="Q62" s="36"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A63" s="40">
         <v>45496</v>
       </c>
@@ -53588,7 +53592,7 @@
       <c r="P63" s="36"/>
       <c r="Q63" s="36"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A64" s="40">
         <v>45527</v>
       </c>
@@ -53609,7 +53613,7 @@
       <c r="P64" s="36"/>
       <c r="Q64" s="36"/>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A65" s="40">
         <v>45558</v>
       </c>
@@ -53630,7 +53634,7 @@
       <c r="P65" s="36"/>
       <c r="Q65" s="36"/>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A66" s="40">
         <v>45588</v>
       </c>
@@ -53651,7 +53655,7 @@
       <c r="P66" s="36"/>
       <c r="Q66" s="36"/>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A67" s="40">
         <v>45619</v>
       </c>
@@ -53672,7 +53676,7 @@
       <c r="P67" s="36"/>
       <c r="Q67" s="36"/>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A68" s="40">
         <v>45649</v>
       </c>
@@ -53693,13 +53697,13 @@
       <c r="P68" s="36"/>
       <c r="Q68" s="36"/>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.75">
       <c r="N69" s="35"/>
       <c r="O69" s="37"/>
       <c r="P69" s="36"/>
       <c r="Q69" s="36"/>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>235</v>
       </c>
@@ -53716,7 +53720,7 @@
       <c r="P70" s="36"/>
       <c r="Q70" s="36"/>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>236</v>
       </c>
@@ -53733,7 +53737,7 @@
       <c r="P71" s="36"/>
       <c r="Q71" s="36"/>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>261</v>
       </c>
@@ -53750,7 +53754,7 @@
       <c r="P72" s="36"/>
       <c r="Q72" s="36"/>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>262</v>
       </c>
@@ -53845,7 +53849,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>263</v>
       </c>
@@ -53940,7 +53944,7 @@
         <v>12352000</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>264</v>
       </c>
@@ -54035,7 +54039,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>265</v>
       </c>
@@ -54130,7 +54134,7 @@
         <v>3464980</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>266</v>
       </c>
@@ -54225,7 +54229,7 @@
         <v>91863</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>267</v>
       </c>
@@ -54320,7 +54324,7 @@
         <v>1369780</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>268</v>
       </c>
@@ -54415,7 +54419,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>269</v>
       </c>
@@ -54510,7 +54514,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>262</v>
       </c>
@@ -54605,7 +54609,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>270</v>
       </c>
@@ -54700,7 +54704,7 @@
         <v>10820700</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>271</v>
       </c>
@@ -54795,7 +54799,7 @@
         <v>3625.18</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>272</v>
       </c>
@@ -54890,7 +54894,7 @@
         <v>5119790</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>273</v>
       </c>
@@ -54985,7 +54989,7 @@
         <v>135736</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>274</v>
       </c>
@@ -55080,7 +55084,7 @@
         <v>1199970</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>275</v>
       </c>
@@ -55175,7 +55179,7 @@
         <v>4199.1000000000004</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>276</v>
       </c>
@@ -55270,7 +55274,7 @@
         <v>695.59699999999998</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>217</v>
       </c>
@@ -55395,7 +55399,7 @@
         <v>0.71462015526210543</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>218</v>
       </c>
@@ -55520,7 +55524,7 @@
         <v>7.924808907666181E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>219</v>
       </c>
@@ -55645,7 +55649,7 @@
         <v>0.79386824433876724</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>217</v>
       </c>
@@ -55770,7 +55774,7 @@
         <v>0.62602706790214713</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A97" t="s">
         <v>218</v>
       </c>
@@ -55895,7 +55899,7 @@
         <v>6.9423761925803282E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A98" t="s">
         <v>219</v>
       </c>
@@ -56020,7 +56024,7 @@
         <v>0.69545082982795037</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.75">
       <c r="B99" s="39"/>
       <c r="C99" s="39"/>
       <c r="D99" s="39"/>
@@ -56052,7 +56056,7 @@
       <c r="AD99" s="39"/>
       <c r="AE99" s="39"/>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A100" s="1" t="s">
         <v>237</v>
       </c>
@@ -56060,7 +56064,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.75">
       <c r="B102" t="s">
         <v>239</v>
       </c>
@@ -56068,7 +56072,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A103">
         <v>2021</v>
       </c>
@@ -56080,7 +56084,7 @@
         <v>9.9649732547720544E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A104">
         <v>2022</v>
       </c>
@@ -56092,7 +56096,7 @@
         <v>1.626220809222113E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A106" t="s">
         <v>262</v>
       </c>
@@ -56187,7 +56191,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A107" t="s">
         <v>277</v>
       </c>
@@ -56282,7 +56286,7 @@
         <v>70446</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A108" t="s">
         <v>278</v>
       </c>
@@ -56377,7 +56381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A109" t="s">
         <v>279</v>
       </c>
@@ -56472,7 +56476,7 @@
         <v>9540</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A110" t="s">
         <v>280</v>
       </c>
@@ -56567,7 +56571,7 @@
         <v>70071</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A111" t="s">
         <v>281</v>
       </c>
@@ -56662,7 +56666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A112" t="s">
         <v>282</v>
       </c>
@@ -56757,7 +56761,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A113" t="s">
         <v>283</v>
       </c>
@@ -56852,7 +56856,7 @@
         <v>5343</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A115" t="s">
         <v>241</v>
       </c>
@@ -56977,7 +56981,7 @@
         <v>0.45311927136599578</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A116" t="s">
         <v>242</v>
       </c>
@@ -57102,7 +57106,7 @@
         <v>3.4366979912394111E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A117" t="s">
         <v>248</v>
       </c>
@@ -57227,12 +57231,12 @@
         <v>0.4874862512783899</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A119" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A121" s="13" t="s">
         <v>262</v>
       </c>
@@ -57327,7 +57331,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A122" t="s">
         <v>284</v>
       </c>
@@ -57422,7 +57426,7 @@
         <v>749913</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A123" t="s">
         <v>285</v>
       </c>
@@ -57517,7 +57521,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A124" t="s">
         <v>286</v>
       </c>
@@ -57612,7 +57616,7 @@
         <v>412581</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A125" t="s">
         <v>287</v>
       </c>
@@ -57707,7 +57711,7 @@
         <v>274524</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A126" t="s">
         <v>288</v>
       </c>
@@ -57802,7 +57806,7 @@
         <v>129612</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A127" t="s">
         <v>289</v>
       </c>
@@ -57897,7 +57901,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A128" t="s">
         <v>290</v>
       </c>
@@ -57992,7 +57996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A130" t="s">
         <v>241</v>
       </c>
@@ -58117,7 +58121,7 @@
         <v>0.47860850451954579</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A131" t="s">
         <v>244</v>
       </c>
@@ -58242,7 +58246,7 @@
         <v>8.2720802930189727E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A132" t="s">
         <v>242</v>
       </c>
@@ -58367,7 +58371,7 @@
         <v>1.3402592827315249E-5</v>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A133" t="s">
         <v>245</v>
       </c>
@@ -58492,12 +58496,12 @@
         <v>0.56134271004256286</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A135" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A137" s="13" t="s">
         <v>262</v>
       </c>
@@ -58592,7 +58596,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A138" t="s">
         <v>291</v>
       </c>
@@ -58687,7 +58691,7 @@
         <v>89520</v>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A139" t="s">
         <v>292</v>
       </c>
@@ -58782,7 +58786,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A140" t="s">
         <v>293</v>
       </c>
@@ -58877,7 +58881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A141" t="s">
         <v>294</v>
       </c>
@@ -58972,7 +58976,7 @@
         <v>206103</v>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A142" t="s">
         <v>295</v>
       </c>
@@ -59067,7 +59071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A143" t="s">
         <v>296</v>
       </c>
@@ -59162,7 +59166,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A144" t="s">
         <v>297</v>
       </c>
@@ -59257,7 +59261,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A146" t="s">
         <v>241</v>
       </c>
@@ -59382,7 +59386,7 @@
         <v>0.29995074535347749</v>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A147" t="s">
         <v>244</v>
       </c>
@@ -59507,7 +59511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A148" t="s">
         <v>242</v>
       </c>
@@ -59632,7 +59636,7 @@
         <v>6.4835197973523119E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A149" t="s">
         <v>245</v>
       </c>
@@ -59770,20 +59774,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.86328125" customWidth="1"/>
+    <col min="3" max="3" width="24.1328125" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
     <col min="6" max="6" width="18" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.1328125" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" customWidth="1"/>
+    <col min="14" max="14" width="11.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>98</v>
       </c>
@@ -59812,7 +59816,7 @@
       </c>
       <c r="X1" s="17"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -59847,7 +59851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -59882,7 +59886,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -59917,12 +59921,12 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="44.25" x14ac:dyDescent="0.75">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -59964,7 +59968,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12" t="s">
@@ -59985,7 +59989,7 @@
         <v>1.8679140068700261E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" ht="88.5" x14ac:dyDescent="0.75">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -59996,7 +60000,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.75">
       <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
@@ -60130,7 +60134,7 @@
       <c r="AK9" s="21"/>
       <c r="AL9" s="21"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -60266,16 +60270,16 @@
         <v>0.99117298738162618</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.75">
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="22">
-        <f>SUM(SUM(INDEX('AEO 39'!$29:$30,0,MATCH($E$9,'AEO 39'!$1:$1,0))),SUM(INDEX('AEO 39'!$51:$52,0,MATCH($E$9,'AEO 39'!$1:$1,0))))/INDEX('AEO 39'!$59:$59,MATCH($E$9,'AEO 39'!$1:$1,0))</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 39'!$29:$30,0,MATCH($E$9,'AEO 2025 Table 39'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 39'!$51:$52,0,MATCH($E$9,'AEO 2025 Table 39'!$1:$1,0))))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH($E$9,'AEO 2025 Table 39'!$1:$1,0))</f>
         <v>5.4649745052120366E-5</v>
       </c>
       <c r="F11" s="22">
-        <f>SUM(SUM(INDEX('AEO 39'!$29:$30,0,MATCH($F$9,'AEO 39'!$1:$1,0))),SUM(INDEX('AEO 39'!$51:$52,0,MATCH($F$9,'AEO 39'!$1:$1,0))))/INDEX('AEO 39'!$59:$59,MATCH($F$9,'AEO 39'!$1:$1,0))*Assumptions!$A$11</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 39'!$29:$30,0,MATCH($F$9,'AEO 2025 Table 39'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 39'!$51:$52,0,MATCH($F$9,'AEO 2025 Table 39'!$1:$1,0))))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH($F$9,'AEO 2025 Table 39'!$1:$1,0))*Assumptions!$A$11</f>
         <v>2.5894039862612868E-5</v>
       </c>
       <c r="G11" s="7" t="str">
@@ -60395,7 +60399,7 @@
         <v>2.6658855168836448E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.75">
       <c r="C12" t="s">
         <v>3</v>
       </c>
@@ -60522,16 +60526,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.75">
       <c r="C13" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="22">
-        <f>SUM(INDEX('AEO 39'!$18:$18,MATCH(E$9,'AEO 39'!$1:$1,0)),INDEX('AEO 39'!$27:$27,MATCH(E$9,'AEO 39'!$1:$1,0)),INDEX('AEO 39'!$40:$40,MATCH(E$9,'AEO 39'!$1:$1,0)),INDEX('AEO 39'!$49:$49,MATCH(E$9,'AEO 39'!$1:$1,0)))/INDEX('AEO 39'!$59:$59,MATCH(E$9,'AEO 39'!$1:$1,0))</f>
+        <f>SUM(INDEX('AEO 2025 Table 39'!$18:$18,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0)),INDEX('AEO 2025 Table 39'!$27:$27,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0)),INDEX('AEO 2025 Table 39'!$40:$40,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0)),INDEX('AEO 2025 Table 39'!$49:$49,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0)))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))</f>
         <v>5.851105507530179E-3</v>
       </c>
       <c r="F13" s="22">
-        <f>SUM(INDEX('AEO 39'!$18:$18,MATCH(F$9,'AEO 39'!$1:$1,0)),INDEX('AEO 39'!$27:$27,MATCH(F$9,'AEO 39'!$1:$1,0)),INDEX('AEO 39'!$40:$40,MATCH(F$9,'AEO 39'!$1:$1,0)),INDEX('AEO 39'!$49:$49,MATCH(F$9,'AEO 39'!$1:$1,0)))/INDEX('AEO 39'!$59:$59,MATCH(F$9,'AEO 39'!$1:$1,0))*Assumptions!A11</f>
+        <f>SUM(INDEX('AEO 2025 Table 39'!$18:$18,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0)),INDEX('AEO 2025 Table 39'!$27:$27,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0)),INDEX('AEO 2025 Table 39'!$40:$40,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0)),INDEX('AEO 2025 Table 39'!$49:$49,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0)))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))*Assumptions!A11</f>
         <v>3.3966473592295425E-2</v>
       </c>
       <c r="G13" s="7" t="str">
@@ -60651,7 +60655,7 @@
         <v>3.3966473592295099E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.75">
       <c r="C14" t="s">
         <v>5</v>
       </c>
@@ -60776,16 +60780,16 @@
         <v>0.24980830595850836</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.75">
       <c r="C15" t="s">
         <v>111</v>
       </c>
       <c r="E15" s="22">
-        <f>SUM(SUM(INDEX('AEO 39'!31:32,0,MATCH(E$9,'AEO 39'!$1:$1,0))),SUM(INDEX('AEO 39'!53:54,0,MATCH(E$9,'AEO 39'!$1:$1,0))))/INDEX('AEO 39'!$59:$59,MATCH(E$9,'AEO 39'!$1:$1,0))</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 39'!31:32,0,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 39'!53:54,0,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))</f>
         <v>5.095393642836949E-5</v>
       </c>
       <c r="F15" s="22">
-        <f>SUM(SUM(INDEX('AEO 39'!31:32,0,MATCH(F$9,'AEO 39'!$1:$1,0))),SUM(INDEX('AEO 39'!53:54,0,MATCH(F$9,'AEO 39'!$1:$1,0))))/INDEX('AEO 39'!$59:$59,MATCH(F$9,'AEO 39'!$1:$1,0))*Assumptions!A11</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 39'!31:32,0,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 39'!53:54,0,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))*Assumptions!A11</f>
         <v>3.6399200194339569E-5</v>
       </c>
       <c r="G15" s="7" t="str">
@@ -60905,7 +60909,7 @@
         <v>3.6399200194339515E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23" t="s">
@@ -60913,11 +60917,11 @@
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="26">
-        <f>SUM(SUM(INDEX('AEO 39'!34:34,0,MATCH(E$9,'AEO 39'!$1:$1,0))),SUM(INDEX('AEO 39'!56:56,0,MATCH(E$9,'AEO 39'!$1:$1,0))))/INDEX('AEO 39'!$59:$59,MATCH(E$9,'AEO 39'!$1:$1,0))</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 39'!34:34,0,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 39'!56:56,0,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH(E$9,'AEO 2025 Table 39'!$1:$1,0))</f>
         <v>6.4399747823034987E-5</v>
       </c>
       <c r="F16" s="26">
-        <f>SUM(SUM(INDEX('AEO 39'!34:34,0,MATCH(F$9,'AEO 39'!$1:$1,0))),SUM(INDEX('AEO 39'!56:56,0,MATCH(F$9,'AEO 39'!$1:$1,0))))/INDEX('AEO 39'!$59:$59,MATCH(F$9,'AEO 39'!$1:$1,0))*Assumptions!A11</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 39'!34:34,0,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 39'!56:56,0,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))))/INDEX('AEO 2025 Table 39'!$59:$59,MATCH(F$9,'AEO 2025 Table 39'!$1:$1,0))*Assumptions!A11</f>
         <v>8.3938001583136517E-5</v>
       </c>
       <c r="G16" s="8" t="str">
@@ -61037,7 +61041,7 @@
         <v>8.341834277337592E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -61171,7 +61175,7 @@
         <v>0.99913450136531945</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C18" t="s">
         <v>2</v>
       </c>
@@ -61299,7 +61303,7 @@
         <v>2.5894039862625617E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C19" t="s">
         <v>3</v>
       </c>
@@ -61426,7 +61430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C20" t="s">
         <v>4</v>
       </c>
@@ -61553,7 +61557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C21" t="s">
         <v>5</v>
       </c>
@@ -61682,7 +61686,7 @@
         <v>0.24335647428993237</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C22" t="s">
         <v>111</v>
       </c>
@@ -61811,7 +61815,7 @@
         <v>3.6399200194339731E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23" t="s">
@@ -61943,7 +61947,7 @@
         <v>8.1705503094174872E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -62079,7 +62083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C25" t="s">
         <v>2</v>
       </c>
@@ -62208,7 +62212,7 @@
         <v>0.44257917668338109</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C26" t="s">
         <v>3</v>
       </c>
@@ -62337,7 +62341,7 @@
         <v>0.3048870377174393</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C27" t="s">
         <v>4</v>
       </c>
@@ -62464,7 +62468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C28" t="s">
         <v>5</v>
       </c>
@@ -62593,7 +62597,7 @@
         <v>5.840418038538805E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C29" t="s">
         <v>111</v>
       </c>
@@ -62722,7 +62726,7 @@
         <v>0.53886894931712348</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23" t="s">
@@ -62853,7 +62857,7 @@
         <v>4.8673044204463882E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -62986,16 +62990,16 @@
         <v>0.99654038294148828</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C32" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="22">
-        <f>SUM(INDEX('AEO 49'!$256:$256,MATCH(E$9,'AEO 49'!$1:$1,0)),INDEX('AEO 49'!$270:$270,MATCH(E$9,'AEO 49'!$1:$1,0)),INDEX('AEO 49'!$284:$284,MATCH(E$9,'AEO 49'!$1:$1,0)))/INDEX('AEO 49'!$294:$294,MATCH(E$9,'AEO 49'!$1:$1,0))</f>
+        <f>SUM(INDEX('AEO 2025 Table 49'!$256:$256,MATCH(E$9,'AEO 2025 Table 49'!$1:$1,0)),INDEX('AEO 2025 Table 49'!$270:$270,MATCH(E$9,'AEO 2025 Table 49'!$1:$1,0)),INDEX('AEO 2025 Table 49'!$284:$284,MATCH(E$9,'AEO 2025 Table 49'!$1:$1,0)))/INDEX('AEO 2025 Table 49'!$294:$294,MATCH(E$9,'AEO 2025 Table 49'!$1:$1,0))</f>
         <v>1.3439511121112888E-2</v>
       </c>
       <c r="F32" s="22">
-        <f>SUM(INDEX('AEO 49'!$256:$256,MATCH(F$9,'AEO 49'!$1:$1,0)),INDEX('AEO 49'!$270:$270,MATCH(F$9,'AEO 49'!$1:$1,0)),INDEX('AEO 49'!$284:$284,MATCH(F$9,'AEO 49'!$1:$1,0)))*Assumptions!A2/INDEX('AEO 49'!$294:$294,MATCH(F$9,'AEO 49'!$1:$1,0))</f>
+        <f>SUM(INDEX('AEO 2025 Table 49'!$256:$256,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0)),INDEX('AEO 2025 Table 49'!$270:$270,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0)),INDEX('AEO 2025 Table 49'!$284:$284,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0)))*Assumptions!A2/INDEX('AEO 2025 Table 49'!$294:$294,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0))</f>
         <v>0.14878047949055351</v>
       </c>
       <c r="G32" s="7" t="str">
@@ -63115,7 +63119,7 @@
         <v>0.14518081662414467</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C33" t="s">
         <v>3</v>
       </c>
@@ -63242,7 +63246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C34" t="s">
         <v>4</v>
       </c>
@@ -63369,7 +63373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C35" t="s">
         <v>5</v>
       </c>
@@ -63496,7 +63500,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C36" t="s">
         <v>111</v>
       </c>
@@ -63505,7 +63509,7 @@
         <v>5.8198516364943692E-4</v>
       </c>
       <c r="F36" s="22">
-        <f>SUM(SUM(INDEX('AEO 49'!166:166,0,MATCH(F$9,'AEO 49'!$1:$1,0))),SUM(INDEX('AEO 49'!180:180,0,MATCH(F$9,'AEO 49'!$1:$1,0))),SUM(INDEX('AEO 49'!194:194,0,MATCH(F$9,'AEO 49'!$1:$1,0))))/INDEX('AEO 49'!$205:$205,MATCH(F$9,'AEO 49'!$1:$1,0))*Assumptions!A11</f>
+        <f>SUM(SUM(INDEX('AEO 2025 Table 49'!166:166,0,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 49'!180:180,0,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0))),SUM(INDEX('AEO 2025 Table 49'!194:194,0,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0))))/INDEX('AEO 2025 Table 49'!$205:$205,MATCH(F$9,'AEO 2025 Table 49'!$1:$1,0))*Assumptions!A11</f>
         <v>8.0617935827825794E-4</v>
       </c>
       <c r="G36" s="7" t="str">
@@ -63625,7 +63629,7 @@
         <v>8.0617935827825837E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23" t="s">
@@ -63755,7 +63759,7 @@
         <v>3.9069105224809692E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -63888,7 +63892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C39" t="s">
         <v>2</v>
       </c>
@@ -64015,7 +64019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C40" t="s">
         <v>3</v>
       </c>
@@ -64142,7 +64146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C41" t="s">
         <v>4</v>
       </c>
@@ -64269,7 +64273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C42" t="s">
         <v>5</v>
       </c>
@@ -64396,7 +64400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C43" t="s">
         <v>111</v>
       </c>
@@ -64523,7 +64527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A44" s="23"/>
       <c r="B44" s="23"/>
       <c r="C44" s="23" t="s">
@@ -64653,7 +64657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -64786,7 +64790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C46" t="s">
         <v>2</v>
       </c>
@@ -64913,7 +64917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C47" t="s">
         <v>3</v>
       </c>
@@ -65040,7 +65044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C48" t="s">
         <v>4</v>
       </c>
@@ -65167,7 +65171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C49" t="s">
         <v>5</v>
       </c>
@@ -65294,7 +65298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C50" t="s">
         <v>111</v>
       </c>
@@ -65421,7 +65425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A51" s="23"/>
       <c r="B51" s="23"/>
       <c r="C51" s="23" t="s">
@@ -65551,7 +65555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -65685,7 +65689,7 @@
         <v>0.99831503173391156</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C53" t="s">
         <v>2</v>
       </c>
@@ -65812,7 +65816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C54" t="s">
         <v>3</v>
       </c>
@@ -65939,7 +65943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C55" t="s">
         <v>4</v>
       </c>
@@ -66067,7 +66071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C56" t="s">
         <v>5</v>
       </c>
@@ -66194,7 +66198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C57" t="s">
         <v>111</v>
       </c>
@@ -66321,7 +66325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A58" s="23"/>
       <c r="B58" s="23"/>
       <c r="C58" s="23" t="s">
@@ -66451,7 +66455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -66584,7 +66588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C60" t="s">
         <v>2</v>
       </c>
@@ -66711,7 +66715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C61" t="s">
         <v>3</v>
       </c>
@@ -66838,7 +66842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C62" t="s">
         <v>4</v>
       </c>
@@ -66965,7 +66969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C63" t="s">
         <v>5</v>
       </c>
@@ -67092,7 +67096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C64" t="s">
         <v>111</v>
       </c>
@@ -67219,7 +67223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A65" s="23"/>
       <c r="B65" s="23"/>
       <c r="C65" s="23" t="s">
@@ -67349,7 +67353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -67482,7 +67486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C67" t="s">
         <v>2</v>
       </c>
@@ -67609,7 +67613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C68" t="s">
         <v>3</v>
       </c>
@@ -67736,7 +67740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C69" t="s">
         <v>4</v>
       </c>
@@ -67863,7 +67867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C70" t="s">
         <v>5</v>
       </c>
@@ -67990,7 +67994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C71" t="s">
         <v>111</v>
       </c>
@@ -68117,7 +68121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A72" s="23"/>
       <c r="B72" s="23"/>
       <c r="C72" s="23" t="s">
@@ -68247,7 +68251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -68380,7 +68384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C74" t="s">
         <v>2</v>
       </c>
@@ -68507,7 +68511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C75" t="s">
         <v>3</v>
       </c>
@@ -68634,7 +68638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C76" t="s">
         <v>4</v>
       </c>
@@ -68761,7 +68765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C77" t="s">
         <v>5</v>
       </c>
@@ -68888,7 +68892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C78" t="s">
         <v>111</v>
       </c>
@@ -69015,7 +69019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A79" s="23"/>
       <c r="B79" s="23"/>
       <c r="C79" s="23" t="s">
@@ -69145,7 +69149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -69279,7 +69283,7 @@
         <v>0.99477987430644166</v>
       </c>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C81" t="s">
         <v>2</v>
       </c>
@@ -69407,7 +69411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C82" t="s">
         <v>3</v>
       </c>
@@ -69534,7 +69538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C83" t="s">
         <v>4</v>
       </c>
@@ -69662,7 +69666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C84" t="s">
         <v>5</v>
       </c>
@@ -69790,7 +69794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C85" t="s">
         <v>111</v>
       </c>
@@ -69918,7 +69922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A86" s="23"/>
       <c r="B86" s="23"/>
       <c r="C86" s="23" t="s">
@@ -70049,7 +70053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -70182,7 +70186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C88" t="s">
         <v>2</v>
       </c>
@@ -70309,7 +70313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C89" t="s">
         <v>3</v>
       </c>
@@ -70436,7 +70440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C90" t="s">
         <v>4</v>
       </c>
@@ -70563,7 +70567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C91" t="s">
         <v>5</v>
       </c>
@@ -70690,7 +70694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.75">
       <c r="C92" t="s">
         <v>111</v>
       </c>
@@ -70817,7 +70821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:36" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A93" s="23"/>
       <c r="B93" s="23"/>
       <c r="C93" s="23" t="s">
@@ -70960,13 +70964,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AC8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -71083,7 +71087,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -71200,7 +71204,7 @@
         <v>0.99117298738162618</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -71317,7 +71321,7 @@
         <v>2.6658855168836448E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -71434,7 +71438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -71551,7 +71555,7 @@
         <v>3.3966473592295099E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -71668,7 +71672,7 @@
         <v>0.24980830595850836</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -71785,7 +71789,7 @@
         <v>3.6399200194339515E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -71913,12 +71917,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="25" t="s">
         <v>114</v>
       </c>
@@ -72043,7 +72047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -72168,7 +72172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -72293,7 +72297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -72418,7 +72422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -72543,7 +72547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -72668,7 +72672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -72793,7 +72797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>112</v>
       </c>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE48FF3-7A01-4D30-8721-C3F5129681FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8605749-F06C-474B-994A-A4F1B91CEA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="243">
   <si>
     <t>Source:</t>
   </si>
@@ -115,145 +115,7 @@
     <t>- -</t>
   </si>
   <si>
-    <t>The technology that is the reference type for a given vehicle type is</t>
-  </si>
-  <si>
-    <t>allowed a 100% share in all years.  (This is "gasoline vehicle" for LDVs</t>
-  </si>
-  <si>
-    <t>and motorbikes, "diesel vehicle" for HDVs.)</t>
-  </si>
-  <si>
-    <t>All nonroad modes have a 100% share of the "nonroad vehicle"</t>
-  </si>
-  <si>
-    <t>technology type and a 0% share of the other technology types.</t>
-  </si>
-  <si>
-    <t>Technology allocation is only used for on-road vehicles in the EPS.</t>
-  </si>
-  <si>
-    <t>On-road modes all have a 0% share of the "nonroad vehicle"</t>
-  </si>
-  <si>
-    <t>technology type.</t>
-  </si>
-  <si>
     <t>Here are the assumptions we use for the U.S.:</t>
-  </si>
-  <si>
-    <t>EIA</t>
-  </si>
-  <si>
-    <t>between the current sales share and the potential 2050 sales share.</t>
-  </si>
-  <si>
-    <t>last year values (on the "Data" tab).</t>
-  </si>
-  <si>
-    <t>First and Last Simulated Year Values</t>
-  </si>
-  <si>
-    <t>See SYVbT variable.</t>
-  </si>
-  <si>
-    <t>Last Simulated Year Values Only</t>
-  </si>
-  <si>
-    <t>For passenger motorbikes, we assume there will be no diesel</t>
-  </si>
-  <si>
-    <t>vehicle, natural gas vehicle, or plug-in hybrid vehicle technologies.</t>
-  </si>
-  <si>
-    <t>In 2014 in China, 9.3 million electric motorcycles and scooters</t>
-  </si>
-  <si>
-    <t>were sold, roughly 20 times the total number of motorcycles</t>
-  </si>
-  <si>
-    <t>and scooters sold in the U.S. in that year.  Therefore, it seems</t>
-  </si>
-  <si>
-    <t>possible that electric motorbikes could account for as much</t>
-  </si>
-  <si>
-    <t>as 100% of U.S. motorbike sales in 205.</t>
-  </si>
-  <si>
-    <t>Clean Rider</t>
-  </si>
-  <si>
-    <t>The electric scooter market</t>
-  </si>
-  <si>
-    <t>http://cleanrider.com/electric-scooter-market/</t>
-  </si>
-  <si>
-    <t>RevZilla Motorsports</t>
-  </si>
-  <si>
-    <t>How Many Motorcycles wer Sold in the U.S. Last Year?</t>
-  </si>
-  <si>
-    <t>https://www.revzilla.com/common-tread/us-motorcycle-sales</t>
-  </si>
-  <si>
-    <t>For freight HDVs, we use estimated sales shares by technology in 2050</t>
-  </si>
-  <si>
-    <t>from AEO 50.  This is a reference case, not a maximum, so we multiply</t>
-  </si>
-  <si>
-    <t>the shares of the three newer technologies (battery electric vehicle,</t>
-  </si>
-  <si>
-    <t>natural gas vehicle, plug-in hybrid vehicle) by a multiplier</t>
-  </si>
-  <si>
-    <t>(see "Assumptions" tab) to represent the potential for sales to</t>
-  </si>
-  <si>
-    <t>greatly exceed the reference case values.</t>
-  </si>
-  <si>
-    <t>For passenger LDVs, predictions of battery electric penetration vary.</t>
-  </si>
-  <si>
-    <t>natural gas vehicle, and plug-in hybrid vehicle), we use the</t>
-  </si>
-  <si>
-    <t>the case when estimating the first year, this is using a share of</t>
-  </si>
-  <si>
-    <t>LDVs (except battery electric vehicles in the Last Year)</t>
-  </si>
-  <si>
-    <t>freight HDVs, Last Year passenger HDVs</t>
-  </si>
-  <si>
-    <t>First Year passenger HDVs, First Year passenger motorbikes</t>
-  </si>
-  <si>
-    <t>Last Year passenger motorbikes</t>
-  </si>
-  <si>
-    <t>For other unusual technologies (diesel vehicle,</t>
-  </si>
-  <si>
-    <t>entire projected stock in 2050 could be built in a single year,</t>
-  </si>
-  <si>
-    <t>which is generous, and thus may compensate for the fact that</t>
-  </si>
-  <si>
-    <t>our AEO source is a reference case, not a maximum.</t>
-  </si>
-  <si>
-    <t>double the percentage of stock estimated by EIA for 2050 (AEO 40).  As was</t>
-  </si>
-  <si>
-    <t>stock to represent a share of sales.  This effectively assumes that twice the</t>
   </si>
   <si>
     <t>L</t>
@@ -283,28 +145,7 @@
     <t>specified 2050 max sales share with a flattening curve.  (Of course, linear interpolation is similarly an assumption.)</t>
   </si>
   <si>
-    <t>To make it easier to set the values for this variable, it is set up to interpolate</t>
-  </si>
-  <si>
-    <t>For freight LDVs, we use the same percentages as passenger LDVs,</t>
-  </si>
-  <si>
-    <t>necessary to avoid a situation where the retirement rate of the</t>
-  </si>
-  <si>
-    <t>start year diesel engine freight LDVs is far in excess of how quickly</t>
-  </si>
-  <si>
-    <t>they can be replaced.</t>
-  </si>
-  <si>
-    <t>except we allow up to 100% diesel engine market share, which is</t>
-  </si>
-  <si>
     <t>linear</t>
-  </si>
-  <si>
-    <t>For passenger HDVs, we use the same percentages as passenger LDVs.</t>
   </si>
   <si>
     <t>LPG vehicle</t>
@@ -319,18 +160,6 @@
     <t>Number of Vehicles</t>
   </si>
   <si>
-    <t>Table 39</t>
-  </si>
-  <si>
-    <t>Table 49</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/supplement/excel/suptab_39.xlsx</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/supplement/excel/suptab_49.xlsx</t>
-  </si>
-  <si>
     <t>*for passenger LDVs only, see Assumptions page</t>
   </si>
   <si>
@@ -338,15 +167,6 @@
   </si>
   <si>
     <t>Sigmoidal Curve Values for Vehicle Technologies (all except battery electric passenger LDVs)</t>
-  </si>
-  <si>
-    <t>Many organizations have released projections.</t>
-  </si>
-  <si>
-    <t>See an explanation on the Assumptions page for how the passenger LDV</t>
-  </si>
-  <si>
-    <t>values were calibrated against one such source.</t>
   </si>
   <si>
     <t>Source: U.S. Energy Information Administration</t>
@@ -454,16 +274,10 @@
     <t>TTS Transportation Technology Shareweights</t>
   </si>
   <si>
-    <t>The easiest way to calibrate this variable is to simply adjust these first and</t>
-  </si>
-  <si>
     <t>This variable provides the shareweights used in the modified logit equation for vehicle</t>
   </si>
   <si>
     <t>technology selection.  We base them on estimated potential maximum sales shares in each year.</t>
-  </si>
-  <si>
-    <t>For more on this, see the "Modified Logit" equation description at:</t>
   </si>
   <si>
     <t>https://jgcri.github.io/gcam-doc/choice.html</t>
@@ -472,61 +286,10 @@
     <t>Psgr LDVs only</t>
   </si>
   <si>
-    <t>LDVs (battery electric vehicles)</t>
-  </si>
-  <si>
-    <t>Argonne National Laboratory</t>
-  </si>
-  <si>
-    <t>Light Duty Electric Drive Vehicles Monthly Sales Updates</t>
-  </si>
-  <si>
-    <t>https://www.anl.gov/es/light-duty-electric-drive-vehicles-monthly-sales-updates</t>
-  </si>
-  <si>
-    <t>Department of Energy</t>
-  </si>
-  <si>
-    <t>New Plug-in Electric Vehicle Sales in the United States Nearly Doubled from 2020 to 2021</t>
-  </si>
-  <si>
-    <t>https://www.energy.gov/energysaver/articles/new-plug-electric-vehicle-sales-united-states-nearly-doubled-2020-2021</t>
-  </si>
-  <si>
-    <t>Deloitte</t>
-  </si>
-  <si>
-    <t>Electric vehicles: Setting a course for 2030</t>
-  </si>
-  <si>
-    <t>https://www2.deloitte.com/us/en/insights/focus/future-of-mobility/electric-vehicle-trends-2030.html</t>
-  </si>
-  <si>
     <t>Sigmoidal Curve Values for battery electric passenger HDV Technologies</t>
   </si>
   <si>
     <t>Sigmoidal Curve Values for PHEV passenger LDV Technologies</t>
-  </si>
-  <si>
-    <t>Historical Year Values</t>
-  </si>
-  <si>
-    <t>For certain onroad technologies, we calibrate historical year values</t>
-  </si>
-  <si>
-    <t>to match with real-world sales.</t>
-  </si>
-  <si>
-    <t>PHEV Values, passengre LDVs</t>
-  </si>
-  <si>
-    <t>We also use calibration for PHEV values between 2027-2032,</t>
-  </si>
-  <si>
-    <t>in order to align with EPA's projected split between BEVs and PHEVs</t>
-  </si>
-  <si>
-    <t>in their tailpipe rules analysis.</t>
   </si>
   <si>
     <t>Plug-in 50 Gasoline Hybrid</t>
@@ -545,12 +308,6 @@
   </si>
   <si>
     <t>Growth (2024-2050)</t>
-  </si>
-  <si>
-    <t>Annual Energy Outlook 2025</t>
-  </si>
-  <si>
-    <t>Alternative Transportation</t>
   </si>
   <si>
     <t>Table 38.  Light-Duty Vehicle Sales by Technology Type</t>
@@ -939,6 +696,87 @@
   <si>
     <t>share of domestic demand</t>
   </si>
+  <si>
+    <t>Onroad modes</t>
+  </si>
+  <si>
+    <t>See supporting Python calibration file and excel/csv files in this folder.</t>
+  </si>
+  <si>
+    <t>Given logit exponents from the GCAM model, we use a solver to solve</t>
+  </si>
+  <si>
+    <t>for historical shareweights given recent sales data. We then allow the</t>
+  </si>
+  <si>
+    <t>shareweights for BEV and PHEV technologies to grow, as explained below.</t>
+  </si>
+  <si>
+    <t>For more on this, see the "Unmodified Logit" equation description at:</t>
+  </si>
+  <si>
+    <t>passenger LDVs</t>
+  </si>
+  <si>
+    <t>The historical data we use for calibration is for states that do not have</t>
+  </si>
+  <si>
+    <t>their own vehicle standards (ACCI) that put an additional constraint on sales</t>
+  </si>
+  <si>
+    <t>that is not purely cost-based. This gives us our 2024 and 2025 shareweights.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 2024/2025 shareweights are slightly less than 10%, which we can roughly </t>
+  </si>
+  <si>
+    <t>correlate to current domestic EV manufacturing capacity (about 1.5 million</t>
+  </si>
+  <si>
+    <t>vehicles per year, compared to domestic demand of about 15 million vehicles).</t>
+  </si>
+  <si>
+    <t>Based on a literature survey on expected growth in manufacturing capacity,</t>
+  </si>
+  <si>
+    <t>or about 30% of demand. We find that setting the growth in the shareweights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of about 0.4 in 2035, aligning with the growth in manufacturing capacity. </t>
+  </si>
+  <si>
+    <t>a mid-range estimate of capacity by 2035 could be roughly 6 million vehicles,</t>
+  </si>
+  <si>
+    <t>for passenger LDV BEVs to a s-curve that reaches 0.7 by 2050 results in a shareweight</t>
+  </si>
+  <si>
+    <t>We set the growth in PHEV shareweights to the same annual increases as</t>
+  </si>
+  <si>
+    <t>BEVs. ICE vehicles use constant shareweights.</t>
+  </si>
+  <si>
+    <t>The solver we used is saved as transport_calibration.py in the TTS folder. It is set up</t>
+  </si>
+  <si>
+    <t>to take in data on the cost per thing*mile for each vehicle type (taken from Vensim),</t>
+  </si>
+  <si>
+    <t>the observed sales share (from historical data sets), the exponent (trans/TTLE), and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the number of vehicles of that type demanded each year (taken from Vensim). </t>
+  </si>
+  <si>
+    <t>The file calibration_parameters specifies all those pieces of input data. Sources for the</t>
+  </si>
+  <si>
+    <t>historical sales shares are noted in that file.</t>
+  </si>
+  <si>
+    <t>2024 and 2025 shareweights for onroad vehicle types copied/pasted from the Python solver outputs, explained on the About page</t>
+  </si>
 </sst>
 </file>
 
@@ -1200,7 +1038,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1390,6 +1228,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1716,14 +1560,11 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1742,7 +1583,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1760,7 +1600,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
@@ -1768,6 +1607,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="88">
@@ -1951,79 +1793,79 @@
                   <c:v>6.6873740826300002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
-                  <c:v>7.8393597159514841E-2</c:v>
+                  <c:v>7.826128265631177E-2</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="General">
-                  <c:v>8.383744382909665E-2</c:v>
+                  <c:v>8.3712995874888008E-2</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>9.1702346693592188E-2</c:v>
+                  <c:v>9.167058838844952E-2</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>0.1028980197241021</c:v>
+                  <c:v>0.10316718187336593</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
-                  <c:v>0.11850365652431405</c:v>
+                  <c:v>0.11953255902288656</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="General">
-                  <c:v>0.1396309892832005</c:v>
+                  <c:v>0.14234424092873754</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="General">
-                  <c:v>0.16713173544079279</c:v>
+                  <c:v>0.17322731225641558</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="General">
-                  <c:v>0.20115393406388254</c:v>
+                  <c:v>0.21342677874098925</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="General">
-                  <c:v>0.2406926533620381</c:v>
+                  <c:v>0.26315903783836003</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="General">
-                  <c:v>0.28343687041315002</c:v>
+                  <c:v>0.32095512133954762</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="General">
-                  <c:v>0.32618108746426189</c:v>
+                  <c:v>0.38343687041314994</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="General">
-                  <c:v>0.36571980676241744</c:v>
+                  <c:v>0.44591861948675221</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="General">
-                  <c:v>0.39974200538550725</c:v>
+                  <c:v>0.50371470298793986</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>0.42724275154309949</c:v>
+                  <c:v>0.55344696208531075</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>0.44837008430198594</c:v>
+                  <c:v>0.59364642856988437</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>0.46397572110219792</c:v>
+                  <c:v>0.62452949989756235</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>0.47517139413270781</c:v>
+                  <c:v>0.64734118180341338</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>0.48303629699720335</c:v>
+                  <c:v>0.66370655895293407</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>0.4884801436667851</c:v>
+                  <c:v>0.67520315243785045</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>0.4922097001624065</c:v>
+                  <c:v>0.68316074495141188</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>0.49474685632562987</c:v>
+                  <c:v>0.68861245816998817</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>0.49646457609119271</c:v>
+                  <c:v>0.69232116932877497</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>0.49762373988097219</c:v>
+                  <c:v>0.69483206186056068</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>0.49840425895445883</c:v>
+                  <c:v>0.69652648010108209</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>0.49892904198182053</c:v>
+                  <c:v>0.69766741097457163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2283,79 +2125,79 @@
                   <c:v>6.6873740826300002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
-                  <c:v>7.8393597159514841E-2</c:v>
+                  <c:v>7.826128265631177E-2</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="General">
-                  <c:v>8.383744382909665E-2</c:v>
+                  <c:v>8.3712995874888008E-2</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>9.1702346693592188E-2</c:v>
+                  <c:v>9.167058838844952E-2</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>0.1028980197241021</c:v>
+                  <c:v>0.10316718187336593</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
-                  <c:v>0.11850365652431405</c:v>
+                  <c:v>0.11953255902288656</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="General">
-                  <c:v>0.1396309892832005</c:v>
+                  <c:v>0.14234424092873754</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="General">
-                  <c:v>0.16713173544079279</c:v>
+                  <c:v>0.17322731225641558</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="General">
-                  <c:v>0.20115393406388254</c:v>
+                  <c:v>0.21342677874098925</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="General">
-                  <c:v>0.2406926533620381</c:v>
+                  <c:v>0.26315903783836003</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="General">
-                  <c:v>0.28343687041315002</c:v>
+                  <c:v>0.32095512133954762</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="General">
-                  <c:v>0.32618108746426189</c:v>
+                  <c:v>0.38343687041314994</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="General">
-                  <c:v>0.36571980676241744</c:v>
+                  <c:v>0.44591861948675221</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="General">
-                  <c:v>0.39974200538550725</c:v>
+                  <c:v>0.50371470298793986</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>0.42724275154309949</c:v>
+                  <c:v>0.55344696208531075</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>0.44837008430198594</c:v>
+                  <c:v>0.59364642856988437</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>0.46397572110219792</c:v>
+                  <c:v>0.62452949989756235</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>0.47517139413270781</c:v>
+                  <c:v>0.64734118180341338</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>0.48303629699720335</c:v>
+                  <c:v>0.66370655895293407</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>0.4884801436667851</c:v>
+                  <c:v>0.67520315243785045</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>0.4922097001624065</c:v>
+                  <c:v>0.68316074495141188</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>0.49474685632562987</c:v>
+                  <c:v>0.68861245816998817</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>0.49646457609119271</c:v>
+                  <c:v>0.69232116932877497</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>0.49762373988097219</c:v>
+                  <c:v>0.69483206186056068</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>0.49840425895445883</c:v>
+                  <c:v>0.69652648010108209</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>0.49892904198182053</c:v>
+                  <c:v>0.69766741097457163</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4578,15 +4420,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>92075</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>39687</xdr:rowOff>
+      <xdr:colOff>454025</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>55562</xdr:rowOff>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4937,523 +4779,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B126"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="56.26953125" customWidth="1"/>
+    <col min="2" max="2" width="63.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>59</v>
+      <c r="B3" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="3">
-        <v>2025</v>
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>90</v>
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B11" s="10" t="s">
-        <v>141</v>
+      <c r="A11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>142</v>
+      <c r="A12" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
-        <v>2021</v>
+      <c r="A13" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>143</v>
-      </c>
+      <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B15" s="25" t="s">
-        <v>144</v>
+      <c r="A15" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>145</v>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
-        <v>2022</v>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>236</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>146</v>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="27" t="s">
-        <v>147</v>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>238</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="27"/>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>239</v>
+      </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>148</v>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>240</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
-        <v>2020</v>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>241</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>149</v>
-      </c>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="10"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="27" t="s">
-        <v>150</v>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B27" s="10" t="s">
-        <v>60</v>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>223</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>31</v>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>224</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B29" s="3">
-        <v>2025</v>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>166</v>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>226</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>93</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>91</v>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="10" t="s">
-        <v>61</v>
+      <c r="B35" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B36" s="11" t="s">
-        <v>35</v>
+      <c r="B36" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B38" s="10" t="s">
-        <v>62</v>
+      <c r="B38" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>44</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B40" s="3">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B44" t="s">
-        <v>47</v>
+      <c r="B40" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B45" s="3">
-        <v>2015</v>
-      </c>
+      <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B46" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B63" s="12"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B65" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B67" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B68" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B71" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B75" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B76" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B78" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B80" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B81" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B83" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B85" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B86" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B87" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B89" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B91" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B92" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B93" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B94" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B96" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B97" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B98" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B99" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B100" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B101" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B102" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B103" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B105" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B106" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B107" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B108" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B109" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B111" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B112" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B113" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B114" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B115" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B116" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B118" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B120" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B121" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B122" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B123" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B124" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B125" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B126" t="s">
-        <v>43</v>
-      </c>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A53" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A13" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -5465,15 +4986,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -5583,20 +5104,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5708,20 +5217,8 @@
         <f>Data!AI38</f>
         <v>0</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ38</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK38</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5833,20 +5330,8 @@
         <f>Data!AI39</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ39</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK39</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5958,20 +5443,8 @@
         <f>Data!AI40</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ40</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK40</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6083,20 +5556,8 @@
         <f>Data!AI41</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ41</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK41</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6208,22 +5669,10 @@
         <f>Data!AI42</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ42</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK42</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I43</f>
@@ -6333,22 +5782,10 @@
         <f>Data!AI43</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ43</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK43</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I44</f>
@@ -6456,18 +5893,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI44</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ44</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK44</f>
         <v>0</v>
       </c>
     </row>
@@ -6481,15 +5906,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -6599,20 +6024,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6724,20 +6137,8 @@
         <f>Data!AI45</f>
         <v>0</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ45</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK45</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6849,20 +6250,8 @@
         <f>Data!AI46</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ46</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK46</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6974,20 +6363,8 @@
         <f>Data!AI47</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ47</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK47</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7099,20 +6476,8 @@
         <f>Data!AI48</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ48</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK48</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7224,22 +6589,10 @@
         <f>Data!AI49</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ49</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK49</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I50</f>
@@ -7349,22 +6702,10 @@
         <f>Data!AI50</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ50</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK50</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I51</f>
@@ -7472,18 +6813,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI51</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ51</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK51</f>
         <v>0</v>
       </c>
     </row>
@@ -7497,15 +6826,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -7615,20 +6944,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7740,20 +7057,8 @@
         <f>Data!AI52</f>
         <v>0.99774649999676845</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ52</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK52</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7865,20 +7170,8 @@
         <f>Data!AI53</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ53</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK53</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7990,20 +7283,8 @@
         <f>Data!AI54</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ54</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK54</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8115,20 +7396,8 @@
         <f>Data!AI55</f>
         <v>1.0000000000000142</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ55</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK55</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8240,22 +7509,10 @@
         <f>Data!AI56</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ56</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK56</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I57</f>
@@ -8365,22 +7622,10 @@
         <f>Data!AI57</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ57</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK57</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I58</f>
@@ -8488,18 +7733,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI58</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ58</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK58</f>
         <v>0</v>
       </c>
     </row>
@@ -8513,15 +7746,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -8631,20 +7864,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8756,20 +7977,8 @@
         <f>Data!AI59</f>
         <v>0</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ59</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK59</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8881,20 +8090,8 @@
         <f>Data!AI60</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ60</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK60</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -9006,20 +8203,8 @@
         <f>Data!AI61</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ61</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK61</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9131,20 +8316,8 @@
         <f>Data!AI62</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ62</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK62</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -9256,22 +8429,10 @@
         <f>Data!AI63</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ63</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK63</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I64</f>
@@ -9381,22 +8542,10 @@
         <f>Data!AI64</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ64</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK64</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I65</f>
@@ -9504,18 +8653,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI65</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ65</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK65</f>
         <v>0</v>
       </c>
     </row>
@@ -9529,15 +8666,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -9647,20 +8784,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -9772,20 +8897,8 @@
         <f>Data!AI66</f>
         <v>0</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ66</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK66</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -9897,20 +9010,8 @@
         <f>Data!AI67</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ67</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK67</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10022,20 +9123,8 @@
         <f>Data!AI68</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ68</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK68</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10147,20 +9236,8 @@
         <f>Data!AI69</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ69</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK69</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10272,22 +9349,10 @@
         <f>Data!AI70</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ70</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK70</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I71</f>
@@ -10397,22 +9462,10 @@
         <f>Data!AI71</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ71</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK71</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I72</f>
@@ -10520,18 +9573,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI72</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ72</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK72</f>
         <v>0</v>
       </c>
     </row>
@@ -10545,15 +9586,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -10663,20 +9704,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10788,20 +9817,8 @@
         <f>Data!AI73</f>
         <v>0</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ73</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK73</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10913,20 +9930,8 @@
         <f>Data!AI74</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ74</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK74</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11038,20 +10043,8 @@
         <f>Data!AI75</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ75</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK75</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11163,20 +10156,8 @@
         <f>Data!AI76</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ76</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK76</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11288,22 +10269,10 @@
         <f>Data!AI77</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ77</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK77</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I78</f>
@@ -11413,22 +10382,10 @@
         <f>Data!AI78</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ78</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK78</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I79</f>
@@ -11536,18 +10493,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI79</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ79</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK79</f>
         <v>0</v>
       </c>
     </row>
@@ -11561,15 +10506,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -11679,20 +10624,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11702,122 +10635,110 @@
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>8.383744382909665E-2</v>
+        <v>8.3712995874888008E-2</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>9.1702346693592188E-2</v>
+        <v>9.167058838844952E-2</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>0.1028980197241021</v>
+        <v>0.10316718187336593</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.11850365652431405</v>
+        <v>0.11953255902288656</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.1396309892832005</v>
+        <v>0.14234424092873754</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.16713173544079279</v>
+        <v>0.17322731225641558</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.20115393406388254</v>
+        <v>0.21342677874098925</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.2406926533620381</v>
+        <v>0.26315903783836003</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.28343687041315002</v>
+        <v>0.32095512133954762</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.32618108746426189</v>
+        <v>0.38343687041314994</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.36571980676241744</v>
+        <v>0.44591861948675221</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.39974200538550725</v>
+        <v>0.50371470298793986</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.42724275154309949</v>
+        <v>0.55344696208531075</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.44837008430198594</v>
+        <v>0.59364642856988437</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.46397572110219792</v>
+        <v>0.62452949989756235</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.47517139413270781</v>
+        <v>0.64734118180341338</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.48303629699720335</v>
+        <v>0.66370655895293407</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.4884801436667851</v>
+        <v>0.67520315243785045</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.4922097001624065</v>
+        <v>0.68316074495141188</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.49474685632562987</v>
+        <v>0.68861245816998817</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.49646457609119271</v>
+        <v>0.69232116932877497</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.49762373988097219</v>
+        <v>0.69483206186056068</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.49840425895445883</v>
+        <v>0.69652648010108209</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.49892904198182053</v>
+        <v>0.69766741097457163</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.49928152969343076</v>
+        <v>0.69843451735049356</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.49951813142989132</v>
-      </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ80</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK80</f>
-        <v>0</v>
+        <v>0.69894976947739584</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11929,20 +10850,8 @@
         <f>Data!AI81</f>
         <v>9.1114481822700006E-5</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ81</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK81</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12054,20 +10963,8 @@
         <f>Data!AI82</f>
         <v>1</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ82</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK82</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12179,20 +11076,8 @@
         <f>Data!AI83</f>
         <v>6.08023121013E-2</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ83</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK83</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12202,124 +11087,112 @@
       </c>
       <c r="C6">
         <f>Data!J84</f>
-        <v>1.8928786332945334E-2</v>
+        <v>1.7172417827862912E-2</v>
       </c>
       <c r="D6">
         <f>Data!K84</f>
-        <v>2.0117011297610617E-2</v>
+        <v>1.7758353292402298E-2</v>
       </c>
       <c r="E6">
         <f>Data!L84</f>
-        <v>2.1701699592911895E-2</v>
+        <v>1.853979207720265E-2</v>
       </c>
       <c r="F6">
         <f>Data!M84</f>
-        <v>2.3806473886134459E-2</v>
+        <v>1.9577694780751151E-2</v>
       </c>
       <c r="G6">
         <f>Data!N84</f>
-        <v>2.6586827110338961E-2</v>
+        <v>2.0948737812545012E-2</v>
       </c>
       <c r="H6">
         <f>Data!O84</f>
-        <v>3.0233275594225367E-2</v>
+        <v>2.2746868259102986E-2</v>
       </c>
       <c r="I6">
         <f>Data!P84</f>
-        <v>3.4970753350781376E-2</v>
+        <v>2.5083005196618512E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q84</f>
-        <v>4.105090059697207E-2</v>
+        <v>2.8081237018963839E-2</v>
       </c>
       <c r="K6">
         <f>Data!R84</f>
-        <v>4.8732958408176291E-2</v>
+        <v>3.1869400242326443E-2</v>
       </c>
       <c r="L6">
         <f>Data!S84</f>
-        <v>5.8249140243472983E-2</v>
+        <v>3.6562003570919627E-2</v>
       </c>
       <c r="M6">
         <f>Data!T84</f>
-        <v>6.9753071712537487E-2</v>
+        <v>4.2234802602923081E-2</v>
       </c>
       <c r="N6">
         <f>Data!U84</f>
-        <v>8.3256562745812834E-2</v>
+        <v>4.8893621031060069E-2</v>
       </c>
       <c r="O6">
         <f>Data!V84</f>
-        <v>9.8570184819839771E-2</v>
+        <v>5.6445048185473662E-2</v>
       </c>
       <c r="P6">
         <f>Data!W84</f>
-        <v>0.11527240063540134</v>
+        <v>6.4681216313354148E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X84</f>
-        <v>0.13273187009869999</v>
+        <v>7.3290800066268216E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y84</f>
-        <v>0.15019133956199868</v>
+        <v>8.1900383819182299E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z84</f>
-        <v>0.1668935553775602</v>
+        <v>9.0136551947062771E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA84</f>
-        <v>0.18220717745158715</v>
+        <v>9.7687979101476377E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB84</f>
-        <v>0.19571066848486252</v>
+        <v>0.10434679752961336</v>
       </c>
       <c r="V6">
         <f>Data!AC84</f>
-        <v>0.20721459995392699</v>
+        <v>0.11001959656161681</v>
       </c>
       <c r="W6">
         <f>Data!AD84</f>
-        <v>0.21673078178922373</v>
+        <v>0.11471219989021002</v>
       </c>
       <c r="X6">
         <f>Data!AE84</f>
-        <v>0.22441283960042793</v>
+        <v>0.11850036311357261</v>
       </c>
       <c r="Y6">
         <f>Data!AF84</f>
-        <v>0.23049298684661862</v>
+        <v>0.12149859493591794</v>
       </c>
       <c r="Z6">
         <f>Data!AG84</f>
-        <v>0.23523046460317465</v>
+        <v>0.12383473187343347</v>
       </c>
       <c r="AA6">
         <f>Data!AH84</f>
-        <v>0.23887691308706105</v>
+        <v>0.12563286231999143</v>
       </c>
       <c r="AB6">
         <f>Data!AI84</f>
-        <v>0.24165726631126555</v>
-      </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ84</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK84</f>
-        <v>0</v>
+        <v>0.1270039053517853</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I85</f>
@@ -12429,22 +11302,10 @@
         <f>Data!AI85</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ85</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK85</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I86</f>
@@ -12552,18 +11413,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI86</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ86</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK86</f>
         <v>0</v>
       </c>
     </row>
@@ -12577,15 +11426,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -12695,20 +11544,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12793,17 +11630,8 @@
       <c r="AB2">
         <v>1</v>
       </c>
-      <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12888,17 +11716,8 @@
       <c r="AB3">
         <v>1</v>
       </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12983,17 +11802,8 @@
       <c r="AB4">
         <v>1</v>
       </c>
-      <c r="AC4">
-        <v>1</v>
-      </c>
-      <c r="AD4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13078,17 +11888,8 @@
       <c r="AB5">
         <v>1</v>
       </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13173,19 +11974,10 @@
       <c r="AB6">
         <v>1</v>
       </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AD6">
-        <v>1</v>
-      </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -13268,19 +12060,10 @@
       <c r="AB7">
         <v>1</v>
       </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -13361,15 +12144,6 @@
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
         <v>1</v>
       </c>
     </row>
@@ -13394,7 +12168,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -13412,10 +12186,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -13443,7 +12217,7 @@
       <c r="H2">
         <v>15809</v>
       </c>
-      <c r="J2" s="4"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -13470,8 +12244,8 @@
       <c r="H3">
         <v>105.315567</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="21"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -13578,13 +12352,13 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13593,7 +12367,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401838DD-2A40-4094-BDED-2341A398F388}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.1796875" customWidth="1"/>
@@ -13685,128 +12459,128 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B2" s="4">
+        <v>212</v>
+      </c>
+      <c r="B2" s="3">
         <f>'AEO Table 38'!F64*1000</f>
         <v>15153429.688000001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <f>'AEO Table 38'!G64*1000</f>
         <v>15455872.07</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <f>'AEO Table 38'!H64*1000</f>
         <v>16087580.078000002</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <f>'AEO Table 38'!I64*1000</f>
         <v>16167304.688000001</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <f>'AEO Table 38'!J64*1000</f>
         <v>15661874.023</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <f>'AEO Table 38'!K64*1000</f>
         <v>15410783.203000002</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <f>'AEO Table 38'!L64*1000</f>
         <v>15199616.211000001</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <f>'AEO Table 38'!M64*1000</f>
         <v>14843441.405999999</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <f>'AEO Table 38'!N64*1000</f>
         <v>14691375.977</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <f>'AEO Table 38'!O64*1000</f>
         <v>14720266.602</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <f>'AEO Table 38'!P64*1000</f>
         <v>14786203.125</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="3">
         <f>'AEO Table 38'!Q64*1000</f>
         <v>14774537.109000001</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="3">
         <f>'AEO Table 38'!R64*1000</f>
         <v>14758954.102</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="3">
         <f>'AEO Table 38'!S64*1000</f>
         <v>14749166.015999999</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="3">
         <f>'AEO Table 38'!T64*1000</f>
         <v>14787875.977</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="3">
         <f>'AEO Table 38'!U64*1000</f>
         <v>14847477.538999999</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="3">
         <f>'AEO Table 38'!V64*1000</f>
         <v>14856637.695</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <f>'AEO Table 38'!W64*1000</f>
         <v>14802121.094000001</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="3">
         <f>'AEO Table 38'!X64*1000</f>
         <v>14746281.25</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2" s="3">
         <f>'AEO Table 38'!Y64*1000</f>
         <v>14671773.438000001</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="3">
         <f>'AEO Table 38'!Z64*1000</f>
         <v>14624125</v>
       </c>
-      <c r="W2" s="4">
+      <c r="W2" s="3">
         <f>'AEO Table 38'!AA64*1000</f>
         <v>14588690.43</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2" s="3">
         <f>'AEO Table 38'!AB64*1000</f>
         <v>14512471.68</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2" s="3">
         <f>'AEO Table 38'!AC64*1000</f>
         <v>14438543.945</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="Z2" s="3">
         <f>'AEO Table 38'!AD64*1000</f>
         <v>14303833.007999999</v>
       </c>
-      <c r="AA2" s="4">
+      <c r="AA2" s="3">
         <f>'AEO Table 38'!AE64*1000</f>
         <v>14195256.836000001</v>
       </c>
-      <c r="AB2" s="4">
+      <c r="AB2" s="3">
         <f>'AEO Table 38'!AF64*1000</f>
         <v>14124661.132999999</v>
       </c>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
     </row>
     <row r="4" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>296</v>
+        <v>213</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
@@ -13817,34 +12591,21 @@
         <f>1.5*10^6</f>
         <v>1500000</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="25">
         <f>B5/B2</f>
         <v>9.8987491999111582E-2</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="B6">
-        <f>3*10^6</f>
-        <v>3000000</v>
-      </c>
-      <c r="C6" s="28">
-        <f>B6/H2</f>
-        <v>0.19737340458826141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>2035</v>
-      </c>
-      <c r="B7">
         <f>6*10^6</f>
         <v>6000000</v>
       </c>
-      <c r="C7" s="28">
-        <f>B7/M2</f>
+      <c r="C6" s="25">
+        <f>B6/M2</f>
         <v>0.40610409353163845</v>
       </c>
     </row>
@@ -13863,33 +12624,33 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>2023</v>
@@ -13976,31 +12737,31 @@
         <v>2050</v>
       </c>
       <c r="AG5" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>4219.4135740000002</v>
@@ -14083,22 +12844,22 @@
       <c r="AF8">
         <v>2022.312134</v>
       </c>
-      <c r="AG8" s="26">
+      <c r="AG8" s="23">
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -14187,16 +12948,16 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F10">
         <v>4219.4135740000002</v>
@@ -14279,27 +13040,27 @@
       <c r="AF10">
         <v>2022.312134</v>
       </c>
-      <c r="AG10" s="26">
+      <c r="AG10" s="23">
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F12">
         <v>3.044959</v>
@@ -14382,22 +13143,22 @@
       <c r="AF12">
         <v>0.88871900000000004</v>
       </c>
-      <c r="AG12" s="26">
+      <c r="AG12" s="23">
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>9.9261549999999996</v>
@@ -14480,22 +13241,22 @@
       <c r="AF13">
         <v>13.201669000000001</v>
       </c>
-      <c r="AG13" s="26">
+      <c r="AG13" s="23">
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>170.783905</v>
@@ -14578,22 +13339,22 @@
       <c r="AF14">
         <v>1015.777466</v>
       </c>
-      <c r="AG14" s="26">
+      <c r="AG14" s="23">
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>1060.3172609999999</v>
@@ -14676,22 +13437,22 @@
       <c r="AF15">
         <v>2001.5986330000001</v>
       </c>
-      <c r="AG15" s="26">
+      <c r="AG15" s="23">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F16">
         <v>20.772348000000001</v>
@@ -14774,22 +13535,22 @@
       <c r="AF16">
         <v>37.635361000000003</v>
       </c>
-      <c r="AG16" s="26">
+      <c r="AG16" s="23">
         <v>2.3E-2</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F17">
         <v>17.630631999999999</v>
@@ -14872,22 +13633,22 @@
       <c r="AF17">
         <v>38.289561999999997</v>
       </c>
-      <c r="AG17" s="26">
+      <c r="AG17" s="23">
         <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -14976,16 +13737,16 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
         <v>112</v>
       </c>
-      <c r="B19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" t="s">
-        <v>193</v>
-      </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F19">
         <v>420.53945900000002</v>
@@ -15068,22 +13829,22 @@
       <c r="AF19">
         <v>664.652466</v>
       </c>
-      <c r="AG19" s="26">
+      <c r="AG19" s="23">
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
         <v>113</v>
       </c>
-      <c r="B20" t="s">
-        <v>194</v>
-      </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -15172,16 +13933,16 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -15270,16 +14031,16 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -15368,16 +14129,16 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -15466,16 +14227,16 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -15564,16 +14325,16 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F25">
         <v>0.67393400000000003</v>
@@ -15656,22 +14417,22 @@
       <c r="AF25">
         <v>0.24720200000000001</v>
       </c>
-      <c r="AG25" s="26">
+      <c r="AG25" s="23">
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>206</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F26">
         <v>1703.6885990000001</v>
@@ -15754,22 +14515,22 @@
       <c r="AF26">
         <v>3772.29126</v>
       </c>
-      <c r="AG26" s="26">
+      <c r="AG26" s="23">
         <v>3.1E-2</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>208</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="F27">
         <v>28.763452999999998</v>
@@ -15852,22 +14613,22 @@
       <c r="AF27">
         <v>65.100075000000004</v>
       </c>
-      <c r="AG27" s="26">
+      <c r="AG27" s="23">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>130</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F28">
         <v>5923.1020509999998</v>
@@ -15950,32 +14711,32 @@
       <c r="AF28">
         <v>5794.6035160000001</v>
       </c>
-      <c r="AG28" s="26">
+      <c r="AG28" s="23">
         <v>-1E-3</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F31">
         <v>7531.2412109999996</v>
@@ -16058,22 +14819,22 @@
       <c r="AF31">
         <v>4644.8364259999998</v>
       </c>
-      <c r="AG31" s="26">
+      <c r="AG31" s="23">
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F32">
         <v>186.34399400000001</v>
@@ -16156,22 +14917,22 @@
       <c r="AF32">
         <v>111.153175</v>
       </c>
-      <c r="AG32" s="26">
+      <c r="AG32" s="23">
         <v>-0.02</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F33">
         <v>7717.5849609999996</v>
@@ -16254,27 +15015,27 @@
       <c r="AF33">
         <v>4755.9897460000002</v>
       </c>
-      <c r="AG33" s="26">
+      <c r="AG33" s="23">
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F35">
         <v>160.72483800000001</v>
@@ -16357,22 +15118,22 @@
       <c r="AF35">
         <v>51.702643999999999</v>
       </c>
-      <c r="AG35" s="26">
+      <c r="AG35" s="23">
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -16461,16 +15222,16 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>145</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F37">
         <v>57.382061</v>
@@ -16553,22 +15314,22 @@
       <c r="AF37">
         <v>265.46343999999999</v>
       </c>
-      <c r="AG37" s="26">
+      <c r="AG37" s="23">
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F38">
         <v>185.394836</v>
@@ -16651,22 +15412,22 @@
       <c r="AF38">
         <v>821.26580799999999</v>
       </c>
-      <c r="AG38" s="26">
+      <c r="AG38" s="23">
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F39">
         <v>220.50981100000001</v>
@@ -16749,22 +15510,22 @@
       <c r="AF39">
         <v>442.437927</v>
       </c>
-      <c r="AG39" s="26">
+      <c r="AG39" s="23">
         <v>2.7E-2</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F40">
         <v>58.561515999999997</v>
@@ -16847,22 +15608,22 @@
       <c r="AF40">
         <v>562.49542199999996</v>
       </c>
-      <c r="AG40" s="26">
+      <c r="AG40" s="23">
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>233</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>153</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -16951,16 +15712,16 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>154</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F42">
         <v>830.17053199999998</v>
@@ -17043,22 +15804,22 @@
       <c r="AF42">
         <v>1430.702759</v>
       </c>
-      <c r="AG42" s="26">
+      <c r="AG42" s="23">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>238</v>
+        <v>157</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -17147,16 +15908,16 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -17245,16 +16006,16 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -17343,16 +16104,16 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>163</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -17441,16 +16202,16 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>245</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>246</v>
+        <v>165</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -17539,16 +16300,16 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>247</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -17637,16 +16398,16 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>249</v>
+        <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F49">
         <v>1512.7436520000001</v>
@@ -17729,22 +16490,22 @@
       <c r="AF49">
         <v>3574.068115</v>
       </c>
-      <c r="AG49" s="26">
+      <c r="AG49" s="23">
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
-        <v>252</v>
+        <v>171</v>
       </c>
       <c r="C50" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="F50">
         <v>16.388839999999998</v>
@@ -17827,22 +16588,22 @@
       <c r="AF50">
         <v>42.905681999999999</v>
       </c>
-      <c r="AG50" s="26">
+      <c r="AG50" s="23">
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="C51" t="s">
-        <v>256</v>
+        <v>175</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F51">
         <v>9230.328125</v>
@@ -17925,22 +16686,22 @@
       <c r="AF51">
         <v>8330.0576170000004</v>
       </c>
-      <c r="AG51" s="26">
+      <c r="AG51" s="23">
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>257</v>
+        <v>176</v>
       </c>
       <c r="B52" t="s">
-        <v>258</v>
+        <v>177</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>178</v>
       </c>
       <c r="D52" t="s">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="F52">
         <v>21.225769</v>
@@ -18023,22 +16784,22 @@
       <c r="AF52">
         <v>52.010876000000003</v>
       </c>
-      <c r="AG52" s="26">
+      <c r="AG52" s="23">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>260</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F53">
         <v>164.151962</v>
@@ -18121,22 +16882,22 @@
       <c r="AF53">
         <v>369.84582499999999</v>
       </c>
-      <c r="AG53" s="26">
+      <c r="AG53" s="23">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>263</v>
+        <v>182</v>
       </c>
       <c r="B54" t="s">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="C54" t="s">
-        <v>265</v>
+        <v>184</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -18225,24 +16986,24 @@
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>266</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s">
-        <v>267</v>
+        <v>186</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F56">
         <v>11750.655273</v>
@@ -18325,22 +17086,22 @@
       <c r="AF56">
         <v>6667.1484380000002</v>
       </c>
-      <c r="AG56" s="26">
+      <c r="AG56" s="23">
         <v>-2.1999999999999999E-2</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>268</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>188</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F57">
         <v>186.34399400000001</v>
@@ -18423,22 +17184,22 @@
       <c r="AF57">
         <v>111.153175</v>
       </c>
-      <c r="AG57" s="26">
+      <c r="AG57" s="23">
         <v>-0.02</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>270</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>271</v>
+        <v>190</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F58">
         <v>163.769791</v>
@@ -18521,22 +17282,22 @@
       <c r="AF58">
         <v>52.591366000000001</v>
       </c>
-      <c r="AG58" s="26">
+      <c r="AG58" s="23">
         <v>-4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="C59" t="s">
-        <v>273</v>
+        <v>192</v>
       </c>
       <c r="D59" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F59">
         <v>1483.8043210000001</v>
@@ -18619,22 +17380,22 @@
       <c r="AF59">
         <v>4117.3071289999998</v>
       </c>
-      <c r="AG59" s="26">
+      <c r="AG59" s="23">
         <v>0.04</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="C60" t="s">
-        <v>275</v>
+        <v>194</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F60">
         <v>317.47430400000002</v>
@@ -18717,22 +17478,22 @@
       <c r="AF60">
         <v>1080.8582759999999</v>
       </c>
-      <c r="AG60" s="26">
+      <c r="AG60" s="23">
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>277</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F61">
         <v>1250.709961</v>
@@ -18815,22 +17576,22 @@
       <c r="AF61">
         <v>2095.3552249999998</v>
       </c>
-      <c r="AG61" s="26">
+      <c r="AG61" s="23">
         <v>0.02</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -18919,16 +17680,16 @@
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="C63" t="s">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F63">
         <v>0.67393400000000003</v>
@@ -19011,22 +17772,22 @@
       <c r="AF63">
         <v>0.24720200000000001</v>
       </c>
-      <c r="AG63" s="26">
+      <c r="AG63" s="23">
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
-        <v>283</v>
+        <v>202</v>
       </c>
       <c r="C64" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F64">
         <v>15153.429688</v>
@@ -19109,22 +17870,22 @@
       <c r="AF64">
         <v>14124.661133</v>
       </c>
-      <c r="AG64" s="26">
+      <c r="AG64" s="23">
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>285</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="C65" t="s">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F65">
         <v>7511.6499020000001</v>
@@ -19207,22 +17968,22 @@
       <c r="AF65">
         <v>5758.0869140000004</v>
       </c>
-      <c r="AG65" s="26">
+      <c r="AG65" s="23">
         <v>-0.01</v>
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="B66" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="C66" t="s">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F66">
         <v>97.115607999999995</v>
@@ -19305,22 +18066,22 @@
       <c r="AF66">
         <v>58.546866999999999</v>
       </c>
-      <c r="AG66" s="26">
+      <c r="AG66" s="23">
         <v>-1.9E-2</v>
       </c>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="B67" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="C67" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F67">
         <v>3402.7761230000001</v>
@@ -19403,7 +18164,7 @@
       <c r="AF67">
         <v>7457.5122069999998</v>
       </c>
-      <c r="AG67" s="26">
+      <c r="AG67" s="23">
         <v>3.1E-2</v>
       </c>
     </row>
@@ -19425,7 +18186,7 @@
     <col min="3" max="3" width="24.08984375" customWidth="1"/>
     <col min="4" max="4" width="14.7265625" customWidth="1"/>
     <col min="5" max="5" width="16.26953125" customWidth="1"/>
-    <col min="6" max="6" width="18" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.08984375" customWidth="1"/>
     <col min="8" max="9" width="9.08984375" customWidth="1"/>
     <col min="14" max="14" width="11.08984375" customWidth="1"/>
@@ -19433,148 +18194,148 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="N1" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="R1" s="14"/>
-      <c r="T1" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="U1" s="14"/>
-      <c r="W1" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="X1" s="14"/>
+        <v>27</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="12"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="N1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="12"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="12"/>
+      <c r="T1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="U1" s="12"/>
+      <c r="W1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="X1" s="12"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="16">
-        <v>1</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="O2" s="16">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="R2" s="16">
-        <v>1</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="U2" s="16">
-        <v>1</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="X2" s="16">
+        <v>28</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="14">
+        <v>1</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="14">
+        <v>1</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="14">
+        <v>1</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="I3" s="16">
+        <v>29</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="14">
         <v>-0.3</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="16">
+      <c r="N3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="14">
         <v>-0.4</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="R3" s="16">
+      <c r="Q3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="14">
         <v>-0.5</v>
       </c>
-      <c r="T3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="16">
+      <c r="T3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" s="14">
         <v>-0.42</v>
       </c>
-      <c r="W3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="X3" s="16">
+      <c r="W3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="X3" s="14">
         <v>-0.4</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="17">
+        <v>30</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="15">
         <v>-16</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O4" s="17">
-        <v>-10</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R4" s="17">
+      <c r="N4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="15">
+        <v>-11</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="R4" s="15">
         <v>-15</v>
       </c>
-      <c r="T4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="U4" s="17">
+      <c r="T4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="U4" s="15">
         <v>-11</v>
       </c>
-      <c r="W4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="X4" s="17">
+      <c r="W4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="X4" s="15">
         <v>-10.5</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
@@ -19582,19 +18343,19 @@
         <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="19"/>
-      <c r="R6" s="22"/>
+        <v>26</v>
+      </c>
+      <c r="N6" s="20"/>
+      <c r="O6" s="17"/>
+      <c r="R6" s="20"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="10"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="9"/>
       <c r="E7" s="2">
         <v>2020</v>
       </c>
@@ -19602,148 +18363,150 @@
         <v>2050</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="N7" s="22"/>
+      <c r="N7" s="20"/>
     </row>
     <row r="8" spans="1:37" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24" t="s">
-        <v>94</v>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="29"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>2024</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>2025</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>2050</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="I9" s="18">
+      <c r="G9" s="4"/>
+      <c r="I9" s="16">
         <v>2024</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="16">
         <f>E9</f>
         <v>2025</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="16">
         <f t="shared" ref="K9:AI9" si="0">J9+1</f>
         <v>2026</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="16">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="16">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="16">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="16">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="P9" s="18">
+      <c r="P9" s="16">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="Q9" s="18">
+      <c r="Q9" s="16">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="R9" s="18">
+      <c r="R9" s="16">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="S9" s="18">
+      <c r="S9" s="16">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="T9" s="18">
+      <c r="T9" s="16">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
-      <c r="U9" s="18">
+      <c r="U9" s="16">
         <f t="shared" si="0"/>
         <v>2036</v>
       </c>
-      <c r="V9" s="18">
+      <c r="V9" s="16">
         <f t="shared" si="0"/>
         <v>2037</v>
       </c>
-      <c r="W9" s="18">
+      <c r="W9" s="16">
         <f t="shared" si="0"/>
         <v>2038</v>
       </c>
-      <c r="X9" s="18">
+      <c r="X9" s="16">
         <f t="shared" si="0"/>
         <v>2039</v>
       </c>
-      <c r="Y9" s="18">
+      <c r="Y9" s="16">
         <f t="shared" si="0"/>
         <v>2040</v>
       </c>
-      <c r="Z9" s="18">
+      <c r="Z9" s="16">
         <f t="shared" si="0"/>
         <v>2041</v>
       </c>
-      <c r="AA9" s="18">
+      <c r="AA9" s="16">
         <f t="shared" si="0"/>
         <v>2042</v>
       </c>
-      <c r="AB9" s="18">
+      <c r="AB9" s="16">
         <f t="shared" si="0"/>
         <v>2043</v>
       </c>
-      <c r="AC9" s="18">
+      <c r="AC9" s="16">
         <f t="shared" si="0"/>
         <v>2044</v>
       </c>
-      <c r="AD9" s="18">
+      <c r="AD9" s="16">
         <f t="shared" si="0"/>
         <v>2045</v>
       </c>
-      <c r="AE9" s="18">
+      <c r="AE9" s="16">
         <f t="shared" si="0"/>
         <v>2046</v>
       </c>
-      <c r="AF9" s="18">
+      <c r="AF9" s="16">
         <f t="shared" si="0"/>
         <v>2047</v>
       </c>
-      <c r="AG9" s="18">
+      <c r="AG9" s="16">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="AH9" s="18">
+      <c r="AH9" s="16">
         <f t="shared" si="0"/>
         <v>2049</v>
       </c>
-      <c r="AI9" s="18">
+      <c r="AI9" s="16">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-      <c r="AJ9" s="18"/>
-      <c r="AK9" s="18"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -19758,13 +18521,13 @@
       <c r="D10">
         <v>8.2556397301899995E-2</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="17">
         <v>6.6873740826300002E-2</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="6" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="G10" s="5" t="str">
         <f>IF(E10=F10,"n/a",IF(OR(C10="battery electric vehicle",C10="natural gas vehicle",C10="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
@@ -19772,109 +18535,109 @@
         <f>D10</f>
         <v>8.2556397301899995E-2</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="17">
         <f>E10</f>
         <v>6.6873740826300002E-2</v>
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>7.8393597159514841E-2</v>
+        <v>7.826128265631177E-2</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>8.383744382909665E-2</v>
+        <v>8.3712995874888008E-2</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>9.1702346693592188E-2</v>
+        <v>9.167058838844952E-2</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.1028980197241021</v>
+        <v>0.10316718187336593</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.11850365652431405</v>
+        <v>0.11953255902288656</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.1396309892832005</v>
+        <v>0.14234424092873754</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.16713173544079279</v>
+        <v>0.17322731225641558</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.20115393406388254</v>
+        <v>0.21342677874098925</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.2406926533620381</v>
+        <v>0.26315903783836003</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.28343687041315002</v>
+        <v>0.32095512133954762</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.32618108746426189</v>
+        <v>0.38343687041314994</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.36571980676241744</v>
+        <v>0.44591861948675221</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.39974200538550725</v>
+        <v>0.50371470298793986</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.42724275154309949</v>
+        <v>0.55344696208531075</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.44837008430198594</v>
+        <v>0.59364642856988437</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.46397572110219792</v>
+        <v>0.62452949989756235</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.47517139413270781</v>
+        <v>0.64734118180341338</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.48303629699720335</v>
+        <v>0.66370655895293407</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.4884801436667851</v>
+        <v>0.67520315243785045</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.4922097001624065</v>
+        <v>0.68316074495141188</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.49474685632562987</v>
+        <v>0.68861245816998817</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.49646457609119271</v>
+        <v>0.69232116932877497</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.49762373988097219</v>
+        <v>0.69483206186056068</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.49840425895445883</v>
+        <v>0.69652648010108209</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.49892904198182053</v>
+        <v>0.69766741097457163</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
@@ -19884,18 +18647,18 @@
       <c r="D11">
         <v>1.0005073039100001E-4</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="17">
         <v>9.1114481822700006E-5</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <f>E11</f>
         <v>9.1114481822700006E-5</v>
       </c>
-      <c r="G11" s="6" t="str">
+      <c r="G11" s="5" t="str">
         <f>IF(E11=F11,"n/a",IF(OR(C11="battery electric vehicle",C11="natural gas vehicle",C11="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="17">
         <f t="shared" ref="I11:I40" si="1">E11</f>
         <v>9.1114481822700006E-5</v>
       </c>
@@ -20017,11 +18780,11 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="6" t="str">
+      <c r="G12" s="5" t="str">
         <f>IF(E12=F12,"n/a",IF(OR(C12="battery electric vehicle",C12="natural gas vehicle",C12="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -20137,18 +18900,18 @@
       <c r="D13">
         <v>6.6777915503600002E-2</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="17">
         <v>6.08023121013E-2</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="17">
         <f>E13</f>
         <v>6.08023121013E-2</v>
       </c>
-      <c r="G13" s="6" t="str">
+      <c r="G13" s="5" t="str">
         <f>IF(E13=F13,"n/a",IF(OR(C13="battery electric vehicle",C13="natural gas vehicle",C13="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="17">
         <f t="shared" si="1"/>
         <v>6.08023121013E-2</v>
       </c>
@@ -20264,14 +19027,15 @@
       <c r="D14">
         <v>1.5463740197399999E-2</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="17">
         <f>D14</f>
         <v>1.5463740197399999E-2</v>
       </c>
-      <c r="F14" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="G14" s="6" t="str">
+      <c r="F14" s="26">
+        <f>D14/D10*F10</f>
+        <v>0.13111785993513644</v>
+      </c>
+      <c r="G14" s="5" t="str">
         <f>IF(E14=F14,"n/a",IF(OR(C14="battery electric vehicle",C14="natural gas vehicle",C14="plugin hybrid vehicle",C14="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
@@ -20285,124 +19049,124 @@
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>2.3336940270317272E-2</v>
+        <v>1.9346159166299389E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>2.7240104411371674E-2</v>
+        <v>2.1270880799131281E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>3.2929173531825326E-2</v>
+        <v>2.4076264844254999E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>4.105090059697207E-2</v>
+        <v>2.8081237018963839E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>5.2308323901729806E-2</v>
+        <v>3.3632478366133998E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>6.7290130392745701E-2</v>
+        <v>4.1020281187147262E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>8.6184580636549449E-2</v>
+        <v>5.0337480210934871E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>0.10846129572320919</v>
+        <v>6.1322535895563066E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>0.13273187009869999</v>
+        <v>7.3290800066268216E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>0.15700244447419082</v>
+        <v>8.5259064236973381E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>0.17927915956085055</v>
+        <v>9.6244119921601576E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>0.19817360980465429</v>
+        <v>0.10556131894538917</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>0.2131554162956702</v>
+        <v>0.11294912176640245</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>0.22441283960042793</v>
+        <v>0.11850036311357261</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>0.23253456666557468</v>
+        <v>0.12250533528828143</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>0.23822363578602834</v>
+        <v>0.12531071933340518</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>0.24212679992708275</v>
+        <v>0.12723544096623707</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>0.24476668954419437</v>
+        <v>0.1285372188240779</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>0.24653495386445468</v>
+        <v>0.12940918230467352</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>0.24771170813627313</v>
+        <v>0.12998946136075354</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>0.24849143733752424</v>
+        <v>0.13037396009233732</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>0.24900661237439095</v>
+        <v>0.1306280023263604</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>0.24934634833070185</v>
+        <v>0.1307955323407107</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>0.2495701093559812</v>
+        <v>0.13090587299520942</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>0.2497173640510624</v>
+        <v>0.13097848697886891</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
-      <c r="E15" s="19">
-        <v>0</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="E15" s="17">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17">
         <f>E15</f>
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="str">
+      <c r="G15" s="5" t="str">
         <f>IF(E15=F15,"n/a",IF(OR(C15="battery electric vehicle",C15="natural gas vehicle",C15="plugin hybrid vehicle",C15="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20512,26 +19276,26 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="20">
-        <v>0</v>
-      </c>
-      <c r="E16" s="23">
-        <v>0</v>
-      </c>
-      <c r="F16" s="23">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="18">
+        <v>0</v>
+      </c>
+      <c r="E16" s="21">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21">
         <f>E16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="7" t="str">
+      <c r="G16" s="6" t="str">
         <f>IF(E16=F16,"n/a",IF(OR(C16="battery electric vehicle",C16="natural gas vehicle",C16="plugin hybrid vehicle",C16="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20653,17 +19417,17 @@
       <c r="D17">
         <v>9.2058503875700002E-3</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="17">
         <v>6.8939837381399999E-3</v>
       </c>
       <c r="F17">
         <v>0.25</v>
       </c>
-      <c r="G17" s="6" t="str">
+      <c r="G17" s="5" t="str">
         <f>IF(E17=F17,"n/a",IF(OR(C17="battery electric vehicle",C17="natural gas vehicle",C17="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="17">
         <f t="shared" si="1"/>
         <v>6.8939837381399999E-3</v>
       </c>
@@ -20779,17 +19543,17 @@
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" s="19">
-        <v>0</v>
-      </c>
-      <c r="F18" s="19">
+      <c r="E18" s="17">
+        <v>0</v>
+      </c>
+      <c r="F18" s="17">
         <f>E18</f>
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I18" s="19">
+      <c r="G18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -20905,18 +19669,18 @@
       <c r="D19">
         <v>0.72915442924999996</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="17">
         <v>0.67797888423399999</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="17">
         <f>E19</f>
         <v>0.67797888423399999</v>
       </c>
-      <c r="G19" s="6" t="str">
+      <c r="G19" s="5" t="str">
         <f>IF(E19=F19,"n/a",IF(OR(C19="battery electric vehicle",C19="natural gas vehicle",C19="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="17">
         <f t="shared" si="1"/>
         <v>0.67797888423399999</v>
       </c>
@@ -21032,17 +19796,17 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="19">
-        <v>1</v>
-      </c>
-      <c r="F20" s="30">
-        <v>1</v>
-      </c>
-      <c r="G20" s="6" t="str">
+      <c r="E20" s="17">
+        <v>1</v>
+      </c>
+      <c r="F20" s="27">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="str">
         <f>IF(E20=F20,"n/a",IF(OR(C20="battery electric vehicle",C20="natural gas vehicle",C20="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -21158,18 +19922,18 @@
       <c r="D21">
         <v>0</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="17">
         <v>4.2783868328800001E-4</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="17">
         <f>E21</f>
         <v>4.2783868328800001E-4</v>
       </c>
-      <c r="G21" s="6" t="str">
+      <c r="G21" s="5" t="str">
         <f>IF(E21=F21,"n/a",IF(OR(C21="battery electric vehicle",C21="natural gas vehicle",C21="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="17">
         <f t="shared" si="1"/>
         <v>4.2783868328800001E-4</v>
       </c>
@@ -21280,23 +20044,23 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
-      <c r="E22" s="19">
-        <v>0</v>
-      </c>
-      <c r="F22" s="19">
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+      <c r="F22" s="17">
         <f>E22</f>
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="str">
+      <c r="G22" s="5" t="str">
         <f>IF(E22=F22,"n/a",IF(OR(C22="battery electric vehicle",C22="natural gas vehicle",C22="plugin hybrid vehicle",C22="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -21406,26 +20170,26 @@
       </c>
     </row>
     <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="20">
-        <v>0</v>
-      </c>
-      <c r="E23" s="23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="23">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="18">
+        <v>0</v>
+      </c>
+      <c r="E23" s="21">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="str">
+      <c r="G23" s="6" t="str">
         <f>IF(E23=F23,"n/a",IF(OR(C23="battery electric vehicle",C23="natural gas vehicle",C23="plugin hybrid vehicle",C23="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -21547,123 +20311,123 @@
       <c r="D24">
         <v>0.154617049501</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="17">
         <v>0.17679125251200001</v>
       </c>
-      <c r="F24" s="30">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6" t="str">
+      <c r="F24" s="27">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="str">
         <f>IF(E24=F24,"n/a",IF(OR(C24="battery electric vehicle",C24="natural gas vehicle",C24="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="17">
         <f>D24</f>
         <v>0.154617049501</v>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="17">
         <f>E24</f>
         <v>0.17679125251200001</v>
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>0.19868613028135812</v>
+        <v>0.1915976578869496</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>0.20903281811998659</v>
+        <v>0.19868613028135812</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>0.22398101555448952</v>
+        <v>0.20903281811998659</v>
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>0.2452597438179614</v>
+        <v>0.22398101555448952</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.27492014064673714</v>
+        <v>0.2452597438179614</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.31507518728691364</v>
+        <v>0.27492014064673714</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.36734367556228731</v>
+        <v>0.31507518728691364</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.43200697159225543</v>
+        <v>0.36734367556228731</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.5071550811823069</v>
+        <v>0.43200697159225543</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.58839562625599995</v>
+        <v>0.5071550811823069</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.669636171329693</v>
+        <v>0.58839562625599995</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.74478428091974458</v>
+        <v>0.669636171329693</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.8094475769497127</v>
+        <v>0.74478428091974458</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.86171606522508637</v>
+        <v>0.8094475769497127</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.90187111186526281</v>
+        <v>0.86171606522508637</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.93153150869403867</v>
+        <v>0.90187111186526281</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.95281023695751044</v>
+        <v>0.93153150869403867</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.96775843439201348</v>
+        <v>0.95281023695751044</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.97810512223064183</v>
+        <v>0.96775843439201348</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.98519359462505041</v>
+        <v>0.97810512223064183</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.99001576622760601</v>
+        <v>0.98519359462505041</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.99328050002472557</v>
+        <v>0.99001576622760601</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.99548363075463853</v>
+        <v>0.99328050002472557</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.99696710148694001</v>
+        <v>0.99548363075463853</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.99796451498821692</v>
+        <v>0.99696710148694001</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.35">
@@ -21673,18 +20437,18 @@
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="19">
-        <v>0</v>
-      </c>
-      <c r="F25" s="19">
+      <c r="E25" s="17">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17">
         <f>E25</f>
         <v>0</v>
       </c>
-      <c r="G25" s="6" t="str">
+      <c r="G25" s="5" t="str">
         <f>IF(E25=F25,"n/a",IF(OR(C25="battery electric vehicle",C25="natural gas vehicle",C25="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -21800,18 +20564,18 @@
       <c r="D26">
         <v>0</v>
       </c>
-      <c r="E26" s="19">
-        <v>0</v>
-      </c>
-      <c r="F26" s="19">
+      <c r="E26" s="17">
+        <v>0</v>
+      </c>
+      <c r="F26" s="17">
         <f>E26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="6" t="str">
+      <c r="G26" s="5" t="str">
         <f>IF(E26=F26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -21933,11 +20697,11 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="6" t="str">
+      <c r="G27" s="5" t="str">
         <f>IF(E27=F27,"n/a",IF(OR(C27="battery electric vehicle",C27="natural gas vehicle",C27="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -22053,18 +20817,18 @@
       <c r="D28">
         <v>0</v>
       </c>
-      <c r="E28" s="19">
-        <v>0</v>
-      </c>
-      <c r="F28" s="19">
+      <c r="E28" s="17">
+        <v>0</v>
+      </c>
+      <c r="F28" s="17">
         <f>E28</f>
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="str">
+      <c r="G28" s="5" t="str">
         <f>IF(E28=F28,"n/a",IF(OR(C28="battery electric vehicle",C28="natural gas vehicle",C28="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -22175,23 +20939,23 @@
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
-      <c r="E29" s="19">
-        <v>0</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="E29" s="17">
+        <v>0</v>
+      </c>
+      <c r="F29" s="17">
         <f>E29</f>
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="str">
+      <c r="G29" s="5" t="str">
         <f>IF(E29=F29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -22301,26 +21065,26 @@
       </c>
     </row>
     <row r="30" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="20">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="18">
         <v>5.0287437714699998E-2</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="21">
         <v>6.7718615476299995E-2</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="21">
         <f>E30</f>
         <v>6.7718615476299995E-2</v>
       </c>
-      <c r="G30" s="7" t="str">
+      <c r="G30" s="6" t="str">
         <f>IF(E30=F30,"n/a",IF(OR(C30="battery electric vehicle",C30="natural gas vehicle",C30="plugin hybrid vehicle",C30="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="17">
         <f t="shared" si="1"/>
         <v>6.7718615476299995E-2</v>
       </c>
@@ -22442,17 +21206,17 @@
       <c r="D31">
         <v>2.7710514836400001E-3</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="17">
         <v>3.7809614281599999E-3</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="17">
         <v>0.5</v>
       </c>
-      <c r="G31" s="6" t="str">
+      <c r="G31" s="5" t="str">
         <f>IF(E31=F31,"n/a",IF(OR(C31="battery electric vehicle",C31="natural gas vehicle",C31="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="17">
         <f>E31</f>
         <v>3.7809614281599999E-3</v>
       </c>
@@ -22568,18 +21332,18 @@
       <c r="D32">
         <v>0</v>
       </c>
-      <c r="E32" s="19">
-        <v>0</v>
-      </c>
-      <c r="F32" s="19">
+      <c r="E32" s="17">
+        <v>0</v>
+      </c>
+      <c r="F32" s="17">
         <f>E32</f>
         <v>0</v>
       </c>
-      <c r="G32" s="6" t="str">
+      <c r="G32" s="5" t="str">
         <f>IF(E32=F32,"n/a",IF(OR(C32="battery electric vehicle",C32="natural gas vehicle",C32="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -22695,18 +21459,18 @@
       <c r="D33">
         <v>0</v>
       </c>
-      <c r="E33" s="19">
-        <v>0</v>
-      </c>
-      <c r="F33" s="19">
+      <c r="E33" s="17">
+        <v>0</v>
+      </c>
+      <c r="F33" s="17">
         <f>E33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="6" t="str">
+      <c r="G33" s="5" t="str">
         <f>IF(E33=F33,"n/a",IF(OR(C33="battery electric vehicle",C33="natural gas vehicle",C33="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -22828,11 +21592,11 @@
       <c r="F34">
         <v>1</v>
       </c>
-      <c r="G34" s="6" t="str">
+      <c r="G34" s="5" t="str">
         <f>IF(E34=F34,"n/a",IF(OR(C34="battery electric vehicle",C34="natural gas vehicle",C34="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -22948,18 +21712,18 @@
       <c r="D35">
         <v>0</v>
       </c>
-      <c r="E35" s="19">
-        <v>0</v>
-      </c>
-      <c r="F35" s="19">
+      <c r="E35" s="17">
+        <v>0</v>
+      </c>
+      <c r="F35" s="17">
         <f>E35</f>
         <v>0</v>
       </c>
-      <c r="G35" s="6" t="str">
+      <c r="G35" s="5" t="str">
         <f>IF(E35=F35,"n/a",IF(OR(C35="battery electric vehicle",C35="natural gas vehicle",C35="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23070,23 +21834,23 @@
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
-      <c r="E36" s="19">
-        <v>0</v>
-      </c>
-      <c r="F36" s="19">
+      <c r="E36" s="17">
+        <v>0</v>
+      </c>
+      <c r="F36" s="17">
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="G36" s="6" t="str">
+      <c r="G36" s="5" t="str">
         <f>IF(E36=F36,"n/a",IF(OR(C36="battery electric vehicle",C36="natural gas vehicle",C36="plugin hybrid vehicle",C36="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23196,26 +21960,26 @@
       </c>
     </row>
     <row r="37" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" s="20">
-        <v>0</v>
-      </c>
-      <c r="E37" s="23">
-        <v>0</v>
-      </c>
-      <c r="F37" s="23">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="18">
+        <v>0</v>
+      </c>
+      <c r="E37" s="21">
+        <v>0</v>
+      </c>
+      <c r="F37" s="21">
         <f>E37</f>
         <v>0</v>
       </c>
-      <c r="G37" s="7" t="str">
+      <c r="G37" s="6" t="str">
         <f>IF(E37=F37,"n/a",IF(OR(C37="battery electric vehicle",C37="natural gas vehicle",C37="plugin hybrid vehicle",C37="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23340,11 +22104,11 @@
       <c r="F38">
         <v>0</v>
       </c>
-      <c r="G38" s="6" t="str">
+      <c r="G38" s="5" t="str">
         <f>IF(E38=F38,"n/a",IF(OR(C38="battery electric vehicle",C38="natural gas vehicle",C38="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23463,11 +22227,11 @@
       <c r="F39">
         <v>0</v>
       </c>
-      <c r="G39" s="6" t="str">
+      <c r="G39" s="5" t="str">
         <f>IF(E39=F39,"n/a",IF(OR(C39="battery electric vehicle",C39="natural gas vehicle",C39="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23586,11 +22350,11 @@
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="G40" s="6" t="str">
+      <c r="G40" s="5" t="str">
         <f>IF(E40=F40,"n/a",IF(OR(C40="battery electric vehicle",C40="natural gas vehicle",C40="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -23709,11 +22473,11 @@
       <c r="F41">
         <v>1</v>
       </c>
-      <c r="G41" s="6" t="str">
+      <c r="G41" s="5" t="str">
         <f>IF(E41=F41,"n/a",IF(OR(C41="battery electric vehicle",C41="natural gas vehicle",C41="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="17">
         <f t="shared" ref="I41:I72" si="2">E41</f>
         <v>1</v>
       </c>
@@ -23832,11 +22596,11 @@
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="G42" s="6" t="str">
+      <c r="G42" s="5" t="str">
         <f>IF(E42=F42,"n/a",IF(OR(C42="battery electric vehicle",C42="natural gas vehicle",C42="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -23947,7 +22711,7 @@
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -23955,11 +22719,11 @@
       <c r="F43">
         <v>0</v>
       </c>
-      <c r="G43" s="6" t="str">
+      <c r="G43" s="5" t="str">
         <f>IF(E43=F43,"n/a",IF(OR(C43="battery electric vehicle",C43="natural gas vehicle",C43="plugin hybrid vehicle",C43="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24069,23 +22833,23 @@
       </c>
     </row>
     <row r="44" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20">
-        <v>0</v>
-      </c>
-      <c r="F44" s="20">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="str">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18">
+        <v>0</v>
+      </c>
+      <c r="F44" s="18">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="str">
         <f>IF(E44=F44,"n/a",IF(OR(C44="battery electric vehicle",C44="natural gas vehicle",C44="plugin hybrid vehicle",C44="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24210,11 +22974,11 @@
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="G45" s="6" t="str">
+      <c r="G45" s="5" t="str">
         <f>IF(E45=F45,"n/a",IF(OR(C45="battery electric vehicle",C45="natural gas vehicle",C45="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I45" s="19">
+      <c r="I45" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24333,11 +23097,11 @@
       <c r="F46">
         <v>0</v>
       </c>
-      <c r="G46" s="6" t="str">
+      <c r="G46" s="5" t="str">
         <f>IF(E46=F46,"n/a",IF(OR(C46="battery electric vehicle",C46="natural gas vehicle",C46="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24456,11 +23220,11 @@
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="G47" s="6" t="str">
+      <c r="G47" s="5" t="str">
         <f>IF(E47=F47,"n/a",IF(OR(C47="battery electric vehicle",C47="natural gas vehicle",C47="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I47" s="19">
+      <c r="I47" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24579,11 +23343,11 @@
       <c r="F48">
         <v>1</v>
       </c>
-      <c r="G48" s="6" t="str">
+      <c r="G48" s="5" t="str">
         <f>IF(E48=F48,"n/a",IF(OR(C48="battery electric vehicle",C48="natural gas vehicle",C48="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I48" s="19">
+      <c r="I48" s="17">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -24702,11 +23466,11 @@
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="G49" s="6" t="str">
+      <c r="G49" s="5" t="str">
         <f>IF(E49=F49,"n/a",IF(OR(C49="battery electric vehicle",C49="natural gas vehicle",C49="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I49" s="19">
+      <c r="I49" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24817,7 +23581,7 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C50" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -24825,11 +23589,11 @@
       <c r="F50">
         <v>0</v>
       </c>
-      <c r="G50" s="6" t="str">
+      <c r="G50" s="5" t="str">
         <f>IF(E50=F50,"n/a",IF(OR(C50="battery electric vehicle",C50="natural gas vehicle",C50="plugin hybrid vehicle",C50="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I50" s="19">
+      <c r="I50" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -24939,23 +23703,23 @@
       </c>
     </row>
     <row r="51" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="20"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20">
-        <v>0</v>
-      </c>
-      <c r="F51" s="20">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="str">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18">
+        <v>0</v>
+      </c>
+      <c r="F51" s="18">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="str">
         <f>IF(E51=F51,"n/a",IF(OR(C51="battery electric vehicle",C51="natural gas vehicle",C51="plugin hybrid vehicle",C51="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I51" s="19">
+      <c r="I51" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -25074,18 +23838,18 @@
       <c r="C52" t="s">
         <v>1</v>
       </c>
-      <c r="E52" s="19">
+      <c r="E52" s="17">
         <f>'SYVbT-passenger'!B5/SUM('SYVbT-passenger'!B5:H5)</f>
         <v>0.93664816810144857</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
-      <c r="G52" s="6" t="str">
+      <c r="G52" s="5" t="str">
         <f>IF(E52=F52,"n/a",IF(OR(C52="battery electric vehicle",C52="natural gas vehicle",C52="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="I52" s="19">
+      <c r="I52" s="17">
         <f t="shared" si="2"/>
         <v>0.93664816810144857</v>
       </c>
@@ -25204,11 +23968,11 @@
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="G53" s="6" t="str">
+      <c r="G53" s="5" t="str">
         <f>IF(E53=F53,"n/a",IF(OR(C53="battery electric vehicle",C53="natural gas vehicle",C53="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I53" s="19">
+      <c r="I53" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -25327,11 +24091,11 @@
       <c r="F54">
         <v>0</v>
       </c>
-      <c r="G54" s="6" t="str">
+      <c r="G54" s="5" t="str">
         <f>IF(E54=F54,"n/a",IF(OR(C54="battery electric vehicle",C54="natural gas vehicle",C54="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I54" s="19">
+      <c r="I54" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -25444,18 +24208,18 @@
       <c r="C55" t="s">
         <v>4</v>
       </c>
-      <c r="E55" s="19">
+      <c r="E55" s="17">
         <f>1-E52</f>
         <v>6.3351831898551425E-2</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="6" t="str">
+      <c r="G55" s="5" t="str">
         <f>IF(E55=F55,"n/a",IF(OR(C55="battery electric vehicle",C55="natural gas vehicle",C55="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>linear</v>
       </c>
-      <c r="I55" s="19">
+      <c r="I55" s="17">
         <f t="shared" si="2"/>
         <v>6.3351831898551425E-2</v>
       </c>
@@ -25574,11 +24338,11 @@
       <c r="F56">
         <v>0</v>
       </c>
-      <c r="G56" s="6" t="str">
+      <c r="G56" s="5" t="str">
         <f>IF(E56=F56,"n/a",IF(OR(C56="battery electric vehicle",C56="natural gas vehicle",C56="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I56" s="19">
+      <c r="I56" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -25689,7 +24453,7 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C57" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -25697,11 +24461,11 @@
       <c r="F57">
         <v>0</v>
       </c>
-      <c r="G57" s="6" t="str">
+      <c r="G57" s="5" t="str">
         <f>IF(E57=F57,"n/a",IF(OR(C57="battery electric vehicle",C57="natural gas vehicle",C57="plugin hybrid vehicle",C57="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I57" s="19">
+      <c r="I57" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -25811,23 +24575,23 @@
       </c>
     </row>
     <row r="58" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20">
-        <v>0</v>
-      </c>
-      <c r="F58" s="20">
-        <v>0</v>
-      </c>
-      <c r="G58" s="7" t="str">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18">
+        <v>0</v>
+      </c>
+      <c r="F58" s="18">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="str">
         <f>IF(E58=F58,"n/a",IF(OR(C58="battery electric vehicle",C58="natural gas vehicle",C58="plugin hybrid vehicle",C58="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I58" s="19">
+      <c r="I58" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -25952,11 +24716,11 @@
       <c r="F59">
         <v>0</v>
       </c>
-      <c r="G59" s="6" t="str">
+      <c r="G59" s="5" t="str">
         <f>IF(E59=F59,"n/a",IF(OR(C59="battery electric vehicle",C59="natural gas vehicle",C59="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I59" s="19">
+      <c r="I59" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26075,11 +24839,11 @@
       <c r="F60">
         <v>0</v>
       </c>
-      <c r="G60" s="6" t="str">
+      <c r="G60" s="5" t="str">
         <f>IF(E60=F60,"n/a",IF(OR(C60="battery electric vehicle",C60="natural gas vehicle",C60="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I60" s="19">
+      <c r="I60" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26198,11 +24962,11 @@
       <c r="F61">
         <v>0</v>
       </c>
-      <c r="G61" s="6" t="str">
+      <c r="G61" s="5" t="str">
         <f>IF(E61=F61,"n/a",IF(OR(C61="battery electric vehicle",C61="natural gas vehicle",C61="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I61" s="19">
+      <c r="I61" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26321,11 +25085,11 @@
       <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="6" t="str">
+      <c r="G62" s="5" t="str">
         <f>IF(E62=F62,"n/a",IF(OR(C62="battery electric vehicle",C62="natural gas vehicle",C62="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I62" s="19">
+      <c r="I62" s="17">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -26444,11 +25208,11 @@
       <c r="F63">
         <v>0</v>
       </c>
-      <c r="G63" s="6" t="str">
+      <c r="G63" s="5" t="str">
         <f>IF(E63=F63,"n/a",IF(OR(C63="battery electric vehicle",C63="natural gas vehicle",C63="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I63" s="19">
+      <c r="I63" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26559,7 +25323,7 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C64" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -26567,11 +25331,11 @@
       <c r="F64">
         <v>0</v>
       </c>
-      <c r="G64" s="6" t="str">
+      <c r="G64" s="5" t="str">
         <f>IF(E64=F64,"n/a",IF(OR(C64="battery electric vehicle",C64="natural gas vehicle",C64="plugin hybrid vehicle",C64="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I64" s="19">
+      <c r="I64" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26681,23 +25445,23 @@
       </c>
     </row>
     <row r="65" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="20"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20">
-        <v>0</v>
-      </c>
-      <c r="F65" s="20">
-        <v>0</v>
-      </c>
-      <c r="G65" s="7" t="str">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18">
+        <v>0</v>
+      </c>
+      <c r="F65" s="18">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="str">
         <f>IF(E65=F65,"n/a",IF(OR(C65="battery electric vehicle",C65="natural gas vehicle",C65="plugin hybrid vehicle",C65="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I65" s="19">
+      <c r="I65" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26822,11 +25586,11 @@
       <c r="F66">
         <v>0</v>
       </c>
-      <c r="G66" s="6" t="str">
+      <c r="G66" s="5" t="str">
         <f>IF(E66=F66,"n/a",IF(OR(C66="battery electric vehicle",C66="natural gas vehicle",C66="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I66" s="19">
+      <c r="I66" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -26945,11 +25709,11 @@
       <c r="F67">
         <v>0</v>
       </c>
-      <c r="G67" s="6" t="str">
+      <c r="G67" s="5" t="str">
         <f>IF(E67=F67,"n/a",IF(OR(C67="battery electric vehicle",C67="natural gas vehicle",C67="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I67" s="19">
+      <c r="I67" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27068,11 +25832,11 @@
       <c r="F68">
         <v>0</v>
       </c>
-      <c r="G68" s="6" t="str">
+      <c r="G68" s="5" t="str">
         <f>IF(E68=F68,"n/a",IF(OR(C68="battery electric vehicle",C68="natural gas vehicle",C68="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I68" s="19">
+      <c r="I68" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27191,11 +25955,11 @@
       <c r="F69">
         <v>1</v>
       </c>
-      <c r="G69" s="6" t="str">
+      <c r="G69" s="5" t="str">
         <f>IF(E69=F69,"n/a",IF(OR(C69="battery electric vehicle",C69="natural gas vehicle",C69="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I69" s="19">
+      <c r="I69" s="17">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -27314,11 +26078,11 @@
       <c r="F70">
         <v>0</v>
       </c>
-      <c r="G70" s="6" t="str">
+      <c r="G70" s="5" t="str">
         <f>IF(E70=F70,"n/a",IF(OR(C70="battery electric vehicle",C70="natural gas vehicle",C70="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I70" s="19">
+      <c r="I70" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27429,7 +26193,7 @@
     </row>
     <row r="71" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C71" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -27437,11 +26201,11 @@
       <c r="F71">
         <v>0</v>
       </c>
-      <c r="G71" s="6" t="str">
+      <c r="G71" s="5" t="str">
         <f>IF(E71=F71,"n/a",IF(OR(C71="battery electric vehicle",C71="natural gas vehicle",C71="plugin hybrid vehicle",C71="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I71" s="19">
+      <c r="I71" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27551,23 +26315,23 @@
       </c>
     </row>
     <row r="72" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="20"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20">
-        <v>0</v>
-      </c>
-      <c r="F72" s="20">
-        <v>0</v>
-      </c>
-      <c r="G72" s="7" t="str">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18">
+        <v>0</v>
+      </c>
+      <c r="F72" s="18">
+        <v>0</v>
+      </c>
+      <c r="G72" s="6" t="str">
         <f>IF(E72=F72,"n/a",IF(OR(C72="battery electric vehicle",C72="natural gas vehicle",C72="plugin hybrid vehicle",C72="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I72" s="19">
+      <c r="I72" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27692,11 +26456,11 @@
       <c r="F73">
         <v>0</v>
       </c>
-      <c r="G73" s="6" t="str">
+      <c r="G73" s="5" t="str">
         <f>IF(E73=F73,"n/a",IF(OR(C73="battery electric vehicle",C73="natural gas vehicle",C73="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I73" s="19">
+      <c r="I73" s="17">
         <f t="shared" ref="I73:I93" si="3">E73</f>
         <v>0</v>
       </c>
@@ -27815,11 +26579,11 @@
       <c r="F74">
         <v>0</v>
       </c>
-      <c r="G74" s="6" t="str">
+      <c r="G74" s="5" t="str">
         <f>IF(E74=F74,"n/a",IF(OR(C74="battery electric vehicle",C74="natural gas vehicle",C74="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I74" s="19">
+      <c r="I74" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -27938,11 +26702,11 @@
       <c r="F75">
         <v>0</v>
       </c>
-      <c r="G75" s="6" t="str">
+      <c r="G75" s="5" t="str">
         <f>IF(E75=F75,"n/a",IF(OR(C75="battery electric vehicle",C75="natural gas vehicle",C75="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I75" s="19">
+      <c r="I75" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28061,11 +26825,11 @@
       <c r="F76">
         <v>1</v>
       </c>
-      <c r="G76" s="6" t="str">
+      <c r="G76" s="5" t="str">
         <f>IF(E76=F76,"n/a",IF(OR(C76="battery electric vehicle",C76="natural gas vehicle",C76="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I76" s="19">
+      <c r="I76" s="17">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -28184,11 +26948,11 @@
       <c r="F77">
         <v>0</v>
       </c>
-      <c r="G77" s="6" t="str">
+      <c r="G77" s="5" t="str">
         <f>IF(E77=F77,"n/a",IF(OR(C77="battery electric vehicle",C77="natural gas vehicle",C77="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I77" s="19">
+      <c r="I77" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28299,7 +27063,7 @@
     </row>
     <row r="78" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C78" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -28307,11 +27071,11 @@
       <c r="F78">
         <v>0</v>
       </c>
-      <c r="G78" s="6" t="str">
+      <c r="G78" s="5" t="str">
         <f>IF(E78=F78,"n/a",IF(OR(C78="battery electric vehicle",C78="natural gas vehicle",C78="plugin hybrid vehicle",C78="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I78" s="19">
+      <c r="I78" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28421,23 +27185,23 @@
       </c>
     </row>
     <row r="79" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="20"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20">
-        <v>0</v>
-      </c>
-      <c r="F79" s="20">
-        <v>0</v>
-      </c>
-      <c r="G79" s="7" t="str">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18">
+        <v>0</v>
+      </c>
+      <c r="F79" s="18">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6" t="str">
         <f>IF(E79=F79,"n/a",IF(OR(C79="battery electric vehicle",C79="natural gas vehicle",C79="plugin hybrid vehicle",C79="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I79" s="19">
+      <c r="I79" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28566,119 +27330,119 @@
       </c>
       <c r="F80">
         <f>F10</f>
-        <v>0.5</v>
-      </c>
-      <c r="G80" s="6" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="G80" s="5" t="str">
         <f>IF(E80=F80,"n/a",IF(OR(C80="battery electric vehicle",C80="natural gas vehicle",C80="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="I80" s="19">
+      <c r="I80" s="17">
         <f t="shared" si="3"/>
         <v>6.6873740826300002E-2</v>
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>8.383744382909665E-2</v>
+        <v>8.3712995874888008E-2</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>9.1702346693592188E-2</v>
+        <v>9.167058838844952E-2</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>0.1028980197241021</v>
+        <v>0.10316718187336593</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.11850365652431405</v>
+        <v>0.11953255902288656</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.1396309892832005</v>
+        <v>0.14234424092873754</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.16713173544079279</v>
+        <v>0.17322731225641558</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.20115393406388254</v>
+        <v>0.21342677874098925</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.2406926533620381</v>
+        <v>0.26315903783836003</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.28343687041315002</v>
+        <v>0.32095512133954762</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.32618108746426189</v>
+        <v>0.38343687041314994</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.36571980676241744</v>
+        <v>0.44591861948675221</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.39974200538550725</v>
+        <v>0.50371470298793986</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.42724275154309949</v>
+        <v>0.55344696208531075</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.44837008430198594</v>
+        <v>0.59364642856988437</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.46397572110219792</v>
+        <v>0.62452949989756235</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.47517139413270781</v>
+        <v>0.64734118180341338</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.48303629699720335</v>
+        <v>0.66370655895293407</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.4884801436667851</v>
+        <v>0.67520315243785045</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.4922097001624065</v>
+        <v>0.68316074495141188</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.49474685632562987</v>
+        <v>0.68861245816998817</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.49646457609119271</v>
+        <v>0.69232116932877497</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.49762373988097219</v>
+        <v>0.69483206186056068</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.49840425895445883</v>
+        <v>0.69652648010108209</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.49892904198182053</v>
+        <v>0.69766741097457163</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.49928152969343076</v>
+        <v>0.69843451735049356</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.49951813142989132</v>
+        <v>0.69894976947739584</v>
       </c>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.35">
@@ -28697,11 +27461,11 @@
         <f t="shared" ref="F81" si="5">F11</f>
         <v>9.1114481822700006E-5</v>
       </c>
-      <c r="G81" s="6" t="str">
+      <c r="G81" s="5" t="str">
         <f>IF(E81=F81,"n/a",IF(OR(C81="battery electric vehicle",C81="natural gas vehicle",C81="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I81" s="19">
+      <c r="I81" s="17">
         <f t="shared" si="3"/>
         <v>9.1114481822700006E-5</v>
       </c>
@@ -28826,11 +27590,11 @@
         <f t="shared" ref="F82" si="7">F12</f>
         <v>1</v>
       </c>
-      <c r="G82" s="6" t="str">
+      <c r="G82" s="5" t="str">
         <f>IF(E82=F82,"n/a",IF(OR(C82="battery electric vehicle",C82="natural gas vehicle",C82="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I82" s="19">
+      <c r="I82" s="17">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -28955,11 +27719,11 @@
         <f t="shared" ref="F83" si="9">F13</f>
         <v>6.08023121013E-2</v>
       </c>
-      <c r="G83" s="6" t="str">
+      <c r="G83" s="5" t="str">
         <f>IF(E83=F83,"n/a",IF(OR(C83="battery electric vehicle",C83="natural gas vehicle",C83="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I83" s="19">
+      <c r="I83" s="17">
         <f t="shared" si="3"/>
         <v>6.08023121013E-2</v>
       </c>
@@ -29082,124 +27846,124 @@
       </c>
       <c r="F84">
         <f t="shared" ref="F84" si="11">F14</f>
-        <v>0.25</v>
-      </c>
-      <c r="G84" s="6" t="str">
+        <v>0.13111785993513644</v>
+      </c>
+      <c r="G84" s="5" t="str">
         <f>IF(E84=F84,"n/a",IF(OR(C84="battery electric vehicle",C84="natural gas vehicle",C84="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
-      <c r="I84" s="19">
+      <c r="I84" s="17">
         <f t="shared" si="3"/>
         <v>1.5463740197399999E-2</v>
       </c>
       <c r="J84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,J$9))</f>
-        <v>1.8928786332945334E-2</v>
+        <v>1.7172417827862912E-2</v>
       </c>
       <c r="K84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,K$9))</f>
-        <v>2.0117011297610617E-2</v>
+        <v>1.7758353292402298E-2</v>
       </c>
       <c r="L84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,L$9))</f>
-        <v>2.1701699592911895E-2</v>
+        <v>1.853979207720265E-2</v>
       </c>
       <c r="M84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,M$9))</f>
-        <v>2.3806473886134459E-2</v>
+        <v>1.9577694780751151E-2</v>
       </c>
       <c r="N84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,N$9))</f>
-        <v>2.6586827110338961E-2</v>
+        <v>2.0948737812545012E-2</v>
       </c>
       <c r="O84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,O$9))</f>
-        <v>3.0233275594225367E-2</v>
+        <v>2.2746868259102986E-2</v>
       </c>
       <c r="P84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,P$9))</f>
-        <v>3.4970753350781376E-2</v>
+        <v>2.5083005196618512E-2</v>
       </c>
       <c r="Q84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Q$9))</f>
-        <v>4.105090059697207E-2</v>
+        <v>2.8081237018963839E-2</v>
       </c>
       <c r="R84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,R$9))</f>
-        <v>4.8732958408176291E-2</v>
+        <v>3.1869400242326443E-2</v>
       </c>
       <c r="S84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,S$9))</f>
-        <v>5.8249140243472983E-2</v>
+        <v>3.6562003570919627E-2</v>
       </c>
       <c r="T84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,T$9))</f>
-        <v>6.9753071712537487E-2</v>
+        <v>4.2234802602923081E-2</v>
       </c>
       <c r="U84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,U$9))</f>
-        <v>8.3256562745812834E-2</v>
+        <v>4.8893621031060069E-2</v>
       </c>
       <c r="V84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,V$9))</f>
-        <v>9.8570184819839771E-2</v>
+        <v>5.6445048185473662E-2</v>
       </c>
       <c r="W84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,W$9))</f>
-        <v>0.11527240063540134</v>
+        <v>6.4681216313354148E-2</v>
       </c>
       <c r="X84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,X$9))</f>
-        <v>0.13273187009869999</v>
+        <v>7.3290800066268216E-2</v>
       </c>
       <c r="Y84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Y$9))</f>
-        <v>0.15019133956199868</v>
+        <v>8.1900383819182299E-2</v>
       </c>
       <c r="Z84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Z$9))</f>
-        <v>0.1668935553775602</v>
+        <v>9.0136551947062771E-2</v>
       </c>
       <c r="AA84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AA$9))</f>
-        <v>0.18220717745158715</v>
+        <v>9.7687979101476377E-2</v>
       </c>
       <c r="AB84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AB$9))</f>
-        <v>0.19571066848486252</v>
+        <v>0.10434679752961336</v>
       </c>
       <c r="AC84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AC$9))</f>
-        <v>0.20721459995392699</v>
+        <v>0.11001959656161681</v>
       </c>
       <c r="AD84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AD$9))</f>
-        <v>0.21673078178922373</v>
+        <v>0.11471219989021002</v>
       </c>
       <c r="AE84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AE$9))</f>
-        <v>0.22441283960042793</v>
+        <v>0.11850036311357261</v>
       </c>
       <c r="AF84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AF$9))</f>
-        <v>0.23049298684661862</v>
+        <v>0.12149859493591794</v>
       </c>
       <c r="AG84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AG$9))</f>
-        <v>0.23523046460317465</v>
+        <v>0.12383473187343347</v>
       </c>
       <c r="AH84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AH$9))</f>
-        <v>0.23887691308706105</v>
+        <v>0.12563286231999143</v>
       </c>
       <c r="AI84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AI$9))</f>
-        <v>0.24165726631126555</v>
+        <v>0.1270039053517853</v>
       </c>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C85" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <f t="shared" ref="D85:E85" si="12">D15</f>
@@ -29213,11 +27977,11 @@
         <f t="shared" ref="F85" si="13">F15</f>
         <v>0</v>
       </c>
-      <c r="G85" s="6" t="str">
+      <c r="G85" s="5" t="str">
         <f>IF(E85=F85,"n/a",IF(OR(C85="battery electric vehicle",C85="natural gas vehicle",C85="plugin hybrid vehicle",C85="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I85" s="19">
+      <c r="I85" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29327,10 +28091,10 @@
       </c>
     </row>
     <row r="86" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="20"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20" t="s">
-        <v>87</v>
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="D86">
         <f t="shared" ref="D86:E86" si="14">D16</f>
@@ -29344,11 +28108,11 @@
         <f t="shared" ref="F86" si="15">F16</f>
         <v>0</v>
       </c>
-      <c r="G86" s="7" t="str">
+      <c r="G86" s="6" t="str">
         <f>IF(E86=F86,"n/a",IF(OR(C86="battery electric vehicle",C86="natural gas vehicle",C86="plugin hybrid vehicle",C86="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I86" s="19">
+      <c r="I86" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29473,11 +28237,11 @@
       <c r="F87">
         <v>0</v>
       </c>
-      <c r="G87" s="6" t="str">
+      <c r="G87" s="5" t="str">
         <f>IF(E87=F87,"n/a",IF(OR(C87="battery electric vehicle",C87="natural gas vehicle",C87="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I87" s="19">
+      <c r="I87" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29596,11 +28360,11 @@
       <c r="F88">
         <v>0</v>
       </c>
-      <c r="G88" s="6" t="str">
+      <c r="G88" s="5" t="str">
         <f>IF(E88=F88,"n/a",IF(OR(C88="battery electric vehicle",C88="natural gas vehicle",C88="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I88" s="19">
+      <c r="I88" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29719,11 +28483,11 @@
       <c r="F89">
         <v>0</v>
       </c>
-      <c r="G89" s="6" t="str">
+      <c r="G89" s="5" t="str">
         <f>IF(E89=F89,"n/a",IF(OR(C89="battery electric vehicle",C89="natural gas vehicle",C89="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I89" s="19">
+      <c r="I89" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29842,11 +28606,11 @@
       <c r="F90">
         <v>0</v>
       </c>
-      <c r="G90" s="6" t="str">
+      <c r="G90" s="5" t="str">
         <f>IF(E90=F90,"n/a",IF(OR(C90="battery electric vehicle",C90="natural gas vehicle",C90="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I90" s="19">
+      <c r="I90" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29965,11 +28729,11 @@
       <c r="F91">
         <v>0</v>
       </c>
-      <c r="G91" s="6" t="str">
+      <c r="G91" s="5" t="str">
         <f>IF(E91=F91,"n/a",IF(OR(C91="battery electric vehicle",C91="natural gas vehicle",C91="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I91" s="19">
+      <c r="I91" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30080,7 +28844,7 @@
     </row>
     <row r="92" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C92" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -30088,11 +28852,11 @@
       <c r="F92">
         <v>0</v>
       </c>
-      <c r="G92" s="6" t="str">
+      <c r="G92" s="5" t="str">
         <f>IF(E92=F92,"n/a",IF(OR(C92="battery electric vehicle",C92="natural gas vehicle",C92="plugin hybrid vehicle",C92="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I92" s="19">
+      <c r="I92" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30202,23 +28966,23 @@
       </c>
     </row>
     <row r="93" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="20"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D93" s="20"/>
-      <c r="E93" s="20">
-        <v>0</v>
-      </c>
-      <c r="F93" s="20">
-        <v>0</v>
-      </c>
-      <c r="G93" s="7" t="str">
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18">
+        <v>0</v>
+      </c>
+      <c r="F93" s="18">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6" t="str">
         <f>IF(E93=F93,"n/a",IF(OR(C93="battery electric vehicle",C93="natural gas vehicle",C93="plugin hybrid vehicle",C93="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
-      <c r="I93" s="19">
+      <c r="I93" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30328,6 +29092,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D8:E8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -30339,16 +29106,16 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
     <col min="2" max="2" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -30458,12 +29225,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -30477,110 +29240,106 @@
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>7.8393597159514841E-2</v>
+        <v>7.826128265631177E-2</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>8.383744382909665E-2</v>
+        <v>8.3712995874888008E-2</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>9.1702346693592188E-2</v>
+        <v>9.167058838844952E-2</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.1028980197241021</v>
+        <v>0.10316718187336593</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.11850365652431405</v>
+        <v>0.11953255902288656</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.1396309892832005</v>
+        <v>0.14234424092873754</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.16713173544079279</v>
+        <v>0.17322731225641558</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.20115393406388254</v>
+        <v>0.21342677874098925</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.2406926533620381</v>
+        <v>0.26315903783836003</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.28343687041315002</v>
+        <v>0.32095512133954762</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.32618108746426189</v>
+        <v>0.38343687041314994</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.36571980676241744</v>
+        <v>0.44591861948675221</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.39974200538550725</v>
+        <v>0.50371470298793986</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.42724275154309949</v>
+        <v>0.55344696208531075</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.44837008430198594</v>
+        <v>0.59364642856988437</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.46397572110219792</v>
+        <v>0.62452949989756235</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.47517139413270781</v>
+        <v>0.64734118180341338</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.48303629699720335</v>
+        <v>0.66370655895293407</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.4884801436667851</v>
+        <v>0.67520315243785045</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.4922097001624065</v>
+        <v>0.68316074495141188</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.49474685632562987</v>
+        <v>0.68861245816998817</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.49646457609119271</v>
+        <v>0.69232116932877497</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.49762373988097219</v>
+        <v>0.69483206186056068</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.49840425895445883</v>
+        <v>0.69652648010108209</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.49892904198182053</v>
-      </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
+        <v>0.69766741097457163</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -30692,12 +29451,8 @@
         <f>Data!AI11</f>
         <v>9.1114481822700006E-5</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -30809,12 +29564,8 @@
         <f>Data!AI12</f>
         <v>1</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -30926,12 +29677,8 @@
         <f>Data!AI13</f>
         <v>6.08023121013E-2</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -30945,112 +29692,108 @@
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>2.3336940270317272E-2</v>
+        <v>1.9346159166299389E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>2.7240104411371674E-2</v>
+        <v>2.1270880799131281E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>3.2929173531825326E-2</v>
+        <v>2.4076264844254999E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>4.105090059697207E-2</v>
+        <v>2.8081237018963839E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>5.2308323901729806E-2</v>
+        <v>3.3632478366133998E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>6.7290130392745701E-2</v>
+        <v>4.1020281187147262E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>8.6184580636549449E-2</v>
+        <v>5.0337480210934871E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>0.10846129572320919</v>
+        <v>6.1322535895563066E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>0.13273187009869999</v>
+        <v>7.3290800066268216E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>0.15700244447419082</v>
+        <v>8.5259064236973381E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>0.17927915956085055</v>
+        <v>9.6244119921601576E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>0.19817360980465429</v>
+        <v>0.10556131894538917</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>0.2131554162956702</v>
+        <v>0.11294912176640245</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>0.22441283960042793</v>
+        <v>0.11850036311357261</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>0.23253456666557468</v>
+        <v>0.12250533528828143</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>0.23822363578602834</v>
+        <v>0.12531071933340518</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>0.24212679992708275</v>
+        <v>0.12723544096623707</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>0.24476668954419437</v>
+        <v>0.1285372188240779</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>0.24653495386445468</v>
+        <v>0.12940918230467352</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>0.24771170813627313</v>
+        <v>0.12998946136075354</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>0.24849143733752424</v>
+        <v>0.13037396009233732</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>0.24900661237439095</v>
+        <v>0.1306280023263604</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>0.24934634833070185</v>
+        <v>0.1307955323407107</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>0.2495701093559812</v>
+        <v>0.13090587299520942</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>0.2497173640510624</v>
-      </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
+        <v>0.13097848697886891</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I15</f>
@@ -31160,14 +29903,10 @@
         <f>Data!AI15</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I16</f>
@@ -31276,10 +30015,6 @@
       <c r="AB8">
         <f>Data!AI16</f>
         <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -31292,15 +30027,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -31410,20 +30145,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -31535,20 +30258,8 @@
         <f>Data!AI17</f>
         <v>0.24966973562683897</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ17</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK17</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -31660,20 +30371,8 @@
         <f>Data!AI18</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ18</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK18</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -31785,20 +30484,8 @@
         <f>Data!AI19</f>
         <v>0.67797888423399999</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ19</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK19</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -31910,20 +30597,8 @@
         <f>Data!AI20</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ20</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK20</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -32035,22 +30710,10 @@
         <f>Data!AI21</f>
         <v>4.2783868328800001E-4</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ21</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK21</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I22</f>
@@ -32160,22 +30823,10 @@
         <f>Data!AI22</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ22</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK22</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I23</f>
@@ -32283,18 +30934,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI23</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ23</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK23</f>
         <v>0</v>
       </c>
     </row>
@@ -32308,15 +30947,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -32426,20 +31065,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -32453,118 +31080,106 @@
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>0.19868613028135812</v>
+        <v>0.1915976578869496</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>0.20903281811998659</v>
+        <v>0.19868613028135812</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>0.22398101555448952</v>
+        <v>0.20903281811998659</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>0.2452597438179614</v>
+        <v>0.22398101555448952</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.27492014064673714</v>
+        <v>0.2452597438179614</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.31507518728691364</v>
+        <v>0.27492014064673714</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.36734367556228731</v>
+        <v>0.31507518728691364</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.43200697159225543</v>
+        <v>0.36734367556228731</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.5071550811823069</v>
+        <v>0.43200697159225543</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.58839562625599995</v>
+        <v>0.5071550811823069</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.669636171329693</v>
+        <v>0.58839562625599995</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.74478428091974458</v>
+        <v>0.669636171329693</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.8094475769497127</v>
+        <v>0.74478428091974458</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.86171606522508637</v>
+        <v>0.8094475769497127</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.90187111186526281</v>
+        <v>0.86171606522508637</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.93153150869403867</v>
+        <v>0.90187111186526281</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.95281023695751044</v>
+        <v>0.93153150869403867</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.96775843439201348</v>
+        <v>0.95281023695751044</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.97810512223064183</v>
+        <v>0.96775843439201348</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.98519359462505041</v>
+        <v>0.97810512223064183</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.99001576622760601</v>
+        <v>0.98519359462505041</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.99328050002472557</v>
+        <v>0.99001576622760601</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.99548363075463853</v>
+        <v>0.99328050002472557</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.99696710148694001</v>
+        <v>0.99548363075463853</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.99796451498821692</v>
-      </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ24</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK24</f>
-        <v>0</v>
+        <v>0.99696710148694001</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -32676,20 +31291,8 @@
         <f>Data!AI25</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ25</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK25</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -32801,20 +31404,8 @@
         <f>Data!AI26</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ26</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK26</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -32926,20 +31517,8 @@
         <f>Data!AI27</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ27</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK27</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -33051,22 +31630,10 @@
         <f>Data!AI28</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ28</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK28</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I29</f>
@@ -33176,22 +31743,10 @@
         <f>Data!AI29</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ29</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK29</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I30</f>
@@ -33300,18 +31855,6 @@
       <c r="AB8">
         <f>Data!AI30</f>
         <v>6.7718615476299995E-2</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ30</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK30</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -33324,15 +31867,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>88</v>
+    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="B1">
         <f>Data!I9</f>
@@ -33442,20 +31985,8 @@
         <f>Data!AI9</f>
         <v>2050</v>
       </c>
-      <c r="AC1" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD1">
-        <f>Data!AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <f>Data!AK9</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -33567,20 +32098,8 @@
         <f>Data!AI31</f>
         <v>0.49667887994904675</v>
       </c>
-      <c r="AC2" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD2">
-        <f>Data!AJ31</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <f>Data!AK31</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -33692,20 +32211,8 @@
         <f>Data!AI32</f>
         <v>0</v>
       </c>
-      <c r="AC3" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD3">
-        <f>Data!AJ32</f>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f>Data!AK32</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -33817,20 +32324,8 @@
         <f>Data!AI33</f>
         <v>0</v>
       </c>
-      <c r="AC4" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4">
-        <f>Data!AJ33</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>Data!AK33</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -33942,20 +32437,8 @@
         <f>Data!AI34</f>
         <v>1</v>
       </c>
-      <c r="AC5" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD5">
-        <f>Data!AJ34</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>Data!AK34</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -34067,22 +32550,10 @@
         <f>Data!AI35</f>
         <v>0</v>
       </c>
-      <c r="AC6" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD6">
-        <f>Data!AJ35</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>Data!AK35</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <f>Data!I36</f>
@@ -34192,22 +32663,10 @@
         <f>Data!AI36</f>
         <v>0</v>
       </c>
-      <c r="AC7" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD7">
-        <f>Data!AJ36</f>
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f>Data!AK36</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <f>Data!I37</f>
@@ -34315,18 +32774,6 @@
       </c>
       <c r="AB8">
         <f>Data!AI37</f>
-        <v>0</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>Data!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD8">
-        <f>Data!AJ37</f>
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f>Data!AK37</f>
         <v>0</v>
       </c>
     </row>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8605749-F06C-474B-994A-A4F1B91CEA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F388FF-DEA0-47BC-B60C-2D2A02D24EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="245">
   <si>
     <t>Source:</t>
   </si>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>Psgr LDVs only</t>
-  </si>
-  <si>
-    <t>Sigmoidal Curve Values for battery electric passenger HDV Technologies</t>
   </si>
   <si>
     <t>Sigmoidal Curve Values for PHEV passenger LDV Technologies</t>
@@ -776,6 +773,15 @@
   </si>
   <si>
     <t>2024 and 2025 shareweights for onroad vehicle types copied/pasted from the Python solver outputs, explained on the About page</t>
+  </si>
+  <si>
+    <t>s-curve</t>
+  </si>
+  <si>
+    <t>Sigmoidal Curve Values for battery electric/PHEV passenger HDV and freight LDV Technologies</t>
+  </si>
+  <si>
+    <t>Sigmoidal Curve Values for battery electric freight HDV Technologies</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1566,7 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1611,6 +1617,7 @@
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -1782,90 +1789,90 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Data!$I$10:$AI$10</c:f>
+              <c:f>Data!$I$17:$AI$17</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
-                <c:pt idx="0" formatCode="General">
-                  <c:v>8.2556397301899995E-2</c:v>
+                <c:pt idx="0" formatCode="0.0000">
+                  <c:v>0.139546683447</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.6873740826300002E-2</c:v>
+                  <c:v>6.2019274287835199E-2</c:v>
                 </c:pt>
-                <c:pt idx="2" formatCode="General">
-                  <c:v>7.826128265631177E-2</c:v>
+                <c:pt idx="2">
+                  <c:v>0.14191438128525985</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="General">
-                  <c:v>8.3712995874888008E-2</c:v>
+                <c:pt idx="3">
+                  <c:v>0.14301211999875416</c:v>
                 </c:pt>
-                <c:pt idx="4" formatCode="General">
-                  <c:v>9.167058838844952E-2</c:v>
+                <c:pt idx="4">
+                  <c:v>0.14457474879671367</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
-                  <c:v>0.10316718187336593</c:v>
+                <c:pt idx="5">
+                  <c:v>0.14675289542604564</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="General">
-                  <c:v>0.11953255902288656</c:v>
+                <c:pt idx="6">
+                  <c:v>0.149701729185583</c:v>
                 </c:pt>
-                <c:pt idx="7" formatCode="General">
-                  <c:v>0.14234424092873754</c:v>
+                <c:pt idx="7">
+                  <c:v>0.15354012798430811</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="General">
-                  <c:v>0.17322731225641558</c:v>
+                <c:pt idx="8">
+                  <c:v>0.15828875427890052</c:v>
                 </c:pt>
-                <c:pt idx="9" formatCode="General">
-                  <c:v>0.21342677874098925</c:v>
+                <c:pt idx="9">
+                  <c:v>0.16380734536684707</c:v>
                 </c:pt>
-                <c:pt idx="10" formatCode="General">
-                  <c:v>0.26315903783836003</c:v>
+                <c:pt idx="10">
+                  <c:v>0.1697733417235</c:v>
                 </c:pt>
-                <c:pt idx="11" formatCode="General">
-                  <c:v>0.32095512133954762</c:v>
+                <c:pt idx="11">
+                  <c:v>0.17573933808015293</c:v>
                 </c:pt>
-                <c:pt idx="12" formatCode="General">
-                  <c:v>0.38343687041314994</c:v>
+                <c:pt idx="12">
+                  <c:v>0.18125792916809949</c:v>
                 </c:pt>
-                <c:pt idx="13" formatCode="General">
-                  <c:v>0.44591861948675221</c:v>
+                <c:pt idx="13">
+                  <c:v>0.1860065554626919</c:v>
                 </c:pt>
-                <c:pt idx="14" formatCode="General">
-                  <c:v>0.50371470298793986</c:v>
+                <c:pt idx="14">
+                  <c:v>0.18984495426141701</c:v>
                 </c:pt>
-                <c:pt idx="15" formatCode="General">
-                  <c:v>0.55344696208531075</c:v>
+                <c:pt idx="15">
+                  <c:v>0.19279378802095437</c:v>
                 </c:pt>
-                <c:pt idx="16" formatCode="General">
-                  <c:v>0.59364642856988437</c:v>
+                <c:pt idx="16">
+                  <c:v>0.19497193465028634</c:v>
                 </c:pt>
-                <c:pt idx="17" formatCode="General">
-                  <c:v>0.62452949989756235</c:v>
+                <c:pt idx="17">
+                  <c:v>0.19653456344824585</c:v>
                 </c:pt>
-                <c:pt idx="18" formatCode="General">
-                  <c:v>0.64734118180341338</c:v>
+                <c:pt idx="18">
+                  <c:v>0.19763230216174016</c:v>
                 </c:pt>
-                <c:pt idx="19" formatCode="General">
-                  <c:v>0.66370655895293407</c:v>
+                <c:pt idx="19">
+                  <c:v>0.19839212352793961</c:v>
                 </c:pt>
-                <c:pt idx="20" formatCode="General">
-                  <c:v>0.67520315243785045</c:v>
+                <c:pt idx="20">
+                  <c:v>0.19891267395557297</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="General">
-                  <c:v>0.68316074495141188</c:v>
+                <c:pt idx="21">
+                  <c:v>0.1992667958806032</c:v>
                 </c:pt>
-                <c:pt idx="22" formatCode="General">
-                  <c:v>0.68861245816998817</c:v>
+                <c:pt idx="22">
+                  <c:v>0.19950654550219166</c:v>
                 </c:pt>
-                <c:pt idx="23" formatCode="General">
-                  <c:v>0.69232116932877497</c:v>
+                <c:pt idx="23">
+                  <c:v>0.19966833503592715</c:v>
                 </c:pt>
-                <c:pt idx="24" formatCode="General">
-                  <c:v>0.69483206186056068</c:v>
+                <c:pt idx="24">
+                  <c:v>0.19977727547910223</c:v>
                 </c:pt>
-                <c:pt idx="25" formatCode="General">
-                  <c:v>0.69652648010108209</c:v>
+                <c:pt idx="25">
+                  <c:v>0.19985052172959569</c:v>
                 </c:pt>
-                <c:pt idx="26" formatCode="General">
-                  <c:v>0.69766741097457163</c:v>
+                <c:pt idx="26">
+                  <c:v>0.19989971997320177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1873,7 +1880,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1230-40DF-9F66-E05480D5A222}"/>
+              <c16:uniqueId val="{00000000-6F5C-4075-B5DD-84C402E7BA4C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1886,11 +1893,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1816859439"/>
-        <c:axId val="1816857039"/>
+        <c:axId val="668187728"/>
+        <c:axId val="668186768"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1816859439"/>
+        <c:axId val="668187728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1932,7 +1939,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1816857039"/>
+        <c:crossAx val="668186768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1940,671 +1947,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1816857039"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1816859439"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Data!$I$10:$AI$10</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="27"/>
-                <c:pt idx="0" formatCode="General">
-                  <c:v>8.2556397301899995E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.6873740826300002E-2</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="General">
-                  <c:v>7.826128265631177E-2</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="General">
-                  <c:v>8.3712995874888008E-2</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="General">
-                  <c:v>9.167058838844952E-2</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="General">
-                  <c:v>0.10316718187336593</c:v>
-                </c:pt>
-                <c:pt idx="6" formatCode="General">
-                  <c:v>0.11953255902288656</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="General">
-                  <c:v>0.14234424092873754</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="General">
-                  <c:v>0.17322731225641558</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="General">
-                  <c:v>0.21342677874098925</c:v>
-                </c:pt>
-                <c:pt idx="10" formatCode="General">
-                  <c:v>0.26315903783836003</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="General">
-                  <c:v>0.32095512133954762</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="General">
-                  <c:v>0.38343687041314994</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="General">
-                  <c:v>0.44591861948675221</c:v>
-                </c:pt>
-                <c:pt idx="14" formatCode="General">
-                  <c:v>0.50371470298793986</c:v>
-                </c:pt>
-                <c:pt idx="15" formatCode="General">
-                  <c:v>0.55344696208531075</c:v>
-                </c:pt>
-                <c:pt idx="16" formatCode="General">
-                  <c:v>0.59364642856988437</c:v>
-                </c:pt>
-                <c:pt idx="17" formatCode="General">
-                  <c:v>0.62452949989756235</c:v>
-                </c:pt>
-                <c:pt idx="18" formatCode="General">
-                  <c:v>0.64734118180341338</c:v>
-                </c:pt>
-                <c:pt idx="19" formatCode="General">
-                  <c:v>0.66370655895293407</c:v>
-                </c:pt>
-                <c:pt idx="20" formatCode="General">
-                  <c:v>0.67520315243785045</c:v>
-                </c:pt>
-                <c:pt idx="21" formatCode="General">
-                  <c:v>0.68316074495141188</c:v>
-                </c:pt>
-                <c:pt idx="22" formatCode="General">
-                  <c:v>0.68861245816998817</c:v>
-                </c:pt>
-                <c:pt idx="23" formatCode="General">
-                  <c:v>0.69232116932877497</c:v>
-                </c:pt>
-                <c:pt idx="24" formatCode="General">
-                  <c:v>0.69483206186056068</c:v>
-                </c:pt>
-                <c:pt idx="25" formatCode="General">
-                  <c:v>0.69652648010108209</c:v>
-                </c:pt>
-                <c:pt idx="26" formatCode="General">
-                  <c:v>0.69766741097457163</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D518-4511-B460-901F646D145D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="923539568"/>
-        <c:axId val="923543408"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="923539568"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="923543408"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="923543408"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="923539568"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Data!$I$17:$AI$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
-                <c:pt idx="0" formatCode="0.0000">
-                  <c:v>6.8939837381399999E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4745205504305832E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.8423498834078463E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.3701949678448984E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.1143927768198666E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.1378831028600141E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.498427054307533E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7.2275261295201787E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9.3037067519099306E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.11633204730802928</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.14056193643011078</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.16385691621904069</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.18461872244293825</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.20190971319506468</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.21551515270953986</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.22575005596994135</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.23319203405969108</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.23847048490406159</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.24214877823383418</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.24468053139197088</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.24640834401092193</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.24758065709350957</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.24837292767436264</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.2489069289438185</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.24926620483188039</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.24950763242856416</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.24966973562683897</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F30E-4BD2-B33A-A6ADED84FF48}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1977182063"/>
-        <c:axId val="1977177743"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1977182063"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1977177743"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1977177743"/>
+        <c:axId val="668186768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2655,7 +1998,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1977182063"/>
+        <c:crossAx val="668187728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2712,86 +2055,6 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3347,1059 +2610,27 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>549275</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>68262</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>74612</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>65087</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>377825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>77787</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49F34C9D-339F-C44A-5F03-4E2DBC4643D0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3014761-5676-B4FA-B42B-342FE5A0C169}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4412,78 +2643,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>454025</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFC3E1CE-A994-5088-23EF-4F5448BC6C19}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>141287</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>144462</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{041161B1-360C-8F9B-5FDE-99B5D57E1D74}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4795,31 +2954,31 @@
         <v>0</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -4839,7 +2998,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -4862,32 +3021,32 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -4898,72 +3057,72 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.35">
@@ -12459,7 +10618,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B2" s="3">
         <f>'AEO Table 38'!F64*1000</f>
@@ -12574,13 +10733,13 @@
     </row>
     <row r="4" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="28" t="s">
         <v>214</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
@@ -12624,17 +10783,17 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
@@ -12737,12 +10896,12 @@
         <v>2050</v>
       </c>
       <c r="AG5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.35">
@@ -12755,10 +10914,10 @@
         <v>45</v>
       </c>
       <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
         <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
       </c>
       <c r="D8" t="s">
         <v>46</v>
@@ -12853,10 +11012,10 @@
         <v>47</v>
       </c>
       <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
         <v>93</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
       </c>
       <c r="D9" t="s">
         <v>46</v>
@@ -12951,10 +11110,10 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
         <v>95</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -13054,10 +11213,10 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
         <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
       </c>
       <c r="D12" t="s">
         <v>46</v>
@@ -13149,13 +11308,13 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
         <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>46</v>
@@ -13247,13 +11406,13 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" t="s">
         <v>101</v>
-      </c>
-      <c r="C14" t="s">
-        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
@@ -13345,13 +11504,13 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
         <v>103</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -13443,13 +11602,13 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
         <v>105</v>
-      </c>
-      <c r="C16" t="s">
-        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>46</v>
@@ -13541,13 +11700,13 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
         <v>107</v>
-      </c>
-      <c r="C17" t="s">
-        <v>108</v>
       </c>
       <c r="D17" t="s">
         <v>46</v>
@@ -13642,10 +11801,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
         <v>109</v>
-      </c>
-      <c r="C18" t="s">
-        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
@@ -13740,10 +11899,10 @@
         <v>52</v>
       </c>
       <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
         <v>111</v>
-      </c>
-      <c r="C19" t="s">
-        <v>112</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
@@ -13838,10 +11997,10 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
         <v>113</v>
-      </c>
-      <c r="C20" t="s">
-        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>46</v>
@@ -13936,10 +12095,10 @@
         <v>54</v>
       </c>
       <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
         <v>115</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
@@ -14034,10 +12193,10 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" t="s">
         <v>117</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
       </c>
       <c r="D22" t="s">
         <v>46</v>
@@ -14132,10 +12291,10 @@
         <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>46</v>
@@ -14230,10 +12389,10 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" t="s">
         <v>120</v>
-      </c>
-      <c r="C24" t="s">
-        <v>121</v>
       </c>
       <c r="D24" t="s">
         <v>46</v>
@@ -14328,10 +12487,10 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
         <v>122</v>
-      </c>
-      <c r="C25" t="s">
-        <v>123</v>
       </c>
       <c r="D25" t="s">
         <v>46</v>
@@ -14426,10 +12585,10 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
         <v>124</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
       </c>
       <c r="D26" t="s">
         <v>46</v>
@@ -14521,16 +12680,16 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
         <v>126</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>127</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>128</v>
-      </c>
-      <c r="D27" t="s">
-        <v>129</v>
       </c>
       <c r="F27">
         <v>28.763452999999998</v>
@@ -14619,13 +12778,13 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" t="s">
         <v>130</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>131</v>
-      </c>
-      <c r="C28" t="s">
-        <v>132</v>
       </c>
       <c r="D28" t="s">
         <v>46</v>
@@ -14717,7 +12876,7 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.35">
@@ -14730,10 +12889,10 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" t="s">
         <v>134</v>
-      </c>
-      <c r="C31" t="s">
-        <v>135</v>
       </c>
       <c r="D31" t="s">
         <v>46</v>
@@ -14828,10 +12987,10 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" t="s">
         <v>136</v>
-      </c>
-      <c r="C32" t="s">
-        <v>137</v>
       </c>
       <c r="D32" t="s">
         <v>46</v>
@@ -14926,10 +13085,10 @@
         <v>61</v>
       </c>
       <c r="B33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" t="s">
         <v>138</v>
-      </c>
-      <c r="C33" t="s">
-        <v>139</v>
       </c>
       <c r="D33" t="s">
         <v>46</v>
@@ -15029,10 +13188,10 @@
         <v>50</v>
       </c>
       <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
         <v>140</v>
-      </c>
-      <c r="C35" t="s">
-        <v>141</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
@@ -15124,13 +13283,13 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
         <v>142</v>
-      </c>
-      <c r="C36" t="s">
-        <v>143</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
@@ -15222,13 +13381,13 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
         <v>144</v>
-      </c>
-      <c r="C37" t="s">
-        <v>145</v>
       </c>
       <c r="D37" t="s">
         <v>46</v>
@@ -15320,13 +13479,13 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" t="s">
         <v>146</v>
-      </c>
-      <c r="C38" t="s">
-        <v>147</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -15418,13 +13577,13 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" t="s">
         <v>148</v>
-      </c>
-      <c r="C39" t="s">
-        <v>149</v>
       </c>
       <c r="D39" t="s">
         <v>46</v>
@@ -15516,13 +13675,13 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" t="s">
         <v>150</v>
-      </c>
-      <c r="C40" t="s">
-        <v>151</v>
       </c>
       <c r="D40" t="s">
         <v>46</v>
@@ -15617,10 +13776,10 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" t="s">
         <v>152</v>
-      </c>
-      <c r="C41" t="s">
-        <v>153</v>
       </c>
       <c r="D41" t="s">
         <v>46</v>
@@ -15715,10 +13874,10 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" t="s">
         <v>154</v>
-      </c>
-      <c r="C42" t="s">
-        <v>155</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
@@ -15813,10 +13972,10 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" t="s">
         <v>156</v>
-      </c>
-      <c r="C43" t="s">
-        <v>157</v>
       </c>
       <c r="D43" t="s">
         <v>46</v>
@@ -15911,10 +14070,10 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" t="s">
         <v>158</v>
-      </c>
-      <c r="C44" t="s">
-        <v>159</v>
       </c>
       <c r="D44" t="s">
         <v>46</v>
@@ -16009,10 +14168,10 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
         <v>160</v>
-      </c>
-      <c r="C45" t="s">
-        <v>161</v>
       </c>
       <c r="D45" t="s">
         <v>46</v>
@@ -16107,10 +14266,10 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" t="s">
         <v>162</v>
-      </c>
-      <c r="C46" t="s">
-        <v>163</v>
       </c>
       <c r="D46" t="s">
         <v>46</v>
@@ -16205,10 +14364,10 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" t="s">
         <v>164</v>
-      </c>
-      <c r="C47" t="s">
-        <v>165</v>
       </c>
       <c r="D47" t="s">
         <v>46</v>
@@ -16303,10 +14462,10 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" t="s">
         <v>166</v>
-      </c>
-      <c r="C48" t="s">
-        <v>167</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
@@ -16401,10 +14560,10 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" t="s">
         <v>168</v>
-      </c>
-      <c r="C49" t="s">
-        <v>169</v>
       </c>
       <c r="D49" t="s">
         <v>46</v>
@@ -16496,16 +14655,16 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" t="s">
         <v>170</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>171</v>
       </c>
-      <c r="C50" t="s">
-        <v>172</v>
-      </c>
       <c r="D50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F50">
         <v>16.388839999999998</v>
@@ -16594,13 +14753,13 @@
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" t="s">
         <v>173</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>174</v>
-      </c>
-      <c r="C51" t="s">
-        <v>175</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
@@ -16692,16 +14851,16 @@
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" t="s">
         <v>176</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>177</v>
       </c>
-      <c r="C52" t="s">
-        <v>178</v>
-      </c>
       <c r="D52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F52">
         <v>21.225769</v>
@@ -16790,13 +14949,13 @@
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" t="s">
         <v>179</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>180</v>
-      </c>
-      <c r="C53" t="s">
-        <v>181</v>
       </c>
       <c r="D53" t="s">
         <v>46</v>
@@ -16888,13 +15047,13 @@
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" t="s">
         <v>182</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>183</v>
-      </c>
-      <c r="C54" t="s">
-        <v>184</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
@@ -16997,10 +15156,10 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" t="s">
         <v>185</v>
-      </c>
-      <c r="C56" t="s">
-        <v>186</v>
       </c>
       <c r="D56" t="s">
         <v>46</v>
@@ -17095,10 +15254,10 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" t="s">
         <v>187</v>
-      </c>
-      <c r="C57" t="s">
-        <v>188</v>
       </c>
       <c r="D57" t="s">
         <v>46</v>
@@ -17193,10 +15352,10 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" t="s">
         <v>189</v>
-      </c>
-      <c r="C58" t="s">
-        <v>190</v>
       </c>
       <c r="D58" t="s">
         <v>46</v>
@@ -17291,10 +15450,10 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" t="s">
         <v>191</v>
-      </c>
-      <c r="C59" t="s">
-        <v>192</v>
       </c>
       <c r="D59" t="s">
         <v>46</v>
@@ -17389,10 +15548,10 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" t="s">
         <v>193</v>
-      </c>
-      <c r="C60" t="s">
-        <v>194</v>
       </c>
       <c r="D60" t="s">
         <v>46</v>
@@ -17487,10 +15646,10 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" t="s">
         <v>195</v>
-      </c>
-      <c r="C61" t="s">
-        <v>196</v>
       </c>
       <c r="D61" t="s">
         <v>46</v>
@@ -17585,10 +15744,10 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
+        <v>196</v>
+      </c>
+      <c r="C62" t="s">
         <v>197</v>
-      </c>
-      <c r="C62" t="s">
-        <v>198</v>
       </c>
       <c r="D62" t="s">
         <v>46</v>
@@ -17683,10 +15842,10 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
+        <v>198</v>
+      </c>
+      <c r="C63" t="s">
         <v>199</v>
-      </c>
-      <c r="C63" t="s">
-        <v>200</v>
       </c>
       <c r="D63" t="s">
         <v>46</v>
@@ -17778,13 +15937,13 @@
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>200</v>
+      </c>
+      <c r="B64" t="s">
         <v>201</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>202</v>
-      </c>
-      <c r="C64" t="s">
-        <v>203</v>
       </c>
       <c r="D64" t="s">
         <v>46</v>
@@ -17876,13 +16035,13 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>203</v>
+      </c>
+      <c r="B65" t="s">
         <v>204</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>205</v>
-      </c>
-      <c r="C65" t="s">
-        <v>206</v>
       </c>
       <c r="D65" t="s">
         <v>46</v>
@@ -17974,13 +16133,13 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>206</v>
+      </c>
+      <c r="B66" t="s">
         <v>207</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>208</v>
-      </c>
-      <c r="C66" t="s">
-        <v>209</v>
       </c>
       <c r="D66" t="s">
         <v>46</v>
@@ -18072,13 +16231,13 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>209</v>
+      </c>
+      <c r="B67" t="s">
         <v>210</v>
       </c>
-      <c r="B67" t="s">
-        <v>211</v>
-      </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D67" t="s">
         <v>46</v>
@@ -18209,15 +16368,15 @@
       <c r="O1" s="12"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="11" t="s">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="R1" s="12"/>
       <c r="T1" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U1" s="12"/>
       <c r="W1" s="11" t="s">
-        <v>38</v>
+        <v>243</v>
       </c>
       <c r="X1" s="12"/>
     </row>
@@ -18276,13 +16435,13 @@
         <v>24</v>
       </c>
       <c r="R3" s="14">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="T3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="U3" s="14">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="W3" s="7" t="s">
         <v>24</v>
@@ -18311,7 +16470,7 @@
         <v>25</v>
       </c>
       <c r="R4" s="15">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="T4" s="8" t="s">
         <v>25</v>
@@ -18323,7 +16482,7 @@
         <v>25</v>
       </c>
       <c r="X4" s="15">
-        <v>-10.5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
@@ -18370,7 +16529,7 @@
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="22"/>
@@ -19049,35 +17208,35 @@
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>1.9346159166299389E-2</v>
+        <v>1.9993417391351978E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>2.1270880799131281E-2</v>
+        <v>2.2093517300674829E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>2.4076264844254999E-2</v>
+        <v>2.5083005196618505E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>2.8081237018963839E-2</v>
+        <v>2.9250049214034041E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>3.3632478366133998E-2</v>
+        <v>3.4891505996859425E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>4.1020281187147262E-2</v>
+        <v>4.2234802602923074E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>5.0337480210934871E-2</v>
+        <v>5.1319468678820979E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>6.1322535895563066E-2</v>
+        <v>6.1877165606985654E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
@@ -19085,67 +17244,67 @@
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>8.5259064236973381E-2</v>
+        <v>8.4704434525550779E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>9.6244119921601576E-2</v>
+        <v>9.5262131453715468E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>0.10556131894538917</v>
+        <v>0.10434679752961337</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>0.11294912176640245</v>
+        <v>0.11169009413567701</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>0.11850036311357261</v>
+        <v>0.11733155091850239</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>0.12250533528828143</v>
+        <v>0.12149859493591794</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>0.12531071933340518</v>
+        <v>0.12448808283186162</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>0.12723544096623707</v>
+        <v>0.12658818274118447</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>0.1285372188240779</v>
+        <v>0.12804180805533377</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>0.12940918230467352</v>
+        <v>0.12903768065455262</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>0.12998946136075354</v>
+        <v>0.12971515646323384</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>0.13037396009233732</v>
+        <v>0.13017382495362109</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>0.1306280023263604</v>
+        <v>0.13048334686530239</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>0.1307955323407107</v>
+        <v>0.13069176241266453</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>0.13090587299520942</v>
+        <v>0.1308318908805127</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>0.13097848697886891</v>
+        <v>0.13092601275638885</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
@@ -19415,125 +17574,125 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>9.2058503875700002E-3</v>
-      </c>
-      <c r="E17" s="17">
-        <v>6.8939837381399999E-3</v>
+        <v>0.139546683447</v>
+      </c>
+      <c r="E17">
+        <v>5.8249127235400003E-2</v>
       </c>
       <c r="F17">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G17" s="5" t="str">
         <f>IF(E17=F17,"n/a",IF(OR(C17="battery electric vehicle",C17="natural gas vehicle",C17="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
       <c r="I17" s="17">
-        <f t="shared" si="1"/>
-        <v>6.8939837381399999E-3</v>
+        <f>D17</f>
+        <v>0.139546683447</v>
       </c>
       <c r="J17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:J$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,J$9))</f>
-        <v>1.4745205504305832E-2</v>
-      </c>
-      <c r="K17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,K$9))</f>
-        <v>1.8423498834078463E-2</v>
-      </c>
-      <c r="L17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,L$9))</f>
-        <v>2.3701949678448984E-2</v>
-      </c>
-      <c r="M17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,M$9))</f>
-        <v>3.1143927768198666E-2</v>
-      </c>
-      <c r="N17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,N$9))</f>
-        <v>4.1378831028600141E-2</v>
-      </c>
-      <c r="O17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,O$9))</f>
-        <v>5.498427054307533E-2</v>
-      </c>
-      <c r="P17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,P$9))</f>
-        <v>7.2275261295201787E-2</v>
-      </c>
-      <c r="Q17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>9.3037067519099306E-2</v>
-      </c>
-      <c r="R17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.11633204730802928</v>
-      </c>
-      <c r="S17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.14056193643011078</v>
-      </c>
-      <c r="T17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.16385691621904069</v>
-      </c>
-      <c r="U17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.18461872244293825</v>
-      </c>
-      <c r="V17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.20190971319506468</v>
-      </c>
-      <c r="W17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.21551515270953986</v>
-      </c>
-      <c r="X17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.22575005596994135</v>
-      </c>
-      <c r="Y17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.23319203405969108</v>
-      </c>
-      <c r="Z17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.23847048490406159</v>
-      </c>
-      <c r="AA17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.24214877823383418</v>
-      </c>
-      <c r="AB17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.24468053139197088</v>
-      </c>
-      <c r="AC17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.24640834401092193</v>
-      </c>
-      <c r="AD17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.24758065709350957</v>
-      </c>
-      <c r="AE17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.24837292767436264</v>
-      </c>
-      <c r="AF17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.2489069289438185</v>
-      </c>
-      <c r="AG17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.24926620483188039</v>
-      </c>
-      <c r="AH17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.24950763242856416</v>
-      </c>
-      <c r="AI17">
-        <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.24966973562683897</v>
+        <v>6.2019274287835199E-2</v>
+      </c>
+      <c r="K17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,K$9))</f>
+        <v>0.14191438128525985</v>
+      </c>
+      <c r="L17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,L$9))</f>
+        <v>0.14301211999875416</v>
+      </c>
+      <c r="M17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,M$9))</f>
+        <v>0.14457474879671367</v>
+      </c>
+      <c r="N17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,N$9))</f>
+        <v>0.14675289542604564</v>
+      </c>
+      <c r="O17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,O$9))</f>
+        <v>0.149701729185583</v>
+      </c>
+      <c r="P17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,P$9))</f>
+        <v>0.15354012798430811</v>
+      </c>
+      <c r="Q17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Q$9))</f>
+        <v>0.15828875427890052</v>
+      </c>
+      <c r="R17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,R$9))</f>
+        <v>0.16380734536684707</v>
+      </c>
+      <c r="S17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,S$9))</f>
+        <v>0.1697733417235</v>
+      </c>
+      <c r="T17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,T$9))</f>
+        <v>0.17573933808015293</v>
+      </c>
+      <c r="U17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,U$9))</f>
+        <v>0.18125792916809949</v>
+      </c>
+      <c r="V17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,V$9))</f>
+        <v>0.1860065554626919</v>
+      </c>
+      <c r="W17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,W$9))</f>
+        <v>0.18984495426141701</v>
+      </c>
+      <c r="X17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,X$9))</f>
+        <v>0.19279378802095437</v>
+      </c>
+      <c r="Y17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Y$9))</f>
+        <v>0.19497193465028634</v>
+      </c>
+      <c r="Z17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Z$9))</f>
+        <v>0.19653456344824585</v>
+      </c>
+      <c r="AA17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AA$9))</f>
+        <v>0.19763230216174016</v>
+      </c>
+      <c r="AB17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AB$9))</f>
+        <v>0.19839212352793961</v>
+      </c>
+      <c r="AC17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AC$9))</f>
+        <v>0.19891267395557297</v>
+      </c>
+      <c r="AD17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AD$9))</f>
+        <v>0.1992667958806032</v>
+      </c>
+      <c r="AE17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AE$9))</f>
+        <v>0.19950654550219166</v>
+      </c>
+      <c r="AF17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AF$9))</f>
+        <v>0.19966833503592715</v>
+      </c>
+      <c r="AG17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AG$9))</f>
+        <v>0.19977727547910223</v>
+      </c>
+      <c r="AH17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AH$9))</f>
+        <v>0.19985052172959569</v>
+      </c>
+      <c r="AI17" s="30">
+        <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AI$9))</f>
+        <v>0.19989971997320177</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.35">
@@ -19543,7 +17702,7 @@
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" s="17">
@@ -19554,11 +17713,11 @@
         <v>32</v>
       </c>
       <c r="I18" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,J$9))</f>
+        <f t="shared" ref="I18:I23" si="2">D18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="17">
+        <f t="shared" ref="J18:J23" si="3">E18</f>
         <v>0</v>
       </c>
       <c r="K18">
@@ -19669,7 +17828,7 @@
       <c r="D19">
         <v>0.72915442924999996</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19">
         <v>0.67797888423399999</v>
       </c>
       <c r="F19" s="17">
@@ -19681,11 +17840,11 @@
         <v>n/a</v>
       </c>
       <c r="I19" s="17">
-        <f t="shared" si="1"/>
-        <v>0.67797888423399999</v>
-      </c>
-      <c r="J19">
-        <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="2"/>
+        <v>0.72915442924999996</v>
+      </c>
+      <c r="J19" s="17">
+        <f t="shared" si="3"/>
         <v>0.67797888423399999</v>
       </c>
       <c r="K19">
@@ -19796,7 +17955,7 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" s="27">
@@ -19807,11 +17966,11 @@
         <v>n/a</v>
       </c>
       <c r="I20" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <f>IF($G20="s-curve",$E20+($F20-$E20)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E20:$F20,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J20" s="17">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K20">
@@ -19922,124 +18081,123 @@
       <c r="D21">
         <v>0</v>
       </c>
-      <c r="E21" s="17">
-        <v>4.2783868328800001E-4</v>
+      <c r="E21">
+        <v>6.4220413235999997E-4</v>
       </c>
       <c r="F21" s="17">
-        <f>E21</f>
-        <v>4.2783868328800001E-4</v>
-      </c>
-      <c r="G21" s="5" t="str">
-        <f>IF(E21=F21,"n/a",IF(OR(C21="battery electric vehicle",C21="natural gas vehicle",C21="plugin hybrid vehicle"),"s-curve","linear"))</f>
-        <v>n/a</v>
+        <f>E21/E17*F17</f>
+        <v>2.2050257672177119E-3</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="I21" s="17">
-        <f t="shared" si="1"/>
-        <v>4.2783868328800001E-4</v>
-      </c>
-      <c r="J21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,J$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="17">
+        <f t="shared" si="3"/>
+        <v>6.4220413235999997E-4</v>
       </c>
       <c r="K21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
+        <v>7.034131712916232E-4</v>
       </c>
       <c r="L21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
+        <v>7.3179159465514107E-4</v>
       </c>
       <c r="M21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
+        <v>7.7218822187015597E-4</v>
       </c>
       <c r="N21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
+        <v>8.284970378344221E-4</v>
       </c>
       <c r="O21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
+        <v>9.0472943433103864E-4</v>
       </c>
       <c r="P21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
+        <v>1.0039586086411079E-3</v>
       </c>
       <c r="Q21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
+        <v>1.126718720611755E-3</v>
       </c>
       <c r="R21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
+        <v>1.2693837394716313E-3</v>
       </c>
       <c r="S21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
+        <v>1.4236149497888558E-3</v>
       </c>
       <c r="T21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
+        <v>1.5778461601060802E-3</v>
       </c>
       <c r="U21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
+        <v>1.7205111789659567E-3</v>
       </c>
       <c r="V21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
+        <v>1.8432712909366039E-3</v>
       </c>
       <c r="W21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
+        <v>1.942500465246673E-3</v>
       </c>
       <c r="X21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
+        <v>2.0187328617432897E-3</v>
       </c>
       <c r="Y21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
+        <v>2.075041677707556E-3</v>
       </c>
       <c r="Z21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
+        <v>2.1154383049225706E-3</v>
       </c>
       <c r="AA21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
+        <v>2.1438167282860888E-3</v>
       </c>
       <c r="AB21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
+        <v>2.163459410233614E-3</v>
       </c>
       <c r="AC21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
+        <v>2.1769165291598619E-3</v>
       </c>
       <c r="AD21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
+        <v>2.1860711866273229E-3</v>
       </c>
       <c r="AE21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
+        <v>2.1922691244234882E-3</v>
       </c>
       <c r="AF21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
+        <v>2.1964516606023544E-3</v>
       </c>
       <c r="AG21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
+        <v>2.1992679573948674E-3</v>
       </c>
       <c r="AH21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
+        <v>2.2011614982536728E-3</v>
       </c>
       <c r="AI21">
-        <f>IF($G21="s-curve",$E21+($F21-$E21)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
-        <v>4.2783868328800001E-4</v>
+        <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
+        <v>2.2024333570016897E-3</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.35">
@@ -20049,7 +18207,7 @@
       <c r="D22">
         <v>0</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22">
         <v>0</v>
       </c>
       <c r="F22" s="17">
@@ -20061,11 +18219,11 @@
         <v>n/a</v>
       </c>
       <c r="I22" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K22">
@@ -20175,10 +18333,10 @@
       <c r="C23" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="18">
-        <v>0</v>
-      </c>
-      <c r="E23" s="21">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" s="21">
@@ -20190,11 +18348,11 @@
         <v>n/a</v>
       </c>
       <c r="I23" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K23">
@@ -20309,13 +18467,13 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0.154617049501</v>
-      </c>
-      <c r="E24" s="17">
-        <v>0.17679125251200001</v>
+        <v>3.0938506857799999E-2</v>
+      </c>
+      <c r="E24">
+        <v>3.0393141812799999E-2</v>
       </c>
       <c r="F24" s="27">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G24" s="5" t="str">
         <f>IF(E24=F24,"n/a",IF(OR(C24="battery electric vehicle",C24="natural gas vehicle",C24="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -20323,111 +18481,111 @@
       </c>
       <c r="I24" s="17">
         <f>D24</f>
-        <v>0.154617049501</v>
+        <v>3.0938506857799999E-2</v>
       </c>
       <c r="J24" s="17">
         <f>E24</f>
-        <v>0.17679125251200001</v>
+        <v>3.0393141812799999E-2</v>
       </c>
       <c r="K24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>0.1915976578869496</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
+        <v>5.6618778403372177E-2</v>
       </c>
       <c r="L24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>0.19868613028135812</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
+        <v>6.8777803134611903E-2</v>
       </c>
       <c r="M24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>0.20903281811998659</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
+        <v>8.608614979905288E-2</v>
       </c>
       <c r="N24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>0.22398101555448952</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
+        <v>0.11021223591476392</v>
       </c>
       <c r="O24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.2452597438179614</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
+        <v>0.14287478317648508</v>
       </c>
       <c r="P24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.27492014064673714</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
+        <v>0.18539053428222468</v>
       </c>
       <c r="Q24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.31507518728691364</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
+        <v>0.2379883554627959</v>
       </c>
       <c r="R24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.36734367556228731</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
+        <v>0.29911463687665474</v>
       </c>
       <c r="S24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.43200697159225543</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
+        <v>0.36519657090640001</v>
       </c>
       <c r="T24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.5071550811823069</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
+        <v>0.43127850493614522</v>
       </c>
       <c r="U24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.58839562625599995</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
+        <v>0.49240478635000412</v>
       </c>
       <c r="V24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.669636171329693</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
+        <v>0.54500260753057528</v>
       </c>
       <c r="W24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.74478428091974458</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
+        <v>0.58751835863631485</v>
       </c>
       <c r="X24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.8094475769497127</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
+        <v>0.62018090589803598</v>
       </c>
       <c r="Y24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.86171606522508637</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
+        <v>0.64430699201374708</v>
       </c>
       <c r="Z24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.90187111186526281</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
+        <v>0.66161533867818811</v>
       </c>
       <c r="AA24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.93153150869403867</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
+        <v>0.67377436340942776</v>
       </c>
       <c r="AB24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.95281023695751044</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
+        <v>0.68219047069376959</v>
       </c>
       <c r="AC24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.96775843439201348</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
+        <v>0.68795631045658845</v>
       </c>
       <c r="AD24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.97810512223064183</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
+        <v>0.69187871675545232</v>
       </c>
       <c r="AE24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.98519359462505041</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
+        <v>0.69453428637540304</v>
       </c>
       <c r="AF24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.99001576622760601</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
+        <v>0.69632633663086296</v>
       </c>
       <c r="AG24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.99328050002472557</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
+        <v>0.6975330076961308</v>
       </c>
       <c r="AH24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.99548363075463853</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
+        <v>0.69834431457660484</v>
       </c>
       <c r="AI24">
-        <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.99696710148694001</v>
+        <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
+        <v>0.69888925542034686</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.35">
@@ -20437,7 +18595,7 @@
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" s="17">
@@ -20449,11 +18607,11 @@
         <v>n/a</v>
       </c>
       <c r="I25" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,J$9))</f>
+        <f t="shared" ref="I25:I30" si="4">D25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="17">
+        <f t="shared" ref="J25:J30" si="5">E25</f>
         <v>0</v>
       </c>
       <c r="K25">
@@ -20564,7 +18722,7 @@
       <c r="D26">
         <v>0</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" s="17">
@@ -20576,11 +18734,11 @@
         <v>n/a</v>
       </c>
       <c r="I26" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="17">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K26">
@@ -20702,11 +18860,11 @@
         <v>n/a</v>
       </c>
       <c r="I27" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <f>IF($G27="s-curve",$E27+($F27-$E27)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E27:$F27,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="17">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K27">
@@ -20817,7 +18975,7 @@
       <c r="D28">
         <v>0</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" s="17">
@@ -20829,11 +18987,11 @@
         <v>n/a</v>
       </c>
       <c r="I28" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <f>IF($G28="s-curve",$E28+($F28-$E28)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E28:$F28,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="17">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K28">
@@ -20944,7 +19102,7 @@
       <c r="D29">
         <v>0</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" s="17">
@@ -20956,11 +19114,11 @@
         <v>n/a</v>
       </c>
       <c r="I29" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="17">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K29">
@@ -21070,127 +19228,127 @@
       <c r="C30" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="18">
-        <v>5.0287437714699998E-2</v>
-      </c>
-      <c r="E30" s="21">
-        <v>6.7718615476299995E-2</v>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
       </c>
       <c r="F30" s="21">
         <f>E30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="str">
         <f>IF(E30=F30,"n/a",IF(OR(C30="battery electric vehicle",C30="natural gas vehicle",C30="plugin hybrid vehicle",C30="hydrogen vehicle"),"s-curve","linear"))</f>
         <v>n/a</v>
       </c>
       <c r="I30" s="17">
-        <f t="shared" si="1"/>
-        <v>6.7718615476299995E-2</v>
-      </c>
-      <c r="J30">
-        <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,J$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,K$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,L$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="M30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,M$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="N30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,N$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,O$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,P$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Q$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="R30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,R$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,S$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,T$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="U30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,U$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,V$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="W30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,W$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="X30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,X$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="Y30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Y$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="Z30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Z$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AA30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AA$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AB30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AB$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AC30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AC$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AD$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AE30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AE$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AF30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AF$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AG30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AG$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AH30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AH$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AI30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AI$9))</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.35">
@@ -21204,125 +19362,125 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>2.7710514836400001E-3</v>
-      </c>
-      <c r="E31" s="17">
-        <v>3.7809614281599999E-3</v>
+        <v>3.9969151262900003E-3</v>
+      </c>
+      <c r="E31">
+        <v>5.0541532112899999E-3</v>
       </c>
       <c r="F31" s="17">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G31" s="5" t="str">
         <f>IF(E31=F31,"n/a",IF(OR(C31="battery electric vehicle",C31="natural gas vehicle",C31="plugin hybrid vehicle"),"s-curve","linear"))</f>
         <v>s-curve</v>
       </c>
       <c r="I31" s="17">
+        <f>D31</f>
+        <v>3.9969151262900003E-3</v>
+      </c>
+      <c r="J31" s="17">
         <f>E31</f>
-        <v>3.7809614281599999E-3</v>
-      </c>
-      <c r="J31">
-        <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT(J$9:$K$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,J$9))</f>
-        <v>4.5258766443191352E-3</v>
+        <v>5.0541532112899999E-3</v>
       </c>
       <c r="K31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:K$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,K$9))</f>
-        <v>4.2330423759352146E-3</v>
+        <v>1.0359111139078626E-2</v>
       </c>
       <c r="L31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:L$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,L$9))</f>
-        <v>4.5258766443191352E-3</v>
+        <v>1.289882600385258E-2</v>
       </c>
       <c r="M31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:M$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,M$9))</f>
-        <v>5.0079241136957754E-3</v>
+        <v>1.6605920486673545E-2</v>
       </c>
       <c r="N31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:N$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,N$9))</f>
-        <v>5.8006412523969614E-3</v>
+        <v>2.1961680813246801E-2</v>
       </c>
       <c r="O31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:O$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,O$9))</f>
-        <v>7.1020814791132817E-3</v>
+        <v>2.9585594608390296E-2</v>
       </c>
       <c r="P31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:P$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,P$9))</f>
-        <v>9.232891537156911E-3</v>
+        <v>4.0212559986792025E-2</v>
       </c>
       <c r="Q31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Q$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Q$9))</f>
-        <v>1.2706061243100324E-2</v>
+        <v>5.4599632852899593E-2</v>
       </c>
       <c r="R31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:R$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,R$9))</f>
-        <v>1.8326248389993957E-2</v>
+        <v>7.3326806952772217E-2</v>
       </c>
       <c r="S31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:S$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,S$9))</f>
-        <v>2.7314582619762204E-2</v>
+        <v>9.6494892401215532E-2</v>
       </c>
       <c r="T31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:T$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,T$9))</f>
-        <v>4.1423234586111038E-2</v>
+        <v>0.12341956112618145</v>
       </c>
       <c r="U31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:U$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,U$9))</f>
-        <v>6.2931720788929196E-2</v>
+        <v>0.15252707660564499</v>
       </c>
       <c r="V31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:V$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,V$9))</f>
-        <v>9.4303979462314474E-2</v>
+        <v>0.18163459208510854</v>
       </c>
       <c r="W31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:W$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,W$9))</f>
-        <v>0.1372348149725231</v>
+        <v>0.20855926081007445</v>
       </c>
       <c r="X31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:X$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,X$9))</f>
-        <v>0.19112382912094522</v>
+        <v>0.23172734625851779</v>
       </c>
       <c r="Y31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Y$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Y$9))</f>
-        <v>0.25189048071407999</v>
+        <v>0.25045452035839039</v>
       </c>
       <c r="Z31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Z$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Z$9))</f>
-        <v>0.31265713230721481</v>
+        <v>0.26484159322449791</v>
       </c>
       <c r="AA31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AA$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AA$9))</f>
-        <v>0.36654614645563693</v>
+        <v>0.2754685586028997</v>
       </c>
       <c r="AB31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AB$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AB$9))</f>
-        <v>0.40947698196584553</v>
+        <v>0.28309247239804319</v>
       </c>
       <c r="AC31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AC$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AC$9))</f>
-        <v>0.44084924063923075</v>
+        <v>0.28844823272461645</v>
       </c>
       <c r="AD31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AD$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AD$9))</f>
-        <v>0.46235772684204901</v>
+        <v>0.29215532720743737</v>
       </c>
       <c r="AE31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AE$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AE$9))</f>
-        <v>0.47646637880839782</v>
+        <v>0.29469504207221137</v>
       </c>
       <c r="AF31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AF$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AF$9))</f>
-        <v>0.48545471303816601</v>
+        <v>0.29642276847334142</v>
       </c>
       <c r="AG31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AG$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AG$9))</f>
-        <v>0.49107490018505967</v>
+        <v>0.29759248353925816</v>
       </c>
       <c r="AH31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AH$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AH$9))</f>
-        <v>0.49454806989100308</v>
+        <v>0.29838183892536557</v>
       </c>
       <c r="AI31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AI$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AI$9))</f>
-        <v>0.49667887994904675</v>
+        <v>0.29891334874308811</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.35">
@@ -21332,7 +19490,7 @@
       <c r="D32">
         <v>0</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" s="17">
@@ -21344,11 +19502,11 @@
         <v>n/a</v>
       </c>
       <c r="I32" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,J$9))</f>
+        <f t="shared" ref="I32:I37" si="6">D32</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="17">
+        <f t="shared" ref="J32:J37" si="7">E32</f>
         <v>0</v>
       </c>
       <c r="K32">
@@ -21459,7 +19617,7 @@
       <c r="D33">
         <v>0</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" s="17">
@@ -21471,11 +19629,11 @@
         <v>n/a</v>
       </c>
       <c r="I33" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="17">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K33">
@@ -21597,11 +19755,11 @@
         <v>n/a</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <f>IF($G34="s-curve",$E34+($F34-$E34)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E34:$F34,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="J34" s="17">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K34">
@@ -21712,7 +19870,7 @@
       <c r="D35">
         <v>0</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35">
         <v>0</v>
       </c>
       <c r="F35" s="17">
@@ -21724,11 +19882,11 @@
         <v>n/a</v>
       </c>
       <c r="I35" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <f>IF($G35="s-curve",$E35+($F35-$E35)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E35:$F35,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="17">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K35">
@@ -21839,7 +19997,7 @@
       <c r="D36">
         <v>0</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36">
         <v>0</v>
       </c>
       <c r="F36" s="17">
@@ -21851,11 +20009,11 @@
         <v>n/a</v>
       </c>
       <c r="I36" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <f>IF($G36="s-curve",$E36+($F36-$E36)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E36:$F36,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="17">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K36">
@@ -21965,10 +20123,10 @@
       <c r="C37" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="18">
-        <v>0</v>
-      </c>
-      <c r="E37" s="21">
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
         <v>0</v>
       </c>
       <c r="F37" s="21">
@@ -21980,11 +20138,11 @@
         <v>n/a</v>
       </c>
       <c r="I37" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,J$9))</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="17">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K37">
@@ -22478,7 +20636,7 @@
         <v>n/a</v>
       </c>
       <c r="I41" s="17">
-        <f t="shared" ref="I41:I72" si="2">E41</f>
+        <f t="shared" ref="I41:I72" si="8">E41</f>
         <v>1</v>
       </c>
       <c r="J41">
@@ -22601,7 +20759,7 @@
         <v>n/a</v>
       </c>
       <c r="I42" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J42">
@@ -22724,7 +20882,7 @@
         <v>n/a</v>
       </c>
       <c r="I43" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J43">
@@ -22850,7 +21008,7 @@
         <v>n/a</v>
       </c>
       <c r="I44" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J44">
@@ -22979,7 +21137,7 @@
         <v>n/a</v>
       </c>
       <c r="I45" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J45">
@@ -23102,7 +21260,7 @@
         <v>n/a</v>
       </c>
       <c r="I46" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J46">
@@ -23225,7 +21383,7 @@
         <v>n/a</v>
       </c>
       <c r="I47" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J47">
@@ -23348,7 +21506,7 @@
         <v>n/a</v>
       </c>
       <c r="I48" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J48">
@@ -23471,7 +21629,7 @@
         <v>n/a</v>
       </c>
       <c r="I49" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J49">
@@ -23594,7 +21752,7 @@
         <v>n/a</v>
       </c>
       <c r="I50" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J50">
@@ -23720,7 +21878,7 @@
         <v>n/a</v>
       </c>
       <c r="I51" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J51">
@@ -23850,7 +22008,7 @@
         <v>s-curve</v>
       </c>
       <c r="I52" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0.93664816810144857</v>
       </c>
       <c r="J52">
@@ -23973,7 +22131,7 @@
         <v>n/a</v>
       </c>
       <c r="I53" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J53">
@@ -24096,7 +22254,7 @@
         <v>n/a</v>
       </c>
       <c r="I54" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J54">
@@ -24220,7 +22378,7 @@
         <v>linear</v>
       </c>
       <c r="I55" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>6.3351831898551425E-2</v>
       </c>
       <c r="J55">
@@ -24343,7 +22501,7 @@
         <v>n/a</v>
       </c>
       <c r="I56" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J56">
@@ -24466,7 +22624,7 @@
         <v>n/a</v>
       </c>
       <c r="I57" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J57">
@@ -24592,7 +22750,7 @@
         <v>n/a</v>
       </c>
       <c r="I58" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J58">
@@ -24721,7 +22879,7 @@
         <v>n/a</v>
       </c>
       <c r="I59" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J59">
@@ -24844,7 +23002,7 @@
         <v>n/a</v>
       </c>
       <c r="I60" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J60">
@@ -24967,7 +23125,7 @@
         <v>n/a</v>
       </c>
       <c r="I61" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J61">
@@ -25090,7 +23248,7 @@
         <v>n/a</v>
       </c>
       <c r="I62" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J62">
@@ -25213,7 +23371,7 @@
         <v>n/a</v>
       </c>
       <c r="I63" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J63">
@@ -25336,7 +23494,7 @@
         <v>n/a</v>
       </c>
       <c r="I64" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J64">
@@ -25462,7 +23620,7 @@
         <v>n/a</v>
       </c>
       <c r="I65" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J65">
@@ -25591,7 +23749,7 @@
         <v>n/a</v>
       </c>
       <c r="I66" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J66">
@@ -25714,7 +23872,7 @@
         <v>n/a</v>
       </c>
       <c r="I67" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J67">
@@ -25837,7 +23995,7 @@
         <v>n/a</v>
       </c>
       <c r="I68" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J68">
@@ -25960,7 +24118,7 @@
         <v>n/a</v>
       </c>
       <c r="I69" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J69">
@@ -26083,7 +24241,7 @@
         <v>n/a</v>
       </c>
       <c r="I70" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J70">
@@ -26206,7 +24364,7 @@
         <v>n/a</v>
       </c>
       <c r="I71" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J71">
@@ -26332,7 +24490,7 @@
         <v>n/a</v>
       </c>
       <c r="I72" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J72">
@@ -26461,7 +24619,7 @@
         <v>n/a</v>
       </c>
       <c r="I73" s="17">
-        <f t="shared" ref="I73:I93" si="3">E73</f>
+        <f t="shared" ref="I73:I93" si="9">E73</f>
         <v>0</v>
       </c>
       <c r="J73">
@@ -26584,7 +24742,7 @@
         <v>n/a</v>
       </c>
       <c r="I74" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J74">
@@ -26707,7 +24865,7 @@
         <v>n/a</v>
       </c>
       <c r="I75" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J75">
@@ -26830,7 +24988,7 @@
         <v>n/a</v>
       </c>
       <c r="I76" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J76">
@@ -26953,7 +25111,7 @@
         <v>n/a</v>
       </c>
       <c r="I77" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J77">
@@ -27076,7 +25234,7 @@
         <v>n/a</v>
       </c>
       <c r="I78" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J78">
@@ -27202,7 +25360,7 @@
         <v>n/a</v>
       </c>
       <c r="I79" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J79">
@@ -27337,7 +25495,7 @@
         <v>s-curve</v>
       </c>
       <c r="I80" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>6.6873740826300002E-2</v>
       </c>
       <c r="J80">
@@ -27450,15 +25608,15 @@
         <v>2</v>
       </c>
       <c r="D81">
-        <f t="shared" ref="D81:E81" si="4">D11</f>
+        <f t="shared" ref="D81:E81" si="10">D11</f>
         <v>1.0005073039100001E-4</v>
       </c>
       <c r="E81">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>9.1114481822700006E-5</v>
       </c>
       <c r="F81">
-        <f t="shared" ref="F81" si="5">F11</f>
+        <f t="shared" ref="F81" si="11">F11</f>
         <v>9.1114481822700006E-5</v>
       </c>
       <c r="G81" s="5" t="str">
@@ -27466,7 +25624,7 @@
         <v>n/a</v>
       </c>
       <c r="I81" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>9.1114481822700006E-5</v>
       </c>
       <c r="J81">
@@ -27579,15 +25737,15 @@
         <v>3</v>
       </c>
       <c r="D82">
-        <f t="shared" ref="D82:E82" si="6">D12</f>
+        <f t="shared" ref="D82:E82" si="12">D12</f>
         <v>1</v>
       </c>
       <c r="E82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F82">
-        <f t="shared" ref="F82" si="7">F12</f>
+        <f t="shared" ref="F82" si="13">F12</f>
         <v>1</v>
       </c>
       <c r="G82" s="5" t="str">
@@ -27595,7 +25753,7 @@
         <v>n/a</v>
       </c>
       <c r="I82" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J82">
@@ -27708,15 +25866,15 @@
         <v>4</v>
       </c>
       <c r="D83">
-        <f t="shared" ref="D83:E83" si="8">D13</f>
+        <f t="shared" ref="D83:E83" si="14">D13</f>
         <v>6.6777915503600002E-2</v>
       </c>
       <c r="E83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>6.08023121013E-2</v>
       </c>
       <c r="F83">
-        <f t="shared" ref="F83" si="9">F13</f>
+        <f t="shared" ref="F83" si="15">F13</f>
         <v>6.08023121013E-2</v>
       </c>
       <c r="G83" s="5" t="str">
@@ -27724,7 +25882,7 @@
         <v>n/a</v>
       </c>
       <c r="I83" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>6.08023121013E-2</v>
       </c>
       <c r="J83">
@@ -27837,15 +25995,15 @@
         <v>5</v>
       </c>
       <c r="D84">
-        <f t="shared" ref="D84:E84" si="10">D14</f>
+        <f t="shared" ref="D84:E84" si="16">D14</f>
         <v>1.5463740197399999E-2</v>
       </c>
       <c r="E84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>1.5463740197399999E-2</v>
       </c>
       <c r="F84">
-        <f t="shared" ref="F84" si="11">F14</f>
+        <f t="shared" ref="F84" si="17">F14</f>
         <v>0.13111785993513644</v>
       </c>
       <c r="G84" s="5" t="str">
@@ -27853,7 +26011,7 @@
         <v>s-curve</v>
       </c>
       <c r="I84" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>1.5463740197399999E-2</v>
       </c>
       <c r="J84">
@@ -27966,15 +26124,15 @@
         <v>33</v>
       </c>
       <c r="D85">
-        <f t="shared" ref="D85:E85" si="12">D15</f>
+        <f t="shared" ref="D85:E85" si="18">D15</f>
         <v>0</v>
       </c>
       <c r="E85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F85">
-        <f t="shared" ref="F85" si="13">F15</f>
+        <f t="shared" ref="F85" si="19">F15</f>
         <v>0</v>
       </c>
       <c r="G85" s="5" t="str">
@@ -27982,7 +26140,7 @@
         <v>n/a</v>
       </c>
       <c r="I85" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J85">
@@ -28097,15 +26255,15 @@
         <v>34</v>
       </c>
       <c r="D86">
-        <f t="shared" ref="D86:E86" si="14">D16</f>
+        <f t="shared" ref="D86:E86" si="20">D16</f>
         <v>0</v>
       </c>
       <c r="E86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F86">
-        <f t="shared" ref="F86" si="15">F16</f>
+        <f t="shared" ref="F86" si="21">F16</f>
         <v>0</v>
       </c>
       <c r="G86" s="6" t="str">
@@ -28113,7 +26271,7 @@
         <v>n/a</v>
       </c>
       <c r="I86" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J86">
@@ -28242,7 +26400,7 @@
         <v>n/a</v>
       </c>
       <c r="I87" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J87">
@@ -28365,7 +26523,7 @@
         <v>n/a</v>
       </c>
       <c r="I88" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J88">
@@ -28488,7 +26646,7 @@
         <v>n/a</v>
       </c>
       <c r="I89" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J89">
@@ -28611,7 +26769,7 @@
         <v>n/a</v>
       </c>
       <c r="I90" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J90">
@@ -28734,7 +26892,7 @@
         <v>n/a</v>
       </c>
       <c r="I91" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J91">
@@ -28857,7 +27015,7 @@
         <v>n/a</v>
       </c>
       <c r="I92" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J92">
@@ -28983,7 +27141,7 @@
         <v>n/a</v>
       </c>
       <c r="I93" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J93">
@@ -29692,35 +27850,35 @@
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>1.9346159166299389E-2</v>
+        <v>1.9993417391351978E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>2.1270880799131281E-2</v>
+        <v>2.2093517300674829E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>2.4076264844254999E-2</v>
+        <v>2.5083005196618505E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>2.8081237018963839E-2</v>
+        <v>2.9250049214034041E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>3.3632478366133998E-2</v>
+        <v>3.4891505996859425E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>4.1020281187147262E-2</v>
+        <v>4.2234802602923074E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>5.0337480210934871E-2</v>
+        <v>5.1319468678820979E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>6.1322535895563066E-2</v>
+        <v>6.1877165606985654E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
@@ -29728,67 +27886,67 @@
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>8.5259064236973381E-2</v>
+        <v>8.4704434525550779E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>9.6244119921601576E-2</v>
+        <v>9.5262131453715468E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>0.10556131894538917</v>
+        <v>0.10434679752961337</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>0.11294912176640245</v>
+        <v>0.11169009413567701</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>0.11850036311357261</v>
+        <v>0.11733155091850239</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>0.12250533528828143</v>
+        <v>0.12149859493591794</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>0.12531071933340518</v>
+        <v>0.12448808283186162</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>0.12723544096623707</v>
+        <v>0.12658818274118447</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>0.1285372188240779</v>
+        <v>0.12804180805533377</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>0.12940918230467352</v>
+        <v>0.12903768065455262</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>0.12998946136075354</v>
+        <v>0.12971515646323384</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>0.13037396009233732</v>
+        <v>0.13017382495362109</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>0.1306280023263604</v>
+        <v>0.13048334686530239</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>0.1307955323407107</v>
+        <v>0.13069176241266453</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>0.13090587299520942</v>
+        <v>0.1308318908805127</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>0.13097848697886891</v>
+        <v>0.13092601275638885</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.35">
@@ -30152,111 +28310,111 @@
       </c>
       <c r="B2">
         <f>Data!I17</f>
-        <v>6.8939837381399999E-3</v>
+        <v>0.139546683447</v>
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>1.4745205504305832E-2</v>
+        <v>6.2019274287835199E-2</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
-        <v>1.8423498834078463E-2</v>
+        <v>0.14191438128525985</v>
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>2.3701949678448984E-2</v>
+        <v>0.14301211999875416</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>3.1143927768198666E-2</v>
+        <v>0.14457474879671367</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>4.1378831028600141E-2</v>
+        <v>0.14675289542604564</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>5.498427054307533E-2</v>
+        <v>0.149701729185583</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>7.2275261295201787E-2</v>
+        <v>0.15354012798430811</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>9.3037067519099306E-2</v>
+        <v>0.15828875427890052</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.11633204730802928</v>
+        <v>0.16380734536684707</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.14056193643011078</v>
+        <v>0.1697733417235</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.16385691621904069</v>
+        <v>0.17573933808015293</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.18461872244293825</v>
+        <v>0.18125792916809949</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.20190971319506468</v>
+        <v>0.1860065554626919</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.21551515270953986</v>
+        <v>0.18984495426141701</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.22575005596994135</v>
+        <v>0.19279378802095437</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.23319203405969108</v>
+        <v>0.19497193465028634</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.23847048490406159</v>
+        <v>0.19653456344824585</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.24214877823383418</v>
+        <v>0.19763230216174016</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.24468053139197088</v>
+        <v>0.19839212352793961</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.24640834401092193</v>
+        <v>0.19891267395557297</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.24758065709350957</v>
+        <v>0.1992667958806032</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.24837292767436264</v>
+        <v>0.19950654550219166</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.2489069289438185</v>
+        <v>0.19966833503592715</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.24926620483188039</v>
+        <v>0.19977727547910223</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.24950763242856416</v>
+        <v>0.19985052172959569</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.24966973562683897</v>
+        <v>0.19989971997320177</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.35">
@@ -30378,7 +28536,7 @@
       </c>
       <c r="B4">
         <f>Data!I19</f>
-        <v>0.67797888423399999</v>
+        <v>0.72915442924999996</v>
       </c>
       <c r="C4">
         <f>Data!J19</f>
@@ -30604,111 +28762,111 @@
       </c>
       <c r="B6">
         <f>Data!I21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <f>Data!J21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>6.4220413235999997E-4</v>
       </c>
       <c r="D6">
         <f>Data!K21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>7.034131712916232E-4</v>
       </c>
       <c r="E6">
         <f>Data!L21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>7.3179159465514107E-4</v>
       </c>
       <c r="F6">
         <f>Data!M21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>7.7218822187015597E-4</v>
       </c>
       <c r="G6">
         <f>Data!N21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>8.284970378344221E-4</v>
       </c>
       <c r="H6">
         <f>Data!O21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>9.0472943433103864E-4</v>
       </c>
       <c r="I6">
         <f>Data!P21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.0039586086411079E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.126718720611755E-3</v>
       </c>
       <c r="K6">
         <f>Data!R21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.2693837394716313E-3</v>
       </c>
       <c r="L6">
         <f>Data!S21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.4236149497888558E-3</v>
       </c>
       <c r="M6">
         <f>Data!T21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.5778461601060802E-3</v>
       </c>
       <c r="N6">
         <f>Data!U21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.7205111789659567E-3</v>
       </c>
       <c r="O6">
         <f>Data!V21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.8432712909366039E-3</v>
       </c>
       <c r="P6">
         <f>Data!W21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>1.942500465246673E-3</v>
       </c>
       <c r="Q6">
         <f>Data!X21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.0187328617432897E-3</v>
       </c>
       <c r="R6">
         <f>Data!Y21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.075041677707556E-3</v>
       </c>
       <c r="S6">
         <f>Data!Z21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1154383049225706E-3</v>
       </c>
       <c r="T6">
         <f>Data!AA21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1438167282860888E-3</v>
       </c>
       <c r="U6">
         <f>Data!AB21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.163459410233614E-3</v>
       </c>
       <c r="V6">
         <f>Data!AC21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1769165291598619E-3</v>
       </c>
       <c r="W6">
         <f>Data!AD21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1860711866273229E-3</v>
       </c>
       <c r="X6">
         <f>Data!AE21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1922691244234882E-3</v>
       </c>
       <c r="Y6">
         <f>Data!AF21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1964516606023544E-3</v>
       </c>
       <c r="Z6">
         <f>Data!AG21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.1992679573948674E-3</v>
       </c>
       <c r="AA6">
         <f>Data!AH21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.2011614982536728E-3</v>
       </c>
       <c r="AB6">
         <f>Data!AI21</f>
-        <v>4.2783868328800001E-4</v>
+        <v>2.2024333570016897E-3</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.35">
@@ -31072,111 +29230,111 @@
       </c>
       <c r="B2">
         <f>Data!I24</f>
-        <v>0.154617049501</v>
+        <v>3.0938506857799999E-2</v>
       </c>
       <c r="C2">
         <f>Data!J24</f>
-        <v>0.17679125251200001</v>
+        <v>3.0393141812799999E-2</v>
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>0.1915976578869496</v>
+        <v>5.6618778403372177E-2</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>0.19868613028135812</v>
+        <v>6.8777803134611903E-2</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>0.20903281811998659</v>
+        <v>8.608614979905288E-2</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>0.22398101555448952</v>
+        <v>0.11021223591476392</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.2452597438179614</v>
+        <v>0.14287478317648508</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.27492014064673714</v>
+        <v>0.18539053428222468</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.31507518728691364</v>
+        <v>0.2379883554627959</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.36734367556228731</v>
+        <v>0.29911463687665474</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.43200697159225543</v>
+        <v>0.36519657090640001</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.5071550811823069</v>
+        <v>0.43127850493614522</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.58839562625599995</v>
+        <v>0.49240478635000412</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.669636171329693</v>
+        <v>0.54500260753057528</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.74478428091974458</v>
+        <v>0.58751835863631485</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.8094475769497127</v>
+        <v>0.62018090589803598</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.86171606522508637</v>
+        <v>0.64430699201374708</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.90187111186526281</v>
+        <v>0.66161533867818811</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.93153150869403867</v>
+        <v>0.67377436340942776</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.95281023695751044</v>
+        <v>0.68219047069376959</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.96775843439201348</v>
+        <v>0.68795631045658845</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.97810512223064183</v>
+        <v>0.69187871675545232</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.98519359462505041</v>
+        <v>0.69453428637540304</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.99001576622760601</v>
+        <v>0.69632633663086296</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.99328050002472557</v>
+        <v>0.6975330076961308</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.99548363075463853</v>
+        <v>0.69834431457660484</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.99696710148694001</v>
+        <v>0.69888925542034686</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.35">
@@ -31750,111 +29908,111 @@
       </c>
       <c r="B8">
         <f>Data!I30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f>Data!J30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f>Data!K30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>Data!L30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>Data!M30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>Data!N30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f>Data!O30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>Data!P30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>Data!Q30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f>Data!R30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>Data!S30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f>Data!T30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f>Data!U30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f>Data!V30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f>Data!W30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f>Data!X30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f>Data!Y30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f>Data!Z30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f>Data!AA30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f>Data!AB30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f>Data!AC30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f>Data!AD30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f>Data!AE30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f>Data!AF30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f>Data!AG30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f>Data!AH30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f>Data!AI30</f>
-        <v>6.7718615476299995E-2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31992,111 +30150,111 @@
       </c>
       <c r="B2">
         <f>Data!I31</f>
-        <v>3.7809614281599999E-3</v>
+        <v>3.9969151262900003E-3</v>
       </c>
       <c r="C2">
         <f>Data!J31</f>
-        <v>4.5258766443191352E-3</v>
+        <v>5.0541532112899999E-3</v>
       </c>
       <c r="D2">
         <f>Data!K31</f>
-        <v>4.2330423759352146E-3</v>
+        <v>1.0359111139078626E-2</v>
       </c>
       <c r="E2">
         <f>Data!L31</f>
-        <v>4.5258766443191352E-3</v>
+        <v>1.289882600385258E-2</v>
       </c>
       <c r="F2">
         <f>Data!M31</f>
-        <v>5.0079241136957754E-3</v>
+        <v>1.6605920486673545E-2</v>
       </c>
       <c r="G2">
         <f>Data!N31</f>
-        <v>5.8006412523969614E-3</v>
+        <v>2.1961680813246801E-2</v>
       </c>
       <c r="H2">
         <f>Data!O31</f>
-        <v>7.1020814791132817E-3</v>
+        <v>2.9585594608390296E-2</v>
       </c>
       <c r="I2">
         <f>Data!P31</f>
-        <v>9.232891537156911E-3</v>
+        <v>4.0212559986792025E-2</v>
       </c>
       <c r="J2">
         <f>Data!Q31</f>
-        <v>1.2706061243100324E-2</v>
+        <v>5.4599632852899593E-2</v>
       </c>
       <c r="K2">
         <f>Data!R31</f>
-        <v>1.8326248389993957E-2</v>
+        <v>7.3326806952772217E-2</v>
       </c>
       <c r="L2">
         <f>Data!S31</f>
-        <v>2.7314582619762204E-2</v>
+        <v>9.6494892401215532E-2</v>
       </c>
       <c r="M2">
         <f>Data!T31</f>
-        <v>4.1423234586111038E-2</v>
+        <v>0.12341956112618145</v>
       </c>
       <c r="N2">
         <f>Data!U31</f>
-        <v>6.2931720788929196E-2</v>
+        <v>0.15252707660564499</v>
       </c>
       <c r="O2">
         <f>Data!V31</f>
-        <v>9.4303979462314474E-2</v>
+        <v>0.18163459208510854</v>
       </c>
       <c r="P2">
         <f>Data!W31</f>
-        <v>0.1372348149725231</v>
+        <v>0.20855926081007445</v>
       </c>
       <c r="Q2">
         <f>Data!X31</f>
-        <v>0.19112382912094522</v>
+        <v>0.23172734625851779</v>
       </c>
       <c r="R2">
         <f>Data!Y31</f>
-        <v>0.25189048071407999</v>
+        <v>0.25045452035839039</v>
       </c>
       <c r="S2">
         <f>Data!Z31</f>
-        <v>0.31265713230721481</v>
+        <v>0.26484159322449791</v>
       </c>
       <c r="T2">
         <f>Data!AA31</f>
-        <v>0.36654614645563693</v>
+        <v>0.2754685586028997</v>
       </c>
       <c r="U2">
         <f>Data!AB31</f>
-        <v>0.40947698196584553</v>
+        <v>0.28309247239804319</v>
       </c>
       <c r="V2">
         <f>Data!AC31</f>
-        <v>0.44084924063923075</v>
+        <v>0.28844823272461645</v>
       </c>
       <c r="W2">
         <f>Data!AD31</f>
-        <v>0.46235772684204901</v>
+        <v>0.29215532720743737</v>
       </c>
       <c r="X2">
         <f>Data!AE31</f>
-        <v>0.47646637880839782</v>
+        <v>0.29469504207221137</v>
       </c>
       <c r="Y2">
         <f>Data!AF31</f>
-        <v>0.48545471303816601</v>
+        <v>0.29642276847334142</v>
       </c>
       <c r="Z2">
         <f>Data!AG31</f>
-        <v>0.49107490018505967</v>
+        <v>0.29759248353925816</v>
       </c>
       <c r="AA2">
         <f>Data!AH31</f>
-        <v>0.49454806989100308</v>
+        <v>0.29838183892536557</v>
       </c>
       <c r="AB2">
         <f>Data!AI31</f>
-        <v>0.49667887994904675</v>
+        <v>0.29891334874308811</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.35">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083EF39E-EFBE-4FC3-9F3C-DB0493FEAEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEBA84A-D1BC-44E9-A87A-A3C050F86028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1494,17 +1494,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="63.453125" customWidth="1"/>
+    <col min="2" max="2" width="63.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1512,192 +1512,192 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B47" s="1"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="1"/>
     </row>
   </sheetData>
@@ -1715,12 +1715,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>0.99774649999676845</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>1.0000000000000142</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -2635,12 +2635,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -3555,12 +3555,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -4475,12 +4475,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -5395,12 +5395,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -5513,233 +5513,233 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Data!I80</f>
-        <v>4.1738099814E-2</v>
+        <v>0.13060041262200001</v>
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>0.10208306765026703</v>
+        <v>0.18534942239376065</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>0.12143932599985952</v>
+        <v>0.20291072063493176</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>0.14628142699716032</v>
+        <v>0.22544914395371735</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.17766857080894907</v>
+        <v>0.25392566991561405</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.21654952889910542</v>
+        <v>0.28920108774646175</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.2635519806241971</v>
+        <v>0.33184487033618731</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.31872417867827213</v>
+        <v>0.38190079577122726</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.38129216112899533</v>
+        <v>0.43866667377928981</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.44953362229243138</v>
+        <v>0.50057991291156378</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.520869049907</v>
+        <v>0.56530020631099998</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.59220447752156857</v>
+        <v>0.63002049971043617</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.66044593868500467</v>
+        <v>0.69193373884271026</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.72301392113572782</v>
+        <v>0.74869961685077269</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.77818611918980285</v>
+        <v>0.7987555422858128</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.8251885709148945</v>
+        <v>0.84139932487553826</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.86406952900505107</v>
+        <v>0.87667474270638612</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.89545667281683972</v>
+        <v>0.90515126866828277</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.92029877381414049</v>
+        <v>0.9276896919870683</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.93965503216373303</v>
+        <v>0.94525099022823955</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.95455359265088469</v>
+        <v>0.95876796542838227</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.96591348457572779</v>
+        <v>0.96907442272382549</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.97451311439579758</v>
+        <v>0.97687658475877748</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.98098779092699173</v>
+        <v>0.98275084638133969</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.98584260831619597</v>
+        <v>0.98715546294195899</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.98947163147757322</v>
+        <v>0.99044795661041651</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.99217811905636955</v>
+        <v>0.99290346400749918</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f>Data!I81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="C3">
         <f>Data!J81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="D3">
         <f>Data!K81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="E3">
         <f>Data!L81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="F3">
         <f>Data!M81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="G3">
         <f>Data!N81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="H3">
         <f>Data!O81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="I3">
         <f>Data!P81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="J3">
         <f>Data!Q81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="K3">
         <f>Data!R81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="L3">
         <f>Data!S81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="M3">
         <f>Data!T81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="N3">
         <f>Data!U81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="O3">
         <f>Data!V81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="P3">
         <f>Data!W81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Q3">
         <f>Data!X81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="R3">
         <f>Data!Y81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="S3">
         <f>Data!Z81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="T3">
         <f>Data!AA81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="U3">
         <f>Data!AB81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="V3">
         <f>Data!AC81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="W3">
         <f>Data!AD81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="X3">
         <f>Data!AE81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Y3">
         <f>Data!AF81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Z3">
         <f>Data!AG81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AA3">
         <f>Data!AH81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AB3">
         <f>Data!AI81</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5852,120 +5852,120 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f>Data!I83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="C5">
         <f>Data!J83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="D5">
         <f>Data!K83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="E5">
         <f>Data!L83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="F5">
         <f>Data!M83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="G5">
         <f>Data!N83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="H5">
         <f>Data!O83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="I5">
         <f>Data!P83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="K5">
         <f>Data!R83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="L5">
         <f>Data!S83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="M5">
         <f>Data!T83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="N5">
         <f>Data!U83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="O5">
         <f>Data!V83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="P5">
         <f>Data!W83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI83</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5975,110 +5975,110 @@
       </c>
       <c r="C6">
         <f>Data!J84</f>
-        <v>4.4996485878868705E-3</v>
+        <v>1.5502361933759918E-3</v>
       </c>
       <c r="D6">
         <f>Data!K84</f>
-        <v>6.0426568409376203E-3</v>
+        <v>2.0818393161168456E-3</v>
       </c>
       <c r="E6">
         <f>Data!L84</f>
-        <v>8.1005054730370115E-3</v>
+        <v>2.7908172213154192E-3</v>
       </c>
       <c r="F6">
         <f>Data!M84</f>
-        <v>1.0833728727748151E-2</v>
+        <v>3.7324777824171446E-3</v>
       </c>
       <c r="G6">
         <f>Data!N84</f>
-        <v>1.4444247020933752E-2</v>
+        <v>4.9763873957167403E-3</v>
       </c>
       <c r="H6">
         <f>Data!O84</f>
-        <v>1.9179461540303897E-2</v>
+        <v>6.6077816675024067E-3</v>
       </c>
       <c r="I6">
         <f>Data!P84</f>
-        <v>2.5331467679199877E-2</v>
+        <v>8.7272944232455497E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q84</f>
-        <v>3.3227041042513977E-2</v>
+        <v>1.1447507647943856E-2</v>
       </c>
       <c r="K6">
         <f>Data!R84</f>
-        <v>4.3202827577549584E-2</v>
+        <v>1.4884403894827813E-2</v>
       </c>
       <c r="L6">
         <f>Data!S84</f>
-        <v>5.5560375639612684E-2</v>
+        <v>1.9141873760089034E-2</v>
       </c>
       <c r="M6">
         <f>Data!T84</f>
-        <v>7.0499180770926387E-2</v>
+        <v>2.4288648213253456E-2</v>
       </c>
       <c r="N6">
         <f>Data!U84</f>
-        <v>8.803457914156243E-2</v>
+        <v>3.0330010930467905E-2</v>
       </c>
       <c r="O6">
         <f>Data!V84</f>
-        <v>0.10792058216875849</v>
+        <v>3.7181212981519933E-2</v>
       </c>
       <c r="P6">
         <f>Data!W84</f>
-        <v>0.12960978885438473</v>
+        <v>4.4653661674554562E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X84</f>
-        <v>0.15228235194377104</v>
+        <v>5.2464900088235525E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y84</f>
-        <v>0.17495491503315735</v>
+        <v>6.0276138501916494E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z84</f>
-        <v>0.19664412171878359</v>
+        <v>6.774858719495111E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA84</f>
-        <v>0.21653012474597963</v>
+        <v>7.4599789246003134E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB84</f>
-        <v>0.23406552311661569</v>
+        <v>8.0641151963217597E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC84</f>
-        <v>0.2490043282479294</v>
+        <v>8.5787926416382013E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD84</f>
-        <v>0.26136187630999252</v>
+        <v>9.004539628164325E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE84</f>
-        <v>0.27133766284502814</v>
+        <v>9.3482292528527203E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF84</f>
-        <v>0.27923323620834223</v>
+        <v>9.6202505753225503E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG84</f>
-        <v>0.28538524234723822</v>
+        <v>9.8322018508968642E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH84</f>
-        <v>0.29012045686660837</v>
+        <v>9.9953412780754314E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI84</f>
-        <v>0.29373097515979396</v>
+        <v>0.10119732239405391</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -6315,12 +6315,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -7043,18 +7043,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.08984375" customWidth="1"/>
-    <col min="6" max="8" width="23.26953125" customWidth="1"/>
-    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -7135,7 +7135,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="18"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -7259,20 +7259,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AK93"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" customWidth="1"/>
-    <col min="3" max="3" width="24.08984375" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="18" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.08984375" customWidth="1"/>
-    <col min="8" max="9" width="9.08984375" customWidth="1"/>
-    <col min="14" max="14" width="11.08984375" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="X1" s="11"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -7412,12 +7412,12 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -7435,7 +7435,7 @@
       <c r="O6" s="16"/>
       <c r="R6" s="19"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
@@ -7451,7 +7451,7 @@
       <c r="G7" s="2"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="1:37" ht="87" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7464,7 +7464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
@@ -7594,7 +7594,7 @@
       <c r="AJ9" s="15"/>
       <c r="AK9" s="15"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -7605,10 +7605,10 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>5.0773251135200002E-2</v>
+        <v>0.15905875518900001</v>
       </c>
       <c r="E10" s="16">
-        <v>4.1738099814E-2</v>
+        <v>0.13060041262200001</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -7619,126 +7619,126 @@
       </c>
       <c r="I10">
         <f>D10</f>
-        <v>5.0773251135200002E-2</v>
+        <v>0.15905875518900001</v>
       </c>
       <c r="J10" s="16">
         <f>E10</f>
-        <v>4.1738099814E-2</v>
+        <v>0.13060041262200001</v>
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>8.7184507163115391E-2</v>
+        <v>0.17183244719361793</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>0.10208306765026703</v>
+        <v>0.18534942239376065</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>0.12143932599985952</v>
+        <v>0.20291072063493176</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.14628142699716032</v>
+        <v>0.22544914395371735</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.17766857080894907</v>
+        <v>0.25392566991561405</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.21654952889910542</v>
+        <v>0.28920108774646175</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.2635519806241971</v>
+        <v>0.33184487033618731</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.31872417867827213</v>
+        <v>0.38190079577122726</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.38129216112899533</v>
+        <v>0.43866667377928981</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.44953362229243138</v>
+        <v>0.50057991291156378</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.520869049907</v>
+        <v>0.56530020631099998</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.59220447752156857</v>
+        <v>0.63002049971043617</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.66044593868500467</v>
+        <v>0.69193373884271026</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.72301392113572782</v>
+        <v>0.74869961685077269</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.77818611918980285</v>
+        <v>0.7987555422858128</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.8251885709148945</v>
+        <v>0.84139932487553826</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.86406952900505107</v>
+        <v>0.87667474270638612</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.89545667281683972</v>
+        <v>0.90515126866828277</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.92029877381414049</v>
+        <v>0.9276896919870683</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.93965503216373303</v>
+        <v>0.94525099022823955</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.95455359265088469</v>
+        <v>0.95876796542838227</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.96591348457572779</v>
+        <v>0.96907442272382549</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.97451311439579758</v>
+        <v>0.97687658475877748</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.98098779092699173</v>
+        <v>0.98275084638133969</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.98584260831619597</v>
+        <v>0.98715546294195899</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>1.0005073039100001E-4</v>
+        <v>1.00045127707E-4</v>
       </c>
       <c r="E11" s="16">
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="F11" s="16">
         <f>E11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="G11" s="5" t="str">
         <f>IF(E11=F11,"n/a",IF(OR(C11="battery electric vehicle",C11="natural gas vehicle",C11="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7746,114 +7746,114 @@
       </c>
       <c r="I11" s="16">
         <f t="shared" ref="I11:I40" si="1">E11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="J11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,J$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="K11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,K$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="L11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,L$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="M11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,M$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="N11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,N$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="O11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,O$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="P11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,P$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Q11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Q$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="R11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,R$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="S11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,S$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="T11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,T$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="U11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,U$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="V11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,V$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="W11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,W$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="X11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,X$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Y11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Y$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Z11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Z$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AA11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AA$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AB11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AB$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AC11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AC$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AD11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AD$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AE11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AE$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AF11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AF$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AG11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AG$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AH11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AH$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AI11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AI$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>3</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -7987,11 +7987,11 @@
         <v>6.6777915503600002E-2</v>
       </c>
       <c r="E13" s="16">
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="F13" s="16">
         <f>E13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="G13" s="5" t="str">
         <f>IF(E13=F13,"n/a",IF(OR(C13="battery electric vehicle",C13="natural gas vehicle",C13="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7999,126 +7999,126 @@
       </c>
       <c r="I13" s="16">
         <f t="shared" si="1"/>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="J13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,J$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="K13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,K$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="L13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,L$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="M13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,M$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="N13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,N$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="O13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,O$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="P13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,P$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Q13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Q$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="R13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,R$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="S13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,S$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="T13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,T$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="U13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,U$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="V13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,V$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="W13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,W$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="X13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,X$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Y13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Y$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Z13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Z$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AA13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AA$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AB13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AB$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AC13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AC$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AD13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AD$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AE13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AE$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AF13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AF$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AG13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AG$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AH13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AH$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AI13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AI$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>5</v>
       </c>
       <c r="D14">
-        <v>1.5463740197399999E-2</v>
+        <v>1.6690003398299999E-2</v>
       </c>
       <c r="E14" s="16">
         <v>0</v>
       </c>
       <c r="F14" s="23">
         <f>D14/D10*F10</f>
-        <v>0.30456470388754209</v>
+        <v>0.10492980017647105</v>
       </c>
       <c r="G14" s="5" t="str">
         <f>IF(E14=F14,"n/a",IF(OR(C14="battery electric vehicle",C14="natural gas vehicle",C14="plugin hybrid vehicle",C14="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="I14">
         <f>D14</f>
-        <v>1.5463740197399999E-2</v>
+        <v>1.6690003398299999E-2</v>
       </c>
       <c r="J14">
         <f>E14</f>
@@ -8134,106 +8134,106 @@
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>1.1928496766138092E-2</v>
+        <v>4.1096514668315402E-3</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.7458920658236333E-2</v>
+        <v>6.0150143223491733E-3</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>2.533146767919987E-2</v>
+        <v>8.7272944232455463E-3</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>3.6305002648196E-2</v>
+        <v>1.2507938788232255E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>5.1161270790237426E-2</v>
+        <v>1.7626277281218222E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>7.0499180770926373E-2</v>
+        <v>2.4288648213253449E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>9.4422830352950293E-2</v>
+        <v>3.2530915744886375E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>0.1222255739642677</v>
+        <v>4.2109623632752446E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>0.15228235194377104</v>
+        <v>5.2464900088235525E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>0.18233912992327439</v>
+        <v>6.2820176543718603E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>0.21014187353459179</v>
+        <v>7.2398884431584667E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>0.23406552311661571</v>
+        <v>8.0641151963217611E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>0.25340343309730462</v>
+        <v>8.7303522895252825E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>0.26825970123934606</v>
+        <v>9.2421861388238782E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>0.27923323620834223</v>
+        <v>9.6202505753225503E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>0.28710578322930574</v>
+        <v>9.8914785854121876E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>0.29263620712140404</v>
+        <v>0.10082014870963951</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>0.29646419841450505</v>
+        <v>0.10213898295515562</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>0.29908673917637851</v>
+        <v>0.10304251075921672</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>0.30087081067793731</v>
+        <v>0.10365716591711784</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>0.30207867282131895</v>
+        <v>0.10407330321644376</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>0.3028937708877924</v>
+        <v>0.10435412392924331</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>0.30344261445351972</v>
+        <v>0.10454321362002106</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>0.30381163014801615</v>
+        <v>0.10467034832273366</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>0.30405949162775042</v>
+        <v>0.10475574251059583</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>31</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -8500,10 +8500,10 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.26000976646599999</v>
+        <v>0.454500581771</v>
       </c>
       <c r="E17">
-        <v>0.111097601666</v>
+        <v>0.23555139071600001</v>
       </c>
       <c r="F17">
         <v>0.3</v>
@@ -8514,114 +8514,114 @@
       </c>
       <c r="I17" s="16">
         <f>D17</f>
-        <v>0.26000976646599999</v>
+        <v>0.454500581771</v>
       </c>
       <c r="J17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:J$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,J$9))</f>
-        <v>0.11612183754114395</v>
+        <v>0.2372655299631645</v>
       </c>
       <c r="K17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,K$9))</f>
-        <v>0.26143226663209485</v>
+        <v>0.44900481233409134</v>
       </c>
       <c r="L17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,L$9))</f>
-        <v>0.26190633820992476</v>
+        <v>0.44717325677406827</v>
       </c>
       <c r="M17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,M$9))</f>
-        <v>0.262528085681139</v>
+        <v>0.44477116162412172</v>
       </c>
       <c r="N17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,N$9))</f>
-        <v>0.26333586202244447</v>
+        <v>0.44165035177522616</v>
       </c>
       <c r="O17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,O$9))</f>
-        <v>0.2643725738234296</v>
+        <v>0.43764505942691106</v>
       </c>
       <c r="P17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,P$9))</f>
-        <v>0.2656824236784171</v>
+        <v>0.43258450971903878</v>
       </c>
       <c r="Q17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>0.26730500576557847</v>
+        <v>0.42631573221303853</v>
       </c>
       <c r="R17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.26926651443120747</v>
+        <v>0.41873752615603005</v>
       </c>
       <c r="S17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.27156896335914493</v>
+        <v>0.40984211176536622</v>
       </c>
       <c r="T17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.27418005353133063</v>
+        <v>0.39975427493600035</v>
       </c>
       <c r="U17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.277027909600843</v>
+        <v>0.38875170304139878</v>
       </c>
       <c r="V17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.28000488323299999</v>
+        <v>0.37725029088549999</v>
       </c>
       <c r="W17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.28298185686515698</v>
+        <v>0.36574887872960121</v>
       </c>
       <c r="X17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.28582971293466936</v>
+        <v>0.35474630683499964</v>
       </c>
       <c r="Y17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.28844080310685505</v>
+        <v>0.34465847000563377</v>
       </c>
       <c r="Z17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.29074325203479251</v>
+        <v>0.33576305561496994</v>
       </c>
       <c r="AA17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.29270476070042151</v>
+        <v>0.32818484955796146</v>
       </c>
       <c r="AB17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.29432734278758288</v>
+        <v>0.32191607205196121</v>
       </c>
       <c r="AC17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.29563719264257038</v>
+        <v>0.31685552234408898</v>
       </c>
       <c r="AD17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.29667390444355551</v>
+        <v>0.31285022999577383</v>
       </c>
       <c r="AE17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.29748168078486098</v>
+        <v>0.30972942014687826</v>
       </c>
       <c r="AF17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.29810342825607522</v>
+        <v>0.30732732499693172</v>
       </c>
       <c r="AG17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.29857749983390514</v>
+        <v>0.30549576943690859</v>
       </c>
       <c r="AH17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.29893638001555883</v>
+        <v>0.30410925098098529</v>
       </c>
       <c r="AI17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.29920658154030827</v>
+        <v>0.30306533877842945</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>2</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>3</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>0.83821626774799995</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>4</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>5</v>
       </c>
@@ -9008,11 +9008,11 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>6.7529269312300005E-4</v>
+        <v>9.7600354280299995E-4</v>
       </c>
       <c r="F21" s="16">
         <f>E21/E17*F17</f>
-        <v>1.8235119831475121E-3</v>
+        <v>1.2430453581737705E-3</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>61</v>
@@ -9023,110 +9023,110 @@
       </c>
       <c r="J21" s="16">
         <f t="shared" si="3"/>
-        <v>6.7529269312300005E-4</v>
+        <v>9.7600354280299995E-4</v>
       </c>
       <c r="K21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
-        <v>7.1613621881495392E-4</v>
+        <v>9.8550253776126203E-4</v>
       </c>
       <c r="L21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
-        <v>7.2974799555173837E-4</v>
+        <v>9.8866823407188129E-4</v>
       </c>
       <c r="M21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
-        <v>7.4759991530522533E-4</v>
+        <v>9.9282006212445028E-4</v>
       </c>
       <c r="N21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
-        <v>7.7079318764067587E-4</v>
+        <v>9.9821413066401919E-4</v>
       </c>
       <c r="O21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
-        <v>8.0055976770015784E-4</v>
+        <v>1.0051369559862567E-3</v>
       </c>
       <c r="P21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
-        <v>8.3816882215225917E-4</v>
+        <v>1.0138837086863031E-3</v>
       </c>
       <c r="Q21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
-        <v>8.8475719855028419E-4</v>
+        <v>1.024718785850213E-3</v>
       </c>
       <c r="R21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
-        <v>9.4107700187202816E-4</v>
+        <v>1.0378171048307644E-3</v>
       </c>
       <c r="S21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
-        <v>1.00718605000015E-3</v>
+        <v>1.053192112355843E-3</v>
       </c>
       <c r="T21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
-        <v>1.0821569576130803E-3</v>
+        <v>1.0706281260536479E-3</v>
       </c>
       <c r="U21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
-        <v>1.1639260043341351E-3</v>
+        <v>1.0896451856582307E-3</v>
       </c>
       <c r="V21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
-        <v>1.2494023381352561E-3</v>
+        <v>1.1095244504883853E-3</v>
       </c>
       <c r="W21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
-        <v>1.334878671936377E-3</v>
+        <v>1.1294037153185398E-3</v>
       </c>
       <c r="X21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
-        <v>1.4166477186574318E-3</v>
+        <v>1.1484207749231225E-3</v>
       </c>
       <c r="Y21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
-        <v>1.4916186262703621E-3</v>
+        <v>1.1658567886209275E-3</v>
       </c>
       <c r="Z21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
-        <v>1.5577276743984837E-3</v>
+        <v>1.1812317961460059E-3</v>
       </c>
       <c r="AA21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
-        <v>1.6140474777202279E-3</v>
+        <v>1.1943301151265573E-3</v>
       </c>
       <c r="AB21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
-        <v>1.6606358541182531E-3</v>
+        <v>1.2051651922904672E-3</v>
       </c>
       <c r="AC21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
-        <v>1.6982449085703544E-3</v>
+        <v>1.2139119449905136E-3</v>
       </c>
       <c r="AD21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
-        <v>1.7280114886298362E-3</v>
+        <v>1.2208347703127514E-3</v>
       </c>
       <c r="AE21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
-        <v>1.7512047609652868E-3</v>
+        <v>1.2262288388523203E-3</v>
       </c>
       <c r="AF21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
-        <v>1.7690566807187739E-3</v>
+        <v>1.2303806669048891E-3</v>
       </c>
       <c r="AG21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
-        <v>1.7826684574555583E-3</v>
+        <v>1.2335463632155085E-3</v>
       </c>
       <c r="AH21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
-        <v>1.7929728020658967E-3</v>
+        <v>1.2359428487255994E-3</v>
       </c>
       <c r="AI21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
-        <v>1.8007309613836603E-3</v>
+        <v>1.2377471669130313E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>31</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17" t="s">
@@ -9382,7 +9382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -9393,10 +9393,10 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>3.0938506857799999E-2</v>
+        <v>3.1135417098900001E-2</v>
       </c>
       <c r="E24">
-        <v>3.0392777097300001E-2</v>
+        <v>3.0643451478599999E-2</v>
       </c>
       <c r="F24" s="26">
         <v>0.75</v>
@@ -9407,114 +9407,114 @@
       </c>
       <c r="I24" s="16">
         <f>D24</f>
-        <v>3.0938506857799999E-2</v>
+        <v>3.1135417098900001E-2</v>
       </c>
       <c r="J24" s="16">
         <f>E24</f>
-        <v>3.0392777097300001E-2</v>
+        <v>3.0643451478599999E-2</v>
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>5.5990061825128029E-2</v>
+        <v>5.6231819420565009E-2</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>6.4520777988344477E-2</v>
+        <v>6.4759563918228083E-2</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>7.570885896633818E-2</v>
+        <v>7.5943747540570206E-2</v>
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>9.0244450242620608E-2</v>
+        <v>9.0474275359685941E-2</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.10889963762538743</v>
+        <v>0.10912296422853242</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.13246982797613069</v>
+        <v>0.13268494392950003</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.16166750167016247</v>
+        <v>0.161872446646149</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.19696401481437317</v>
+        <v>0.19715666428899051</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.23839560279196509</v>
+        <v>0.23857381961867116</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.28538105852724005</v>
+        <v>0.28554290802233562</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.33662701575992449</v>
+        <v>0.33677101378241864</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.39019638854864996</v>
+        <v>0.39032172573929996</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.44376576133737544</v>
+        <v>0.44387243769618129</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.49501171857005988</v>
+        <v>0.49510054345626425</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.54199717430533489</v>
+        <v>0.54206963185992885</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.58342876228292684</v>
+        <v>0.58348678718960945</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.61872527542713751</v>
+        <v>0.61877100483245095</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.64792294912116932</v>
+        <v>0.6479585075491</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.67149313947191258</v>
+        <v>0.67152048725006763</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.69014832685467942</v>
+        <v>0.69016917611891404</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.70468391813096187</v>
+        <v>0.70469970393802983</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.7158719991089556</v>
+        <v>0.71588388756037202</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.72440271527217204</v>
+        <v>0.72441163205803505</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.73086061131459057</v>
+        <v>0.73086727849949984</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.73572277268915998</v>
+        <v>0.73572774614552472</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>2</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>3</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>5</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>31</v>
       </c>
@@ -10148,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17" t="s">
@@ -10277,7 +10277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -10288,10 +10288,10 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>4.0521955492299998E-3</v>
+        <v>4.7888143043300002E-3</v>
       </c>
       <c r="E31">
-        <v>5.1262373158299998E-3</v>
+        <v>6.2858930445499998E-3</v>
       </c>
       <c r="F31" s="16">
         <v>0.25</v>
@@ -10302,114 +10302,114 @@
       </c>
       <c r="I31" s="16">
         <f>D31</f>
-        <v>4.0521955492299998E-3</v>
+        <v>4.7888143043300002E-3</v>
       </c>
       <c r="J31" s="16">
         <f>E31</f>
-        <v>5.1262373158299998E-3</v>
+        <v>6.2858930445499998E-3</v>
       </c>
       <c r="K31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:K$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,K$9))</f>
-        <v>1.3836688276171205E-2</v>
+        <v>1.495509367147381E-2</v>
       </c>
       <c r="L31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:L$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,L$9))</f>
-        <v>1.6739589329403032E-2</v>
+        <v>1.7844247372603116E-2</v>
       </c>
       <c r="M31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:M$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,M$9))</f>
-        <v>2.0546759962356699E-2</v>
+        <v>2.1633388277968481E-2</v>
       </c>
       <c r="N31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:N$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,N$9))</f>
-        <v>2.5493048458885243E-2</v>
+        <v>2.655625249364298E-2</v>
       </c>
       <c r="O31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:O$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,O$9))</f>
-        <v>3.1841186418881846E-2</v>
+        <v>3.2874327393917213E-2</v>
       </c>
       <c r="P31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:P$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,P$9))</f>
-        <v>3.9861841318768847E-2</v>
+        <v>4.0856998647451973E-2</v>
       </c>
       <c r="Q31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Q$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Q$9))</f>
-        <v>4.979746173992311E-2</v>
+        <v>5.0745566664896324E-2</v>
       </c>
       <c r="R31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:R$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,R$9))</f>
-        <v>6.1808444548558425E-2</v>
+        <v>6.2699668716406365E-2</v>
       </c>
       <c r="S31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:S$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,S$9))</f>
-        <v>7.5907120213776075E-2</v>
+        <v>7.6731576877325819E-2</v>
       </c>
       <c r="T31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:T$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,T$9))</f>
-        <v>9.1895710893726751E-2</v>
+        <v>9.2644449928025716E-2</v>
       </c>
       <c r="U31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:U$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,U$9))</f>
-        <v>0.10933409946256448</v>
+        <v>0.11000025501800546</v>
       </c>
       <c r="V31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:V$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,V$9))</f>
-        <v>0.127563118657915</v>
+        <v>0.12814294652227501</v>
       </c>
       <c r="W31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:W$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,W$9))</f>
-        <v>0.14579213785326553</v>
+        <v>0.14628563802654454</v>
       </c>
       <c r="X31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:X$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,X$9))</f>
-        <v>0.16323052642210323</v>
+        <v>0.16364144311652429</v>
       </c>
       <c r="Y31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Y$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Y$9))</f>
-        <v>0.1792191171020539</v>
+        <v>0.17955431616722417</v>
       </c>
       <c r="Z31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Z$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Z$9))</f>
-        <v>0.19331779276727157</v>
+        <v>0.19358622432814362</v>
       </c>
       <c r="AA31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AA$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AA$9))</f>
-        <v>0.20532877557590687</v>
+        <v>0.20554032637965367</v>
       </c>
       <c r="AB31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AB$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AB$9))</f>
-        <v>0.21526439599706118</v>
+        <v>0.21542889439709806</v>
       </c>
       <c r="AC31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AC$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AC$9))</f>
-        <v>0.22328505089694817</v>
+        <v>0.2234115656506328</v>
       </c>
       <c r="AD31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AD$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AD$9))</f>
-        <v>0.22963318885694475</v>
+        <v>0.22972964055090703</v>
       </c>
       <c r="AE31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AE$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AE$9))</f>
-        <v>0.23457947735347331</v>
+        <v>0.23465250476658153</v>
       </c>
       <c r="AF31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AF$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AF$9))</f>
-        <v>0.238386647986427</v>
+        <v>0.23844164567194689</v>
       </c>
       <c r="AG31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AG$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AG$9))</f>
-        <v>0.2412895490396588</v>
+        <v>0.24133079937307619</v>
       </c>
       <c r="AH31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AH$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AH$9))</f>
-        <v>0.24348709410674613</v>
+        <v>0.24351793746271427</v>
       </c>
       <c r="AI31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AI$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AI$9))</f>
-        <v>0.24514162968209213</v>
+        <v>0.24516463760629623</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>2</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>3</v>
       </c>
@@ -10663,7 +10663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>4</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>5</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>31</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17" t="s">
@@ -11172,7 +11172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -11301,7 +11301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>2</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>3</v>
       </c>
@@ -11547,7 +11547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>4</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>5</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>31</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17" t="s">
@@ -12042,7 +12042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>2</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>3</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>4</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>5</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>31</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17" t="s">
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>0.99774649999676845</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>2</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>3</v>
       </c>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>4</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>1.0000000000000142</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>5</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>31</v>
       </c>
@@ -13658,7 +13658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17" t="s">
@@ -13784,7 +13784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -13913,7 +13913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>2</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>3</v>
       </c>
@@ -14159,7 +14159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>4</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>5</v>
       </c>
@@ -14405,7 +14405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>31</v>
       </c>
@@ -14528,7 +14528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17" t="s">
@@ -14654,7 +14654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -14783,7 +14783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>2</v>
       </c>
@@ -14906,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>3</v>
       </c>
@@ -15029,7 +15029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>4</v>
       </c>
@@ -15152,7 +15152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>5</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>31</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17" t="s">
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>2</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>3</v>
       </c>
@@ -15899,7 +15899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>4</v>
       </c>
@@ -16022,7 +16022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>5</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>31</v>
       </c>
@@ -16268,7 +16268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="17"/>
       <c r="B79" s="17"/>
       <c r="C79" s="17" t="s">
@@ -16394,7 +16394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -16406,11 +16406,11 @@
       </c>
       <c r="D80">
         <f>D10</f>
-        <v>5.0773251135200002E-2</v>
+        <v>0.15905875518900001</v>
       </c>
       <c r="E80">
         <f>E10</f>
-        <v>4.1738099814E-2</v>
+        <v>0.13060041262200001</v>
       </c>
       <c r="F80">
         <f>F10</f>
@@ -16422,128 +16422,128 @@
       </c>
       <c r="I80" s="16">
         <f t="shared" si="9"/>
-        <v>4.1738099814E-2</v>
+        <v>0.13060041262200001</v>
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>0.10208306765026703</v>
+        <v>0.18534942239376065</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>0.12143932599985952</v>
+        <v>0.20291072063493176</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>0.14628142699716032</v>
+        <v>0.22544914395371735</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.17766857080894907</v>
+        <v>0.25392566991561405</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.21654952889910542</v>
+        <v>0.28920108774646175</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.2635519806241971</v>
+        <v>0.33184487033618731</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.31872417867827213</v>
+        <v>0.38190079577122726</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.38129216112899533</v>
+        <v>0.43866667377928981</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.44953362229243138</v>
+        <v>0.50057991291156378</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.520869049907</v>
+        <v>0.56530020631099998</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.59220447752156857</v>
+        <v>0.63002049971043617</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.66044593868500467</v>
+        <v>0.69193373884271026</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.72301392113572782</v>
+        <v>0.74869961685077269</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.77818611918980285</v>
+        <v>0.7987555422858128</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.8251885709148945</v>
+        <v>0.84139932487553826</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.86406952900505107</v>
+        <v>0.87667474270638612</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.89545667281683972</v>
+        <v>0.90515126866828277</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.92029877381414049</v>
+        <v>0.9276896919870683</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.93965503216373303</v>
+        <v>0.94525099022823955</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.95455359265088469</v>
+        <v>0.95876796542838227</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.96591348457572779</v>
+        <v>0.96907442272382549</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.97451311439579758</v>
+        <v>0.97687658475877748</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.98098779092699173</v>
+        <v>0.98275084638133969</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.98584260831619597</v>
+        <v>0.98715546294195899</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.98947163147757322</v>
+        <v>0.99044795661041651</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.99217811905636955</v>
+        <v>0.99290346400749918</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
         <v>2</v>
       </c>
       <c r="D81">
         <f t="shared" ref="D81:E81" si="10">D11</f>
-        <v>1.0005073039100001E-4</v>
+        <v>1.00045127707E-4</v>
       </c>
       <c r="E81">
         <f t="shared" si="10"/>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="F81">
         <f t="shared" ref="F81" si="11">F11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="G81" s="5" t="str">
         <f>IF(E81=F81,"n/a",IF(OR(C81="battery electric vehicle",C81="natural gas vehicle",C81="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16551,114 +16551,114 @@
       </c>
       <c r="I81" s="16">
         <f t="shared" si="9"/>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="J81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,J$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="K81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,K$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="L81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,L$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="M81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,M$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="N81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,N$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="O81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,O$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="P81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,P$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Q81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Q$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="R81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,R$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="S81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,S$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="T81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,T$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="U81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,U$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="V81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,V$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="W81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,W$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="X81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,X$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Y81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Y$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Z81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Z$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AA81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AA$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AB81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AB$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AC81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AC$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AD81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AD$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AE81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AE$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AF81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AF$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AG81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AG$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AH81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AH$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AI81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AI$9))</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C82" t="s">
         <v>3</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>4</v>
       </c>
@@ -16797,11 +16797,11 @@
       </c>
       <c r="E83">
         <f t="shared" si="14"/>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="F83">
         <f t="shared" ref="F83" si="15">F13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="G83" s="5" t="str">
         <f>IF(E83=F83,"n/a",IF(OR(C83="battery electric vehicle",C83="natural gas vehicle",C83="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16809,120 +16809,120 @@
       </c>
       <c r="I83" s="16">
         <f t="shared" si="9"/>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="J83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,J$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="K83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,K$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="L83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,L$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="M83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,M$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="N83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,N$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="O83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,O$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="P83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,P$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Q83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Q$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="R83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,R$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="S83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,S$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="T83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,T$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="U83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,U$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="V83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,V$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="W83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,W$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="X83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,X$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Y83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Y$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Z83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Z$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AA83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AA$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AB83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AB$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AC83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AC$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AD83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AD$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AE83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AE$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AF83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AF$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AG83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AG$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AH83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AH$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AI83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AI$9))</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C84" t="s">
         <v>5</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:E84" si="16">D14</f>
-        <v>1.5463740197399999E-2</v>
+        <v>1.6690003398299999E-2</v>
       </c>
       <c r="E84">
         <f t="shared" si="16"/>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="F84">
         <f t="shared" ref="F84" si="17">F14</f>
-        <v>0.30456470388754209</v>
+        <v>0.10492980017647105</v>
       </c>
       <c r="G84" s="5" t="str">
         <f>IF(E84=F84,"n/a",IF(OR(C84="battery electric vehicle",C84="natural gas vehicle",C84="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16942,110 +16942,110 @@
       </c>
       <c r="J84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,J$9))</f>
-        <v>4.4996485878868705E-3</v>
+        <v>1.5502361933759918E-3</v>
       </c>
       <c r="K84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,K$9))</f>
-        <v>6.0426568409376203E-3</v>
+        <v>2.0818393161168456E-3</v>
       </c>
       <c r="L84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,L$9))</f>
-        <v>8.1005054730370115E-3</v>
+        <v>2.7908172213154192E-3</v>
       </c>
       <c r="M84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,M$9))</f>
-        <v>1.0833728727748151E-2</v>
+        <v>3.7324777824171446E-3</v>
       </c>
       <c r="N84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,N$9))</f>
-        <v>1.4444247020933752E-2</v>
+        <v>4.9763873957167403E-3</v>
       </c>
       <c r="O84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,O$9))</f>
-        <v>1.9179461540303897E-2</v>
+        <v>6.6077816675024067E-3</v>
       </c>
       <c r="P84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,P$9))</f>
-        <v>2.5331467679199877E-2</v>
+        <v>8.7272944232455497E-3</v>
       </c>
       <c r="Q84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Q$9))</f>
-        <v>3.3227041042513977E-2</v>
+        <v>1.1447507647943856E-2</v>
       </c>
       <c r="R84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,R$9))</f>
-        <v>4.3202827577549584E-2</v>
+        <v>1.4884403894827813E-2</v>
       </c>
       <c r="S84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,S$9))</f>
-        <v>5.5560375639612684E-2</v>
+        <v>1.9141873760089034E-2</v>
       </c>
       <c r="T84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,T$9))</f>
-        <v>7.0499180770926387E-2</v>
+        <v>2.4288648213253456E-2</v>
       </c>
       <c r="U84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,U$9))</f>
-        <v>8.803457914156243E-2</v>
+        <v>3.0330010930467905E-2</v>
       </c>
       <c r="V84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,V$9))</f>
-        <v>0.10792058216875849</v>
+        <v>3.7181212981519933E-2</v>
       </c>
       <c r="W84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,W$9))</f>
-        <v>0.12960978885438473</v>
+        <v>4.4653661674554562E-2</v>
       </c>
       <c r="X84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,X$9))</f>
-        <v>0.15228235194377104</v>
+        <v>5.2464900088235525E-2</v>
       </c>
       <c r="Y84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Y$9))</f>
-        <v>0.17495491503315735</v>
+        <v>6.0276138501916494E-2</v>
       </c>
       <c r="Z84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Z$9))</f>
-        <v>0.19664412171878359</v>
+        <v>6.774858719495111E-2</v>
       </c>
       <c r="AA84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AA$9))</f>
-        <v>0.21653012474597963</v>
+        <v>7.4599789246003134E-2</v>
       </c>
       <c r="AB84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AB$9))</f>
-        <v>0.23406552311661569</v>
+        <v>8.0641151963217597E-2</v>
       </c>
       <c r="AC84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AC$9))</f>
-        <v>0.2490043282479294</v>
+        <v>8.5787926416382013E-2</v>
       </c>
       <c r="AD84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AD$9))</f>
-        <v>0.26136187630999252</v>
+        <v>9.004539628164325E-2</v>
       </c>
       <c r="AE84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AE$9))</f>
-        <v>0.27133766284502814</v>
+        <v>9.3482292528527203E-2</v>
       </c>
       <c r="AF84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AF$9))</f>
-        <v>0.27923323620834223</v>
+        <v>9.6202505753225503E-2</v>
       </c>
       <c r="AG84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AG$9))</f>
-        <v>0.28538524234723822</v>
+        <v>9.8322018508968642E-2</v>
       </c>
       <c r="AH84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AH$9))</f>
-        <v>0.29012045686660837</v>
+        <v>9.9953412780754314E-2</v>
       </c>
       <c r="AI84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AI$9))</f>
-        <v>0.29373097515979396</v>
+        <v>0.10119732239405391</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C85" t="s">
         <v>31</v>
       </c>
@@ -17174,7 +17174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="17"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17" t="s">
@@ -17305,7 +17305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -17434,7 +17434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>2</v>
       </c>
@@ -17557,7 +17557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>3</v>
       </c>
@@ -17680,7 +17680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
         <v>4</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>5</v>
       </c>
@@ -17926,7 +17926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C92" t="s">
         <v>31</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="17"/>
       <c r="B93" s="17"/>
       <c r="C93" s="17" t="s">
@@ -18190,13 +18190,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -18309,233 +18309,233 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Data!I10</f>
-        <v>5.0773251135200002E-2</v>
+        <v>0.15905875518900001</v>
       </c>
       <c r="C2">
         <f>Data!J10</f>
-        <v>4.1738099814E-2</v>
+        <v>0.13060041262200001</v>
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>8.7184507163115391E-2</v>
+        <v>0.17183244719361793</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>0.10208306765026703</v>
+        <v>0.18534942239376065</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>0.12143932599985952</v>
+        <v>0.20291072063493176</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.14628142699716032</v>
+        <v>0.22544914395371735</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.17766857080894907</v>
+        <v>0.25392566991561405</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.21654952889910542</v>
+        <v>0.28920108774646175</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.2635519806241971</v>
+        <v>0.33184487033618731</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.31872417867827213</v>
+        <v>0.38190079577122726</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.38129216112899533</v>
+        <v>0.43866667377928981</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.44953362229243138</v>
+        <v>0.50057991291156378</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.520869049907</v>
+        <v>0.56530020631099998</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.59220447752156857</v>
+        <v>0.63002049971043617</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.66044593868500467</v>
+        <v>0.69193373884271026</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.72301392113572782</v>
+        <v>0.74869961685077269</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.77818611918980285</v>
+        <v>0.7987555422858128</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.8251885709148945</v>
+        <v>0.84139932487553826</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.86406952900505107</v>
+        <v>0.87667474270638612</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.89545667281683972</v>
+        <v>0.90515126866828277</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.92029877381414049</v>
+        <v>0.9276896919870683</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.93965503216373303</v>
+        <v>0.94525099022823955</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.95455359265088469</v>
+        <v>0.95876796542838227</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.96591348457572779</v>
+        <v>0.96907442272382549</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.97451311439579758</v>
+        <v>0.97687658475877748</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.98098779092699173</v>
+        <v>0.98275084638133969</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.98584260831619597</v>
+        <v>0.98715546294195899</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f>Data!I11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="C3">
         <f>Data!J11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="D3">
         <f>Data!K11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="E3">
         <f>Data!L11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="F3">
         <f>Data!M11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="G3">
         <f>Data!N11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="H3">
         <f>Data!O11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="I3">
         <f>Data!P11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="J3">
         <f>Data!Q11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="K3">
         <f>Data!R11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="L3">
         <f>Data!S11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="M3">
         <f>Data!T11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="N3">
         <f>Data!U11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="O3">
         <f>Data!V11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="P3">
         <f>Data!W11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Q3">
         <f>Data!X11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="R3">
         <f>Data!Y11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="S3">
         <f>Data!Z11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="T3">
         <f>Data!AA11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="U3">
         <f>Data!AB11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="V3">
         <f>Data!AC11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="W3">
         <f>Data!AD11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="X3">
         <f>Data!AE11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Y3">
         <f>Data!AF11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="Z3">
         <f>Data!AG11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AA3">
         <f>Data!AH11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
       <c r="AB3">
         <f>Data!AI11</f>
-        <v>9.1114481822700006E-5</v>
+        <v>9.1108650682499996E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -18648,126 +18648,126 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f>Data!I13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="C5">
         <f>Data!J13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="D5">
         <f>Data!K13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="E5">
         <f>Data!L13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="F5">
         <f>Data!M13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="G5">
         <f>Data!N13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="H5">
         <f>Data!O13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="I5">
         <f>Data!P13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="K5">
         <f>Data!R13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="L5">
         <f>Data!S13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="M5">
         <f>Data!T13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="N5">
         <f>Data!U13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="O5">
         <f>Data!V13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="P5">
         <f>Data!W13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI13</f>
-        <v>6.08023121013E-2</v>
+        <v>6.0801825684799998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
         <f>Data!I14</f>
-        <v>1.5463740197399999E-2</v>
+        <v>1.6690003398299999E-2</v>
       </c>
       <c r="C6">
         <f>Data!J14</f>
@@ -18775,106 +18775,106 @@
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>1.1928496766138092E-2</v>
+        <v>4.1096514668315402E-3</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.7458920658236333E-2</v>
+        <v>6.0150143223491733E-3</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>2.533146767919987E-2</v>
+        <v>8.7272944232455463E-3</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>3.6305002648196E-2</v>
+        <v>1.2507938788232255E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>5.1161270790237426E-2</v>
+        <v>1.7626277281218222E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>7.0499180770926373E-2</v>
+        <v>2.4288648213253449E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>9.4422830352950293E-2</v>
+        <v>3.2530915744886375E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>0.1222255739642677</v>
+        <v>4.2109623632752446E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>0.15228235194377104</v>
+        <v>5.2464900088235525E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>0.18233912992327439</v>
+        <v>6.2820176543718603E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>0.21014187353459179</v>
+        <v>7.2398884431584667E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>0.23406552311661571</v>
+        <v>8.0641151963217611E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>0.25340343309730462</v>
+        <v>8.7303522895252825E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>0.26825970123934606</v>
+        <v>9.2421861388238782E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>0.27923323620834223</v>
+        <v>9.6202505753225503E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>0.28710578322930574</v>
+        <v>9.8914785854121876E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>0.29263620712140404</v>
+        <v>0.10082014870963951</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>0.29646419841450505</v>
+        <v>0.10213898295515562</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>0.29908673917637851</v>
+        <v>0.10304251075921672</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>0.30087081067793731</v>
+        <v>0.10365716591711784</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>0.30207867282131895</v>
+        <v>0.10407330321644376</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>0.3028937708877924</v>
+        <v>0.10435412392924331</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>0.30344261445351972</v>
+        <v>0.10454321362002106</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>0.30381163014801615</v>
+        <v>0.10467034832273366</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>0.30405949162775042</v>
+        <v>0.10475574251059583</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -18987,7 +18987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -19111,12 +19111,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -19229,120 +19229,120 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Data!I17</f>
-        <v>0.26000976646599999</v>
+        <v>0.454500581771</v>
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.11612183754114395</v>
+        <v>0.2372655299631645</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
-        <v>0.26143226663209485</v>
+        <v>0.44900481233409134</v>
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>0.26190633820992476</v>
+        <v>0.44717325677406827</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>0.262528085681139</v>
+        <v>0.44477116162412172</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>0.26333586202244447</v>
+        <v>0.44165035177522616</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>0.2643725738234296</v>
+        <v>0.43764505942691106</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>0.2656824236784171</v>
+        <v>0.43258450971903878</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>0.26730500576557847</v>
+        <v>0.42631573221303853</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.26926651443120747</v>
+        <v>0.41873752615603005</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.27156896335914493</v>
+        <v>0.40984211176536622</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.27418005353133063</v>
+        <v>0.39975427493600035</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.277027909600843</v>
+        <v>0.38875170304139878</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.28000488323299999</v>
+        <v>0.37725029088549999</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.28298185686515698</v>
+        <v>0.36574887872960121</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.28582971293466936</v>
+        <v>0.35474630683499964</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.28844080310685505</v>
+        <v>0.34465847000563377</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.29074325203479251</v>
+        <v>0.33576305561496994</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.29270476070042151</v>
+        <v>0.32818484955796146</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.29432734278758288</v>
+        <v>0.32191607205196121</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.29563719264257038</v>
+        <v>0.31685552234408898</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.29667390444355551</v>
+        <v>0.31285022999577383</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.29748168078486098</v>
+        <v>0.30972942014687826</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.29810342825607522</v>
+        <v>0.30732732499693172</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.29857749983390514</v>
+        <v>0.30549576943690859</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.29893638001555883</v>
+        <v>0.30410925098098529</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.29920658154030827</v>
+        <v>0.30306533877842945</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -19455,7 +19455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -19568,7 +19568,7 @@
         <v>0.83821626774799995</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -19681,7 +19681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -19691,110 +19691,110 @@
       </c>
       <c r="C6">
         <f>Data!J21</f>
-        <v>6.7529269312300005E-4</v>
+        <v>9.7600354280299995E-4</v>
       </c>
       <c r="D6">
         <f>Data!K21</f>
-        <v>7.1613621881495392E-4</v>
+        <v>9.8550253776126203E-4</v>
       </c>
       <c r="E6">
         <f>Data!L21</f>
-        <v>7.2974799555173837E-4</v>
+        <v>9.8866823407188129E-4</v>
       </c>
       <c r="F6">
         <f>Data!M21</f>
-        <v>7.4759991530522533E-4</v>
+        <v>9.9282006212445028E-4</v>
       </c>
       <c r="G6">
         <f>Data!N21</f>
-        <v>7.7079318764067587E-4</v>
+        <v>9.9821413066401919E-4</v>
       </c>
       <c r="H6">
         <f>Data!O21</f>
-        <v>8.0055976770015784E-4</v>
+        <v>1.0051369559862567E-3</v>
       </c>
       <c r="I6">
         <f>Data!P21</f>
-        <v>8.3816882215225917E-4</v>
+        <v>1.0138837086863031E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q21</f>
-        <v>8.8475719855028419E-4</v>
+        <v>1.024718785850213E-3</v>
       </c>
       <c r="K6">
         <f>Data!R21</f>
-        <v>9.4107700187202816E-4</v>
+        <v>1.0378171048307644E-3</v>
       </c>
       <c r="L6">
         <f>Data!S21</f>
-        <v>1.00718605000015E-3</v>
+        <v>1.053192112355843E-3</v>
       </c>
       <c r="M6">
         <f>Data!T21</f>
-        <v>1.0821569576130803E-3</v>
+        <v>1.0706281260536479E-3</v>
       </c>
       <c r="N6">
         <f>Data!U21</f>
-        <v>1.1639260043341351E-3</v>
+        <v>1.0896451856582307E-3</v>
       </c>
       <c r="O6">
         <f>Data!V21</f>
-        <v>1.2494023381352561E-3</v>
+        <v>1.1095244504883853E-3</v>
       </c>
       <c r="P6">
         <f>Data!W21</f>
-        <v>1.334878671936377E-3</v>
+        <v>1.1294037153185398E-3</v>
       </c>
       <c r="Q6">
         <f>Data!X21</f>
-        <v>1.4166477186574318E-3</v>
+        <v>1.1484207749231225E-3</v>
       </c>
       <c r="R6">
         <f>Data!Y21</f>
-        <v>1.4916186262703621E-3</v>
+        <v>1.1658567886209275E-3</v>
       </c>
       <c r="S6">
         <f>Data!Z21</f>
-        <v>1.5577276743984837E-3</v>
+        <v>1.1812317961460059E-3</v>
       </c>
       <c r="T6">
         <f>Data!AA21</f>
-        <v>1.6140474777202279E-3</v>
+        <v>1.1943301151265573E-3</v>
       </c>
       <c r="U6">
         <f>Data!AB21</f>
-        <v>1.6606358541182531E-3</v>
+        <v>1.2051651922904672E-3</v>
       </c>
       <c r="V6">
         <f>Data!AC21</f>
-        <v>1.6982449085703544E-3</v>
+        <v>1.2139119449905136E-3</v>
       </c>
       <c r="W6">
         <f>Data!AD21</f>
-        <v>1.7280114886298362E-3</v>
+        <v>1.2208347703127514E-3</v>
       </c>
       <c r="X6">
         <f>Data!AE21</f>
-        <v>1.7512047609652868E-3</v>
+        <v>1.2262288388523203E-3</v>
       </c>
       <c r="Y6">
         <f>Data!AF21</f>
-        <v>1.7690566807187739E-3</v>
+        <v>1.2303806669048891E-3</v>
       </c>
       <c r="Z6">
         <f>Data!AG21</f>
-        <v>1.7826684574555583E-3</v>
+        <v>1.2335463632155085E-3</v>
       </c>
       <c r="AA6">
         <f>Data!AH21</f>
-        <v>1.7929728020658967E-3</v>
+        <v>1.2359428487255994E-3</v>
       </c>
       <c r="AB6">
         <f>Data!AI21</f>
-        <v>1.8007309613836603E-3</v>
+        <v>1.2377471669130313E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -19907,7 +19907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -20031,12 +20031,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -20149,120 +20149,120 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Data!I24</f>
-        <v>3.0938506857799999E-2</v>
+        <v>3.1135417098900001E-2</v>
       </c>
       <c r="C2">
         <f>Data!J24</f>
-        <v>3.0392777097300001E-2</v>
+        <v>3.0643451478599999E-2</v>
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>5.5990061825128029E-2</v>
+        <v>5.6231819420565009E-2</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>6.4520777988344477E-2</v>
+        <v>6.4759563918228083E-2</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>7.570885896633818E-2</v>
+        <v>7.5943747540570206E-2</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>9.0244450242620608E-2</v>
+        <v>9.0474275359685941E-2</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.10889963762538743</v>
+        <v>0.10912296422853242</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.13246982797613069</v>
+        <v>0.13268494392950003</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.16166750167016247</v>
+        <v>0.161872446646149</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.19696401481437317</v>
+        <v>0.19715666428899051</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.23839560279196509</v>
+        <v>0.23857381961867116</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.28538105852724005</v>
+        <v>0.28554290802233562</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.33662701575992449</v>
+        <v>0.33677101378241864</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.39019638854864996</v>
+        <v>0.39032172573929996</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.44376576133737544</v>
+        <v>0.44387243769618129</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.49501171857005988</v>
+        <v>0.49510054345626425</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.54199717430533489</v>
+        <v>0.54206963185992885</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.58342876228292684</v>
+        <v>0.58348678718960945</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.61872527542713751</v>
+        <v>0.61877100483245095</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.64792294912116932</v>
+        <v>0.6479585075491</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.67149313947191258</v>
+        <v>0.67152048725006763</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.69014832685467942</v>
+        <v>0.69016917611891404</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.70468391813096187</v>
+        <v>0.70469970393802983</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.7158719991089556</v>
+        <v>0.71588388756037202</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.72440271527217204</v>
+        <v>0.72441163205803505</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.73086061131459057</v>
+        <v>0.73086727849949984</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.73572277268915998</v>
+        <v>0.73572774614552472</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -20375,7 +20375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -20488,7 +20488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -20601,7 +20601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -20714,7 +20714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -20827,7 +20827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -20951,12 +20951,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -21069,120 +21069,120 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Data!I31</f>
-        <v>4.0521955492299998E-3</v>
+        <v>4.7888143043300002E-3</v>
       </c>
       <c r="C2">
         <f>Data!J31</f>
-        <v>5.1262373158299998E-3</v>
+        <v>6.2858930445499998E-3</v>
       </c>
       <c r="D2">
         <f>Data!K31</f>
-        <v>1.3836688276171205E-2</v>
+        <v>1.495509367147381E-2</v>
       </c>
       <c r="E2">
         <f>Data!L31</f>
-        <v>1.6739589329403032E-2</v>
+        <v>1.7844247372603116E-2</v>
       </c>
       <c r="F2">
         <f>Data!M31</f>
-        <v>2.0546759962356699E-2</v>
+        <v>2.1633388277968481E-2</v>
       </c>
       <c r="G2">
         <f>Data!N31</f>
-        <v>2.5493048458885243E-2</v>
+        <v>2.655625249364298E-2</v>
       </c>
       <c r="H2">
         <f>Data!O31</f>
-        <v>3.1841186418881846E-2</v>
+        <v>3.2874327393917213E-2</v>
       </c>
       <c r="I2">
         <f>Data!P31</f>
-        <v>3.9861841318768847E-2</v>
+        <v>4.0856998647451973E-2</v>
       </c>
       <c r="J2">
         <f>Data!Q31</f>
-        <v>4.979746173992311E-2</v>
+        <v>5.0745566664896324E-2</v>
       </c>
       <c r="K2">
         <f>Data!R31</f>
-        <v>6.1808444548558425E-2</v>
+        <v>6.2699668716406365E-2</v>
       </c>
       <c r="L2">
         <f>Data!S31</f>
-        <v>7.5907120213776075E-2</v>
+        <v>7.6731576877325819E-2</v>
       </c>
       <c r="M2">
         <f>Data!T31</f>
-        <v>9.1895710893726751E-2</v>
+        <v>9.2644449928025716E-2</v>
       </c>
       <c r="N2">
         <f>Data!U31</f>
-        <v>0.10933409946256448</v>
+        <v>0.11000025501800546</v>
       </c>
       <c r="O2">
         <f>Data!V31</f>
-        <v>0.127563118657915</v>
+        <v>0.12814294652227501</v>
       </c>
       <c r="P2">
         <f>Data!W31</f>
-        <v>0.14579213785326553</v>
+        <v>0.14628563802654454</v>
       </c>
       <c r="Q2">
         <f>Data!X31</f>
-        <v>0.16323052642210323</v>
+        <v>0.16364144311652429</v>
       </c>
       <c r="R2">
         <f>Data!Y31</f>
-        <v>0.1792191171020539</v>
+        <v>0.17955431616722417</v>
       </c>
       <c r="S2">
         <f>Data!Z31</f>
-        <v>0.19331779276727157</v>
+        <v>0.19358622432814362</v>
       </c>
       <c r="T2">
         <f>Data!AA31</f>
-        <v>0.20532877557590687</v>
+        <v>0.20554032637965367</v>
       </c>
       <c r="U2">
         <f>Data!AB31</f>
-        <v>0.21526439599706118</v>
+        <v>0.21542889439709806</v>
       </c>
       <c r="V2">
         <f>Data!AC31</f>
-        <v>0.22328505089694817</v>
+        <v>0.2234115656506328</v>
       </c>
       <c r="W2">
         <f>Data!AD31</f>
-        <v>0.22963318885694475</v>
+        <v>0.22972964055090703</v>
       </c>
       <c r="X2">
         <f>Data!AE31</f>
-        <v>0.23457947735347331</v>
+        <v>0.23465250476658153</v>
       </c>
       <c r="Y2">
         <f>Data!AF31</f>
-        <v>0.238386647986427</v>
+        <v>0.23844164567194689</v>
       </c>
       <c r="Z2">
         <f>Data!AG31</f>
-        <v>0.2412895490396588</v>
+        <v>0.24133079937307619</v>
       </c>
       <c r="AA2">
         <f>Data!AH31</f>
-        <v>0.24348709410674613</v>
+        <v>0.24351793746271427</v>
       </c>
       <c r="AB2">
         <f>Data!AI31</f>
-        <v>0.24514162968209213</v>
+        <v>0.24516463760629623</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -21295,7 +21295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -21408,7 +21408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -21521,7 +21521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -21634,7 +21634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -21747,7 +21747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -21871,12 +21871,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -21989,7 +21989,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -22102,7 +22102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -22215,7 +22215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -22328,7 +22328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -22441,7 +22441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -22554,7 +22554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -22667,7 +22667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -22791,12 +22791,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
@@ -22909,7 +22909,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -23022,7 +23022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -23135,7 +23135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -23248,7 +23248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -23361,7 +23361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -23474,7 +23474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F805FB-F374-4D13-9550-481F01E73012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06641E14-21DC-4145-949A-E72A3CBD9CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5070,111 +5070,111 @@
       </c>
       <c r="B2">
         <f>Data!I80</f>
-        <v>0.14828894775500001</v>
+        <v>0.18123793393000001</v>
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>0.20192405110570355</v>
+        <v>0.23279812904258823</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>0.21912805260389268</v>
+        <v>0.24933658275197695</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>0.2412079161321001</v>
+        <v>0.2705622726537894</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.2691050675034683</v>
+        <v>0.29738020490215311</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.30366278259245705</v>
+        <v>0.33060103270559432</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.34543894796969088</v>
+        <v>0.37076106043634494</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.39447645102619855</v>
+        <v>0.41790151635931294</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.45008738803580778</v>
+        <v>0.47136110874344317</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.51074095955207577</v>
+        <v>0.52966825809683538</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.57414447387750001</v>
+        <v>0.59061896696500005</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.63754798820292424</v>
+        <v>0.65156967583316472</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.69820155971919218</v>
+        <v>0.70987682518655681</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.75381249672880146</v>
+        <v>0.76333641757068704</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.80284999978530913</v>
+        <v>0.81047687349365505</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.84462616516254285</v>
+        <v>0.85063690122440572</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.87918388025153182</v>
+        <v>0.88385772902784698</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.90708103162289988</v>
+        <v>0.91067566127621058</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.92916089515110734</v>
+        <v>0.93190135117802309</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.94636489664929646</v>
+        <v>0.94843980488741186</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.95960685965229675</v>
+        <v>0.96116949409196173</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.96970362495499696</v>
+        <v>0.97087565957856936</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.97734704661409399</v>
+        <v>0.97822339058775476</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.98310179232636641</v>
+        <v>0.98375551028570629</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.98741679392062143</v>
+        <v>0.98790358328663208</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.99064229953114202</v>
+        <v>0.99100430815198304</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.99304784793411749</v>
+        <v>0.99331679637819548</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -5183,111 +5183,111 @@
       </c>
       <c r="B3">
         <f>Data!I81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="C3">
         <f>Data!J81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="D3">
         <f>Data!K81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="E3">
         <f>Data!L81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="F3">
         <f>Data!M81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="G3">
         <f>Data!N81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="H3">
         <f>Data!O81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="I3">
         <f>Data!P81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="K3">
         <f>Data!R81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="L3">
         <f>Data!S81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="M3">
         <f>Data!T81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="N3">
         <f>Data!U81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="O3">
         <f>Data!V81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="P3">
         <f>Data!W81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI81</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -5409,111 +5409,111 @@
       </c>
       <c r="B5">
         <f>Data!I83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="C5">
         <f>Data!J83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="D5">
         <f>Data!K83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="E5">
         <f>Data!L83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="F5">
         <f>Data!M83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="G5">
         <f>Data!N83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="H5">
         <f>Data!O83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="I5">
         <f>Data!P83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="K5">
         <f>Data!R83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="L5">
         <f>Data!S83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="M5">
         <f>Data!T83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="N5">
         <f>Data!U83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="O5">
         <f>Data!V83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="P5">
         <f>Data!W83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI83</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -5522,111 +5522,111 @@
       </c>
       <c r="B6">
         <f>Data!I84</f>
-        <v>1.4073498597800001E-2</v>
+        <v>1.3970074369600001E-2</v>
       </c>
       <c r="C6">
         <f>Data!J84</f>
-        <v>1.5378299229133533E-2</v>
+        <v>1.5110140554321749E-2</v>
       </c>
       <c r="D6">
         <f>Data!K84</f>
-        <v>1.5825738202068743E-2</v>
+        <v>1.550108920235292E-2</v>
       </c>
       <c r="E6">
         <f>Data!L84</f>
-        <v>1.6422469733855565E-2</v>
+        <v>1.6022481838446352E-2</v>
       </c>
       <c r="F6">
         <f>Data!M84</f>
-        <v>1.7215045278070985E-2</v>
+        <v>1.6714992675043627E-2</v>
       </c>
       <c r="G6">
         <f>Data!N84</f>
-        <v>1.8262017381864146E-2</v>
+        <v>1.7629781849127387E-2</v>
       </c>
       <c r="H6">
         <f>Data!O84</f>
-        <v>1.96351270311391E-2</v>
+        <v>1.8829532862010948E-2</v>
       </c>
       <c r="I6">
         <f>Data!P84</f>
-        <v>2.1419075563388585E-2</v>
+        <v>2.0388253288765361E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q84</f>
-        <v>2.3708620826306676E-2</v>
+        <v>2.2388737554300295E-2</v>
       </c>
       <c r="K6">
         <f>Data!R84</f>
-        <v>2.6601382853102151E-2</v>
+        <v>2.4916280910733307E-2</v>
       </c>
       <c r="L6">
         <f>Data!S84</f>
-        <v>3.0184804135493147E-2</v>
+        <v>2.8047286009566623E-2</v>
       </c>
       <c r="M6">
         <f>Data!T84</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.18322986028182E-2</v>
       </c>
       <c r="N6">
         <f>Data!U84</f>
-        <v>3.9601619783156121E-2</v>
+        <v>3.6275204382572757E-2</v>
       </c>
       <c r="O6">
         <f>Data!V84</f>
-        <v>4.5368129944513266E-2</v>
+        <v>4.1313677756162917E-2</v>
       </c>
       <c r="P6">
         <f>Data!W84</f>
-        <v>5.1657530110720232E-2</v>
+        <v>4.6809024922225891E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X84</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.2553522963420404E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y84</f>
-        <v>6.4806634559729431E-2</v>
+        <v>5.8298021004614918E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z84</f>
-        <v>7.1096034725936397E-2</v>
+        <v>6.3793368170677878E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA84</f>
-        <v>7.6862544887293549E-2</v>
+        <v>6.8831841544268038E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB84</f>
-        <v>8.194743061065532E-2</v>
+        <v>7.3274747324022602E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC84</f>
-        <v>8.6279360534956523E-2</v>
+        <v>7.7059759917274179E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD84</f>
-        <v>8.9862781817347526E-2</v>
+        <v>8.0190765016107501E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE84</f>
-        <v>9.2755543844143001E-2</v>
+        <v>8.2718308372540517E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF84</f>
-        <v>9.5045089107061081E-2</v>
+        <v>8.4718792638075455E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG84</f>
-        <v>9.6829037639310556E-2</v>
+        <v>8.6277513064829864E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH84</f>
-        <v>9.8202147288585534E-2</v>
+        <v>8.7477264077713432E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI84</f>
-        <v>9.9249119392378682E-2</v>
+        <v>8.8392053251797179E-2</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -7156,10 +7156,10 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>0.16449392895100001</v>
+        <v>0.18218700570900001</v>
       </c>
       <c r="E10" s="16">
-        <v>0.14828894775500001</v>
+        <v>0.18123793393000001</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -7170,111 +7170,111 @@
       </c>
       <c r="I10">
         <f>D10</f>
-        <v>0.16449392895100001</v>
+        <v>0.18218700570900001</v>
       </c>
       <c r="J10" s="16">
         <f>E10</f>
-        <v>0.14828894775500001</v>
+        <v>0.18123793393000001</v>
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>0.18868208810270334</v>
+        <v>0.22006843983803839</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>0.20192405110570355</v>
+        <v>0.23279812904258823</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>0.21912805260389268</v>
+        <v>0.24933658275197695</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.2412079161321001</v>
+        <v>0.2705622726537894</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.2691050675034683</v>
+        <v>0.29738020490215311</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.30366278259245705</v>
+        <v>0.33060103270559432</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.34543894796969088</v>
+        <v>0.37076106043634494</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.39447645102619855</v>
+        <v>0.41790151635931294</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.45008738803580778</v>
+        <v>0.47136110874344317</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.51074095955207577</v>
+        <v>0.52966825809683538</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.57414447387750001</v>
+        <v>0.59061896696500005</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.63754798820292424</v>
+        <v>0.65156967583316472</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.69820155971919218</v>
+        <v>0.70987682518655681</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.75381249672880146</v>
+        <v>0.76333641757068704</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.80284999978530913</v>
+        <v>0.81047687349365505</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.84462616516254285</v>
+        <v>0.85063690122440572</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.87918388025153182</v>
+        <v>0.88385772902784698</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.90708103162289988</v>
+        <v>0.91067566127621058</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.92916089515110734</v>
+        <v>0.93190135117802309</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.94636489664929646</v>
+        <v>0.94843980488741186</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.95960685965229675</v>
+        <v>0.96116949409196173</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.96970362495499696</v>
+        <v>0.97087565957856936</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.97734704661409399</v>
+        <v>0.97822339058775476</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.98310179232636641</v>
+        <v>0.98375551028570629</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.98741679392062143</v>
+        <v>0.98790358328663208</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -7282,14 +7282,14 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>1.0004432735E-4</v>
+        <v>1.06995776452E-4</v>
       </c>
       <c r="E11" s="16">
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="F11" s="16">
         <f>E11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="G11" s="5" t="str">
         <f>IF(E11=F11,"n/a",IF(OR(C11="battery electric vehicle",C11="natural gas vehicle",C11="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7297,111 +7297,111 @@
       </c>
       <c r="I11" s="16">
         <f>E11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="J11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,J$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="K11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,K$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="L11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,L$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="M11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,M$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="N11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,N$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="O11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,O$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="P11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,P$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Q11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Q$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="R11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,R$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="S11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,S$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="T11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,T$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="U11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,U$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="V11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,V$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="W11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,W$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="X11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,X$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Y11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Y$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Z11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,Z$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AA11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AA$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AB11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AB$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AC11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AC$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AD11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AD$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AE11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AE$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AF11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AF$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AG11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AG$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AH11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AH$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AI11">
         <f>IF($G11="s-curve",$E11+($F11-$E11)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E11:$F11,$E$9:$F$9,AI$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
@@ -7535,14 +7535,14 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>6.6777915503600002E-2</v>
+        <v>6.8106756297200005E-2</v>
       </c>
       <c r="E13" s="16">
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="F13" s="16">
         <f>E13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="G13" s="5" t="str">
         <f>IF(E13=F13,"n/a",IF(OR(C13="battery electric vehicle",C13="natural gas vehicle",C13="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -7550,111 +7550,111 @@
       </c>
       <c r="I13" s="16">
         <f>E13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="J13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,J$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="K13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,K$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="L13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,L$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="M13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,M$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="N13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,N$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="O13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,O$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="P13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,P$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Q13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Q$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="R13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,R$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="S13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,S$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="T13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,T$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="U13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,U$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="V13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,V$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="W13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,W$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="X13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,X$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Y13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Y$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Z13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,Z$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AA13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AA$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AB13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AB$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AC13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AC$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AD13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AD$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AE13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AE$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AF13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AF$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AG13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AG$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AH13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AH$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AI13">
         <f>IF($G13="s-curve",$E13+($F13-$E13)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E13:$F13,$E$9:$F$9,AI$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
@@ -7662,14 +7662,14 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>1.68426429502E-2</v>
+        <v>1.6603971957400002E-2</v>
       </c>
       <c r="E14" s="16">
-        <v>1.4073498597800001E-2</v>
+        <v>1.3970074369600001E-2</v>
       </c>
       <c r="F14" s="23">
         <f>D14/D10*F10</f>
-        <v>0.10239066607264966</v>
+        <v>9.1136971557240806E-2</v>
       </c>
       <c r="G14" s="5" t="str">
         <f>IF(E14=F14,"n/a",IF(OR(C14="battery electric vehicle",C14="natural gas vehicle",C14="plugin hybrid vehicle",C14="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -7677,111 +7677,111 @@
       </c>
       <c r="I14">
         <f>D14</f>
-        <v>1.68426429502E-2</v>
+        <v>1.6603971957400002E-2</v>
       </c>
       <c r="J14">
         <f>E14</f>
-        <v>1.4073498597800001E-2</v>
+        <v>1.3970074369600001E-2</v>
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:K$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>1.7532504297315375E-2</v>
+        <v>1.6992371673937554E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:L$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.9136207441018131E-2</v>
+        <v>1.8393603157554242E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:M$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>2.1419075563388582E-2</v>
+        <v>2.0388253288765361E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:N$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>2.4601163025518801E-2</v>
+        <v>2.3168593997747108E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:O$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>2.8909159010622888E-2</v>
+        <v>2.6932694373384324E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:P$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.18322986028182E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Q$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>4.1454074269529816E-2</v>
+        <v>3.7893781709970521E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:R$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>4.9516267729372364E-2</v>
+        <v>4.493810244183398E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:S$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.2553522963420404E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:T$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>6.6947896941077292E-2</v>
+        <v>6.0168943485006829E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:U$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>7.5010090400919854E-2</v>
+        <v>6.721326421687028E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:V$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>8.194743061065532E-2</v>
+        <v>7.3274747324022602E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:W$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>8.7555005659826768E-2</v>
+        <v>7.8174351553456478E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:X$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>9.1863001644930858E-2</v>
+        <v>8.1938451929093686E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Y$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>9.5045089107061081E-2</v>
+        <v>8.4718792638075455E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:Z$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>9.7327957229431522E-2</v>
+        <v>8.6713442769286567E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AA$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>9.8931660373134278E-2</v>
+        <v>8.8114674252903258E-2</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AB$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>0.10004169493659409</v>
+        <v>8.908456408839445E-2</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AC$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>0.10080217495518981</v>
+        <v>8.9749031542300767E-2</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AD$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>0.10131951704893569</v>
+        <v>9.0201057861762329E-2</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AE$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>0.10166977090909066</v>
+        <v>9.050709126827812E-2</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AF$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>0.10190613169392981</v>
+        <v>9.0713610894126245E-2</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AG$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>0.10206528444043367</v>
+        <v>9.0852670195706434E-2</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AH$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>0.10217229099922295</v>
+        <v>9.0946166900329001E-2</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$U$2/(1+EXP($U$3*(COUNT($I$9:AI$9)+$U$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>0.10224416545984444</v>
+        <v>9.1008967024832244E-2</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
@@ -8051,10 +8051,10 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.464269858905</v>
+        <v>0.30732944248799998</v>
       </c>
       <c r="E17">
-        <v>0.21897752724899999</v>
+        <v>0.30732944248799998</v>
       </c>
       <c r="F17">
         <v>0.3</v>
@@ -8065,111 +8065,111 @@
       </c>
       <c r="I17" s="16">
         <f t="shared" ref="I17:I37" si="1">D17</f>
-        <v>0.464269858905</v>
+        <v>0.30732944248799998</v>
       </c>
       <c r="J17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$X$2/(1+EXP($X$3*(COUNT($I$9:J$9)+$X$4))),TREND($E17:$F17,$E$9:$F$9,J$9))</f>
-        <v>0.22113248143634012</v>
+        <v>0.30713450135322462</v>
       </c>
       <c r="K17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,K$9))</f>
-        <v>0.45842658466210101</v>
+        <v>0.30706872550199643</v>
       </c>
       <c r="L17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,L$9))</f>
-        <v>0.45647921740967468</v>
+        <v>0.3069818372781018</v>
       </c>
       <c r="M17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,M$9))</f>
-        <v>0.45392523459074285</v>
+        <v>0.30686788289650391</v>
       </c>
       <c r="N17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,N$9))</f>
-        <v>0.45060709178719499</v>
+        <v>0.3067198329924759</v>
       </c>
       <c r="O17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,O$9))</f>
-        <v>0.44634853948021264</v>
+        <v>0.30652982361142311</v>
       </c>
       <c r="P17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,P$9))</f>
-        <v>0.44096800448827289</v>
+        <v>0.30628975326595032</v>
       </c>
       <c r="Q17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>0.43430284384865914</v>
+        <v>0.305992365102918</v>
       </c>
       <c r="R17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.42624545775037931</v>
+        <v>0.30563285820125868</v>
       </c>
       <c r="S17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.41678757448478931</v>
+        <v>0.30521086349136217</v>
       </c>
       <c r="T17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.40606187032483487</v>
+        <v>0.30473230076349644</v>
       </c>
       <c r="U17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.39436359118568431</v>
+        <v>0.30421034338963299</v>
       </c>
       <c r="V17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.38213492945249999</v>
+        <v>0.30366472124400001</v>
       </c>
       <c r="W17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.36990626771931567</v>
+        <v>0.30311909909836698</v>
       </c>
       <c r="X17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.35820798858016512</v>
+        <v>0.30259714172450353</v>
       </c>
       <c r="Y17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.34748228442021067</v>
+        <v>0.3021185789966378</v>
       </c>
       <c r="Z17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.33802440115462073</v>
+        <v>0.30169658428674129</v>
       </c>
       <c r="AA17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.32996701505634085</v>
+        <v>0.30133707738508198</v>
       </c>
       <c r="AB17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.3233018544167271</v>
+        <v>0.30103968922204966</v>
       </c>
       <c r="AC17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.3179213194247873</v>
+        <v>0.30079961887657686</v>
       </c>
       <c r="AD17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.313662767117805</v>
+        <v>0.30060960949552407</v>
       </c>
       <c r="AE17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.31034462431425713</v>
+        <v>0.30046155959149606</v>
       </c>
       <c r="AF17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.30779064149532531</v>
+        <v>0.30034760520989817</v>
       </c>
       <c r="AG17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.30584327424289898</v>
+        <v>0.30026071698600354</v>
       </c>
       <c r="AH17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.30436908438216892</v>
+        <v>0.30019494113477535</v>
       </c>
       <c r="AI17" s="25">
         <f>IF($G17="s-curve",$D17+($F17-$D17)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($D17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.30325916422356897</v>
+        <v>0.30014541837982223</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
@@ -8177,125 +8177,125 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="F18" s="16">
         <f>E18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="J18" s="16">
         <f t="shared" ref="J18:J37" si="2">E18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="K18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="L18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="M18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="N18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="O18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="P18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="Q18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="R18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="S18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="T18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="U18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="V18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="W18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="X18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="Y18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="Z18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AA18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AB18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AC18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AD18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AE18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AF18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AG18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AH18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AI18">
         <f>IF($G18="s-curve",$E18+($F18-$E18)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E18:$F18,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
@@ -8303,14 +8303,14 @@
         <v>39</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="E19">
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="F19" s="16">
         <f>E19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="G19" s="5" t="str">
         <f>IF(E19=F19,"n/a",IF(OR(C19="battery electric vehicle",C19="natural gas vehicle",C19="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -8318,111 +8318,111 @@
       </c>
       <c r="I19" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="J19" s="16">
         <f t="shared" si="2"/>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="K19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,K$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="L19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,L$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="M19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,M$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="N19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,N$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="O19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,O$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="P19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,P$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="Q19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Q$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="R19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,R$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="S19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,S$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="T19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,T$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="U19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,U$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="V19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,V$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="W19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,W$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="X19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,X$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="Y19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Y$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="Z19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,Z$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AA19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AA$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AB19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AB$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AC19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AC$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AD19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AD$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AE19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AE$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AF19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AF$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AG19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AG$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AH19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AH$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AI19">
         <f>IF($G19="s-curve",$E19+($F19-$E19)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E19:$F19,$E$9:$F$9,AI$9))</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
@@ -8430,7 +8430,7 @@
         <v>40</v>
       </c>
       <c r="D20">
-        <v>0.97299803336400004</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="I20" s="16">
         <f t="shared" si="1"/>
-        <v>0.97299803336400004</v>
+        <v>1</v>
       </c>
       <c r="J20" s="16">
         <f t="shared" si="2"/>
@@ -8556,125 +8556,125 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1.03300009982E-3</v>
       </c>
       <c r="E21">
-        <v>9.0197447039299999E-4</v>
+        <v>1.03300009982E-3</v>
       </c>
       <c r="F21" s="16">
         <f>E21/E17*F17</f>
-        <v>1.235708268868196E-3</v>
+        <v>1.0083642733256849E-3</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I21" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.03300009982E-3</v>
       </c>
       <c r="J21" s="16">
         <f t="shared" si="2"/>
-        <v>9.0197447039299999E-4</v>
+        <v>1.03300009982E-3</v>
       </c>
       <c r="K21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,K$9))</f>
-        <v>9.1384577850523699E-4</v>
+        <v>1.0321237741728829E-3</v>
       </c>
       <c r="L21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,L$9))</f>
-        <v>9.1780208719455226E-4</v>
+        <v>1.0318317242370562E-3</v>
       </c>
       <c r="M21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,M$9))</f>
-        <v>9.229908077126324E-4</v>
+        <v>1.0314486991464152E-3</v>
       </c>
       <c r="N21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,N$9))</f>
-        <v>9.2973201032334131E-4</v>
+        <v>1.0309510717001113E-3</v>
       </c>
       <c r="O21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,O$9))</f>
-        <v>9.3838376693218116E-4</v>
+        <v>1.0303124094619435E-3</v>
       </c>
       <c r="P21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,P$9))</f>
-        <v>9.4931496509999139E-4</v>
+        <v>1.0295054815970778E-3</v>
       </c>
       <c r="Q21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Q$9))</f>
-        <v>9.6285603339172255E-4</v>
+        <v>1.028505896267372E-3</v>
       </c>
       <c r="R21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,R$9))</f>
-        <v>9.7922557364874116E-4</v>
+        <v>1.0272975165485478E-3</v>
       </c>
       <c r="S21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,S$9))</f>
-        <v>9.9844039083310217E-4</v>
+        <v>1.025879101918574E-3</v>
       </c>
       <c r="T21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,T$9))</f>
-        <v>1.020230937281997E-3</v>
+        <v>1.024270550060824E-3</v>
       </c>
       <c r="U21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,U$9))</f>
-        <v>1.0439973857269895E-3</v>
+        <v>1.0225161395008146E-3</v>
       </c>
       <c r="V21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,V$9))</f>
-        <v>1.0688413696305979E-3</v>
+        <v>1.0206821865728424E-3</v>
       </c>
       <c r="W21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,W$9))</f>
-        <v>1.0936853535342065E-3</v>
+        <v>1.0188482336448703E-3</v>
       </c>
       <c r="X21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,X$9))</f>
-        <v>1.117451801979199E-3</v>
+        <v>1.0170938230848608E-3</v>
       </c>
       <c r="Y21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Y$9))</f>
-        <v>1.1392423484280938E-3</v>
+        <v>1.0154852712271109E-3</v>
       </c>
       <c r="Z21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,Z$9))</f>
-        <v>1.1584571656124548E-3</v>
+        <v>1.0140668565971371E-3</v>
       </c>
       <c r="AA21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AA$9))</f>
-        <v>1.1748267058694735E-3</v>
+        <v>1.0128584768783128E-3</v>
       </c>
       <c r="AB21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AB$9))</f>
-        <v>1.1883677741612046E-3</v>
+        <v>1.0118588915486071E-3</v>
       </c>
       <c r="AC21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AC$9))</f>
-        <v>1.1992989723290147E-3</v>
+        <v>1.0110519636837413E-3</v>
       </c>
       <c r="AD21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AD$9))</f>
-        <v>1.2079507289378547E-3</v>
+        <v>1.0104133014455735E-3</v>
       </c>
       <c r="AE21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AE$9))</f>
-        <v>1.2146919315485635E-3</v>
+        <v>1.0099156739992697E-3</v>
       </c>
       <c r="AF21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AF$9))</f>
-        <v>1.2198806520666437E-3</v>
+        <v>1.0095326489086287E-3</v>
       </c>
       <c r="AG21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AG$9))</f>
-        <v>1.223836960755959E-3</v>
+        <v>1.0092405989728019E-3</v>
       </c>
       <c r="AH21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AH$9))</f>
-        <v>1.2268319531737681E-3</v>
+        <v>1.0090195122447148E-3</v>
       </c>
       <c r="AI21">
         <f>IF($G21="s-curve",$E21+($F21-$E21)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E21:$F21,$E$9:$F$9,AI$9))</f>
-        <v>1.2290868882726532E-3</v>
+        <v>1.0088530556553437E-3</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
@@ -8682,14 +8682,14 @@
         <v>42</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="F22" s="16">
         <f>E22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="G22" s="5" t="str">
         <f>IF(E22=F22,"n/a",IF(OR(C22="battery electric vehicle",C22="natural gas vehicle",C22="plugin hybrid vehicle",C22="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -8697,111 +8697,111 @@
       </c>
       <c r="I22" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="J22" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="K22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="L22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="M22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="N22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="O22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="P22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="Q22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="R22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="S22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="T22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="U22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="V22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="W22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="X22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="Y22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="Z22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AA22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AB22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AC22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AD22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AE22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AF22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AG22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AH22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AI22">
         <f>IF($G22="s-curve",$E22+($F22-$E22)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E22:$F22,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
     </row>
     <row r="23" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8814,11 +8814,11 @@
         <v>0</v>
       </c>
       <c r="E23" s="6">
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="F23" s="20">
         <f>E23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="str">
         <f>IF(E23=F23,"n/a",IF(OR(C23="battery electric vehicle",C23="natural gas vehicle",C23="plugin hybrid vehicle",C23="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -8830,107 +8830,107 @@
       </c>
       <c r="J23" s="16">
         <f t="shared" si="2"/>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,K$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,L$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,M$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,N$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,O$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,P$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,Q$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,R$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,S$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,T$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="U23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,U$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,V$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="W23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,W$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="X23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,X$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Y23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,Y$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Z23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,Z$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AA$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AB23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AB$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AC23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AC$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AD23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AD$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AE$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AF23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AF$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AG23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AG$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AH23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AH$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AI23">
         <f>IF($G23="s-curve",$E23+($F23-$E23)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E23:$F23,$E$9:$F$9,AI$9))</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
@@ -8944,10 +8944,10 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>3.1162890650799999E-2</v>
+        <v>0.120763672591</v>
       </c>
       <c r="E24">
-        <v>3.0635270769200001E-2</v>
+        <v>0.120763672591</v>
       </c>
       <c r="F24" s="26">
         <v>0.75</v>
@@ -8958,111 +8958,111 @@
       </c>
       <c r="I24" s="16">
         <f t="shared" si="1"/>
-        <v>3.1162890650799999E-2</v>
+        <v>0.120763672591</v>
       </c>
       <c r="J24" s="16">
         <f t="shared" si="2"/>
-        <v>3.0635270769200001E-2</v>
+        <v>0.120763672591</v>
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:K$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>5.6223929708727458E-2</v>
+        <v>0.14314635709048401</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:L$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>6.4751771186114582E-2</v>
+        <v>0.15060575485341712</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:M$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>7.593608199789606E-2</v>
+        <v>0.16038879588092381</v>
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:N$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>9.0466775061945975E-2</v>
+        <v>0.17309895467353914</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:O$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.10911567600852309</v>
+        <v>0.18941135569212383</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:P$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.13267792366244005</v>
+        <v>0.21002151570803868</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Q$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.16186575830694638</v>
+        <v>0.23555243921657476</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:R$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.19715037721106998</v>
+        <v>0.2664162877082813</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:S$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.2385680035473921</v>
+        <v>0.30264474599498731</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:T$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.2855376260957222</v>
+        <v>0.34372959710201983</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:U$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.33676631443512162</v>
+        <v>0.388539900413849</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:V$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.39031763538459996</v>
+        <v>0.43538183629550004</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:W$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.4438689563340783</v>
+        <v>0.48222377217715112</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:X$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.49509764467347783</v>
+        <v>0.52703407548898018</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Y$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.54206726722180787</v>
+        <v>0.56811892659601271</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:Z$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.58348489355812994</v>
+        <v>0.60434738488271866</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AA$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.61876951246225353</v>
+        <v>0.6352112333744252</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AB$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.64795734710676001</v>
+        <v>0.66074215688296134</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AC$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.67151959476067691</v>
+        <v>0.68135231689887621</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AD$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.69016849570725403</v>
+        <v>0.69766471791746087</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AE$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.704699188771304</v>
+        <v>0.71037487671007626</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AF$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.7158834995830855</v>
+        <v>0.72015791773758298</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AG$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.72441134106047256</v>
+        <v>0.727617315500516</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AH$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.73086706091722453</v>
+        <v>0.73326420544157211</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$X$2/(1+EXP($X$3*(COUNT($I$9:AI$9)+$X$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.73572758383774906</v>
+        <v>0.73751575888521737</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
@@ -9070,14 +9070,14 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="F25" s="16">
         <f>E25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="G25" s="5" t="str">
         <f>IF(E25=F25,"n/a",IF(OR(C25="battery electric vehicle",C25="natural gas vehicle",C25="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9085,111 +9085,111 @@
       </c>
       <c r="I25" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="J25" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="K25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="L25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="M25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="N25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="O25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="P25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="Q25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="R25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="S25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="T25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="U25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="V25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="W25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="X25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="Y25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="Z25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AA25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AB25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AC25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AD25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AE25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AF25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AG25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AH25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AI25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
@@ -9197,14 +9197,14 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="F26" s="16">
         <f>E26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>IF(E26=F26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9212,111 +9212,111 @@
       </c>
       <c r="I26" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="J26" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="K26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="L26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="M26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="N26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="O26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="P26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="Q26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="R26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="S26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="T26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="U26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="V26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="W26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="X26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="Y26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="Z26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AA26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AB26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AC26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AD26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AE26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AF26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AG26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AH26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AI26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
@@ -9577,14 +9577,14 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="F29" s="16">
         <f>E29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="G29" s="5" t="str">
         <f>IF(E29=F29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -9592,111 +9592,111 @@
       </c>
       <c r="I29" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="J29" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="K29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="L29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="M29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="N29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="O29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="P29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="Q29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="R29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="S29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="T29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="U29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="V29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="W29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="X29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="Y29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="Z29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AA29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AB29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AC29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AD29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AE29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AF29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AG29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AH29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AI29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
     </row>
     <row r="30" spans="1:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9706,14 +9706,14 @@
         <v>43</v>
       </c>
       <c r="D30" s="20">
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="E30" s="6">
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="F30" s="20">
         <f>E30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="G30" s="6" t="str">
         <f>IF(E30=F30,"n/a",IF(OR(C30="battery electric vehicle",C30="natural gas vehicle",C30="plugin hybrid vehicle",C30="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -9721,111 +9721,111 @@
       </c>
       <c r="I30" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="J30" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="K30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="L30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="M30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="N30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="O30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="P30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="Q30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="R30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="S30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="T30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="U30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="V30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="W30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="X30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="Y30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="Z30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AA30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AB30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AC30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AD30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AE30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AF30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AG30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AH30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AI30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
@@ -9839,10 +9839,10 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>4.7973229575300003E-3</v>
+        <v>4.9483952094699999E-3</v>
       </c>
       <c r="E31">
-        <v>6.1405058414400002E-3</v>
+        <v>4.9483952094699999E-3</v>
       </c>
       <c r="F31" s="16">
         <v>0.25</v>
@@ -9853,111 +9853,111 @@
       </c>
       <c r="I31" s="16">
         <f t="shared" si="1"/>
-        <v>4.7973229575300003E-3</v>
+        <v>4.9483952094699999E-3</v>
       </c>
       <c r="J31" s="16">
         <f t="shared" si="2"/>
-        <v>6.1405058414400002E-3</v>
+        <v>4.9483952094699999E-3</v>
       </c>
       <c r="K31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:K$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,K$9))</f>
-        <v>1.4814878064083456E-2</v>
+        <v>1.3665172225037181E-2</v>
       </c>
       <c r="L31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:L$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,L$9))</f>
-        <v>1.7705755284549454E-2</v>
+        <v>1.6570181540224892E-2</v>
       </c>
       <c r="M31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:M$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,M$9))</f>
-        <v>2.1497156594966059E-2</v>
+        <v>2.0380117170282437E-2</v>
       </c>
       <c r="N31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:N$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,N$9))</f>
-        <v>2.6422957536251346E-2</v>
+        <v>2.5329997960061364E-2</v>
       </c>
       <c r="O31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:O$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,O$9))</f>
-        <v>3.2744801472509036E-2</v>
+        <v>3.1682746321000453E-2</v>
       </c>
       <c r="P31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:P$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,P$9))</f>
-        <v>4.0732234773926027E-2</v>
+        <v>3.970922630458016E-2</v>
       </c>
       <c r="Q31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Q$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Q$9))</f>
-        <v>5.0626701798468406E-2</v>
+        <v>4.9652062572970661E-2</v>
       </c>
       <c r="R31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:R$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,R$9))</f>
-        <v>6.2587935047612731E-2</v>
+        <v>6.16717684822711E-2</v>
       </c>
       <c r="S31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:S$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,S$9))</f>
-        <v>7.6628213917586716E-2</v>
+        <v>7.5780683456713668E-2</v>
       </c>
       <c r="T31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:T$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,T$9))</f>
-        <v>9.2550579763493207E-2</v>
+        <v>9.1780886016242957E-2</v>
       </c>
       <c r="U31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:U$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,U$9))</f>
-        <v>0.10991673842713874</v>
+        <v>0.10923193939539196</v>
       </c>
       <c r="V31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:V$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,V$9))</f>
-        <v>0.12807025292072</v>
+        <v>0.127474197604735</v>
       </c>
       <c r="W31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:W$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,W$9))</f>
-        <v>0.14622376741430126</v>
+        <v>0.14571645581407805</v>
       </c>
       <c r="X31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:X$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,X$9))</f>
-        <v>0.16358992607794678</v>
+        <v>0.16316750919322703</v>
       </c>
       <c r="Y31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Y$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Y$9))</f>
-        <v>0.17951229192385326</v>
+        <v>0.17916771175275634</v>
       </c>
       <c r="Z31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:Z$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,Z$9))</f>
-        <v>0.19355257079382726</v>
+        <v>0.19327662672719889</v>
       </c>
       <c r="AA31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AA$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AA$9))</f>
-        <v>0.20551380404297159</v>
+        <v>0.20529633263649932</v>
       </c>
       <c r="AB31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AB$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AB$9))</f>
-        <v>0.21540827106751401</v>
+        <v>0.21523916890488987</v>
       </c>
       <c r="AC31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AC$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AC$9))</f>
-        <v>0.22339570436893097</v>
+        <v>0.22326564888846956</v>
       </c>
       <c r="AD31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AD$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AD$9))</f>
-        <v>0.22971754830518867</v>
+        <v>0.22961839724940863</v>
       </c>
       <c r="AE31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AE$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AE$9))</f>
-        <v>0.23464334924647395</v>
+        <v>0.23456827803918759</v>
       </c>
       <c r="AF31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AF$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AF$9))</f>
-        <v>0.23843475055689056</v>
+        <v>0.23837821366924514</v>
       </c>
       <c r="AG31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AG$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AG$9))</f>
-        <v>0.24132562777735656</v>
+        <v>0.24128322298443283</v>
       </c>
       <c r="AH31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AH$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AH$9))</f>
-        <v>0.24351407060020699</v>
+        <v>0.2434823640413856</v>
       </c>
       <c r="AI31">
         <f>IF($G31="s-curve",$E31+($F31-$E31)*$R$2/(1+EXP($R$3*(COUNT($K$9:AI$9)+$R$4))),TREND($E31:$F31,$E$9:$F$9,AI$9))</f>
-        <v>0.2451617530797367</v>
+        <v>0.24513810124032956</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
@@ -9965,14 +9965,14 @@
         <v>38</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="F32" s="16">
         <f>E32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="G32" s="5" t="str">
         <f>IF(E32=F32,"n/a",IF(OR(C32="battery electric vehicle",C32="natural gas vehicle",C32="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -9980,111 +9980,111 @@
       </c>
       <c r="I32" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="J32" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="K32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="L32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="M32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="N32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="O32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="P32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="Q32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="R32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="S32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="T32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="U32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="V32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="W32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="X32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="Y32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="Z32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AA32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AB32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AC32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AD32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AE32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AF32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AG32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AH32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AI32">
         <f>IF($G32="s-curve",$E32+($F32-$E32)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E32:$F32,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
@@ -10092,14 +10092,14 @@
         <v>39</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="F33" s="16">
         <f>E33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="G33" s="5" t="str">
         <f>IF(E33=F33,"n/a",IF(OR(C33="battery electric vehicle",C33="natural gas vehicle",C33="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -10107,111 +10107,111 @@
       </c>
       <c r="I33" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="J33" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="K33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,K$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="L33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,L$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="M33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,M$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="N33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,N$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="O33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,O$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="P33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,P$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="Q33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Q$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="R33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,R$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="S33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,S$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="T33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,T$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="U33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,U$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="V33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,V$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="W33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,W$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="X33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,X$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="Y33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Y$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="Z33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,Z$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AA33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AA$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AB33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AB$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AC33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AC$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AD33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AD$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AE33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AE$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AF33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AF$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AG33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AG$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AH33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AH$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AI33">
         <f>IF($G33="s-curve",$E33+($F33-$E33)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E33:$F33,$E$9:$F$9,AI$9))</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
@@ -10601,14 +10601,14 @@
         <v>43</v>
       </c>
       <c r="D37" s="20">
-        <v>6.2247642917999998E-4</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6">
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="20">
         <f>E37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="str">
         <f>IF(E37=F37,"n/a",IF(OR(C37="battery electric vehicle",C37="natural gas vehicle",C37="plugin hybrid vehicle",C37="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -10616,111 +10616,111 @@
       </c>
       <c r="I37" s="16">
         <f t="shared" si="1"/>
-        <v>6.2247642917999998E-4</v>
+        <v>0</v>
       </c>
       <c r="J37" s="16">
         <f t="shared" si="2"/>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,K$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,L$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,M$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="N37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,N$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,O$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="P37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,P$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,Q$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,R$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,S$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,T$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="U37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,U$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="V37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,V$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="W37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,W$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="X37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,X$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Y37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,Y$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Z37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,Z$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AA37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AA$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AB37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AB$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AC37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AC$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AD37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AD$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AE$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AF$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AG$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AH37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AH$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AI37">
         <f>IF($G37="s-curve",$E37+($F37-$E37)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E37:$F37,$E$9:$F$9,AI$9))</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.25">
@@ -15958,11 +15958,11 @@
       </c>
       <c r="D80">
         <f t="shared" ref="D80:F86" si="5">D10</f>
-        <v>0.16449392895100001</v>
+        <v>0.18218700570900001</v>
       </c>
       <c r="E80">
         <f t="shared" si="5"/>
-        <v>0.14828894775500001</v>
+        <v>0.18123793393000001</v>
       </c>
       <c r="F80">
         <f t="shared" si="5"/>
@@ -15974,111 +15974,111 @@
       </c>
       <c r="I80" s="16">
         <f t="shared" si="4"/>
-        <v>0.14828894775500001</v>
+        <v>0.18123793393000001</v>
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>0.20192405110570355</v>
+        <v>0.23279812904258823</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>0.21912805260389268</v>
+        <v>0.24933658275197695</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>0.2412079161321001</v>
+        <v>0.2705622726537894</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.2691050675034683</v>
+        <v>0.29738020490215311</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.30366278259245705</v>
+        <v>0.33060103270559432</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.34543894796969088</v>
+        <v>0.37076106043634494</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.39447645102619855</v>
+        <v>0.41790151635931294</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.45008738803580778</v>
+        <v>0.47136110874344317</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.51074095955207577</v>
+        <v>0.52966825809683538</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.57414447387750001</v>
+        <v>0.59061896696500005</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.63754798820292424</v>
+        <v>0.65156967583316472</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.69820155971919218</v>
+        <v>0.70987682518655681</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.75381249672880146</v>
+        <v>0.76333641757068704</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.80284999978530913</v>
+        <v>0.81047687349365505</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.84462616516254285</v>
+        <v>0.85063690122440572</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.87918388025153182</v>
+        <v>0.88385772902784698</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.90708103162289988</v>
+        <v>0.91067566127621058</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.92916089515110734</v>
+        <v>0.93190135117802309</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.94636489664929646</v>
+        <v>0.94843980488741186</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.95960685965229675</v>
+        <v>0.96116949409196173</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.96970362495499696</v>
+        <v>0.97087565957856936</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.97734704661409399</v>
+        <v>0.97822339058775476</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.98310179232636641</v>
+        <v>0.98375551028570629</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.98741679392062143</v>
+        <v>0.98790358328663208</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.99064229953114202</v>
+        <v>0.99100430815198304</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.99304784793411749</v>
+        <v>0.99331679637819548</v>
       </c>
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
@@ -16087,15 +16087,15 @@
       </c>
       <c r="D81">
         <f t="shared" si="5"/>
-        <v>1.0004432735E-4</v>
+        <v>1.06995776452E-4</v>
       </c>
       <c r="E81">
         <f t="shared" si="5"/>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="F81">
         <f t="shared" si="5"/>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="G81" s="5" t="str">
         <f>IF(E81=F81,"n/a",IF(OR(C81="battery electric vehicle",C81="natural gas vehicle",C81="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16103,111 +16103,111 @@
       </c>
       <c r="I81" s="16">
         <f t="shared" si="4"/>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="J81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,J$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="K81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,K$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="L81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,L$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="M81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,M$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="N81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,N$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="O81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,O$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="P81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,P$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Q81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Q$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="R81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,R$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="S81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,S$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="T81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,T$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="U81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,U$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="V81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,V$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="W81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,W$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="X81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,X$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Y81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Y$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Z81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,Z$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AA81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AA$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AB81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AB$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AC81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AC$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AD81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AD$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AE81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AE$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AF81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AF$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AG81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AG$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AH81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AH$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AI81">
         <f>IF($G81="s-curve",$E81+($F81-$E81)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E81:$F81,$E$9:$F$9,AI$9))</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
@@ -16345,15 +16345,15 @@
       </c>
       <c r="D83">
         <f t="shared" si="5"/>
-        <v>6.6777915503600002E-2</v>
+        <v>6.8106756297200005E-2</v>
       </c>
       <c r="E83">
         <f t="shared" si="5"/>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="F83">
         <f t="shared" si="5"/>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="G83" s="5" t="str">
         <f>IF(E83=F83,"n/a",IF(OR(C83="battery electric vehicle",C83="natural gas vehicle",C83="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16361,111 +16361,111 @@
       </c>
       <c r="I83" s="16">
         <f t="shared" si="4"/>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="J83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,J$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="K83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,K$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="L83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,L$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="M83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,M$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="N83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,N$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="O83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,O$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="P83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,P$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Q83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Q$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="R83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,R$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="S83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,S$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="T83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,T$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="U83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,U$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="V83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,V$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="W83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,W$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="X83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,X$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Y83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Y$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Z83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,Z$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AA83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AA$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AB83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AB$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AC83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AC$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AD83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AD$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AE83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AE$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AF83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AF$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AG83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AG$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AH83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AH$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AI83">
         <f>IF($G83="s-curve",$E83+($F83-$E83)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E83:$F83,$E$9:$F$9,AI$9))</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
     </row>
     <row r="84" spans="1:35" x14ac:dyDescent="0.25">
@@ -16474,15 +16474,15 @@
       </c>
       <c r="D84">
         <f t="shared" si="5"/>
-        <v>1.68426429502E-2</v>
+        <v>1.6603971957400002E-2</v>
       </c>
       <c r="E84">
         <f t="shared" si="5"/>
-        <v>1.4073498597800001E-2</v>
+        <v>1.3970074369600001E-2</v>
       </c>
       <c r="F84">
         <f t="shared" si="5"/>
-        <v>0.10239066607264966</v>
+        <v>9.1136971557240806E-2</v>
       </c>
       <c r="G84" s="5" t="str">
         <f>IF(E84=F84,"n/a",IF(OR(C84="battery electric vehicle",C84="natural gas vehicle",C84="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -16490,111 +16490,111 @@
       </c>
       <c r="I84" s="16">
         <f t="shared" si="4"/>
-        <v>1.4073498597800001E-2</v>
+        <v>1.3970074369600001E-2</v>
       </c>
       <c r="J84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,J$9))</f>
-        <v>1.5378299229133533E-2</v>
+        <v>1.5110140554321749E-2</v>
       </c>
       <c r="K84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,K$9))</f>
-        <v>1.5825738202068743E-2</v>
+        <v>1.550108920235292E-2</v>
       </c>
       <c r="L84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,L$9))</f>
-        <v>1.6422469733855565E-2</v>
+        <v>1.6022481838446352E-2</v>
       </c>
       <c r="M84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,M$9))</f>
-        <v>1.7215045278070985E-2</v>
+        <v>1.6714992675043627E-2</v>
       </c>
       <c r="N84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,N$9))</f>
-        <v>1.8262017381864146E-2</v>
+        <v>1.7629781849127387E-2</v>
       </c>
       <c r="O84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,O$9))</f>
-        <v>1.96351270311391E-2</v>
+        <v>1.8829532862010948E-2</v>
       </c>
       <c r="P84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,P$9))</f>
-        <v>2.1419075563388585E-2</v>
+        <v>2.0388253288765361E-2</v>
       </c>
       <c r="Q84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Q$9))</f>
-        <v>2.3708620826306676E-2</v>
+        <v>2.2388737554300295E-2</v>
       </c>
       <c r="R84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,R$9))</f>
-        <v>2.6601382853102151E-2</v>
+        <v>2.4916280910733307E-2</v>
       </c>
       <c r="S84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,S$9))</f>
-        <v>3.0184804135493147E-2</v>
+        <v>2.8047286009566623E-2</v>
       </c>
       <c r="T84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,T$9))</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.18322986028182E-2</v>
       </c>
       <c r="U84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,U$9))</f>
-        <v>3.9601619783156121E-2</v>
+        <v>3.6275204382572757E-2</v>
       </c>
       <c r="V84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,V$9))</f>
-        <v>4.5368129944513266E-2</v>
+        <v>4.1313677756162917E-2</v>
       </c>
       <c r="W84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,W$9))</f>
-        <v>5.1657530110720232E-2</v>
+        <v>4.6809024922225891E-2</v>
       </c>
       <c r="X84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,X$9))</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.2553522963420404E-2</v>
       </c>
       <c r="Y84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Y$9))</f>
-        <v>6.4806634559729431E-2</v>
+        <v>5.8298021004614918E-2</v>
       </c>
       <c r="Z84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,Z$9))</f>
-        <v>7.1096034725936397E-2</v>
+        <v>6.3793368170677878E-2</v>
       </c>
       <c r="AA84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AA$9))</f>
-        <v>7.6862544887293549E-2</v>
+        <v>6.8831841544268038E-2</v>
       </c>
       <c r="AB84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AB$9))</f>
-        <v>8.194743061065532E-2</v>
+        <v>7.3274747324022602E-2</v>
       </c>
       <c r="AC84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AC$9))</f>
-        <v>8.6279360534956523E-2</v>
+        <v>7.7059759917274179E-2</v>
       </c>
       <c r="AD84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AD$9))</f>
-        <v>8.9862781817347526E-2</v>
+        <v>8.0190765016107501E-2</v>
       </c>
       <c r="AE84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AE$9))</f>
-        <v>9.2755543844143001E-2</v>
+        <v>8.2718308372540517E-2</v>
       </c>
       <c r="AF84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AF$9))</f>
-        <v>9.5045089107061081E-2</v>
+        <v>8.4718792638075455E-2</v>
       </c>
       <c r="AG84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AG$9))</f>
-        <v>9.6829037639310556E-2</v>
+        <v>8.6277513064829864E-2</v>
       </c>
       <c r="AH84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AH$9))</f>
-        <v>9.8202147288585534E-2</v>
+        <v>8.7477264077713432E-2</v>
       </c>
       <c r="AI84">
         <f>IF($G84="s-curve",$E84+($F84-$E84)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E84:$F84,$E$9:$F$9,AI$9))</f>
-        <v>9.9249119392378682E-2</v>
+        <v>8.8392053251797179E-2</v>
       </c>
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
@@ -17867,111 +17867,111 @@
       </c>
       <c r="B2">
         <f>Data!I10</f>
-        <v>0.16449392895100001</v>
+        <v>0.18218700570900001</v>
       </c>
       <c r="C2">
         <f>Data!J10</f>
-        <v>0.14828894775500001</v>
+        <v>0.18123793393000001</v>
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>0.18868208810270334</v>
+        <v>0.22006843983803839</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>0.20192405110570355</v>
+        <v>0.23279812904258823</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>0.21912805260389268</v>
+        <v>0.24933658275197695</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.2412079161321001</v>
+        <v>0.2705622726537894</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.2691050675034683</v>
+        <v>0.29738020490215311</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.30366278259245705</v>
+        <v>0.33060103270559432</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.34543894796969088</v>
+        <v>0.37076106043634494</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.39447645102619855</v>
+        <v>0.41790151635931294</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.45008738803580778</v>
+        <v>0.47136110874344317</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.51074095955207577</v>
+        <v>0.52966825809683538</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.57414447387750001</v>
+        <v>0.59061896696500005</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.63754798820292424</v>
+        <v>0.65156967583316472</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.69820155971919218</v>
+        <v>0.70987682518655681</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.75381249672880146</v>
+        <v>0.76333641757068704</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.80284999978530913</v>
+        <v>0.81047687349365505</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.84462616516254285</v>
+        <v>0.85063690122440572</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.87918388025153182</v>
+        <v>0.88385772902784698</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.90708103162289988</v>
+        <v>0.91067566127621058</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.92916089515110734</v>
+        <v>0.93190135117802309</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.94636489664929646</v>
+        <v>0.94843980488741186</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.95960685965229675</v>
+        <v>0.96116949409196173</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.96970362495499696</v>
+        <v>0.97087565957856936</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.97734704661409399</v>
+        <v>0.97822339058775476</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.98310179232636641</v>
+        <v>0.98375551028570629</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.98741679392062143</v>
+        <v>0.98790358328663208</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -17980,111 +17980,111 @@
       </c>
       <c r="B3">
         <f>Data!I11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="C3">
         <f>Data!J11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="D3">
         <f>Data!K11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="E3">
         <f>Data!L11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="F3">
         <f>Data!M11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="G3">
         <f>Data!N11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="H3">
         <f>Data!O11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="I3">
         <f>Data!P11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="J3">
         <f>Data!Q11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="K3">
         <f>Data!R11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="L3">
         <f>Data!S11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="M3">
         <f>Data!T11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="N3">
         <f>Data!U11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="O3">
         <f>Data!V11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="P3">
         <f>Data!W11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Q3">
         <f>Data!X11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="R3">
         <f>Data!Y11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="S3">
         <f>Data!Z11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="T3">
         <f>Data!AA11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="U3">
         <f>Data!AB11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="V3">
         <f>Data!AC11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="W3">
         <f>Data!AD11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="X3">
         <f>Data!AE11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Y3">
         <f>Data!AF11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="Z3">
         <f>Data!AG11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AA3">
         <f>Data!AH11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
       <c r="AB3">
         <f>Data!AI11</f>
-        <v>1.00970167475E-4</v>
+        <v>1.06732008758E-4</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -18206,111 +18206,111 @@
       </c>
       <c r="B5">
         <f>Data!I13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="C5">
         <f>Data!J13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="D5">
         <f>Data!K13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="E5">
         <f>Data!L13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="F5">
         <f>Data!M13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="G5">
         <f>Data!N13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="H5">
         <f>Data!O13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="I5">
         <f>Data!P13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="J5">
         <f>Data!Q13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="K5">
         <f>Data!R13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="L5">
         <f>Data!S13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="M5">
         <f>Data!T13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="N5">
         <f>Data!U13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="O5">
         <f>Data!V13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="P5">
         <f>Data!W13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Q5">
         <f>Data!X13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="R5">
         <f>Data!Y13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="S5">
         <f>Data!Z13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="T5">
         <f>Data!AA13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="U5">
         <f>Data!AB13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="V5">
         <f>Data!AC13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="W5">
         <f>Data!AD13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="X5">
         <f>Data!AE13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Y5">
         <f>Data!AF13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="Z5">
         <f>Data!AG13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AA5">
         <f>Data!AH13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
       <c r="AB5">
         <f>Data!AI13</f>
-        <v>6.7382959534800002E-2</v>
+        <v>6.7938858436000005E-2</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -18319,111 +18319,111 @@
       </c>
       <c r="B6">
         <f>Data!I14</f>
-        <v>1.68426429502E-2</v>
+        <v>1.6603971957400002E-2</v>
       </c>
       <c r="C6">
         <f>Data!J14</f>
-        <v>1.4073498597800001E-2</v>
+        <v>1.3970074369600001E-2</v>
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>1.7532504297315375E-2</v>
+        <v>1.6992371673937554E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.9136207441018131E-2</v>
+        <v>1.8393603157554242E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>2.1419075563388582E-2</v>
+        <v>2.0388253288765361E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>2.4601163025518801E-2</v>
+        <v>2.3168593997747108E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>2.8909159010622888E-2</v>
+        <v>2.6932694373384324E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>3.4516734059794343E-2</v>
+        <v>3.18322986028182E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>4.1454074269529816E-2</v>
+        <v>3.7893781709970521E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>4.9516267729372364E-2</v>
+        <v>4.493810244183398E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>5.8232082335224832E-2</v>
+        <v>5.2553522963420404E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>6.6947896941077292E-2</v>
+        <v>6.0168943485006829E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>7.5010090400919854E-2</v>
+        <v>6.721326421687028E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>8.194743061065532E-2</v>
+        <v>7.3274747324022602E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>8.7555005659826768E-2</v>
+        <v>7.8174351553456478E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>9.1863001644930858E-2</v>
+        <v>8.1938451929093686E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>9.5045089107061081E-2</v>
+        <v>8.4718792638075455E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>9.7327957229431522E-2</v>
+        <v>8.6713442769286567E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>9.8931660373134278E-2</v>
+        <v>8.8114674252903258E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>0.10004169493659409</v>
+        <v>8.908456408839445E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>0.10080217495518981</v>
+        <v>8.9749031542300767E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>0.10131951704893569</v>
+        <v>9.0201057861762329E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>0.10166977090909066</v>
+        <v>9.050709126827812E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>0.10190613169392981</v>
+        <v>9.0713610894126245E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>0.10206528444043367</v>
+        <v>9.0852670195706434E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>0.10217229099922295</v>
+        <v>9.0946166900329001E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>0.10224416545984444</v>
+        <v>9.1008967024832244E-2</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -18787,111 +18787,111 @@
       </c>
       <c r="B2">
         <f>Data!I17</f>
-        <v>0.464269858905</v>
+        <v>0.30732944248799998</v>
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.22113248143634012</v>
+        <v>0.30713450135322462</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
-        <v>0.45842658466210101</v>
+        <v>0.30706872550199643</v>
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>0.45647921740967468</v>
+        <v>0.3069818372781018</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>0.45392523459074285</v>
+        <v>0.30686788289650391</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>0.45060709178719499</v>
+        <v>0.3067198329924759</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>0.44634853948021264</v>
+        <v>0.30652982361142311</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>0.44096800448827289</v>
+        <v>0.30628975326595032</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>0.43430284384865914</v>
+        <v>0.305992365102918</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.42624545775037931</v>
+        <v>0.30563285820125868</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.41678757448478931</v>
+        <v>0.30521086349136217</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.40606187032483487</v>
+        <v>0.30473230076349644</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.39436359118568431</v>
+        <v>0.30421034338963299</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.38213492945249999</v>
+        <v>0.30366472124400001</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.36990626771931567</v>
+        <v>0.30311909909836698</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.35820798858016512</v>
+        <v>0.30259714172450353</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.34748228442021067</v>
+        <v>0.3021185789966378</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.33802440115462073</v>
+        <v>0.30169658428674129</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.32996701505634085</v>
+        <v>0.30133707738508198</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.3233018544167271</v>
+        <v>0.30103968922204966</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.3179213194247873</v>
+        <v>0.30079961887657686</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.313662767117805</v>
+        <v>0.30060960949552407</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.31034462431425713</v>
+        <v>0.30046155959149606</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.30779064149532531</v>
+        <v>0.30034760520989817</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.30584327424289898</v>
+        <v>0.30026071698600354</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.30436908438216892</v>
+        <v>0.30019494113477535</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.30325916422356897</v>
+        <v>0.30014541837982223</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -18900,111 +18900,111 @@
       </c>
       <c r="B3">
         <f>Data!I18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="C3">
         <f>Data!J18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="D3">
         <f>Data!K18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="E3">
         <f>Data!L18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="F3">
         <f>Data!M18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="G3">
         <f>Data!N18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="H3">
         <f>Data!O18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="I3">
         <f>Data!P18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="J3">
         <f>Data!Q18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="K3">
         <f>Data!R18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="L3">
         <f>Data!S18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="M3">
         <f>Data!T18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="N3">
         <f>Data!U18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="O3">
         <f>Data!V18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="P3">
         <f>Data!W18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="Q3">
         <f>Data!X18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="R3">
         <f>Data!Y18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="S3">
         <f>Data!Z18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="T3">
         <f>Data!AA18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="U3">
         <f>Data!AB18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="V3">
         <f>Data!AC18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="W3">
         <f>Data!AD18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="X3">
         <f>Data!AE18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="Y3">
         <f>Data!AF18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="Z3">
         <f>Data!AG18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AA3">
         <f>Data!AH18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
       <c r="AB3">
         <f>Data!AI18</f>
-        <v>0</v>
+        <v>0.59353215226599998</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -19013,111 +19013,111 @@
       </c>
       <c r="B4">
         <f>Data!I19</f>
-        <v>1</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="C4">
         <f>Data!J19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="D4">
         <f>Data!K19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="E4">
         <f>Data!L19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="F4">
         <f>Data!M19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="G4">
         <f>Data!N19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="H4">
         <f>Data!O19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="I4">
         <f>Data!P19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="J4">
         <f>Data!Q19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="K4">
         <f>Data!R19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="L4">
         <f>Data!S19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="M4">
         <f>Data!T19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="N4">
         <f>Data!U19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="O4">
         <f>Data!V19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="P4">
         <f>Data!W19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="Q4">
         <f>Data!X19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="R4">
         <f>Data!Y19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="S4">
         <f>Data!Z19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="T4">
         <f>Data!AA19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="U4">
         <f>Data!AB19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="V4">
         <f>Data!AC19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="W4">
         <f>Data!AD19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="X4">
         <f>Data!AE19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="Y4">
         <f>Data!AF19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="Z4">
         <f>Data!AG19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AA4">
         <f>Data!AH19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
       <c r="AB4">
         <f>Data!AI19</f>
-        <v>0.95569574619999997</v>
+        <v>0.97401567340499995</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="B5">
         <f>Data!I20</f>
-        <v>0.97299803336400004</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <f>Data!J20</f>
@@ -19239,111 +19239,111 @@
       </c>
       <c r="B6">
         <f>Data!I21</f>
-        <v>0</v>
+        <v>1.03300009982E-3</v>
       </c>
       <c r="C6">
         <f>Data!J21</f>
-        <v>9.0197447039299999E-4</v>
+        <v>1.03300009982E-3</v>
       </c>
       <c r="D6">
         <f>Data!K21</f>
-        <v>9.1384577850523699E-4</v>
+        <v>1.0321237741728829E-3</v>
       </c>
       <c r="E6">
         <f>Data!L21</f>
-        <v>9.1780208719455226E-4</v>
+        <v>1.0318317242370562E-3</v>
       </c>
       <c r="F6">
         <f>Data!M21</f>
-        <v>9.229908077126324E-4</v>
+        <v>1.0314486991464152E-3</v>
       </c>
       <c r="G6">
         <f>Data!N21</f>
-        <v>9.2973201032334131E-4</v>
+        <v>1.0309510717001113E-3</v>
       </c>
       <c r="H6">
         <f>Data!O21</f>
-        <v>9.3838376693218116E-4</v>
+        <v>1.0303124094619435E-3</v>
       </c>
       <c r="I6">
         <f>Data!P21</f>
-        <v>9.4931496509999139E-4</v>
+        <v>1.0295054815970778E-3</v>
       </c>
       <c r="J6">
         <f>Data!Q21</f>
-        <v>9.6285603339172255E-4</v>
+        <v>1.028505896267372E-3</v>
       </c>
       <c r="K6">
         <f>Data!R21</f>
-        <v>9.7922557364874116E-4</v>
+        <v>1.0272975165485478E-3</v>
       </c>
       <c r="L6">
         <f>Data!S21</f>
-        <v>9.9844039083310217E-4</v>
+        <v>1.025879101918574E-3</v>
       </c>
       <c r="M6">
         <f>Data!T21</f>
-        <v>1.020230937281997E-3</v>
+        <v>1.024270550060824E-3</v>
       </c>
       <c r="N6">
         <f>Data!U21</f>
-        <v>1.0439973857269895E-3</v>
+        <v>1.0225161395008146E-3</v>
       </c>
       <c r="O6">
         <f>Data!V21</f>
-        <v>1.0688413696305979E-3</v>
+        <v>1.0206821865728424E-3</v>
       </c>
       <c r="P6">
         <f>Data!W21</f>
-        <v>1.0936853535342065E-3</v>
+        <v>1.0188482336448703E-3</v>
       </c>
       <c r="Q6">
         <f>Data!X21</f>
-        <v>1.117451801979199E-3</v>
+        <v>1.0170938230848608E-3</v>
       </c>
       <c r="R6">
         <f>Data!Y21</f>
-        <v>1.1392423484280938E-3</v>
+        <v>1.0154852712271109E-3</v>
       </c>
       <c r="S6">
         <f>Data!Z21</f>
-        <v>1.1584571656124548E-3</v>
+        <v>1.0140668565971371E-3</v>
       </c>
       <c r="T6">
         <f>Data!AA21</f>
-        <v>1.1748267058694735E-3</v>
+        <v>1.0128584768783128E-3</v>
       </c>
       <c r="U6">
         <f>Data!AB21</f>
-        <v>1.1883677741612046E-3</v>
+        <v>1.0118588915486071E-3</v>
       </c>
       <c r="V6">
         <f>Data!AC21</f>
-        <v>1.1992989723290147E-3</v>
+        <v>1.0110519636837413E-3</v>
       </c>
       <c r="W6">
         <f>Data!AD21</f>
-        <v>1.2079507289378547E-3</v>
+        <v>1.0104133014455735E-3</v>
       </c>
       <c r="X6">
         <f>Data!AE21</f>
-        <v>1.2146919315485635E-3</v>
+        <v>1.0099156739992697E-3</v>
       </c>
       <c r="Y6">
         <f>Data!AF21</f>
-        <v>1.2198806520666437E-3</v>
+        <v>1.0095326489086287E-3</v>
       </c>
       <c r="Z6">
         <f>Data!AG21</f>
-        <v>1.223836960755959E-3</v>
+        <v>1.0092405989728019E-3</v>
       </c>
       <c r="AA6">
         <f>Data!AH21</f>
-        <v>1.2268319531737681E-3</v>
+        <v>1.0090195122447148E-3</v>
       </c>
       <c r="AB6">
         <f>Data!AI21</f>
-        <v>1.2290868882726532E-3</v>
+        <v>1.0088530556553437E-3</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -19352,111 +19352,111 @@
       </c>
       <c r="B7">
         <f>Data!I22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="C7">
         <f>Data!J22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="D7">
         <f>Data!K22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="E7">
         <f>Data!L22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="F7">
         <f>Data!M22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="G7">
         <f>Data!N22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="H7">
         <f>Data!O22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="I7">
         <f>Data!P22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="J7">
         <f>Data!Q22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="K7">
         <f>Data!R22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="L7">
         <f>Data!S22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="M7">
         <f>Data!T22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="N7">
         <f>Data!U22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="O7">
         <f>Data!V22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="P7">
         <f>Data!W22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="Q7">
         <f>Data!X22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="R7">
         <f>Data!Y22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="S7">
         <f>Data!Z22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="T7">
         <f>Data!AA22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="U7">
         <f>Data!AB22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="V7">
         <f>Data!AC22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="W7">
         <f>Data!AD22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="X7">
         <f>Data!AE22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="Y7">
         <f>Data!AF22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="Z7">
         <f>Data!AG22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AA7">
         <f>Data!AH22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
       <c r="AB7">
         <f>Data!AI22</f>
-        <v>0</v>
+        <v>1.3472785756799999E-3</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -19469,107 +19469,107 @@
       </c>
       <c r="C8">
         <f>Data!J23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f>Data!K23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>Data!L23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>Data!M23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>Data!N23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f>Data!O23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>Data!P23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>Data!Q23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f>Data!R23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>Data!S23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f>Data!T23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f>Data!U23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f>Data!V23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f>Data!W23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f>Data!X23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f>Data!Y23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f>Data!Z23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f>Data!AA23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f>Data!AB23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f>Data!AC23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f>Data!AD23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f>Data!AE23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f>Data!AF23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f>Data!AG23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f>Data!AH23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f>Data!AI23</f>
-        <v>0.87530894177700003</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19707,111 +19707,111 @@
       </c>
       <c r="B2">
         <f>Data!I24</f>
-        <v>3.1162890650799999E-2</v>
+        <v>0.120763672591</v>
       </c>
       <c r="C2">
         <f>Data!J24</f>
-        <v>3.0635270769200001E-2</v>
+        <v>0.120763672591</v>
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>5.6223929708727458E-2</v>
+        <v>0.14314635709048401</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>6.4751771186114582E-2</v>
+        <v>0.15060575485341712</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>7.593608199789606E-2</v>
+        <v>0.16038879588092381</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>9.0466775061945975E-2</v>
+        <v>0.17309895467353914</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.10911567600852309</v>
+        <v>0.18941135569212383</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.13267792366244005</v>
+        <v>0.21002151570803868</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.16186575830694638</v>
+        <v>0.23555243921657476</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.19715037721106998</v>
+        <v>0.2664162877082813</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.2385680035473921</v>
+        <v>0.30264474599498731</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.2855376260957222</v>
+        <v>0.34372959710201983</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.33676631443512162</v>
+        <v>0.388539900413849</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.39031763538459996</v>
+        <v>0.43538183629550004</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.4438689563340783</v>
+        <v>0.48222377217715112</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.49509764467347783</v>
+        <v>0.52703407548898018</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.54206726722180787</v>
+        <v>0.56811892659601271</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.58348489355812994</v>
+        <v>0.60434738488271866</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.61876951246225353</v>
+        <v>0.6352112333744252</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.64795734710676001</v>
+        <v>0.66074215688296134</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.67151959476067691</v>
+        <v>0.68135231689887621</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.69016849570725403</v>
+        <v>0.69766471791746087</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.704699188771304</v>
+        <v>0.71037487671007626</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.7158834995830855</v>
+        <v>0.72015791773758298</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.72441134106047256</v>
+        <v>0.727617315500516</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.73086706091722453</v>
+        <v>0.73326420544157211</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.73572758383774906</v>
+        <v>0.73751575888521737</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -19820,111 +19820,111 @@
       </c>
       <c r="B3">
         <f>Data!I25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="C3">
         <f>Data!J25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="D3">
         <f>Data!K25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="E3">
         <f>Data!L25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="F3">
         <f>Data!M25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="G3">
         <f>Data!N25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="H3">
         <f>Data!O25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="I3">
         <f>Data!P25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="J3">
         <f>Data!Q25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="K3">
         <f>Data!R25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="L3">
         <f>Data!S25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="M3">
         <f>Data!T25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="N3">
         <f>Data!U25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="O3">
         <f>Data!V25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="P3">
         <f>Data!W25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="Q3">
         <f>Data!X25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="R3">
         <f>Data!Y25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="S3">
         <f>Data!Z25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="T3">
         <f>Data!AA25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="U3">
         <f>Data!AB25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="V3">
         <f>Data!AC25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="W3">
         <f>Data!AD25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="X3">
         <f>Data!AE25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="Y3">
         <f>Data!AF25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="Z3">
         <f>Data!AG25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AA3">
         <f>Data!AH25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
       <c r="AB3">
         <f>Data!AI25</f>
-        <v>0</v>
+        <v>1.5317430015500001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -19933,111 +19933,111 @@
       </c>
       <c r="B4">
         <f>Data!I26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="C4">
         <f>Data!J26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="D4">
         <f>Data!K26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="E4">
         <f>Data!L26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="F4">
         <f>Data!M26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="G4">
         <f>Data!N26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="H4">
         <f>Data!O26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="I4">
         <f>Data!P26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="J4">
         <f>Data!Q26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="K4">
         <f>Data!R26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="L4">
         <f>Data!S26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="M4">
         <f>Data!T26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="N4">
         <f>Data!U26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="O4">
         <f>Data!V26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="P4">
         <f>Data!W26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="Q4">
         <f>Data!X26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="R4">
         <f>Data!Y26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="S4">
         <f>Data!Z26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="T4">
         <f>Data!AA26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="U4">
         <f>Data!AB26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="V4">
         <f>Data!AC26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="W4">
         <f>Data!AD26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="X4">
         <f>Data!AE26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="Y4">
         <f>Data!AF26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="Z4">
         <f>Data!AG26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AA4">
         <f>Data!AH26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
       <c r="AB4">
         <f>Data!AI26</f>
-        <v>0</v>
+        <v>0.38138758163300002</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -20272,111 +20272,111 @@
       </c>
       <c r="B7">
         <f>Data!I29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="C7">
         <f>Data!J29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="D7">
         <f>Data!K29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="E7">
         <f>Data!L29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="F7">
         <f>Data!M29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="G7">
         <f>Data!N29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="H7">
         <f>Data!O29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="I7">
         <f>Data!P29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="J7">
         <f>Data!Q29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="K7">
         <f>Data!R29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="L7">
         <f>Data!S29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="M7">
         <f>Data!T29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="N7">
         <f>Data!U29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="O7">
         <f>Data!V29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="P7">
         <f>Data!W29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="Q7">
         <f>Data!X29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="R7">
         <f>Data!Y29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="S7">
         <f>Data!Z29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="T7">
         <f>Data!AA29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="U7">
         <f>Data!AB29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="V7">
         <f>Data!AC29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="W7">
         <f>Data!AD29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="X7">
         <f>Data!AE29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="Y7">
         <f>Data!AF29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="Z7">
         <f>Data!AG29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AA7">
         <f>Data!AH29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
       <c r="AB7">
         <f>Data!AI29</f>
-        <v>0</v>
+        <v>5.5226931821800003E-2</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -20385,111 +20385,111 @@
       </c>
       <c r="B8">
         <f>Data!I30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="C8">
         <f>Data!J30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="D8">
         <f>Data!K30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="E8">
         <f>Data!L30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="F8">
         <f>Data!M30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="G8">
         <f>Data!N30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="H8">
         <f>Data!O30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="I8">
         <f>Data!P30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="J8">
         <f>Data!Q30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="K8">
         <f>Data!R30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="L8">
         <f>Data!S30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="M8">
         <f>Data!T30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="N8">
         <f>Data!U30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="O8">
         <f>Data!V30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="P8">
         <f>Data!W30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="Q8">
         <f>Data!X30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="R8">
         <f>Data!Y30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="S8">
         <f>Data!Z30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="T8">
         <f>Data!AA30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="U8">
         <f>Data!AB30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="V8">
         <f>Data!AC30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="W8">
         <f>Data!AD30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="X8">
         <f>Data!AE30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="Y8">
         <f>Data!AF30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="Z8">
         <f>Data!AG30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AA8">
         <f>Data!AH30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
       <c r="AB8">
         <f>Data!AI30</f>
-        <v>0</v>
+        <v>2.0026390066599999E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20627,111 +20627,111 @@
       </c>
       <c r="B2">
         <f>Data!I31</f>
-        <v>4.7973229575300003E-3</v>
+        <v>4.9483952094699999E-3</v>
       </c>
       <c r="C2">
         <f>Data!J31</f>
-        <v>6.1405058414400002E-3</v>
+        <v>4.9483952094699999E-3</v>
       </c>
       <c r="D2">
         <f>Data!K31</f>
-        <v>1.4814878064083456E-2</v>
+        <v>1.3665172225037181E-2</v>
       </c>
       <c r="E2">
         <f>Data!L31</f>
-        <v>1.7705755284549454E-2</v>
+        <v>1.6570181540224892E-2</v>
       </c>
       <c r="F2">
         <f>Data!M31</f>
-        <v>2.1497156594966059E-2</v>
+        <v>2.0380117170282437E-2</v>
       </c>
       <c r="G2">
         <f>Data!N31</f>
-        <v>2.6422957536251346E-2</v>
+        <v>2.5329997960061364E-2</v>
       </c>
       <c r="H2">
         <f>Data!O31</f>
-        <v>3.2744801472509036E-2</v>
+        <v>3.1682746321000453E-2</v>
       </c>
       <c r="I2">
         <f>Data!P31</f>
-        <v>4.0732234773926027E-2</v>
+        <v>3.970922630458016E-2</v>
       </c>
       <c r="J2">
         <f>Data!Q31</f>
-        <v>5.0626701798468406E-2</v>
+        <v>4.9652062572970661E-2</v>
       </c>
       <c r="K2">
         <f>Data!R31</f>
-        <v>6.2587935047612731E-2</v>
+        <v>6.16717684822711E-2</v>
       </c>
       <c r="L2">
         <f>Data!S31</f>
-        <v>7.6628213917586716E-2</v>
+        <v>7.5780683456713668E-2</v>
       </c>
       <c r="M2">
         <f>Data!T31</f>
-        <v>9.2550579763493207E-2</v>
+        <v>9.1780886016242957E-2</v>
       </c>
       <c r="N2">
         <f>Data!U31</f>
-        <v>0.10991673842713874</v>
+        <v>0.10923193939539196</v>
       </c>
       <c r="O2">
         <f>Data!V31</f>
-        <v>0.12807025292072</v>
+        <v>0.127474197604735</v>
       </c>
       <c r="P2">
         <f>Data!W31</f>
-        <v>0.14622376741430126</v>
+        <v>0.14571645581407805</v>
       </c>
       <c r="Q2">
         <f>Data!X31</f>
-        <v>0.16358992607794678</v>
+        <v>0.16316750919322703</v>
       </c>
       <c r="R2">
         <f>Data!Y31</f>
-        <v>0.17951229192385326</v>
+        <v>0.17916771175275634</v>
       </c>
       <c r="S2">
         <f>Data!Z31</f>
-        <v>0.19355257079382726</v>
+        <v>0.19327662672719889</v>
       </c>
       <c r="T2">
         <f>Data!AA31</f>
-        <v>0.20551380404297159</v>
+        <v>0.20529633263649932</v>
       </c>
       <c r="U2">
         <f>Data!AB31</f>
-        <v>0.21540827106751401</v>
+        <v>0.21523916890488987</v>
       </c>
       <c r="V2">
         <f>Data!AC31</f>
-        <v>0.22339570436893097</v>
+        <v>0.22326564888846956</v>
       </c>
       <c r="W2">
         <f>Data!AD31</f>
-        <v>0.22971754830518867</v>
+        <v>0.22961839724940863</v>
       </c>
       <c r="X2">
         <f>Data!AE31</f>
-        <v>0.23464334924647395</v>
+        <v>0.23456827803918759</v>
       </c>
       <c r="Y2">
         <f>Data!AF31</f>
-        <v>0.23843475055689056</v>
+        <v>0.23837821366924514</v>
       </c>
       <c r="Z2">
         <f>Data!AG31</f>
-        <v>0.24132562777735656</v>
+        <v>0.24128322298443283</v>
       </c>
       <c r="AA2">
         <f>Data!AH31</f>
-        <v>0.24351407060020699</v>
+        <v>0.2434823640413856</v>
       </c>
       <c r="AB2">
         <f>Data!AI31</f>
-        <v>0.2451617530797367</v>
+        <v>0.24513810124032956</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -20740,111 +20740,111 @@
       </c>
       <c r="B3">
         <f>Data!I32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="C3">
         <f>Data!J32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="D3">
         <f>Data!K32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="E3">
         <f>Data!L32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="F3">
         <f>Data!M32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="G3">
         <f>Data!N32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="H3">
         <f>Data!O32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="I3">
         <f>Data!P32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="J3">
         <f>Data!Q32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="K3">
         <f>Data!R32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="L3">
         <f>Data!S32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="M3">
         <f>Data!T32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="N3">
         <f>Data!U32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="O3">
         <f>Data!V32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="P3">
         <f>Data!W32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="Q3">
         <f>Data!X32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="R3">
         <f>Data!Y32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="S3">
         <f>Data!Z32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="T3">
         <f>Data!AA32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="U3">
         <f>Data!AB32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="V3">
         <f>Data!AC32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="W3">
         <f>Data!AD32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="X3">
         <f>Data!AE32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="Y3">
         <f>Data!AF32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="Z3">
         <f>Data!AG32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AA3">
         <f>Data!AH32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
       <c r="AB3">
         <f>Data!AI32</f>
-        <v>0</v>
+        <v>2.32516282526E-2</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -20853,111 +20853,111 @@
       </c>
       <c r="B4">
         <f>Data!I33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="C4">
         <f>Data!J33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="D4">
         <f>Data!K33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="E4">
         <f>Data!L33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="F4">
         <f>Data!M33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="G4">
         <f>Data!N33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="H4">
         <f>Data!O33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="I4">
         <f>Data!P33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="J4">
         <f>Data!Q33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="K4">
         <f>Data!R33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="L4">
         <f>Data!S33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="M4">
         <f>Data!T33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="N4">
         <f>Data!U33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="O4">
         <f>Data!V33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="P4">
         <f>Data!W33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="Q4">
         <f>Data!X33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="R4">
         <f>Data!Y33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="S4">
         <f>Data!Z33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="T4">
         <f>Data!AA33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="U4">
         <f>Data!AB33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="V4">
         <f>Data!AC33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="W4">
         <f>Data!AD33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="X4">
         <f>Data!AE33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="Y4">
         <f>Data!AF33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="Z4">
         <f>Data!AG33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AA4">
         <f>Data!AH33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
       <c r="AB4">
         <f>Data!AI33</f>
-        <v>0</v>
+        <v>7.3518745439599999E-4</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -21305,111 +21305,111 @@
       </c>
       <c r="B8">
         <f>Data!I37</f>
-        <v>6.2247642917999998E-4</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f>Data!J37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f>Data!K37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>Data!L37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>Data!M37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>Data!N37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f>Data!O37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>Data!P37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>Data!Q37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f>Data!R37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>Data!S37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f>Data!T37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f>Data!U37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f>Data!V37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f>Data!W37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f>Data!X37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f>Data!Y37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f>Data!Z37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f>Data!AA37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f>Data!AB37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f>Data!AC37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f>Data!AD37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f>Data!AE37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f>Data!AF37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f>Data!AG37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f>Data!AH37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f>Data!AI37</f>
-        <v>3.70282921188E-3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
